--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -13,12 +13,13 @@
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
     <sheet name="Theme view" r:id="rId8" sheetId="6"/>
     <sheet name="Sector view" r:id="rId9" sheetId="7"/>
+    <sheet name="Speaker view" r:id="rId10" sheetId="8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2763" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3476" uniqueCount="355">
   <si>
     <t>Conference name</t>
   </si>
@@ -176,829 +177,913 @@
     <t>Large, Recorded</t>
   </si>
   <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>R 2</t>
+  </si>
+  <si>
+    <t>R 3</t>
+  </si>
+  <si>
+    <t>Recorded</t>
+  </si>
+  <si>
+    <t>R 4</t>
+  </si>
+  <si>
+    <t>R 5</t>
+  </si>
+  <si>
+    <t>Lab_room, Large, Recorded</t>
+  </si>
+  <si>
+    <t>R 6</t>
+  </si>
+  <si>
+    <t>R 7</t>
+  </si>
+  <si>
+    <t>R 8</t>
+  </si>
+  <si>
+    <t>R 9</t>
+  </si>
+  <si>
+    <t>R 10</t>
+  </si>
+  <si>
+    <t>Lab_room</t>
+  </si>
+  <si>
+    <t>Required timeslot tags</t>
+  </si>
+  <si>
+    <t>Preferred timeslot tags</t>
+  </si>
+  <si>
+    <t>Prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t>Undesired timeslot tags</t>
+  </si>
+  <si>
+    <t>Required room tags</t>
+  </si>
+  <si>
+    <t>Preferred room tags</t>
+  </si>
+  <si>
+    <t>Prohibited room tags</t>
+  </si>
+  <si>
+    <t>Undesired room tags</t>
+  </si>
+  <si>
+    <t>Amy Cole</t>
+  </si>
+  <si>
+    <t>Beth Fox</t>
+  </si>
+  <si>
+    <t>Chad Green</t>
+  </si>
+  <si>
+    <t>Dan Jones</t>
+  </si>
+  <si>
+    <t>Elsa King</t>
+  </si>
+  <si>
+    <t>Flo Li</t>
+  </si>
+  <si>
+    <t>Gus Poe</t>
+  </si>
+  <si>
+    <t>Hugo Rye</t>
+  </si>
+  <si>
+    <t>Ivy Smith</t>
+  </si>
+  <si>
+    <t>Jay Watt</t>
+  </si>
+  <si>
+    <t>Amy Fox</t>
+  </si>
+  <si>
+    <t>Beth Green</t>
+  </si>
+  <si>
+    <t>Chad Jones</t>
+  </si>
+  <si>
+    <t>Dan King</t>
+  </si>
+  <si>
+    <t>Elsa Li</t>
+  </si>
+  <si>
+    <t>Flo Poe</t>
+  </si>
+  <si>
+    <t>Gus Rye</t>
+  </si>
+  <si>
+    <t>Hugo Smith</t>
+  </si>
+  <si>
+    <t>Ivy Watt</t>
+  </si>
+  <si>
+    <t>Jay Cole</t>
+  </si>
+  <si>
+    <t>Amy Green</t>
+  </si>
+  <si>
+    <t>Beth Jones</t>
+  </si>
+  <si>
+    <t>Chad King</t>
+  </si>
+  <si>
+    <t>Dan Li</t>
+  </si>
+  <si>
+    <t>Elsa Poe</t>
+  </si>
+  <si>
+    <t>Flo Rye</t>
+  </si>
+  <si>
+    <t>Gus Smith</t>
+  </si>
+  <si>
+    <t>Hugo Watt</t>
+  </si>
+  <si>
+    <t>Ivy Cole</t>
+  </si>
+  <si>
+    <t>Jay Fox</t>
+  </si>
+  <si>
+    <t>Amy Jones</t>
+  </si>
+  <si>
+    <t>Beth King</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>Chad Li</t>
+  </si>
+  <si>
+    <t>Dan Poe</t>
+  </si>
+  <si>
+    <t>Elsa Rye</t>
+  </si>
+  <si>
+    <t>Flo Smith</t>
+  </si>
+  <si>
+    <t>Gus Watt</t>
+  </si>
+  <si>
+    <t>Hugo Cole</t>
+  </si>
+  <si>
+    <t>Ivy Fox</t>
+  </si>
+  <si>
+    <t>Jay Green</t>
+  </si>
+  <si>
+    <t>Amy King</t>
+  </si>
+  <si>
+    <t>Beth Li</t>
+  </si>
+  <si>
+    <t>Chad Poe</t>
+  </si>
+  <si>
+    <t>Dan Rye</t>
+  </si>
+  <si>
+    <t>Elsa Smith</t>
+  </si>
+  <si>
+    <t>Flo Watt</t>
+  </si>
+  <si>
+    <t>Gus Cole</t>
+  </si>
+  <si>
+    <t>Hugo Fox</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Speakers</t>
+  </si>
+  <si>
+    <t>Theme tags</t>
+  </si>
+  <si>
+    <t>Sector tags</t>
+  </si>
+  <si>
+    <t>Audience level</t>
+  </si>
+  <si>
+    <t>Content tags</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Pinned by user</t>
+  </si>
+  <si>
+    <t>Timeslot day</t>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>S00</t>
+  </si>
+  <si>
+    <t>Hands on real-time OpenShift</t>
+  </si>
+  <si>
+    <t>Amy Cole, Beth Fox</t>
+  </si>
+  <si>
+    <t>IoT</t>
+  </si>
+  <si>
+    <t>OpenShift, Kubernetes</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>S01</t>
+  </si>
+  <si>
+    <t>Advanced containerized WildFly</t>
+  </si>
+  <si>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>Telecommunications</t>
+  </si>
+  <si>
+    <t>WildFly</t>
+  </si>
+  <si>
+    <t>S02</t>
+  </si>
+  <si>
+    <t>Learn virtualized Spring</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>S03</t>
+  </si>
+  <si>
+    <t>Intro to serverless Drools</t>
+  </si>
+  <si>
+    <t>Modern Web</t>
+  </si>
+  <si>
+    <t>Financial services</t>
+  </si>
+  <si>
+    <t>Drools</t>
+  </si>
+  <si>
+    <t>S04</t>
+  </si>
+  <si>
+    <t>Discover AI-driven OptaPlanner</t>
+  </si>
+  <si>
+    <t>OptaPlanner</t>
+  </si>
+  <si>
+    <t>S05</t>
+  </si>
+  <si>
+    <t>Mastering machine learning jBPM</t>
+  </si>
+  <si>
+    <t>Gus Poe, Hugo Rye</t>
+  </si>
+  <si>
+    <t>jBPM</t>
+  </si>
+  <si>
+    <t>S06</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Camel</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>S07</t>
+  </si>
+  <si>
+    <t>Building deep learning XStream</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>XStream</t>
+  </si>
+  <si>
+    <t>S08</t>
+  </si>
+  <si>
+    <t>Securing scalable Docker</t>
+  </si>
+  <si>
+    <t>Mobile, Big Data</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
+    <t>S09</t>
+  </si>
+  <si>
+    <t>Debug enterprise Hibernate</t>
+  </si>
+  <si>
+    <t>Culture, Big Data</t>
+  </si>
+  <si>
+    <t>Hibernate</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>Prepare for streaming GWT</t>
+  </si>
+  <si>
+    <t>Chad Jones, Dan King</t>
+  </si>
+  <si>
+    <t>Security, Big Data</t>
+  </si>
+  <si>
+    <t>GWT</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>Understand mobile Errai</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Errai</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>Applying modern Angular</t>
+  </si>
+  <si>
+    <t>Flo Poe, Gus Rye</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>Grok distributed Weld</t>
+  </si>
+  <si>
+    <t>Hugo Smith, Ivy Watt</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Culture</t>
+  </si>
+  <si>
+    <t>Weld</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable RestEasy</t>
+  </si>
+  <si>
+    <t>IoT, Big Data</t>
+  </si>
+  <si>
+    <t>RestEasy</t>
+  </si>
+  <si>
+    <t>S15</t>
+  </si>
+  <si>
+    <t>Using secure Android</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>Deliver stable Tensorflow</t>
+  </si>
+  <si>
+    <t>Middleware</t>
+  </si>
+  <si>
+    <t>Tensorflow</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>Implement platform-independent VertX</t>
+  </si>
+  <si>
+    <t>IoT, Security</t>
+  </si>
+  <si>
+    <t>VertX</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>Program flexible JUnit</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>JUnit</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>Hack modularized Keycloak</t>
+  </si>
+  <si>
+    <t>Elsa Poe, Flo Rye</t>
+  </si>
+  <si>
+    <t>Keycloak</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>Hands on real-time WildFly</t>
+  </si>
+  <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>Advanced containerized Spring</t>
+  </si>
+  <si>
+    <t>Modern Web, Culture</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>Learn virtualized Drools</t>
+  </si>
+  <si>
+    <t>Ivy Cole, Jay Fox</t>
+  </si>
+  <si>
+    <t>S23</t>
+  </si>
+  <si>
+    <t>Intro to serverless OptaPlanner</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>Discover AI-driven jBPM</t>
+  </si>
+  <si>
+    <t>S25</t>
+  </si>
+  <si>
+    <t>Mastering machine learning Camel</t>
+  </si>
+  <si>
+    <t>S26</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven XStream</t>
+  </si>
+  <si>
+    <t>S27</t>
+  </si>
+  <si>
+    <t>Building deep learning Docker</t>
+  </si>
+  <si>
+    <t>Elsa Rye, Flo Smith</t>
+  </si>
+  <si>
+    <t>Cloud, Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>S28</t>
+  </si>
+  <si>
+    <t>Securing scalable Hibernate</t>
+  </si>
+  <si>
+    <t>S29</t>
+  </si>
+  <si>
+    <t>Debug enterprise GWT</t>
+  </si>
+  <si>
+    <t>S30</t>
+  </si>
+  <si>
+    <t>Prepare for streaming Errai</t>
+  </si>
+  <si>
+    <t>Ivy Fox, Jay Green</t>
+  </si>
+  <si>
+    <t>Culture, Security</t>
+  </si>
+  <si>
+    <t>S31</t>
+  </si>
+  <si>
+    <t>Understand mobile Angular</t>
+  </si>
+  <si>
+    <t>Amy King, Beth Li</t>
+  </si>
+  <si>
+    <t>S32</t>
+  </si>
+  <si>
+    <t>Applying modern Weld</t>
+  </si>
+  <si>
+    <t>Chad Poe, Dan Rye, Elsa Smith</t>
+  </si>
+  <si>
+    <t>S33</t>
+  </si>
+  <si>
+    <t>Grok distributed RestEasy</t>
+  </si>
+  <si>
+    <t>Flo Watt, Gus Cole</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable Android</t>
+  </si>
+  <si>
+    <t>S35</t>
+  </si>
+  <si>
+    <t>Using secure Tensorflow</t>
+  </si>
+  <si>
+    <t>S36</t>
+  </si>
+  <si>
+    <t>Deliver stable VertX</t>
+  </si>
+  <si>
+    <t>Chad Green, Dan Jones</t>
+  </si>
+  <si>
+    <t>S37</t>
+  </si>
+  <si>
+    <t>Implement platform-independent JUnit</t>
+  </si>
+  <si>
+    <t>Elsa King, Flo Li</t>
+  </si>
+  <si>
+    <t>S38</t>
+  </si>
+  <si>
+    <t>Program flexible Keycloak</t>
+  </si>
+  <si>
+    <t>S39</t>
+  </si>
+  <si>
+    <t>Hack modularized OpenShift</t>
+  </si>
+  <si>
+    <t>OpenShift</t>
+  </si>
+  <si>
+    <t>S40</t>
+  </si>
+  <si>
+    <t>Hands on real-time Spring</t>
+  </si>
+  <si>
+    <t>S41</t>
+  </si>
+  <si>
+    <t>Advanced containerized Drools</t>
+  </si>
+  <si>
+    <t>Jay Watt, Amy Fox</t>
+  </si>
+  <si>
     <t>S42</t>
   </si>
   <si>
-    <t>R 2</t>
-  </si>
-  <si>
-    <t>R 3</t>
-  </si>
-  <si>
-    <t>Recorded</t>
-  </si>
-  <si>
-    <t>R 4</t>
-  </si>
-  <si>
-    <t>R 5</t>
-  </si>
-  <si>
-    <t>Lab_room, Large, Recorded</t>
-  </si>
-  <si>
-    <t>R 6</t>
-  </si>
-  <si>
-    <t>R 7</t>
-  </si>
-  <si>
-    <t>R 8</t>
-  </si>
-  <si>
-    <t>R 9</t>
-  </si>
-  <si>
-    <t>R 10</t>
-  </si>
-  <si>
-    <t>Lab_room</t>
-  </si>
-  <si>
-    <t>Required timeslot tags</t>
-  </si>
-  <si>
-    <t>Preferred timeslot tags</t>
-  </si>
-  <si>
-    <t>Prohibited timeslot tags</t>
-  </si>
-  <si>
-    <t>Undesired timeslot tags</t>
-  </si>
-  <si>
-    <t>Required room tags</t>
-  </si>
-  <si>
-    <t>Preferred room tags</t>
-  </si>
-  <si>
-    <t>Prohibited room tags</t>
-  </si>
-  <si>
-    <t>Undesired room tags</t>
-  </si>
-  <si>
-    <t>Amy Cole</t>
-  </si>
-  <si>
-    <t>Beth Fox</t>
-  </si>
-  <si>
-    <t>Chad Green</t>
-  </si>
-  <si>
-    <t>Dan Jones</t>
-  </si>
-  <si>
-    <t>Elsa King</t>
-  </si>
-  <si>
-    <t>Flo Li</t>
-  </si>
-  <si>
-    <t>Gus Poe</t>
-  </si>
-  <si>
-    <t>Hugo Rye</t>
-  </si>
-  <si>
-    <t>Ivy Smith</t>
-  </si>
-  <si>
-    <t>Jay Watt</t>
-  </si>
-  <si>
-    <t>Amy Fox</t>
-  </si>
-  <si>
-    <t>Beth Green</t>
-  </si>
-  <si>
-    <t>Chad Jones</t>
-  </si>
-  <si>
-    <t>Dan King</t>
-  </si>
-  <si>
-    <t>Elsa Li</t>
-  </si>
-  <si>
-    <t>Flo Poe</t>
-  </si>
-  <si>
-    <t>Gus Rye</t>
-  </si>
-  <si>
-    <t>Hugo Smith</t>
-  </si>
-  <si>
-    <t>Ivy Watt</t>
-  </si>
-  <si>
-    <t>Jay Cole</t>
-  </si>
-  <si>
-    <t>Amy Green</t>
-  </si>
-  <si>
-    <t>Beth Jones</t>
-  </si>
-  <si>
-    <t>Chad King</t>
-  </si>
-  <si>
-    <t>Dan Li</t>
-  </si>
-  <si>
-    <t>Elsa Poe</t>
-  </si>
-  <si>
-    <t>Flo Rye</t>
-  </si>
-  <si>
-    <t>Gus Smith</t>
-  </si>
-  <si>
-    <t>Hugo Watt</t>
-  </si>
-  <si>
-    <t>Ivy Cole</t>
-  </si>
-  <si>
-    <t>Jay Fox</t>
-  </si>
-  <si>
-    <t>Amy Jones</t>
-  </si>
-  <si>
-    <t>Beth King</t>
-  </si>
-  <si>
-    <t>Large</t>
-  </si>
-  <si>
-    <t>Chad Li</t>
-  </si>
-  <si>
-    <t>Dan Poe</t>
-  </si>
-  <si>
-    <t>Elsa Rye</t>
-  </si>
-  <si>
-    <t>Flo Smith</t>
-  </si>
-  <si>
-    <t>Gus Watt</t>
-  </si>
-  <si>
-    <t>Hugo Cole</t>
-  </si>
-  <si>
-    <t>Ivy Fox</t>
-  </si>
-  <si>
-    <t>Jay Green</t>
-  </si>
-  <si>
-    <t>Amy King</t>
-  </si>
-  <si>
-    <t>Beth Li</t>
-  </si>
-  <si>
-    <t>Chad Poe</t>
-  </si>
-  <si>
-    <t>Dan Rye</t>
-  </si>
-  <si>
-    <t>Elsa Smith</t>
-  </si>
-  <si>
-    <t>Flo Watt</t>
-  </si>
-  <si>
-    <t>Gus Cole</t>
-  </si>
-  <si>
-    <t>Hugo Fox</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Theme tags</t>
-  </si>
-  <si>
-    <t>Sector tags</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>Speakers</t>
-  </si>
-  <si>
-    <t>Pinned by user</t>
-  </si>
-  <si>
-    <t>Timeslot day</t>
-  </si>
-  <si>
-    <t>Room</t>
-  </si>
-  <si>
-    <t>S00</t>
-  </si>
-  <si>
-    <t>Hands on real-time OpenShift</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>S01</t>
-  </si>
-  <si>
-    <t>Advanced containerized WildFly</t>
-  </si>
-  <si>
-    <t>Big Data, Middleware</t>
-  </si>
-  <si>
-    <t>S02</t>
-  </si>
-  <si>
-    <t>Learn virtualized Spring</t>
-  </si>
-  <si>
-    <t>Modern Web</t>
-  </si>
-  <si>
-    <t>Chad Green, Dan Jones</t>
-  </si>
-  <si>
-    <t>S03</t>
-  </si>
-  <si>
-    <t>Intro to serverless Drools</t>
-  </si>
-  <si>
-    <t>Security, Culture</t>
-  </si>
-  <si>
-    <t>S04</t>
-  </si>
-  <si>
-    <t>Discover AI-driven OptaPlanner</t>
-  </si>
-  <si>
-    <t>Financial services</t>
-  </si>
-  <si>
-    <t>Flo Li, Gus Poe</t>
-  </si>
-  <si>
-    <t>S05</t>
-  </si>
-  <si>
-    <t>Mastering machine learning jBPM</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Hugo Rye, Ivy Smith</t>
-  </si>
-  <si>
-    <t>S06</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Camel</t>
+    <t>Learn virtualized OptaPlanner</t>
+  </si>
+  <si>
+    <t>S43</t>
+  </si>
+  <si>
+    <t>Intro to serverless jBPM</t>
+  </si>
+  <si>
+    <t>S44</t>
+  </si>
+  <si>
+    <t>Discover AI-driven Camel</t>
+  </si>
+  <si>
+    <t>Dan King, Elsa Li</t>
+  </si>
+  <si>
+    <t>S45</t>
+  </si>
+  <si>
+    <t>Mastering machine learning XStream</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>S46</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Docker</t>
+  </si>
+  <si>
+    <t>Docker, Kubernetes</t>
+  </si>
+  <si>
+    <t>S47</t>
+  </si>
+  <si>
+    <t>Building deep learning Hibernate</t>
+  </si>
+  <si>
+    <t>Mobile, Security</t>
+  </si>
+  <si>
+    <t>S48</t>
+  </si>
+  <si>
+    <t>Securing scalable GWT</t>
   </si>
   <si>
     <t>Big Data</t>
   </si>
   <si>
-    <t>Jay Watt, Amy Fox</t>
-  </si>
-  <si>
-    <t>S07</t>
-  </si>
-  <si>
-    <t>Building deep learning XStream</t>
-  </si>
-  <si>
-    <t>Cloud</t>
-  </si>
-  <si>
-    <t>Beth Green, Chad Jones</t>
-  </si>
-  <si>
-    <t>S08</t>
-  </si>
-  <si>
-    <t>Securing scalable Docker</t>
-  </si>
-  <si>
-    <t>S09</t>
-  </si>
-  <si>
-    <t>Debug enterprise JUnit</t>
-  </si>
-  <si>
-    <t>S10</t>
-  </si>
-  <si>
-    <t>Hands on real-time WildFly</t>
-  </si>
-  <si>
-    <t>Middleware</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>Advanced containerized Spring</t>
-  </si>
-  <si>
-    <t>Modern Web, Mobile</t>
-  </si>
-  <si>
-    <t>Gus Rye, Hugo Smith</t>
-  </si>
-  <si>
-    <t>S12</t>
-  </si>
-  <si>
-    <t>Learn virtualized Drools</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>S13</t>
-  </si>
-  <si>
-    <t>Intro to serverless OptaPlanner</t>
-  </si>
-  <si>
-    <t>Jay Cole, Amy Green</t>
-  </si>
-  <si>
-    <t>S14</t>
-  </si>
-  <si>
-    <t>Discover AI-driven jBPM</t>
-  </si>
-  <si>
-    <t>Culture</t>
-  </si>
-  <si>
-    <t>S15</t>
-  </si>
-  <si>
-    <t>Mastering machine learning Camel</t>
+    <t>S49</t>
+  </si>
+  <si>
+    <t>Debug enterprise Errai</t>
+  </si>
+  <si>
+    <t>S50</t>
+  </si>
+  <si>
+    <t>Prepare for streaming Angular</t>
+  </si>
+  <si>
+    <t>S51</t>
+  </si>
+  <si>
+    <t>Understand mobile Weld</t>
   </si>
   <si>
     <t>Chad King, Dan Li</t>
   </si>
   <si>
-    <t>S16</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven XStream</t>
-  </si>
-  <si>
-    <t>S17</t>
-  </si>
-  <si>
-    <t>Building deep learning Docker</t>
-  </si>
-  <si>
-    <t>IoT, Big Data</t>
-  </si>
-  <si>
-    <t>S18</t>
-  </si>
-  <si>
-    <t>Securing scalable JUnit</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>S19</t>
-  </si>
-  <si>
-    <t>Debug enterprise OpenShift</t>
+    <t>S52</t>
+  </si>
+  <si>
+    <t>Applying modern RestEasy</t>
+  </si>
+  <si>
+    <t>S53</t>
+  </si>
+  <si>
+    <t>Grok distributed Android</t>
+  </si>
+  <si>
+    <t>Flo Rye, Gus Smith</t>
+  </si>
+  <si>
+    <t>S54</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable Tensorflow</t>
+  </si>
+  <si>
+    <t>Hugo Watt, Ivy Cole</t>
+  </si>
+  <si>
+    <t>S55</t>
+  </si>
+  <si>
+    <t>Using secure VertX</t>
+  </si>
+  <si>
+    <t>S56</t>
+  </si>
+  <si>
+    <t>Deliver stable JUnit</t>
+  </si>
+  <si>
+    <t>Amy Jones, Beth King</t>
+  </si>
+  <si>
+    <t>IoT, Middleware</t>
+  </si>
+  <si>
+    <t>S57</t>
+  </si>
+  <si>
+    <t>Implement platform-independent Keycloak</t>
   </si>
   <si>
     <t>Artificial Intelligence, Cloud</t>
   </si>
   <si>
-    <t>S20</t>
-  </si>
-  <si>
-    <t>Hands on real-time Spring</t>
-  </si>
-  <si>
-    <t>Ivy Cole, Jay Fox</t>
-  </si>
-  <si>
-    <t>S21</t>
-  </si>
-  <si>
-    <t>Advanced containerized Drools</t>
-  </si>
-  <si>
-    <t>Amy Jones, Beth King</t>
-  </si>
-  <si>
-    <t>S22</t>
-  </si>
-  <si>
-    <t>Learn virtualized OptaPlanner</t>
-  </si>
-  <si>
-    <t>Chad Li, Dan Poe</t>
-  </si>
-  <si>
-    <t>S23</t>
-  </si>
-  <si>
-    <t>Intro to serverless jBPM</t>
-  </si>
-  <si>
-    <t>Security, Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>Discover AI-driven Camel</t>
-  </si>
-  <si>
-    <t>S25</t>
-  </si>
-  <si>
-    <t>Mastering machine learning XStream</t>
-  </si>
-  <si>
-    <t>S26</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Docker</t>
-  </si>
-  <si>
-    <t>Hugo Cole, Ivy Fox, Jay Green, Amy King</t>
-  </si>
-  <si>
-    <t>S27</t>
-  </si>
-  <si>
-    <t>Building deep learning JUnit</t>
-  </si>
-  <si>
-    <t>S28</t>
-  </si>
-  <si>
-    <t>Securing scalable OpenShift</t>
-  </si>
-  <si>
-    <t>Chad Poe, Dan Rye</t>
-  </si>
-  <si>
-    <t>S29</t>
-  </si>
-  <si>
-    <t>Debug enterprise WildFly</t>
-  </si>
-  <si>
-    <t>Culture, Mobile</t>
-  </si>
-  <si>
-    <t>Elsa Smith, Flo Watt</t>
-  </si>
-  <si>
-    <t>S30</t>
+    <t>S58</t>
+  </si>
+  <si>
+    <t>Program flexible OpenShift</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Security</t>
+  </si>
+  <si>
+    <t>S59</t>
+  </si>
+  <si>
+    <t>Hack modularized WildFly</t>
+  </si>
+  <si>
+    <t>S60</t>
   </si>
   <si>
     <t>Hands on real-time Drools</t>
   </si>
   <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>S31</t>
+    <t>Gus Watt, Hugo Cole</t>
+  </si>
+  <si>
+    <t>S61</t>
   </si>
   <si>
     <t>Advanced containerized OptaPlanner</t>
   </si>
   <si>
-    <t>Hugo Fox, Amy Cole</t>
-  </si>
-  <si>
-    <t>S32</t>
+    <t>Middleware, Big Data</t>
+  </si>
+  <si>
+    <t>S62</t>
   </si>
   <si>
     <t>Learn virtualized jBPM</t>
   </si>
   <si>
-    <t>Cloud, Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>S33</t>
+    <t>S63</t>
   </si>
   <si>
     <t>Intro to serverless Camel</t>
   </si>
   <si>
-    <t>Chad Green, Dan Jones, Elsa King, Flo Li</t>
-  </si>
-  <si>
-    <t>S34</t>
+    <t>S64</t>
   </si>
   <si>
     <t>Discover AI-driven XStream</t>
   </si>
   <si>
-    <t>S35</t>
+    <t>Big Data, Mobile</t>
+  </si>
+  <si>
+    <t>S65</t>
   </si>
   <si>
     <t>Mastering machine learning Docker</t>
   </si>
   <si>
-    <t>IoT</t>
-  </si>
-  <si>
-    <t>S36</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven JUnit</t>
-  </si>
-  <si>
-    <t>S37</t>
-  </si>
-  <si>
-    <t>Building deep learning OpenShift</t>
-  </si>
-  <si>
-    <t>Amy Fox, Beth Green, Chad Jones</t>
-  </si>
-  <si>
-    <t>S38</t>
-  </si>
-  <si>
-    <t>Securing scalable WildFly</t>
-  </si>
-  <si>
-    <t>S39</t>
-  </si>
-  <si>
-    <t>Debug enterprise Spring</t>
-  </si>
-  <si>
-    <t>S40</t>
-  </si>
-  <si>
-    <t>Hands on real-time OptaPlanner</t>
-  </si>
-  <si>
-    <t>S41</t>
-  </si>
-  <si>
-    <t>Advanced containerized jBPM</t>
-  </si>
-  <si>
-    <t>Learn virtualized Camel</t>
-  </si>
-  <si>
-    <t>S43</t>
-  </si>
-  <si>
-    <t>Intro to serverless XStream</t>
-  </si>
-  <si>
-    <t>S44</t>
-  </si>
-  <si>
-    <t>Discover AI-driven Docker</t>
-  </si>
-  <si>
-    <t>S45</t>
-  </si>
-  <si>
-    <t>Mastering machine learning JUnit</t>
-  </si>
-  <si>
-    <t>S46</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven OpenShift</t>
-  </si>
-  <si>
-    <t>S47</t>
-  </si>
-  <si>
-    <t>Building deep learning WildFly</t>
-  </si>
-  <si>
-    <t>Flo Rye, Gus Smith</t>
-  </si>
-  <si>
-    <t>S48</t>
-  </si>
-  <si>
-    <t>Securing scalable Spring</t>
-  </si>
-  <si>
-    <t>Hugo Watt, Ivy Cole</t>
-  </si>
-  <si>
-    <t>S49</t>
-  </si>
-  <si>
-    <t>Debug enterprise Drools</t>
-  </si>
-  <si>
-    <t>Jay Fox, Amy Jones</t>
-  </si>
-  <si>
-    <t>S50</t>
-  </si>
-  <si>
-    <t>Hands on real-time jBPM</t>
-  </si>
-  <si>
-    <t>S51</t>
-  </si>
-  <si>
-    <t>Advanced containerized Camel</t>
-  </si>
-  <si>
-    <t>Telecommunications</t>
-  </si>
-  <si>
-    <t>S52</t>
-  </si>
-  <si>
-    <t>Learn virtualized XStream</t>
-  </si>
-  <si>
-    <t>Modern Web, Middleware</t>
-  </si>
-  <si>
-    <t>Dan Poe, Elsa Rye, Flo Smith, Gus Watt</t>
-  </si>
-  <si>
-    <t>S53</t>
-  </si>
-  <si>
-    <t>Intro to serverless Docker</t>
-  </si>
-  <si>
-    <t>Hugo Cole, Ivy Fox</t>
-  </si>
-  <si>
-    <t>S54</t>
-  </si>
-  <si>
-    <t>Discover AI-driven JUnit</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>S55</t>
-  </si>
-  <si>
-    <t>Mastering machine learning OpenShift</t>
-  </si>
-  <si>
-    <t>S56</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven WildFly</t>
-  </si>
-  <si>
-    <t>S57</t>
-  </si>
-  <si>
-    <t>Building deep learning Spring</t>
-  </si>
-  <si>
-    <t>S58</t>
-  </si>
-  <si>
-    <t>Securing scalable Drools</t>
-  </si>
-  <si>
-    <t>Dan Rye, Elsa Smith</t>
-  </si>
-  <si>
-    <t>S59</t>
-  </si>
-  <si>
-    <t>Debug enterprise OptaPlanner</t>
-  </si>
-  <si>
-    <t>Flo Watt, Gus Cole</t>
-  </si>
-  <si>
-    <t>S60</t>
-  </si>
-  <si>
-    <t>Hands on real-time Camel</t>
-  </si>
-  <si>
-    <t>S61</t>
-  </si>
-  <si>
-    <t>Advanced containerized XStream</t>
-  </si>
-  <si>
-    <t>S62</t>
-  </si>
-  <si>
-    <t>Learn virtualized Docker</t>
-  </si>
-  <si>
-    <t>S63</t>
-  </si>
-  <si>
-    <t>Intro to serverless JUnit</t>
-  </si>
-  <si>
-    <t>S64</t>
-  </si>
-  <si>
-    <t>Discover AI-driven OpenShift</t>
-  </si>
-  <si>
-    <t>S65</t>
-  </si>
-  <si>
-    <t>Mastering machine learning WildFly</t>
-  </si>
-  <si>
     <t>S66</t>
   </si>
   <si>
-    <t>Tuning IOT-driven Spring</t>
-  </si>
-  <si>
-    <t>IoT, Middleware</t>
+    <t>Tuning IOT-driven Hibernate</t>
+  </si>
+  <si>
+    <t>Dan Rye, Elsa Smith, Flo Watt</t>
   </si>
   <si>
     <t>S67</t>
   </si>
   <si>
-    <t>Building deep learning Drools</t>
+    <t>Building deep learning GWT</t>
+  </si>
+  <si>
+    <t>Gus Cole, Hugo Fox</t>
   </si>
   <si>
     <t>S68</t>
   </si>
   <si>
-    <t>Securing scalable OptaPlanner</t>
+    <t>Securing scalable Errai</t>
   </si>
   <si>
     <t>S69</t>
   </si>
   <si>
-    <t>Debug enterprise jBPM</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
-    <t>Amy Fox, Beth Green</t>
+    <t>Debug enterprise Angular</t>
   </si>
   <si>
     <t>S70</t>
   </si>
   <si>
-    <t>Hands on real-time XStream</t>
+    <t>Prepare for streaming Weld</t>
   </si>
   <si>
     <t>S71</t>
   </si>
   <si>
-    <t>Advanced containerized Docker</t>
+    <t>Understand mobile RestEasy</t>
   </si>
   <si>
     <t>Theme tag</t>
   </si>
   <si>
     <t>Sector tag</t>
+  </si>
+  <si>
+    <t>Speaker</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1105,7 @@
       <b val="true"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1040,6 +1125,16 @@
         <fgColor rgb="AD7FA8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="EF2929"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FCAF3E"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1053,11 +1148,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -1067,9 +1164,9 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="33.8671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="14.33984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="81.296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="29.5" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="70.88671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1223,11 +1320,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.14453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="6.3984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="6.32421875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="10.78515625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="6.078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="15.99609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="6.0859375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="6.0859375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="9.41796875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="5.1484375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1461,20 +1558,20 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="7.109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="26.3125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="6.48828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="25.6328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2019,27 +2116,27 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.9453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="24.85546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="25.390625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="26.30859375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="26.0234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="21.671875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="22.20703125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="23.125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="22.84375" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="11.5703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="21.69921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="22.09765625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="23.01171875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="22.7734375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="19.07421875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="19.47265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="20.3828125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="20.1484375" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="11.86328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3374,7 +3471,7 @@
         <v>32</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="L21" t="s">
         <v>32</v>
@@ -5259,7 +5356,7 @@
         <v>32</v>
       </c>
       <c r="K50" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="L50" t="s">
         <v>32</v>
@@ -5306,26 +5403,28 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="36.37109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.78515625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="28.52734375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.05859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.3046875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="38.2109375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="24.85546875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="25.390625" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="26.30859375" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="26.0234375" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="21.671875" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="22.20703125" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="23.125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="22.84375" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="16.65234375" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="16.14453125" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="6.3984375" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="6.32421875" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.02734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="5.69140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.66796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.41796875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="28.05859375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="27.59375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="19.625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="14.4375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="21.28515625" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="9.7109375" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="21.69921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="22.09765625" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="23.01171875" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="22.7734375" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="19.07421875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="19.47265625" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="20.3828125" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="20.1484375" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="14.578125" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="15.99609375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="6.0859375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="6.0859375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="6.44921875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5351,72 +5450,78 @@
         <v>127</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="R1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>130</v>
+      <c r="V1" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s">
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="F2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G2" t="s">
-        <v>73</v>
+        <v>32</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.0</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J2" t="s">
         <v>32</v>
@@ -5425,60 +5530,66 @@
         <v>32</v>
       </c>
       <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" t="s">
         <v>64</v>
       </c>
-      <c r="M2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" t="s">
-        <v>32</v>
-      </c>
       <c r="O2" t="s">
         <v>32</v>
       </c>
-      <c r="P2" t="b">
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" t="b">
         <v>0</v>
       </c>
-      <c r="Q2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" t="s">
-        <v>32</v>
-      </c>
       <c r="S2" t="s">
         <v>32</v>
       </c>
       <c r="T2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" t="s">
+        <v>32</v>
+      </c>
+      <c r="V2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C3" t="s">
         <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G3" t="s">
-        <v>74</v>
+        <v>142</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.0</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J3" t="s">
         <v>32</v>
@@ -5487,60 +5598,66 @@
         <v>32</v>
       </c>
       <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" t="s">
         <v>64</v>
       </c>
-      <c r="M3" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
       <c r="O3" t="s">
         <v>32</v>
       </c>
-      <c r="P3" t="b">
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" t="b">
         <v>0</v>
       </c>
-      <c r="Q3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" t="s">
-        <v>32</v>
-      </c>
       <c r="S3" t="s">
         <v>32</v>
       </c>
       <c r="T3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U3" t="s">
+        <v>32</v>
+      </c>
+      <c r="V3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G4" t="s">
-        <v>141</v>
+        <v>147</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.0</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>148</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J4" t="s">
         <v>32</v>
@@ -5549,60 +5666,66 @@
         <v>32</v>
       </c>
       <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" t="s">
         <v>64</v>
       </c>
-      <c r="M4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" t="s">
-        <v>32</v>
-      </c>
       <c r="O4" t="s">
         <v>32</v>
       </c>
-      <c r="P4" t="b">
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" t="b">
         <v>0</v>
       </c>
-      <c r="Q4" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4" t="s">
-        <v>32</v>
-      </c>
       <c r="S4" t="s">
         <v>32</v>
       </c>
       <c r="T4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U4" t="s">
+        <v>32</v>
+      </c>
+      <c r="V4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s">
         <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>151</v>
       </c>
       <c r="F5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G5" t="s">
-        <v>77</v>
+        <v>152</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.0</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J5" t="s">
         <v>32</v>
@@ -5611,60 +5734,66 @@
         <v>32</v>
       </c>
       <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" t="s">
         <v>64</v>
       </c>
-      <c r="M5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
       <c r="O5" t="s">
         <v>32</v>
       </c>
-      <c r="P5" t="b">
+      <c r="P5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" t="b">
         <v>0</v>
       </c>
-      <c r="Q5" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" t="s">
-        <v>32</v>
-      </c>
       <c r="S5" t="s">
         <v>32</v>
       </c>
       <c r="T5" t="s">
+        <v>32</v>
+      </c>
+      <c r="U5" t="s">
+        <v>32</v>
+      </c>
+      <c r="V5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C6" t="s">
         <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G6" t="s">
-        <v>148</v>
+        <v>32</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.0</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J6" t="s">
         <v>32</v>
@@ -5673,60 +5802,66 @@
         <v>32</v>
       </c>
       <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" t="s">
         <v>64</v>
       </c>
-      <c r="M6" t="s">
-        <v>32</v>
-      </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
       <c r="O6" t="s">
         <v>32</v>
       </c>
-      <c r="P6" t="b">
+      <c r="P6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" t="b">
         <v>0</v>
       </c>
-      <c r="Q6" t="s">
-        <v>32</v>
-      </c>
-      <c r="R6" t="s">
-        <v>32</v>
-      </c>
       <c r="S6" t="s">
         <v>32</v>
       </c>
       <c r="T6" t="s">
+        <v>32</v>
+      </c>
+      <c r="U6" t="s">
+        <v>32</v>
+      </c>
+      <c r="V6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="F7" t="s">
-        <v>134</v>
-      </c>
-      <c r="G7" t="s">
-        <v>152</v>
+        <v>32</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.0</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J7" t="s">
         <v>32</v>
@@ -5735,60 +5870,66 @@
         <v>32</v>
       </c>
       <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" t="s">
         <v>64</v>
       </c>
-      <c r="M7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N7" t="s">
-        <v>32</v>
-      </c>
       <c r="O7" t="s">
         <v>32</v>
       </c>
-      <c r="P7" t="b">
+      <c r="P7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" t="b">
         <v>0</v>
       </c>
-      <c r="Q7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R7" t="s">
-        <v>32</v>
-      </c>
       <c r="S7" t="s">
         <v>32</v>
       </c>
       <c r="T7" t="s">
+        <v>32</v>
+      </c>
+      <c r="U7" t="s">
+        <v>32</v>
+      </c>
+      <c r="V7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C8" t="s">
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="F8" t="s">
-        <v>134</v>
-      </c>
-      <c r="G8" t="s">
-        <v>156</v>
+        <v>32</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.0</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="I8" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J8" t="s">
         <v>32</v>
@@ -5797,60 +5938,66 @@
         <v>32</v>
       </c>
       <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" t="s">
         <v>64</v>
       </c>
-      <c r="M8" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" t="s">
-        <v>32</v>
-      </c>
       <c r="O8" t="s">
         <v>32</v>
       </c>
-      <c r="P8" t="b">
+      <c r="P8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" t="b">
         <v>0</v>
       </c>
-      <c r="Q8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R8" t="s">
-        <v>32</v>
-      </c>
       <c r="S8" t="s">
         <v>32</v>
       </c>
       <c r="T8" t="s">
+        <v>32</v>
+      </c>
+      <c r="U8" t="s">
+        <v>32</v>
+      </c>
+      <c r="V8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>167</v>
       </c>
       <c r="F9" t="s">
-        <v>134</v>
-      </c>
-      <c r="G9" t="s">
-        <v>160</v>
+        <v>32</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.0</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J9" t="s">
         <v>32</v>
@@ -5859,60 +6006,66 @@
         <v>32</v>
       </c>
       <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" t="s">
         <v>64</v>
       </c>
-      <c r="M9" t="s">
-        <v>32</v>
-      </c>
-      <c r="N9" t="s">
-        <v>32</v>
-      </c>
       <c r="O9" t="s">
         <v>32</v>
       </c>
-      <c r="P9" t="b">
+      <c r="P9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" t="b">
         <v>0</v>
       </c>
-      <c r="Q9" t="s">
-        <v>32</v>
-      </c>
-      <c r="R9" t="s">
-        <v>32</v>
-      </c>
       <c r="S9" t="s">
         <v>32</v>
       </c>
       <c r="T9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U9" t="s">
+        <v>32</v>
+      </c>
+      <c r="V9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C10" t="s">
         <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>171</v>
       </c>
       <c r="F10" t="s">
-        <v>134</v>
-      </c>
-      <c r="G10" t="s">
-        <v>86</v>
+        <v>32</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.0</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J10" t="s">
         <v>32</v>
@@ -5932,49 +6085,55 @@
       <c r="O10" t="s">
         <v>32</v>
       </c>
-      <c r="P10" t="b">
+      <c r="P10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R10" t="b">
         <v>0</v>
       </c>
-      <c r="Q10" t="s">
-        <v>32</v>
-      </c>
-      <c r="R10" t="s">
-        <v>32</v>
-      </c>
       <c r="S10" t="s">
         <v>32</v>
       </c>
       <c r="T10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U10" t="s">
+        <v>32</v>
+      </c>
+      <c r="V10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B11" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="C11" t="s">
         <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>175</v>
       </c>
       <c r="F11" t="s">
-        <v>134</v>
-      </c>
-      <c r="G11" t="s">
-        <v>87</v>
+        <v>32</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.0</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J11" t="s">
         <v>32</v>
@@ -5994,49 +6153,55 @@
       <c r="O11" t="s">
         <v>32</v>
       </c>
-      <c r="P11" t="b">
+      <c r="P11" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" t="b">
         <v>0</v>
       </c>
-      <c r="Q11" t="s">
-        <v>32</v>
-      </c>
-      <c r="R11" t="s">
-        <v>32</v>
-      </c>
       <c r="S11" t="s">
         <v>32</v>
       </c>
       <c r="T11" t="s">
+        <v>32</v>
+      </c>
+      <c r="U11" t="s">
+        <v>32</v>
+      </c>
+      <c r="V11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="B12" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C12" t="s">
         <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="F12" t="s">
-        <v>134</v>
-      </c>
-      <c r="G12" t="s">
-        <v>88</v>
+        <v>32</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.0</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>181</v>
       </c>
       <c r="I12" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J12" t="s">
         <v>32</v>
@@ -6056,49 +6221,55 @@
       <c r="O12" t="s">
         <v>32</v>
       </c>
-      <c r="P12" t="b">
+      <c r="P12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12" t="b">
         <v>0</v>
       </c>
-      <c r="Q12" t="s">
-        <v>32</v>
-      </c>
-      <c r="R12" t="s">
-        <v>32</v>
-      </c>
       <c r="S12" t="s">
         <v>32</v>
       </c>
       <c r="T12" t="s">
+        <v>32</v>
+      </c>
+      <c r="U12" t="s">
+        <v>32</v>
+      </c>
+      <c r="V12" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B13" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="C13" t="s">
         <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>170</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>151</v>
       </c>
       <c r="F13" t="s">
-        <v>134</v>
-      </c>
-      <c r="G13" t="s">
-        <v>171</v>
+        <v>184</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.0</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>185</v>
       </c>
       <c r="I13" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J13" t="s">
         <v>32</v>
@@ -6118,49 +6289,55 @@
       <c r="O13" t="s">
         <v>32</v>
       </c>
-      <c r="P13" t="b">
+      <c r="P13" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" t="b">
         <v>0</v>
       </c>
-      <c r="Q13" t="s">
-        <v>32</v>
-      </c>
-      <c r="R13" t="s">
-        <v>32</v>
-      </c>
       <c r="S13" t="s">
         <v>32</v>
       </c>
       <c r="T13" t="s">
+        <v>32</v>
+      </c>
+      <c r="U13" t="s">
+        <v>32</v>
+      </c>
+      <c r="V13" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B14" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="C14" t="s">
         <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="E14" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F14" t="s">
-        <v>134</v>
-      </c>
-      <c r="G14" t="s">
-        <v>91</v>
+        <v>32</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.0</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J14" t="s">
         <v>32</v>
@@ -6180,49 +6357,55 @@
       <c r="O14" t="s">
         <v>32</v>
       </c>
-      <c r="P14" t="b">
+      <c r="P14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" t="b">
         <v>0</v>
       </c>
-      <c r="Q14" t="s">
-        <v>32</v>
-      </c>
-      <c r="R14" t="s">
-        <v>32</v>
-      </c>
       <c r="S14" t="s">
         <v>32</v>
       </c>
       <c r="T14" t="s">
+        <v>32</v>
+      </c>
+      <c r="U14" t="s">
+        <v>32</v>
+      </c>
+      <c r="V14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="C15" t="s">
         <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="E15" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="F15" t="s">
-        <v>134</v>
-      </c>
-      <c r="G15" t="s">
-        <v>177</v>
+        <v>32</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.0</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>194</v>
       </c>
       <c r="I15" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J15" t="s">
         <v>32</v>
@@ -6242,49 +6425,55 @@
       <c r="O15" t="s">
         <v>32</v>
       </c>
-      <c r="P15" t="b">
+      <c r="P15" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" t="b">
         <v>0</v>
       </c>
-      <c r="Q15" t="s">
-        <v>32</v>
-      </c>
-      <c r="R15" t="s">
-        <v>32</v>
-      </c>
       <c r="S15" t="s">
         <v>32</v>
       </c>
       <c r="T15" t="s">
+        <v>32</v>
+      </c>
+      <c r="U15" t="s">
+        <v>32</v>
+      </c>
+      <c r="V15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="C16" t="s">
         <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>197</v>
       </c>
       <c r="F16" t="s">
-        <v>134</v>
-      </c>
-      <c r="G16" t="s">
-        <v>94</v>
+        <v>32</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.0</v>
       </c>
       <c r="H16" t="s">
-        <v>32</v>
+        <v>198</v>
       </c>
       <c r="I16" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J16" t="s">
         <v>32</v>
@@ -6304,49 +6493,55 @@
       <c r="O16" t="s">
         <v>32</v>
       </c>
-      <c r="P16" t="b">
+      <c r="P16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" t="b">
         <v>0</v>
       </c>
-      <c r="Q16" t="s">
-        <v>32</v>
-      </c>
-      <c r="R16" t="s">
-        <v>32</v>
-      </c>
       <c r="S16" t="s">
         <v>32</v>
       </c>
       <c r="T16" t="s">
+        <v>32</v>
+      </c>
+      <c r="U16" t="s">
+        <v>32</v>
+      </c>
+      <c r="V16" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C17" t="s">
         <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>180</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>167</v>
       </c>
       <c r="F17" t="s">
-        <v>134</v>
-      </c>
-      <c r="G17" t="s">
-        <v>183</v>
+        <v>32</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.0</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="I17" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J17" t="s">
         <v>32</v>
@@ -6366,49 +6561,55 @@
       <c r="O17" t="s">
         <v>32</v>
       </c>
-      <c r="P17" t="b">
+      <c r="P17" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" t="b">
         <v>0</v>
       </c>
-      <c r="Q17" t="s">
-        <v>32</v>
-      </c>
-      <c r="R17" t="s">
-        <v>32</v>
-      </c>
       <c r="S17" t="s">
         <v>32</v>
       </c>
       <c r="T17" t="s">
+        <v>32</v>
+      </c>
+      <c r="U17" t="s">
+        <v>32</v>
+      </c>
+      <c r="V17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="B18" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="C18" t="s">
         <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>180</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>204</v>
       </c>
       <c r="F18" t="s">
-        <v>134</v>
-      </c>
-      <c r="G18" t="s">
-        <v>97</v>
+        <v>32</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.0</v>
       </c>
       <c r="H18" t="s">
-        <v>32</v>
+        <v>205</v>
       </c>
       <c r="I18" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J18" t="s">
         <v>32</v>
@@ -6428,49 +6629,55 @@
       <c r="O18" t="s">
         <v>32</v>
       </c>
-      <c r="P18" t="b">
+      <c r="P18" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" t="b">
         <v>0</v>
       </c>
-      <c r="Q18" t="s">
-        <v>32</v>
-      </c>
-      <c r="R18" t="s">
-        <v>32</v>
-      </c>
       <c r="S18" t="s">
         <v>32</v>
       </c>
       <c r="T18" t="s">
+        <v>32</v>
+      </c>
+      <c r="U18" t="s">
+        <v>32</v>
+      </c>
+      <c r="V18" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="C19" t="s">
         <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>188</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>208</v>
       </c>
       <c r="F19" t="s">
-        <v>134</v>
-      </c>
-      <c r="G19" t="s">
-        <v>98</v>
+        <v>142</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.0</v>
       </c>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>209</v>
       </c>
       <c r="I19" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J19" t="s">
         <v>32</v>
@@ -6490,49 +6697,55 @@
       <c r="O19" t="s">
         <v>32</v>
       </c>
-      <c r="P19" t="b">
+      <c r="P19" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" t="b">
         <v>0</v>
       </c>
-      <c r="Q19" t="s">
-        <v>32</v>
-      </c>
-      <c r="R19" t="s">
-        <v>32</v>
-      </c>
       <c r="S19" t="s">
         <v>32</v>
       </c>
       <c r="T19" t="s">
+        <v>32</v>
+      </c>
+      <c r="U19" t="s">
+        <v>32</v>
+      </c>
+      <c r="V19" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>191</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="F20" t="s">
-        <v>134</v>
-      </c>
-      <c r="G20" t="s">
-        <v>99</v>
+        <v>32</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.0</v>
       </c>
       <c r="H20" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="I20" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J20" t="s">
         <v>32</v>
@@ -6552,49 +6765,55 @@
       <c r="O20" t="s">
         <v>32</v>
       </c>
-      <c r="P20" t="b">
+      <c r="P20" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>32</v>
+      </c>
+      <c r="R20" t="b">
         <v>0</v>
       </c>
-      <c r="Q20" t="s">
-        <v>32</v>
-      </c>
-      <c r="R20" t="s">
-        <v>32</v>
-      </c>
       <c r="S20" t="s">
         <v>32</v>
       </c>
       <c r="T20" t="s">
+        <v>32</v>
+      </c>
+      <c r="U20" t="s">
+        <v>32</v>
+      </c>
+      <c r="V20" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="C21" t="s">
         <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>204</v>
       </c>
       <c r="F21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G21" t="s">
-        <v>100</v>
+        <v>184</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.0</v>
       </c>
       <c r="H21" t="s">
-        <v>32</v>
+        <v>217</v>
       </c>
       <c r="I21" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J21" t="s">
         <v>32</v>
@@ -6614,49 +6833,55 @@
       <c r="O21" t="s">
         <v>32</v>
       </c>
-      <c r="P21" t="b">
+      <c r="P21" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>32</v>
+      </c>
+      <c r="R21" t="b">
         <v>0</v>
       </c>
-      <c r="Q21" t="s">
-        <v>32</v>
-      </c>
-      <c r="R21" t="s">
-        <v>32</v>
-      </c>
       <c r="S21" t="s">
         <v>32</v>
       </c>
       <c r="T21" t="s">
+        <v>32</v>
+      </c>
+      <c r="U21" t="s">
+        <v>32</v>
+      </c>
+      <c r="V21" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C22" t="s">
         <v>34</v>
       </c>
       <c r="D22" t="s">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="F22" t="s">
-        <v>134</v>
-      </c>
-      <c r="G22" t="s">
-        <v>197</v>
+        <v>220</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.0</v>
       </c>
       <c r="H22" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="I22" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J22" t="s">
         <v>32</v>
@@ -6676,49 +6901,55 @@
       <c r="O22" t="s">
         <v>32</v>
       </c>
-      <c r="P22" t="b">
+      <c r="P22" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>32</v>
+      </c>
+      <c r="R22" t="b">
         <v>0</v>
       </c>
-      <c r="Q22" t="s">
-        <v>32</v>
-      </c>
-      <c r="R22" t="s">
-        <v>32</v>
-      </c>
       <c r="S22" t="s">
         <v>32</v>
       </c>
       <c r="T22" t="s">
+        <v>32</v>
+      </c>
+      <c r="U22" t="s">
+        <v>32</v>
+      </c>
+      <c r="V22" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C23" t="s">
         <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>223</v>
       </c>
       <c r="F23" t="s">
-        <v>134</v>
-      </c>
-      <c r="G23" t="s">
-        <v>200</v>
+        <v>32</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.0</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>148</v>
       </c>
       <c r="I23" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J23" t="s">
         <v>32</v>
@@ -6738,49 +6969,55 @@
       <c r="O23" t="s">
         <v>32</v>
       </c>
-      <c r="P23" t="b">
+      <c r="P23" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>32</v>
+      </c>
+      <c r="R23" t="b">
         <v>0</v>
       </c>
-      <c r="Q23" t="s">
-        <v>32</v>
-      </c>
-      <c r="R23" t="s">
-        <v>32</v>
-      </c>
       <c r="S23" t="s">
         <v>32</v>
       </c>
       <c r="T23" t="s">
+        <v>32</v>
+      </c>
+      <c r="U23" t="s">
+        <v>32</v>
+      </c>
+      <c r="V23" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>159</v>
+        <v>226</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F24" t="s">
-        <v>134</v>
-      </c>
-      <c r="G24" t="s">
-        <v>203</v>
+        <v>32</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.0</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="I24" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J24" t="s">
         <v>32</v>
@@ -6800,49 +7037,55 @@
       <c r="O24" t="s">
         <v>32</v>
       </c>
-      <c r="P24" t="b">
+      <c r="P24" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>32</v>
+      </c>
+      <c r="R24" t="b">
         <v>0</v>
       </c>
-      <c r="Q24" t="s">
-        <v>32</v>
-      </c>
-      <c r="R24" t="s">
-        <v>32</v>
-      </c>
       <c r="S24" t="s">
         <v>32</v>
       </c>
       <c r="T24" t="s">
+        <v>32</v>
+      </c>
+      <c r="U24" t="s">
+        <v>32</v>
+      </c>
+      <c r="V24" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C25" t="s">
         <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>151</v>
       </c>
       <c r="F25" t="s">
-        <v>134</v>
-      </c>
-      <c r="G25" t="s">
-        <v>108</v>
+        <v>32</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.0</v>
       </c>
       <c r="H25" t="s">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="I25" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J25" t="s">
         <v>32</v>
@@ -6862,49 +7105,55 @@
       <c r="O25" t="s">
         <v>32</v>
       </c>
-      <c r="P25" t="b">
+      <c r="P25" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>32</v>
+      </c>
+      <c r="R25" t="b">
         <v>0</v>
       </c>
-      <c r="Q25" t="s">
-        <v>32</v>
-      </c>
-      <c r="R25" t="s">
-        <v>32</v>
-      </c>
       <c r="S25" t="s">
         <v>32</v>
       </c>
       <c r="T25" t="s">
+        <v>32</v>
+      </c>
+      <c r="U25" t="s">
+        <v>32</v>
+      </c>
+      <c r="V25" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="C26" t="s">
         <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>191</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F26" t="s">
-        <v>134</v>
-      </c>
-      <c r="G26" t="s">
-        <v>109</v>
+        <v>147</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.0</v>
       </c>
       <c r="H26" t="s">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="I26" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J26" t="s">
         <v>32</v>
@@ -6924,49 +7173,55 @@
       <c r="O26" t="s">
         <v>32</v>
       </c>
-      <c r="P26" t="b">
+      <c r="P26" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>32</v>
+      </c>
+      <c r="R26" t="b">
         <v>0</v>
       </c>
-      <c r="Q26" t="s">
-        <v>32</v>
-      </c>
-      <c r="R26" t="s">
-        <v>32</v>
-      </c>
       <c r="S26" t="s">
         <v>32</v>
       </c>
       <c r="T26" t="s">
+        <v>32</v>
+      </c>
+      <c r="U26" t="s">
+        <v>32</v>
+      </c>
+      <c r="V26" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="C27" t="s">
         <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F27" t="s">
-        <v>134</v>
-      </c>
-      <c r="G27" t="s">
-        <v>110</v>
+        <v>32</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.0</v>
       </c>
       <c r="H27" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="I27" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J27" t="s">
         <v>32</v>
@@ -6986,49 +7241,55 @@
       <c r="O27" t="s">
         <v>32</v>
       </c>
-      <c r="P27" t="b">
+      <c r="P27" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>32</v>
+      </c>
+      <c r="R27" t="b">
         <v>0</v>
       </c>
-      <c r="Q27" t="s">
-        <v>32</v>
-      </c>
-      <c r="R27" t="s">
-        <v>32</v>
-      </c>
       <c r="S27" t="s">
         <v>32</v>
       </c>
       <c r="T27" t="s">
+        <v>32</v>
+      </c>
+      <c r="U27" t="s">
+        <v>32</v>
+      </c>
+      <c r="V27" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="B28" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="C28" t="s">
         <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F28" t="s">
-        <v>134</v>
-      </c>
-      <c r="G28" t="s">
-        <v>213</v>
+        <v>32</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.0</v>
       </c>
       <c r="H28" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="I28" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J28" t="s">
         <v>32</v>
@@ -7048,49 +7309,55 @@
       <c r="O28" t="s">
         <v>32</v>
       </c>
-      <c r="P28" t="b">
+      <c r="P28" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>32</v>
+      </c>
+      <c r="R28" t="b">
         <v>0</v>
       </c>
-      <c r="Q28" t="s">
-        <v>32</v>
-      </c>
-      <c r="R28" t="s">
-        <v>32</v>
-      </c>
       <c r="S28" t="s">
         <v>32</v>
       </c>
       <c r="T28" t="s">
+        <v>32</v>
+      </c>
+      <c r="U28" t="s">
+        <v>32</v>
+      </c>
+      <c r="V28" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="B29" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="C29" t="s">
         <v>34</v>
       </c>
       <c r="D29" t="s">
-        <v>191</v>
+        <v>237</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>238</v>
       </c>
       <c r="F29" t="s">
-        <v>134</v>
-      </c>
-      <c r="G29" t="s">
-        <v>115</v>
+        <v>32</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.0</v>
       </c>
       <c r="H29" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="I29" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J29" t="s">
         <v>32</v>
@@ -7110,49 +7377,55 @@
       <c r="O29" t="s">
         <v>32</v>
       </c>
-      <c r="P29" t="b">
+      <c r="P29" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>32</v>
+      </c>
+      <c r="R29" t="b">
         <v>0</v>
       </c>
-      <c r="Q29" t="s">
-        <v>32</v>
-      </c>
-      <c r="R29" t="s">
-        <v>32</v>
-      </c>
       <c r="S29" t="s">
         <v>32</v>
       </c>
       <c r="T29" t="s">
+        <v>32</v>
+      </c>
+      <c r="U29" t="s">
+        <v>32</v>
+      </c>
+      <c r="V29" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="B30" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C30" t="s">
         <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="F30" t="s">
-        <v>134</v>
-      </c>
-      <c r="G30" t="s">
-        <v>218</v>
+        <v>32</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.0</v>
       </c>
       <c r="H30" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="I30" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J30" t="s">
         <v>32</v>
@@ -7172,49 +7445,55 @@
       <c r="O30" t="s">
         <v>32</v>
       </c>
-      <c r="P30" t="b">
+      <c r="P30" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>32</v>
+      </c>
+      <c r="R30" t="b">
         <v>0</v>
       </c>
-      <c r="Q30" t="s">
-        <v>32</v>
-      </c>
-      <c r="R30" t="s">
-        <v>32</v>
-      </c>
       <c r="S30" t="s">
         <v>32</v>
       </c>
       <c r="T30" t="s">
+        <v>32</v>
+      </c>
+      <c r="U30" t="s">
+        <v>32</v>
+      </c>
+      <c r="V30" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="B31" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>221</v>
+        <v>111</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G31" t="s">
-        <v>222</v>
+        <v>32</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.0</v>
       </c>
       <c r="H31" t="s">
-        <v>32</v>
+        <v>181</v>
       </c>
       <c r="I31" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J31" t="s">
         <v>32</v>
@@ -7234,49 +7513,55 @@
       <c r="O31" t="s">
         <v>32</v>
       </c>
-      <c r="P31" t="b">
+      <c r="P31" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" t="b">
         <v>0</v>
       </c>
-      <c r="Q31" t="s">
-        <v>32</v>
-      </c>
-      <c r="R31" t="s">
-        <v>32</v>
-      </c>
       <c r="S31" t="s">
         <v>32</v>
       </c>
       <c r="T31" t="s">
+        <v>32</v>
+      </c>
+      <c r="U31" t="s">
+        <v>32</v>
+      </c>
+      <c r="V31" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="B32" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="C32" t="s">
         <v>34</v>
       </c>
       <c r="D32" t="s">
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="E32" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="F32" t="s">
-        <v>134</v>
-      </c>
-      <c r="G32" t="s">
-        <v>120</v>
+        <v>32</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.0</v>
       </c>
       <c r="H32" t="s">
-        <v>32</v>
+        <v>185</v>
       </c>
       <c r="I32" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J32" t="s">
         <v>32</v>
@@ -7296,49 +7581,55 @@
       <c r="O32" t="s">
         <v>32</v>
       </c>
-      <c r="P32" t="b">
+      <c r="P32" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>32</v>
+      </c>
+      <c r="R32" t="b">
         <v>0</v>
       </c>
-      <c r="Q32" t="s">
-        <v>32</v>
-      </c>
-      <c r="R32" t="s">
-        <v>32</v>
-      </c>
       <c r="S32" t="s">
         <v>32</v>
       </c>
       <c r="T32" t="s">
+        <v>32</v>
+      </c>
+      <c r="U32" t="s">
+        <v>32</v>
+      </c>
+      <c r="V32" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="B33" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="C33" t="s">
         <v>34</v>
       </c>
       <c r="D33" t="s">
-        <v>159</v>
+        <v>249</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F33" t="s">
-        <v>134</v>
-      </c>
-      <c r="G33" t="s">
-        <v>228</v>
+        <v>32</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.0</v>
       </c>
       <c r="H33" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="I33" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J33" t="s">
         <v>32</v>
@@ -7358,49 +7649,55 @@
       <c r="O33" t="s">
         <v>32</v>
       </c>
-      <c r="P33" t="b">
+      <c r="P33" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>32</v>
+      </c>
+      <c r="R33" t="b">
         <v>0</v>
       </c>
-      <c r="Q33" t="s">
-        <v>32</v>
-      </c>
-      <c r="R33" t="s">
-        <v>32</v>
-      </c>
       <c r="S33" t="s">
         <v>32</v>
       </c>
       <c r="T33" t="s">
+        <v>32</v>
+      </c>
+      <c r="U33" t="s">
+        <v>32</v>
+      </c>
+      <c r="V33" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="B34" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="C34" t="s">
         <v>34</v>
       </c>
       <c r="D34" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="F34" t="s">
-        <v>134</v>
-      </c>
-      <c r="G34" t="s">
-        <v>74</v>
+        <v>32</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.0</v>
       </c>
       <c r="H34" t="s">
-        <v>32</v>
+        <v>194</v>
       </c>
       <c r="I34" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J34" t="s">
         <v>32</v>
@@ -7420,49 +7717,55 @@
       <c r="O34" t="s">
         <v>32</v>
       </c>
-      <c r="P34" t="b">
+      <c r="P34" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>32</v>
+      </c>
+      <c r="R34" t="b">
         <v>0</v>
       </c>
-      <c r="Q34" t="s">
-        <v>32</v>
-      </c>
-      <c r="R34" t="s">
-        <v>32</v>
-      </c>
       <c r="S34" t="s">
         <v>32</v>
       </c>
       <c r="T34" t="s">
+        <v>32</v>
+      </c>
+      <c r="U34" t="s">
+        <v>32</v>
+      </c>
+      <c r="V34" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="B35" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="C35" t="s">
         <v>34</v>
       </c>
       <c r="D35" t="s">
+        <v>255</v>
+      </c>
+      <c r="E35" t="s">
         <v>151</v>
       </c>
-      <c r="E35" t="s">
-        <v>32</v>
-      </c>
       <c r="F35" t="s">
-        <v>134</v>
-      </c>
-      <c r="G35" t="s">
-        <v>234</v>
+        <v>147</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.0</v>
       </c>
       <c r="H35" t="s">
-        <v>32</v>
+        <v>198</v>
       </c>
       <c r="I35" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J35" t="s">
         <v>32</v>
@@ -7482,49 +7785,55 @@
       <c r="O35" t="s">
         <v>32</v>
       </c>
-      <c r="P35" t="b">
+      <c r="P35" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>32</v>
+      </c>
+      <c r="R35" t="b">
         <v>0</v>
       </c>
-      <c r="Q35" t="s">
-        <v>32</v>
-      </c>
-      <c r="R35" t="s">
-        <v>32</v>
-      </c>
       <c r="S35" t="s">
         <v>32</v>
       </c>
       <c r="T35" t="s">
+        <v>32</v>
+      </c>
+      <c r="U35" t="s">
+        <v>32</v>
+      </c>
+      <c r="V35" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>235</v>
+        <v>52</v>
       </c>
       <c r="B36" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C36" t="s">
         <v>34</v>
       </c>
       <c r="D36" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="E36" t="s">
-        <v>32</v>
+        <v>151</v>
       </c>
       <c r="F36" t="s">
-        <v>134</v>
-      </c>
-      <c r="G36" t="s">
-        <v>79</v>
+        <v>32</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.0</v>
       </c>
       <c r="H36" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="I36" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J36" t="s">
         <v>32</v>
@@ -7544,49 +7853,55 @@
       <c r="O36" t="s">
         <v>32</v>
       </c>
-      <c r="P36" t="b">
-        <v>0</v>
+      <c r="P36" t="s">
+        <v>32</v>
       </c>
       <c r="Q36" t="s">
         <v>32</v>
       </c>
-      <c r="R36" t="s">
-        <v>32</v>
+      <c r="R36" s="3" t="b">
+        <v>1</v>
       </c>
       <c r="S36" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="T36" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="U36" t="s">
+        <v>33</v>
+      </c>
+      <c r="V36" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="B37" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="C37" t="s">
         <v>34</v>
       </c>
       <c r="D37" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="E37" t="s">
-        <v>225</v>
+        <v>136</v>
       </c>
       <c r="F37" t="s">
-        <v>134</v>
-      </c>
-      <c r="G37" t="s">
-        <v>152</v>
+        <v>32</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.0</v>
       </c>
       <c r="H37" t="s">
-        <v>32</v>
+        <v>205</v>
       </c>
       <c r="I37" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J37" t="s">
         <v>32</v>
@@ -7606,49 +7921,55 @@
       <c r="O37" t="s">
         <v>32</v>
       </c>
-      <c r="P37" t="b">
+      <c r="P37" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>32</v>
+      </c>
+      <c r="R37" t="b">
         <v>0</v>
       </c>
-      <c r="Q37" t="s">
-        <v>32</v>
-      </c>
-      <c r="R37" t="s">
-        <v>32</v>
-      </c>
       <c r="S37" t="s">
         <v>32</v>
       </c>
       <c r="T37" t="s">
+        <v>32</v>
+      </c>
+      <c r="U37" t="s">
+        <v>32</v>
+      </c>
+      <c r="V37" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="B38" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="C38" t="s">
         <v>34</v>
       </c>
       <c r="D38" t="s">
-        <v>151</v>
+        <v>261</v>
       </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="F38" t="s">
-        <v>134</v>
-      </c>
-      <c r="G38" t="s">
-        <v>82</v>
+        <v>32</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.0</v>
       </c>
       <c r="H38" t="s">
-        <v>32</v>
+        <v>209</v>
       </c>
       <c r="I38" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J38" t="s">
         <v>32</v>
@@ -7668,49 +7989,55 @@
       <c r="O38" t="s">
         <v>32</v>
       </c>
-      <c r="P38" t="b">
+      <c r="P38" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>32</v>
+      </c>
+      <c r="R38" t="b">
         <v>0</v>
       </c>
-      <c r="Q38" t="s">
-        <v>32</v>
-      </c>
-      <c r="R38" t="s">
-        <v>32</v>
-      </c>
       <c r="S38" t="s">
         <v>32</v>
       </c>
       <c r="T38" t="s">
+        <v>32</v>
+      </c>
+      <c r="U38" t="s">
+        <v>32</v>
+      </c>
+      <c r="V38" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="B39" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="C39" t="s">
         <v>34</v>
       </c>
       <c r="D39" t="s">
-        <v>159</v>
+        <v>264</v>
       </c>
       <c r="E39" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="F39" t="s">
-        <v>134</v>
-      </c>
-      <c r="G39" t="s">
-        <v>244</v>
+        <v>32</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3.0</v>
       </c>
       <c r="H39" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="I39" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J39" t="s">
         <v>32</v>
@@ -7730,49 +8057,55 @@
       <c r="O39" t="s">
         <v>32</v>
       </c>
-      <c r="P39" t="b">
+      <c r="P39" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>32</v>
+      </c>
+      <c r="R39" t="b">
         <v>0</v>
       </c>
-      <c r="Q39" t="s">
-        <v>32</v>
-      </c>
-      <c r="R39" t="s">
-        <v>32</v>
-      </c>
       <c r="S39" t="s">
         <v>32</v>
       </c>
       <c r="T39" t="s">
+        <v>32</v>
+      </c>
+      <c r="U39" t="s">
+        <v>32</v>
+      </c>
+      <c r="V39" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="B40" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="C40" t="s">
         <v>34</v>
       </c>
       <c r="D40" t="s">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="E40" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F40" t="s">
-        <v>134</v>
-      </c>
-      <c r="G40" t="s">
-        <v>86</v>
+        <v>32</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.0</v>
       </c>
       <c r="H40" t="s">
-        <v>32</v>
+        <v>217</v>
       </c>
       <c r="I40" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J40" t="s">
         <v>32</v>
@@ -7792,49 +8125,55 @@
       <c r="O40" t="s">
         <v>32</v>
       </c>
-      <c r="P40" t="b">
+      <c r="P40" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>32</v>
+      </c>
+      <c r="R40" t="b">
         <v>0</v>
       </c>
-      <c r="Q40" t="s">
-        <v>32</v>
-      </c>
-      <c r="R40" t="s">
-        <v>32</v>
-      </c>
       <c r="S40" t="s">
         <v>32</v>
       </c>
       <c r="T40" t="s">
+        <v>32</v>
+      </c>
+      <c r="U40" t="s">
+        <v>32</v>
+      </c>
+      <c r="V40" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="B41" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="C41" t="s">
         <v>34</v>
       </c>
       <c r="D41" t="s">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="F41" t="s">
-        <v>134</v>
-      </c>
-      <c r="G41" t="s">
-        <v>87</v>
+        <v>32</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.0</v>
       </c>
       <c r="H41" t="s">
-        <v>32</v>
+        <v>269</v>
       </c>
       <c r="I41" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J41" t="s">
         <v>32</v>
@@ -7854,49 +8193,55 @@
       <c r="O41" t="s">
         <v>32</v>
       </c>
-      <c r="P41" t="b">
+      <c r="P41" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>32</v>
+      </c>
+      <c r="R41" t="b">
         <v>0</v>
       </c>
-      <c r="Q41" t="s">
-        <v>32</v>
-      </c>
-      <c r="R41" t="s">
-        <v>32</v>
-      </c>
       <c r="S41" t="s">
         <v>32</v>
       </c>
       <c r="T41" t="s">
+        <v>32</v>
+      </c>
+      <c r="U41" t="s">
+        <v>32</v>
+      </c>
+      <c r="V41" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="B42" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C42" t="s">
         <v>34</v>
       </c>
       <c r="D42" t="s">
-        <v>239</v>
+        <v>81</v>
       </c>
       <c r="E42" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="F42" t="s">
-        <v>134</v>
-      </c>
-      <c r="G42" t="s">
-        <v>88</v>
+        <v>32</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.0</v>
       </c>
       <c r="H42" t="s">
-        <v>32</v>
+        <v>148</v>
       </c>
       <c r="I42" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J42" t="s">
         <v>32</v>
@@ -7916,49 +8261,55 @@
       <c r="O42" t="s">
         <v>32</v>
       </c>
-      <c r="P42" t="b">
+      <c r="P42" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>32</v>
+      </c>
+      <c r="R42" t="b">
         <v>0</v>
       </c>
-      <c r="Q42" t="s">
-        <v>32</v>
-      </c>
-      <c r="R42" t="s">
-        <v>32</v>
-      </c>
       <c r="S42" t="s">
         <v>32</v>
       </c>
       <c r="T42" t="s">
+        <v>32</v>
+      </c>
+      <c r="U42" t="s">
+        <v>32</v>
+      </c>
+      <c r="V42" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="B43" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="C43" t="s">
         <v>34</v>
       </c>
       <c r="D43" t="s">
-        <v>159</v>
+        <v>274</v>
       </c>
       <c r="E43" t="s">
-        <v>32</v>
+        <v>151</v>
       </c>
       <c r="F43" t="s">
-        <v>134</v>
-      </c>
-      <c r="G43" t="s">
-        <v>171</v>
+        <v>32</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.0</v>
       </c>
       <c r="H43" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="I43" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J43" t="s">
         <v>32</v>
@@ -7978,49 +8329,55 @@
       <c r="O43" t="s">
         <v>32</v>
       </c>
-      <c r="P43" t="b">
+      <c r="P43" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>32</v>
+      </c>
+      <c r="R43" t="b">
         <v>0</v>
       </c>
-      <c r="Q43" t="s">
-        <v>32</v>
-      </c>
-      <c r="R43" t="s">
-        <v>32</v>
-      </c>
       <c r="S43" t="s">
         <v>32</v>
       </c>
       <c r="T43" t="s">
+        <v>32</v>
+      </c>
+      <c r="U43" t="s">
+        <v>32</v>
+      </c>
+      <c r="V43" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>275</v>
       </c>
       <c r="B44" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="C44" t="s">
         <v>34</v>
       </c>
       <c r="D44" t="s">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="E44" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="F44" t="s">
-        <v>134</v>
-      </c>
-      <c r="G44" t="s">
-        <v>91</v>
+        <v>147</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.0</v>
       </c>
       <c r="H44" t="s">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="I44" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J44" t="s">
         <v>32</v>
@@ -8040,49 +8397,55 @@
       <c r="O44" t="s">
         <v>32</v>
       </c>
-      <c r="P44" s="3" t="b">
-        <v>1</v>
+      <c r="P44" t="s">
+        <v>32</v>
       </c>
       <c r="Q44" t="s">
-        <v>28</v>
-      </c>
-      <c r="R44" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="R44" t="b">
+        <v>0</v>
       </c>
       <c r="S44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T44" t="s">
-        <v>50</v>
+        <v>32</v>
+      </c>
+      <c r="U44" t="s">
+        <v>32</v>
+      </c>
+      <c r="V44" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="B45" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="C45" t="s">
         <v>34</v>
       </c>
       <c r="D45" t="s">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>167</v>
       </c>
       <c r="F45" t="s">
-        <v>134</v>
-      </c>
-      <c r="G45" t="s">
-        <v>177</v>
+        <v>32</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3.0</v>
       </c>
       <c r="H45" t="s">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="I45" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J45" t="s">
         <v>32</v>
@@ -8102,49 +8465,55 @@
       <c r="O45" t="s">
         <v>32</v>
       </c>
-      <c r="P45" t="b">
+      <c r="P45" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>32</v>
+      </c>
+      <c r="R45" t="b">
         <v>0</v>
       </c>
-      <c r="Q45" t="s">
-        <v>32</v>
-      </c>
-      <c r="R45" t="s">
-        <v>32</v>
-      </c>
       <c r="S45" t="s">
         <v>32</v>
       </c>
       <c r="T45" t="s">
+        <v>32</v>
+      </c>
+      <c r="U45" t="s">
+        <v>32</v>
+      </c>
+      <c r="V45" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="B46" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="C46" t="s">
         <v>34</v>
       </c>
       <c r="D46" t="s">
-        <v>191</v>
+        <v>281</v>
       </c>
       <c r="E46" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F46" t="s">
-        <v>134</v>
-      </c>
-      <c r="G46" t="s">
-        <v>94</v>
+        <v>32</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.0</v>
       </c>
       <c r="H46" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="I46" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J46" t="s">
         <v>32</v>
@@ -8164,49 +8533,55 @@
       <c r="O46" t="s">
         <v>32</v>
       </c>
-      <c r="P46" t="b">
+      <c r="P46" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>32</v>
+      </c>
+      <c r="R46" t="b">
         <v>0</v>
       </c>
-      <c r="Q46" t="s">
-        <v>32</v>
-      </c>
-      <c r="R46" t="s">
-        <v>32</v>
-      </c>
       <c r="S46" t="s">
         <v>32</v>
       </c>
       <c r="T46" t="s">
+        <v>32</v>
+      </c>
+      <c r="U46" t="s">
+        <v>32</v>
+      </c>
+      <c r="V46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="B47" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="C47" t="s">
         <v>34</v>
       </c>
       <c r="D47" t="s">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="E47" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F47" t="s">
-        <v>134</v>
-      </c>
-      <c r="G47" t="s">
-        <v>183</v>
+        <v>284</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.0</v>
       </c>
       <c r="H47" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="I47" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J47" t="s">
         <v>32</v>
@@ -8226,49 +8601,55 @@
       <c r="O47" t="s">
         <v>32</v>
       </c>
-      <c r="P47" t="b">
+      <c r="P47" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>32</v>
+      </c>
+      <c r="R47" t="b">
         <v>0</v>
       </c>
-      <c r="Q47" t="s">
-        <v>32</v>
-      </c>
-      <c r="R47" t="s">
-        <v>32</v>
-      </c>
       <c r="S47" t="s">
         <v>32</v>
       </c>
       <c r="T47" t="s">
+        <v>32</v>
+      </c>
+      <c r="U47" t="s">
+        <v>32</v>
+      </c>
+      <c r="V47" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="B48" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="C48" t="s">
         <v>34</v>
       </c>
       <c r="D48" t="s">
-        <v>239</v>
+        <v>89</v>
       </c>
       <c r="E48" t="s">
-        <v>32</v>
+        <v>151</v>
       </c>
       <c r="F48" t="s">
-        <v>134</v>
-      </c>
-      <c r="G48" t="s">
-        <v>97</v>
+        <v>32</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.0</v>
       </c>
       <c r="H48" t="s">
-        <v>32</v>
+        <v>287</v>
       </c>
       <c r="I48" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J48" t="s">
         <v>32</v>
@@ -8288,49 +8669,55 @@
       <c r="O48" t="s">
         <v>32</v>
       </c>
-      <c r="P48" t="b">
+      <c r="P48" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>32</v>
+      </c>
+      <c r="R48" t="b">
         <v>0</v>
       </c>
-      <c r="Q48" t="s">
-        <v>32</v>
-      </c>
-      <c r="R48" t="s">
-        <v>32</v>
-      </c>
       <c r="S48" t="s">
         <v>32</v>
       </c>
       <c r="T48" t="s">
+        <v>32</v>
+      </c>
+      <c r="U48" t="s">
+        <v>32</v>
+      </c>
+      <c r="V48" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="B49" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="C49" t="s">
         <v>34</v>
       </c>
       <c r="D49" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="E49" t="s">
-        <v>32</v>
+        <v>290</v>
       </c>
       <c r="F49" t="s">
-        <v>134</v>
-      </c>
-      <c r="G49" t="s">
-        <v>264</v>
+        <v>220</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.0</v>
       </c>
       <c r="H49" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="I49" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J49" t="s">
         <v>32</v>
@@ -8350,49 +8737,55 @@
       <c r="O49" t="s">
         <v>32</v>
       </c>
-      <c r="P49" t="b">
+      <c r="P49" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>32</v>
+      </c>
+      <c r="R49" t="b">
         <v>0</v>
       </c>
-      <c r="Q49" t="s">
-        <v>32</v>
-      </c>
-      <c r="R49" t="s">
-        <v>32</v>
-      </c>
       <c r="S49" t="s">
         <v>32</v>
       </c>
       <c r="T49" t="s">
+        <v>32</v>
+      </c>
+      <c r="U49" t="s">
+        <v>32</v>
+      </c>
+      <c r="V49" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="B50" t="s">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="C50" t="s">
         <v>34</v>
       </c>
       <c r="D50" t="s">
-        <v>155</v>
+        <v>92</v>
       </c>
       <c r="E50" t="s">
-        <v>32</v>
+        <v>293</v>
       </c>
       <c r="F50" t="s">
-        <v>134</v>
-      </c>
-      <c r="G50" t="s">
-        <v>267</v>
+        <v>32</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3.0</v>
       </c>
       <c r="H50" t="s">
-        <v>32</v>
+        <v>181</v>
       </c>
       <c r="I50" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J50" t="s">
         <v>32</v>
@@ -8412,49 +8805,55 @@
       <c r="O50" t="s">
         <v>32</v>
       </c>
-      <c r="P50" t="b">
+      <c r="P50" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>32</v>
+      </c>
+      <c r="R50" t="b">
         <v>0</v>
       </c>
-      <c r="Q50" t="s">
-        <v>32</v>
-      </c>
-      <c r="R50" t="s">
-        <v>32</v>
-      </c>
       <c r="S50" t="s">
         <v>32</v>
       </c>
       <c r="T50" t="s">
+        <v>32</v>
+      </c>
+      <c r="U50" t="s">
+        <v>32</v>
+      </c>
+      <c r="V50" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="B51" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="C51" t="s">
         <v>34</v>
       </c>
       <c r="D51" t="s">
-        <v>159</v>
+        <v>93</v>
       </c>
       <c r="E51" t="s">
-        <v>32</v>
+        <v>204</v>
       </c>
       <c r="F51" t="s">
-        <v>134</v>
-      </c>
-      <c r="G51" t="s">
-        <v>270</v>
+        <v>220</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.0</v>
       </c>
       <c r="H51" t="s">
-        <v>32</v>
+        <v>185</v>
       </c>
       <c r="I51" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J51" t="s">
         <v>32</v>
@@ -8474,49 +8873,55 @@
       <c r="O51" t="s">
         <v>32</v>
       </c>
-      <c r="P51" t="b">
+      <c r="P51" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>32</v>
+      </c>
+      <c r="R51" t="b">
         <v>0</v>
       </c>
-      <c r="Q51" t="s">
-        <v>32</v>
-      </c>
-      <c r="R51" t="s">
-        <v>32</v>
-      </c>
       <c r="S51" t="s">
         <v>32</v>
       </c>
       <c r="T51" t="s">
+        <v>32</v>
+      </c>
+      <c r="U51" t="s">
+        <v>32</v>
+      </c>
+      <c r="V51" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="B52" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="C52" t="s">
         <v>34</v>
       </c>
       <c r="D52" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="E52" t="s">
-        <v>32</v>
+        <v>167</v>
       </c>
       <c r="F52" t="s">
-        <v>134</v>
-      </c>
-      <c r="G52" t="s">
-        <v>104</v>
+        <v>142</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3.0</v>
       </c>
       <c r="H52" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="I52" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J52" t="s">
         <v>32</v>
@@ -8536,49 +8941,55 @@
       <c r="O52" t="s">
         <v>32</v>
       </c>
-      <c r="P52" t="b">
+      <c r="P52" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>32</v>
+      </c>
+      <c r="R52" t="b">
         <v>0</v>
       </c>
-      <c r="Q52" t="s">
-        <v>32</v>
-      </c>
-      <c r="R52" t="s">
-        <v>32</v>
-      </c>
       <c r="S52" t="s">
         <v>32</v>
       </c>
       <c r="T52" t="s">
+        <v>32</v>
+      </c>
+      <c r="U52" t="s">
+        <v>32</v>
+      </c>
+      <c r="V52" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="B53" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="C53" t="s">
         <v>34</v>
       </c>
       <c r="D53" t="s">
-        <v>159</v>
+        <v>300</v>
       </c>
       <c r="E53" t="s">
-        <v>275</v>
+        <v>136</v>
       </c>
       <c r="F53" t="s">
-        <v>134</v>
-      </c>
-      <c r="G53" t="s">
-        <v>106</v>
+        <v>32</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2.0</v>
       </c>
       <c r="H53" t="s">
-        <v>32</v>
+        <v>194</v>
       </c>
       <c r="I53" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J53" t="s">
         <v>32</v>
@@ -8598,49 +9009,55 @@
       <c r="O53" t="s">
         <v>32</v>
       </c>
-      <c r="P53" t="b">
+      <c r="P53" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>32</v>
+      </c>
+      <c r="R53" t="b">
         <v>0</v>
       </c>
-      <c r="Q53" t="s">
-        <v>32</v>
-      </c>
-      <c r="R53" t="s">
-        <v>32</v>
-      </c>
       <c r="S53" t="s">
         <v>32</v>
       </c>
       <c r="T53" t="s">
+        <v>32</v>
+      </c>
+      <c r="U53" t="s">
+        <v>32</v>
+      </c>
+      <c r="V53" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="B54" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="C54" t="s">
         <v>34</v>
       </c>
       <c r="D54" t="s">
-        <v>278</v>
+        <v>97</v>
       </c>
       <c r="E54" t="s">
-        <v>32</v>
+        <v>151</v>
       </c>
       <c r="F54" t="s">
-        <v>134</v>
-      </c>
-      <c r="G54" t="s">
-        <v>279</v>
+        <v>32</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.0</v>
       </c>
       <c r="H54" t="s">
-        <v>32</v>
+        <v>198</v>
       </c>
       <c r="I54" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J54" t="s">
         <v>32</v>
@@ -8660,49 +9077,55 @@
       <c r="O54" t="s">
         <v>32</v>
       </c>
-      <c r="P54" t="b">
+      <c r="P54" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>32</v>
+      </c>
+      <c r="R54" t="b">
         <v>0</v>
       </c>
-      <c r="Q54" t="s">
-        <v>32</v>
-      </c>
-      <c r="R54" t="s">
-        <v>32</v>
-      </c>
       <c r="S54" t="s">
         <v>32</v>
       </c>
       <c r="T54" t="s">
+        <v>32</v>
+      </c>
+      <c r="U54" t="s">
+        <v>32</v>
+      </c>
+      <c r="V54" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="B55" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="C55" t="s">
         <v>34</v>
       </c>
       <c r="D55" t="s">
-        <v>239</v>
+        <v>305</v>
       </c>
       <c r="E55" t="s">
-        <v>32</v>
+        <v>151</v>
       </c>
       <c r="F55" t="s">
-        <v>134</v>
-      </c>
-      <c r="G55" t="s">
-        <v>282</v>
+        <v>32</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2.0</v>
       </c>
       <c r="H55" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="I55" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J55" t="s">
         <v>32</v>
@@ -8722,49 +9145,55 @@
       <c r="O55" t="s">
         <v>32</v>
       </c>
-      <c r="P55" t="b">
+      <c r="P55" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>32</v>
+      </c>
+      <c r="R55" t="b">
         <v>0</v>
       </c>
-      <c r="Q55" t="s">
-        <v>32</v>
-      </c>
-      <c r="R55" t="s">
-        <v>32</v>
-      </c>
       <c r="S55" t="s">
         <v>32</v>
       </c>
       <c r="T55" t="s">
+        <v>32</v>
+      </c>
+      <c r="U55" t="s">
+        <v>32</v>
+      </c>
+      <c r="V55" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="B56" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="C56" t="s">
         <v>34</v>
       </c>
       <c r="D56" t="s">
-        <v>159</v>
+        <v>308</v>
       </c>
       <c r="E56" t="s">
-        <v>285</v>
+        <v>136</v>
       </c>
       <c r="F56" t="s">
-        <v>134</v>
-      </c>
-      <c r="G56" t="s">
-        <v>113</v>
+        <v>220</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2.0</v>
       </c>
       <c r="H56" t="s">
-        <v>32</v>
+        <v>205</v>
       </c>
       <c r="I56" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J56" t="s">
         <v>32</v>
@@ -8784,49 +9213,55 @@
       <c r="O56" t="s">
         <v>32</v>
       </c>
-      <c r="P56" t="b">
+      <c r="P56" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>32</v>
+      </c>
+      <c r="R56" t="b">
         <v>0</v>
       </c>
-      <c r="Q56" t="s">
-        <v>32</v>
-      </c>
-      <c r="R56" t="s">
-        <v>32</v>
-      </c>
       <c r="S56" t="s">
         <v>32</v>
       </c>
       <c r="T56" t="s">
+        <v>32</v>
+      </c>
+      <c r="U56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V56" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="B57" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="C57" t="s">
         <v>34</v>
       </c>
       <c r="D57" t="s">
-        <v>239</v>
+        <v>102</v>
       </c>
       <c r="E57" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="F57" t="s">
-        <v>134</v>
-      </c>
-      <c r="G57" t="s">
-        <v>114</v>
+        <v>32</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1.0</v>
       </c>
       <c r="H57" t="s">
-        <v>32</v>
+        <v>209</v>
       </c>
       <c r="I57" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J57" t="s">
         <v>32</v>
@@ -8846,49 +9281,55 @@
       <c r="O57" t="s">
         <v>32</v>
       </c>
-      <c r="P57" t="b">
+      <c r="P57" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>32</v>
+      </c>
+      <c r="R57" t="b">
         <v>0</v>
       </c>
-      <c r="Q57" t="s">
-        <v>32</v>
-      </c>
-      <c r="R57" t="s">
-        <v>32</v>
-      </c>
       <c r="S57" t="s">
         <v>32</v>
       </c>
       <c r="T57" t="s">
+        <v>32</v>
+      </c>
+      <c r="U57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V57" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="B58" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="C58" t="s">
         <v>34</v>
       </c>
       <c r="D58" t="s">
-        <v>151</v>
+        <v>313</v>
       </c>
       <c r="E58" t="s">
-        <v>32</v>
+        <v>314</v>
       </c>
       <c r="F58" t="s">
-        <v>134</v>
-      </c>
-      <c r="G58" t="s">
-        <v>115</v>
+        <v>284</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1.0</v>
       </c>
       <c r="H58" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="I58" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J58" t="s">
         <v>32</v>
@@ -8908,49 +9349,55 @@
       <c r="O58" t="s">
         <v>32</v>
       </c>
-      <c r="P58" t="b">
+      <c r="P58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>32</v>
+      </c>
+      <c r="R58" t="b">
         <v>0</v>
       </c>
-      <c r="Q58" t="s">
-        <v>32</v>
-      </c>
-      <c r="R58" t="s">
-        <v>32</v>
-      </c>
       <c r="S58" t="s">
         <v>32</v>
       </c>
       <c r="T58" t="s">
+        <v>32</v>
+      </c>
+      <c r="U58" t="s">
+        <v>32</v>
+      </c>
+      <c r="V58" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B59" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="C59" t="s">
         <v>34</v>
       </c>
       <c r="D59" t="s">
-        <v>221</v>
+        <v>106</v>
       </c>
       <c r="E59" t="s">
-        <v>32</v>
+        <v>317</v>
       </c>
       <c r="F59" t="s">
-        <v>134</v>
-      </c>
-      <c r="G59" t="s">
-        <v>116</v>
+        <v>32</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3.0</v>
       </c>
       <c r="H59" t="s">
-        <v>32</v>
+        <v>217</v>
       </c>
       <c r="I59" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J59" t="s">
         <v>32</v>
@@ -8970,49 +9417,55 @@
       <c r="O59" t="s">
         <v>32</v>
       </c>
-      <c r="P59" t="b">
+      <c r="P59" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>32</v>
+      </c>
+      <c r="R59" t="b">
         <v>0</v>
       </c>
-      <c r="Q59" t="s">
-        <v>32</v>
-      </c>
-      <c r="R59" t="s">
-        <v>32</v>
-      </c>
       <c r="S59" t="s">
         <v>32</v>
       </c>
       <c r="T59" t="s">
+        <v>32</v>
+      </c>
+      <c r="U59" t="s">
+        <v>32</v>
+      </c>
+      <c r="V59" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="B60" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="C60" t="s">
         <v>34</v>
       </c>
       <c r="D60" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="E60" t="s">
-        <v>147</v>
+        <v>320</v>
       </c>
       <c r="F60" t="s">
-        <v>134</v>
-      </c>
-      <c r="G60" t="s">
-        <v>294</v>
+        <v>142</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.0</v>
       </c>
       <c r="H60" t="s">
-        <v>32</v>
+        <v>269</v>
       </c>
       <c r="I60" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J60" t="s">
         <v>32</v>
@@ -9032,49 +9485,55 @@
       <c r="O60" t="s">
         <v>32</v>
       </c>
-      <c r="P60" t="b">
+      <c r="P60" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>32</v>
+      </c>
+      <c r="R60" t="b">
         <v>0</v>
       </c>
-      <c r="Q60" t="s">
-        <v>32</v>
-      </c>
-      <c r="R60" t="s">
-        <v>32</v>
-      </c>
       <c r="S60" t="s">
         <v>32</v>
       </c>
       <c r="T60" t="s">
+        <v>32</v>
+      </c>
+      <c r="U60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V60" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="B61" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="C61" t="s">
         <v>34</v>
       </c>
       <c r="D61" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="E61" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F61" t="s">
-        <v>134</v>
-      </c>
-      <c r="G61" t="s">
-        <v>297</v>
+        <v>32</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2.0</v>
       </c>
       <c r="H61" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="I61" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J61" t="s">
         <v>32</v>
@@ -9094,49 +9553,55 @@
       <c r="O61" t="s">
         <v>32</v>
       </c>
-      <c r="P61" t="b">
+      <c r="P61" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>32</v>
+      </c>
+      <c r="R61" t="b">
         <v>0</v>
       </c>
-      <c r="Q61" t="s">
-        <v>32</v>
-      </c>
-      <c r="R61" t="s">
-        <v>32</v>
-      </c>
       <c r="S61" t="s">
         <v>32</v>
       </c>
       <c r="T61" t="s">
+        <v>32</v>
+      </c>
+      <c r="U61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V61" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="B62" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="C62" t="s">
         <v>34</v>
       </c>
       <c r="D62" t="s">
-        <v>167</v>
+        <v>325</v>
       </c>
       <c r="E62" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F62" t="s">
-        <v>134</v>
-      </c>
-      <c r="G62" t="s">
-        <v>228</v>
+        <v>32</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.0</v>
       </c>
       <c r="H62" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="I62" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J62" t="s">
         <v>32</v>
@@ -9156,49 +9621,55 @@
       <c r="O62" t="s">
         <v>32</v>
       </c>
-      <c r="P62" t="b">
+      <c r="P62" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>32</v>
+      </c>
+      <c r="R62" t="b">
         <v>0</v>
       </c>
-      <c r="Q62" t="s">
-        <v>32</v>
-      </c>
-      <c r="R62" t="s">
-        <v>32</v>
-      </c>
       <c r="S62" t="s">
         <v>32</v>
       </c>
       <c r="T62" t="s">
+        <v>32</v>
+      </c>
+      <c r="U62" t="s">
+        <v>32</v>
+      </c>
+      <c r="V62" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="B63" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="C63" t="s">
         <v>34</v>
       </c>
       <c r="D63" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="E63" t="s">
-        <v>32</v>
+        <v>328</v>
       </c>
       <c r="F63" t="s">
-        <v>134</v>
-      </c>
-      <c r="G63" t="s">
-        <v>74</v>
+        <v>32</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1.0</v>
       </c>
       <c r="H63" t="s">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="I63" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J63" t="s">
         <v>32</v>
@@ -9218,49 +9689,55 @@
       <c r="O63" t="s">
         <v>32</v>
       </c>
-      <c r="P63" t="b">
+      <c r="P63" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>32</v>
+      </c>
+      <c r="R63" t="b">
         <v>0</v>
       </c>
-      <c r="Q63" t="s">
-        <v>32</v>
-      </c>
-      <c r="R63" t="s">
-        <v>32</v>
-      </c>
       <c r="S63" t="s">
         <v>32</v>
       </c>
       <c r="T63" t="s">
+        <v>32</v>
+      </c>
+      <c r="U63" t="s">
+        <v>32</v>
+      </c>
+      <c r="V63" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>302</v>
+        <v>329</v>
       </c>
       <c r="B64" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="C64" t="s">
         <v>34</v>
       </c>
       <c r="D64" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E64" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="F64" t="s">
-        <v>134</v>
-      </c>
-      <c r="G64" t="s">
-        <v>75</v>
+        <v>32</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2.0</v>
       </c>
       <c r="H64" t="s">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="I64" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J64" t="s">
         <v>32</v>
@@ -9280,49 +9757,55 @@
       <c r="O64" t="s">
         <v>32</v>
       </c>
-      <c r="P64" t="b">
+      <c r="P64" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>32</v>
+      </c>
+      <c r="R64" t="b">
         <v>0</v>
       </c>
-      <c r="Q64" t="s">
-        <v>32</v>
-      </c>
-      <c r="R64" t="s">
-        <v>32</v>
-      </c>
       <c r="S64" t="s">
         <v>32</v>
       </c>
       <c r="T64" t="s">
+        <v>32</v>
+      </c>
+      <c r="U64" t="s">
+        <v>32</v>
+      </c>
+      <c r="V64" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>304</v>
+        <v>331</v>
       </c>
       <c r="B65" t="s">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="C65" t="s">
         <v>34</v>
       </c>
       <c r="D65" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="E65" t="s">
-        <v>225</v>
+        <v>146</v>
       </c>
       <c r="F65" t="s">
-        <v>134</v>
-      </c>
-      <c r="G65" t="s">
-        <v>76</v>
+        <v>32</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3.0</v>
       </c>
       <c r="H65" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="I65" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J65" t="s">
         <v>32</v>
@@ -9342,49 +9825,55 @@
       <c r="O65" t="s">
         <v>32</v>
       </c>
-      <c r="P65" t="b">
+      <c r="P65" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>32</v>
+      </c>
+      <c r="R65" t="b">
         <v>0</v>
       </c>
-      <c r="Q65" t="s">
-        <v>32</v>
-      </c>
-      <c r="R65" t="s">
-        <v>32</v>
-      </c>
       <c r="S65" t="s">
         <v>32</v>
       </c>
       <c r="T65" t="s">
+        <v>32</v>
+      </c>
+      <c r="U65" t="s">
+        <v>32</v>
+      </c>
+      <c r="V65" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>306</v>
+        <v>333</v>
       </c>
       <c r="B66" t="s">
-        <v>307</v>
+        <v>334</v>
       </c>
       <c r="C66" t="s">
         <v>34</v>
       </c>
       <c r="D66" t="s">
-        <v>239</v>
+        <v>115</v>
       </c>
       <c r="E66" t="s">
-        <v>32</v>
+        <v>335</v>
       </c>
       <c r="F66" t="s">
-        <v>134</v>
-      </c>
-      <c r="G66" t="s">
-        <v>77</v>
+        <v>32</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1.0</v>
       </c>
       <c r="H66" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="I66" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J66" t="s">
         <v>32</v>
@@ -9404,49 +9893,55 @@
       <c r="O66" t="s">
         <v>32</v>
       </c>
-      <c r="P66" t="b">
+      <c r="P66" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>32</v>
+      </c>
+      <c r="R66" t="b">
         <v>0</v>
       </c>
-      <c r="Q66" t="s">
-        <v>32</v>
-      </c>
-      <c r="R66" t="s">
-        <v>32</v>
-      </c>
       <c r="S66" t="s">
         <v>32</v>
       </c>
       <c r="T66" t="s">
+        <v>32</v>
+      </c>
+      <c r="U66" t="s">
+        <v>32</v>
+      </c>
+      <c r="V66" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c r="B67" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="C67" t="s">
         <v>34</v>
       </c>
       <c r="D67" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="E67" t="s">
-        <v>32</v>
+        <v>204</v>
       </c>
       <c r="F67" t="s">
-        <v>134</v>
-      </c>
-      <c r="G67" t="s">
-        <v>148</v>
+        <v>32</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1.0</v>
       </c>
       <c r="H67" t="s">
-        <v>32</v>
+        <v>287</v>
       </c>
       <c r="I67" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J67" t="s">
         <v>32</v>
@@ -9466,49 +9961,55 @@
       <c r="O67" t="s">
         <v>32</v>
       </c>
-      <c r="P67" t="b">
+      <c r="P67" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>32</v>
+      </c>
+      <c r="R67" t="b">
         <v>0</v>
       </c>
-      <c r="Q67" t="s">
-        <v>32</v>
-      </c>
-      <c r="R67" t="s">
-        <v>32</v>
-      </c>
       <c r="S67" t="s">
         <v>32</v>
       </c>
       <c r="T67" t="s">
+        <v>32</v>
+      </c>
+      <c r="U67" t="s">
+        <v>32</v>
+      </c>
+      <c r="V67" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="B68" t="s">
-        <v>311</v>
+        <v>339</v>
       </c>
       <c r="C68" t="s">
         <v>34</v>
       </c>
       <c r="D68" t="s">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="E68" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="F68" t="s">
-        <v>134</v>
-      </c>
-      <c r="G68" t="s">
-        <v>80</v>
+        <v>147</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2.0</v>
       </c>
       <c r="H68" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="I68" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J68" t="s">
         <v>32</v>
@@ -9528,49 +10029,55 @@
       <c r="O68" t="s">
         <v>32</v>
       </c>
-      <c r="P68" t="b">
+      <c r="P68" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>32</v>
+      </c>
+      <c r="R68" t="b">
         <v>0</v>
       </c>
-      <c r="Q68" t="s">
-        <v>32</v>
-      </c>
-      <c r="R68" t="s">
-        <v>32</v>
-      </c>
       <c r="S68" t="s">
         <v>32</v>
       </c>
       <c r="T68" t="s">
+        <v>32</v>
+      </c>
+      <c r="U68" t="s">
+        <v>32</v>
+      </c>
+      <c r="V68" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="B69" t="s">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="C69" t="s">
         <v>34</v>
       </c>
       <c r="D69" t="s">
-        <v>151</v>
+        <v>343</v>
       </c>
       <c r="E69" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="F69" t="s">
-        <v>134</v>
-      </c>
-      <c r="G69" t="s">
-        <v>81</v>
+        <v>32</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2.0</v>
       </c>
       <c r="H69" t="s">
-        <v>32</v>
+        <v>181</v>
       </c>
       <c r="I69" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J69" t="s">
         <v>32</v>
@@ -9590,49 +10097,55 @@
       <c r="O69" t="s">
         <v>32</v>
       </c>
-      <c r="P69" t="b">
+      <c r="P69" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>32</v>
+      </c>
+      <c r="R69" t="b">
         <v>0</v>
       </c>
-      <c r="Q69" t="s">
-        <v>32</v>
-      </c>
-      <c r="R69" t="s">
-        <v>32</v>
-      </c>
       <c r="S69" t="s">
         <v>32</v>
       </c>
       <c r="T69" t="s">
+        <v>32</v>
+      </c>
+      <c r="U69" t="s">
+        <v>32</v>
+      </c>
+      <c r="V69" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="B70" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="C70" t="s">
         <v>34</v>
       </c>
       <c r="D70" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="E70" t="s">
-        <v>32</v>
+        <v>204</v>
       </c>
       <c r="F70" t="s">
-        <v>134</v>
-      </c>
-      <c r="G70" t="s">
-        <v>82</v>
+        <v>32</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1.0</v>
       </c>
       <c r="H70" t="s">
-        <v>32</v>
+        <v>185</v>
       </c>
       <c r="I70" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J70" t="s">
         <v>32</v>
@@ -9652,49 +10165,55 @@
       <c r="O70" t="s">
         <v>32</v>
       </c>
-      <c r="P70" t="b">
+      <c r="P70" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>32</v>
+      </c>
+      <c r="R70" t="b">
         <v>0</v>
       </c>
-      <c r="Q70" t="s">
-        <v>32</v>
-      </c>
-      <c r="R70" t="s">
-        <v>32</v>
-      </c>
       <c r="S70" t="s">
         <v>32</v>
       </c>
       <c r="T70" t="s">
+        <v>32</v>
+      </c>
+      <c r="U70" t="s">
+        <v>32</v>
+      </c>
+      <c r="V70" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="B71" t="s">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="C71" t="s">
         <v>34</v>
       </c>
       <c r="D71" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="E71" t="s">
-        <v>319</v>
+        <v>151</v>
       </c>
       <c r="F71" t="s">
-        <v>134</v>
-      </c>
-      <c r="G71" t="s">
-        <v>320</v>
+        <v>32</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1.0</v>
       </c>
       <c r="H71" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="I71" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J71" t="s">
         <v>32</v>
@@ -9714,49 +10233,55 @@
       <c r="O71" t="s">
         <v>32</v>
       </c>
-      <c r="P71" t="b">
+      <c r="P71" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>32</v>
+      </c>
+      <c r="R71" t="b">
         <v>0</v>
       </c>
-      <c r="Q71" t="s">
-        <v>32</v>
-      </c>
-      <c r="R71" t="s">
-        <v>32</v>
-      </c>
       <c r="S71" t="s">
         <v>32</v>
       </c>
       <c r="T71" t="s">
+        <v>32</v>
+      </c>
+      <c r="U71" t="s">
+        <v>32</v>
+      </c>
+      <c r="V71" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="B72" t="s">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="C72" t="s">
         <v>34</v>
       </c>
       <c r="D72" t="s">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="E72" t="s">
-        <v>32</v>
+        <v>167</v>
       </c>
       <c r="F72" t="s">
-        <v>134</v>
-      </c>
-      <c r="G72" t="s">
-        <v>85</v>
+        <v>32</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2.0</v>
       </c>
       <c r="H72" t="s">
-        <v>32</v>
+        <v>194</v>
       </c>
       <c r="I72" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J72" t="s">
         <v>32</v>
@@ -9776,49 +10301,55 @@
       <c r="O72" t="s">
         <v>32</v>
       </c>
-      <c r="P72" t="b">
+      <c r="P72" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>32</v>
+      </c>
+      <c r="R72" t="b">
         <v>0</v>
       </c>
-      <c r="Q72" t="s">
-        <v>32</v>
-      </c>
-      <c r="R72" t="s">
-        <v>32</v>
-      </c>
       <c r="S72" t="s">
         <v>32</v>
       </c>
       <c r="T72" t="s">
+        <v>32</v>
+      </c>
+      <c r="U72" t="s">
+        <v>32</v>
+      </c>
+      <c r="V72" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="B73" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="C73" t="s">
         <v>34</v>
       </c>
       <c r="D73" t="s">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E73" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F73" t="s">
-        <v>134</v>
-      </c>
-      <c r="G73" t="s">
-        <v>86</v>
+        <v>32</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2.0</v>
       </c>
       <c r="H73" t="s">
-        <v>32</v>
+        <v>198</v>
       </c>
       <c r="I73" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="J73" t="s">
         <v>32</v>
@@ -9838,19 +10369,25 @@
       <c r="O73" t="s">
         <v>32</v>
       </c>
-      <c r="P73" t="b">
+      <c r="P73" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>32</v>
+      </c>
+      <c r="R73" t="b">
         <v>0</v>
       </c>
-      <c r="Q73" t="s">
-        <v>32</v>
-      </c>
-      <c r="R73" t="s">
-        <v>32</v>
-      </c>
       <c r="S73" t="s">
         <v>32</v>
       </c>
       <c r="T73" t="s">
+        <v>32</v>
+      </c>
+      <c r="U73" t="s">
+        <v>32</v>
+      </c>
+      <c r="V73" t="s">
         <v>32</v>
       </c>
     </row>
@@ -9864,19 +10401,19 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="12.203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="13.19140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9922,7 +10459,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>44</v>
@@ -9965,42 +10502,20 @@
       <c r="A3" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B3"/>
       <c r="C3" t="s">
         <v>52</v>
       </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" t="s">
-        <v>32</v>
-      </c>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
@@ -10017,19 +10532,19 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.94140625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.6171875" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.23828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10075,7 +10590,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>44</v>
@@ -10112,6 +10627,2086 @@
       </c>
       <c r="M2" s="1" t="s">
         <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" t="s">
+        <v>32</v>
+      </c>
+      <c r="M21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" t="s">
+        <v>32</v>
+      </c>
+      <c r="M25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" t="s">
+        <v>32</v>
+      </c>
+      <c r="M26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" t="s">
+        <v>32</v>
+      </c>
+      <c r="M27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" t="s">
+        <v>32</v>
+      </c>
+      <c r="M28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" t="s">
+        <v>32</v>
+      </c>
+      <c r="H30" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" t="s">
+        <v>32</v>
+      </c>
+      <c r="K30" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" t="s">
+        <v>32</v>
+      </c>
+      <c r="M30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" t="s">
+        <v>32</v>
+      </c>
+      <c r="J31" t="s">
+        <v>32</v>
+      </c>
+      <c r="K31" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" t="s">
+        <v>32</v>
+      </c>
+      <c r="M31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" t="s">
+        <v>32</v>
+      </c>
+      <c r="H32" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" t="s">
+        <v>32</v>
+      </c>
+      <c r="J32" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" t="s">
+        <v>32</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" t="s">
+        <v>32</v>
+      </c>
+      <c r="J33" t="s">
+        <v>32</v>
+      </c>
+      <c r="K33" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" t="s">
+        <v>32</v>
+      </c>
+      <c r="J34" t="s">
+        <v>32</v>
+      </c>
+      <c r="K34" t="s">
+        <v>32</v>
+      </c>
+      <c r="L34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" t="s">
+        <v>32</v>
+      </c>
+      <c r="J35" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" t="s">
+        <v>32</v>
+      </c>
+      <c r="M35" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" t="s">
+        <v>32</v>
+      </c>
+      <c r="F36" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H36" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" t="s">
+        <v>32</v>
+      </c>
+      <c r="J36" t="s">
+        <v>32</v>
+      </c>
+      <c r="K36" t="s">
+        <v>32</v>
+      </c>
+      <c r="L36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M36" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G37" t="s">
+        <v>32</v>
+      </c>
+      <c r="H37" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" t="s">
+        <v>32</v>
+      </c>
+      <c r="K37" t="s">
+        <v>32</v>
+      </c>
+      <c r="L37" t="s">
+        <v>32</v>
+      </c>
+      <c r="M37" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H38" t="s">
+        <v>32</v>
+      </c>
+      <c r="I38" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" t="s">
+        <v>32</v>
+      </c>
+      <c r="K38" t="s">
+        <v>32</v>
+      </c>
+      <c r="L38" t="s">
+        <v>32</v>
+      </c>
+      <c r="M38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" t="s">
+        <v>32</v>
+      </c>
+      <c r="J39" t="s">
+        <v>32</v>
+      </c>
+      <c r="K39" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39" t="s">
+        <v>32</v>
+      </c>
+      <c r="M39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>111</v>
+      </c>
+      <c r="B40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G40" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" t="s">
+        <v>32</v>
+      </c>
+      <c r="J40" t="s">
+        <v>32</v>
+      </c>
+      <c r="K40" t="s">
+        <v>32</v>
+      </c>
+      <c r="L40" t="s">
+        <v>32</v>
+      </c>
+      <c r="M40" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" t="s">
+        <v>32</v>
+      </c>
+      <c r="G41" t="s">
+        <v>32</v>
+      </c>
+      <c r="H41" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" t="s">
+        <v>32</v>
+      </c>
+      <c r="J41" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41" t="s">
+        <v>32</v>
+      </c>
+      <c r="L41" t="s">
+        <v>32</v>
+      </c>
+      <c r="M41" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" t="s">
+        <v>32</v>
+      </c>
+      <c r="G42" t="s">
+        <v>32</v>
+      </c>
+      <c r="H42" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" t="s">
+        <v>32</v>
+      </c>
+      <c r="K42" t="s">
+        <v>32</v>
+      </c>
+      <c r="L42" t="s">
+        <v>32</v>
+      </c>
+      <c r="M42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" t="s">
+        <v>32</v>
+      </c>
+      <c r="G43" t="s">
+        <v>32</v>
+      </c>
+      <c r="H43" t="s">
+        <v>32</v>
+      </c>
+      <c r="I43" t="s">
+        <v>32</v>
+      </c>
+      <c r="J43" t="s">
+        <v>32</v>
+      </c>
+      <c r="K43" t="s">
+        <v>32</v>
+      </c>
+      <c r="L43" t="s">
+        <v>32</v>
+      </c>
+      <c r="M43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H44" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" t="s">
+        <v>32</v>
+      </c>
+      <c r="J44" t="s">
+        <v>32</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45" t="s">
+        <v>32</v>
+      </c>
+      <c r="G45" t="s">
+        <v>32</v>
+      </c>
+      <c r="H45" t="s">
+        <v>32</v>
+      </c>
+      <c r="I45" t="s">
+        <v>32</v>
+      </c>
+      <c r="J45" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" t="s">
+        <v>32</v>
+      </c>
+      <c r="L45" t="s">
+        <v>32</v>
+      </c>
+      <c r="M45" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" t="s">
+        <v>32</v>
+      </c>
+      <c r="E46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" t="s">
+        <v>32</v>
+      </c>
+      <c r="G46" t="s">
+        <v>32</v>
+      </c>
+      <c r="H46" t="s">
+        <v>32</v>
+      </c>
+      <c r="I46" t="s">
+        <v>32</v>
+      </c>
+      <c r="J46" t="s">
+        <v>32</v>
+      </c>
+      <c r="K46" t="s">
+        <v>32</v>
+      </c>
+      <c r="L46" t="s">
+        <v>32</v>
+      </c>
+      <c r="M46" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" t="s">
+        <v>32</v>
+      </c>
+      <c r="G47" t="s">
+        <v>32</v>
+      </c>
+      <c r="H47" t="s">
+        <v>32</v>
+      </c>
+      <c r="I47" t="s">
+        <v>32</v>
+      </c>
+      <c r="J47" t="s">
+        <v>32</v>
+      </c>
+      <c r="K47" t="s">
+        <v>32</v>
+      </c>
+      <c r="L47" t="s">
+        <v>32</v>
+      </c>
+      <c r="M47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" t="s">
+        <v>32</v>
+      </c>
+      <c r="F48" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" t="s">
+        <v>32</v>
+      </c>
+      <c r="I48" t="s">
+        <v>32</v>
+      </c>
+      <c r="J48" t="s">
+        <v>32</v>
+      </c>
+      <c r="K48" t="s">
+        <v>32</v>
+      </c>
+      <c r="L48" t="s">
+        <v>32</v>
+      </c>
+      <c r="M48" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>120</v>
+      </c>
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H49" t="s">
+        <v>32</v>
+      </c>
+      <c r="I49" t="s">
+        <v>32</v>
+      </c>
+      <c r="J49" t="s">
+        <v>32</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>121</v>
+      </c>
+      <c r="B50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" t="s">
+        <v>32</v>
+      </c>
+      <c r="G50" t="s">
+        <v>32</v>
+      </c>
+      <c r="H50" t="s">
+        <v>32</v>
+      </c>
+      <c r="I50" t="s">
+        <v>32</v>
+      </c>
+      <c r="J50" t="s">
+        <v>32</v>
+      </c>
+      <c r="K50" t="s">
+        <v>32</v>
+      </c>
+      <c r="L50" t="s">
+        <v>32</v>
+      </c>
+      <c r="M50" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView activeTab="2"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" r:id="rId3" sheetId="1"/>
@@ -11,15 +11,17 @@
     <sheet name="Rooms" r:id="rId5" sheetId="3"/>
     <sheet name="Speakers" r:id="rId6" sheetId="4"/>
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
-    <sheet name="Theme view" r:id="rId8" sheetId="6"/>
-    <sheet name="Sector view" r:id="rId9" sheetId="7"/>
-    <sheet name="Speaker view" r:id="rId10" sheetId="8"/>
+    <sheet name="Room view" r:id="rId8" sheetId="6"/>
+    <sheet name="Speaker view" r:id="rId9" sheetId="7"/>
+    <sheet name="Theme view" r:id="rId10" sheetId="8"/>
+    <sheet name="Sector view" r:id="rId11" sheetId="9"/>
+    <sheet name="Content view" r:id="rId12" sheetId="10"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3476" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3660" uniqueCount="357">
   <si>
     <t>Conference name</t>
   </si>
@@ -1077,13 +1079,19 @@
     <t>Understand mobile RestEasy</t>
   </si>
   <si>
+    <t>Speaker</t>
+  </si>
+  <si>
     <t>Theme tag</t>
   </si>
   <si>
     <t>Sector tag</t>
   </si>
   <si>
-    <t>Speaker</t>
+    <t>Content tag</t>
+  </si>
+  <si>
+    <t>(2) S34</t>
   </si>
 </sst>
 </file>
@@ -1315,6 +1323,137 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="11.78515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3"/>
+      <c r="C3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+    </row>
+  </sheetData>
+  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -10401,6 +10540,2608 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
+    <col min="1" max="1" width="6.44921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" t="s">
+        <v>32</v>
+      </c>
+      <c r="M21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" t="s">
+        <v>32</v>
+      </c>
+      <c r="M25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" t="s">
+        <v>32</v>
+      </c>
+      <c r="M26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" t="s">
+        <v>32</v>
+      </c>
+      <c r="M27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" t="s">
+        <v>32</v>
+      </c>
+      <c r="M28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" t="s">
+        <v>32</v>
+      </c>
+      <c r="H30" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" t="s">
+        <v>32</v>
+      </c>
+      <c r="K30" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" t="s">
+        <v>32</v>
+      </c>
+      <c r="M30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" t="s">
+        <v>32</v>
+      </c>
+      <c r="J31" t="s">
+        <v>32</v>
+      </c>
+      <c r="K31" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" t="s">
+        <v>32</v>
+      </c>
+      <c r="M31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" t="s">
+        <v>32</v>
+      </c>
+      <c r="H32" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" t="s">
+        <v>32</v>
+      </c>
+      <c r="J32" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" t="s">
+        <v>32</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" t="s">
+        <v>32</v>
+      </c>
+      <c r="J33" t="s">
+        <v>32</v>
+      </c>
+      <c r="K33" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" t="s">
+        <v>32</v>
+      </c>
+      <c r="J34" t="s">
+        <v>32</v>
+      </c>
+      <c r="K34" t="s">
+        <v>32</v>
+      </c>
+      <c r="L34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" t="s">
+        <v>32</v>
+      </c>
+      <c r="J35" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" t="s">
+        <v>32</v>
+      </c>
+      <c r="M35" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" t="s">
+        <v>32</v>
+      </c>
+      <c r="F36" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H36" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" t="s">
+        <v>32</v>
+      </c>
+      <c r="J36" t="s">
+        <v>32</v>
+      </c>
+      <c r="K36" t="s">
+        <v>32</v>
+      </c>
+      <c r="L36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M36" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G37" t="s">
+        <v>32</v>
+      </c>
+      <c r="H37" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" t="s">
+        <v>32</v>
+      </c>
+      <c r="K37" t="s">
+        <v>32</v>
+      </c>
+      <c r="L37" t="s">
+        <v>32</v>
+      </c>
+      <c r="M37" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H38" t="s">
+        <v>32</v>
+      </c>
+      <c r="I38" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" t="s">
+        <v>32</v>
+      </c>
+      <c r="K38" t="s">
+        <v>32</v>
+      </c>
+      <c r="L38" t="s">
+        <v>32</v>
+      </c>
+      <c r="M38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" t="s">
+        <v>32</v>
+      </c>
+      <c r="J39" t="s">
+        <v>32</v>
+      </c>
+      <c r="K39" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39" t="s">
+        <v>32</v>
+      </c>
+      <c r="M39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>111</v>
+      </c>
+      <c r="B40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G40" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" t="s">
+        <v>32</v>
+      </c>
+      <c r="J40" t="s">
+        <v>32</v>
+      </c>
+      <c r="K40" t="s">
+        <v>32</v>
+      </c>
+      <c r="L40" t="s">
+        <v>32</v>
+      </c>
+      <c r="M40" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" t="s">
+        <v>32</v>
+      </c>
+      <c r="G41" t="s">
+        <v>32</v>
+      </c>
+      <c r="H41" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" t="s">
+        <v>32</v>
+      </c>
+      <c r="J41" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41" t="s">
+        <v>32</v>
+      </c>
+      <c r="L41" t="s">
+        <v>32</v>
+      </c>
+      <c r="M41" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" t="s">
+        <v>32</v>
+      </c>
+      <c r="G42" t="s">
+        <v>32</v>
+      </c>
+      <c r="H42" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" t="s">
+        <v>32</v>
+      </c>
+      <c r="K42" t="s">
+        <v>32</v>
+      </c>
+      <c r="L42" t="s">
+        <v>32</v>
+      </c>
+      <c r="M42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" t="s">
+        <v>32</v>
+      </c>
+      <c r="G43" t="s">
+        <v>32</v>
+      </c>
+      <c r="H43" t="s">
+        <v>32</v>
+      </c>
+      <c r="I43" t="s">
+        <v>32</v>
+      </c>
+      <c r="J43" t="s">
+        <v>32</v>
+      </c>
+      <c r="K43" t="s">
+        <v>32</v>
+      </c>
+      <c r="L43" t="s">
+        <v>32</v>
+      </c>
+      <c r="M43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H44" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" t="s">
+        <v>32</v>
+      </c>
+      <c r="J44" t="s">
+        <v>32</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45" t="s">
+        <v>32</v>
+      </c>
+      <c r="G45" t="s">
+        <v>32</v>
+      </c>
+      <c r="H45" t="s">
+        <v>32</v>
+      </c>
+      <c r="I45" t="s">
+        <v>32</v>
+      </c>
+      <c r="J45" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" t="s">
+        <v>32</v>
+      </c>
+      <c r="L45" t="s">
+        <v>32</v>
+      </c>
+      <c r="M45" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" t="s">
+        <v>32</v>
+      </c>
+      <c r="E46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" t="s">
+        <v>32</v>
+      </c>
+      <c r="G46" t="s">
+        <v>32</v>
+      </c>
+      <c r="H46" t="s">
+        <v>32</v>
+      </c>
+      <c r="I46" t="s">
+        <v>32</v>
+      </c>
+      <c r="J46" t="s">
+        <v>32</v>
+      </c>
+      <c r="K46" t="s">
+        <v>32</v>
+      </c>
+      <c r="L46" t="s">
+        <v>32</v>
+      </c>
+      <c r="M46" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" t="s">
+        <v>32</v>
+      </c>
+      <c r="G47" t="s">
+        <v>32</v>
+      </c>
+      <c r="H47" t="s">
+        <v>32</v>
+      </c>
+      <c r="I47" t="s">
+        <v>32</v>
+      </c>
+      <c r="J47" t="s">
+        <v>32</v>
+      </c>
+      <c r="K47" t="s">
+        <v>32</v>
+      </c>
+      <c r="L47" t="s">
+        <v>32</v>
+      </c>
+      <c r="M47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" t="s">
+        <v>32</v>
+      </c>
+      <c r="F48" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" t="s">
+        <v>32</v>
+      </c>
+      <c r="I48" t="s">
+        <v>32</v>
+      </c>
+      <c r="J48" t="s">
+        <v>32</v>
+      </c>
+      <c r="K48" t="s">
+        <v>32</v>
+      </c>
+      <c r="L48" t="s">
+        <v>32</v>
+      </c>
+      <c r="M48" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>120</v>
+      </c>
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H49" t="s">
+        <v>32</v>
+      </c>
+      <c r="I49" t="s">
+        <v>32</v>
+      </c>
+      <c r="J49" t="s">
+        <v>32</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>121</v>
+      </c>
+      <c r="B50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" t="s">
+        <v>32</v>
+      </c>
+      <c r="G50" t="s">
+        <v>32</v>
+      </c>
+      <c r="H50" t="s">
+        <v>32</v>
+      </c>
+      <c r="I50" t="s">
+        <v>32</v>
+      </c>
+      <c r="J50" t="s">
+        <v>32</v>
+      </c>
+      <c r="K50" t="s">
+        <v>32</v>
+      </c>
+      <c r="L50" t="s">
+        <v>32</v>
+      </c>
+      <c r="M50" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
     <col min="1" max="1" width="13.19140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
@@ -10459,7 +13200,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>44</v>
@@ -10527,7 +13268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -10590,7 +13331,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>44</v>
@@ -10627,2086 +13368,6 @@
       </c>
       <c r="M2" s="1" t="s">
         <v>49</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
-  <mergeCells>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:M1"/>
-  </mergeCells>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" t="s">
-        <v>32</v>
-      </c>
-      <c r="M11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" t="s">
-        <v>32</v>
-      </c>
-      <c r="M12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" t="s">
-        <v>32</v>
-      </c>
-      <c r="K13" t="s">
-        <v>32</v>
-      </c>
-      <c r="L13" t="s">
-        <v>32</v>
-      </c>
-      <c r="M13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" t="s">
-        <v>32</v>
-      </c>
-      <c r="L14" t="s">
-        <v>32</v>
-      </c>
-      <c r="M14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H15" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" t="s">
-        <v>32</v>
-      </c>
-      <c r="J15" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" t="s">
-        <v>32</v>
-      </c>
-      <c r="L15" t="s">
-        <v>32</v>
-      </c>
-      <c r="M15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" t="s">
-        <v>32</v>
-      </c>
-      <c r="J16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K16" t="s">
-        <v>32</v>
-      </c>
-      <c r="L16" t="s">
-        <v>32</v>
-      </c>
-      <c r="M16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" t="s">
-        <v>32</v>
-      </c>
-      <c r="J17" t="s">
-        <v>32</v>
-      </c>
-      <c r="K17" t="s">
-        <v>32</v>
-      </c>
-      <c r="L17" t="s">
-        <v>32</v>
-      </c>
-      <c r="M17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" t="s">
-        <v>32</v>
-      </c>
-      <c r="H18" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" t="s">
-        <v>32</v>
-      </c>
-      <c r="K18" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18" t="s">
-        <v>32</v>
-      </c>
-      <c r="M18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" t="s">
-        <v>32</v>
-      </c>
-      <c r="H19" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" t="s">
-        <v>32</v>
-      </c>
-      <c r="J19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K19" t="s">
-        <v>32</v>
-      </c>
-      <c r="L19" t="s">
-        <v>32</v>
-      </c>
-      <c r="M19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H20" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" t="s">
-        <v>32</v>
-      </c>
-      <c r="K20" t="s">
-        <v>32</v>
-      </c>
-      <c r="L20" t="s">
-        <v>32</v>
-      </c>
-      <c r="M20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" t="s">
-        <v>32</v>
-      </c>
-      <c r="H21" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" t="s">
-        <v>32</v>
-      </c>
-      <c r="J21" t="s">
-        <v>32</v>
-      </c>
-      <c r="K21" t="s">
-        <v>32</v>
-      </c>
-      <c r="L21" t="s">
-        <v>32</v>
-      </c>
-      <c r="M21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" t="s">
-        <v>32</v>
-      </c>
-      <c r="K22" t="s">
-        <v>32</v>
-      </c>
-      <c r="L22" t="s">
-        <v>32</v>
-      </c>
-      <c r="M22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" t="s">
-        <v>32</v>
-      </c>
-      <c r="J23" t="s">
-        <v>32</v>
-      </c>
-      <c r="K23" t="s">
-        <v>32</v>
-      </c>
-      <c r="L23" t="s">
-        <v>32</v>
-      </c>
-      <c r="M23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" t="s">
-        <v>32</v>
-      </c>
-      <c r="J24" t="s">
-        <v>32</v>
-      </c>
-      <c r="K24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L24" t="s">
-        <v>32</v>
-      </c>
-      <c r="M24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" t="s">
-        <v>32</v>
-      </c>
-      <c r="H25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" t="s">
-        <v>32</v>
-      </c>
-      <c r="J25" t="s">
-        <v>32</v>
-      </c>
-      <c r="K25" t="s">
-        <v>32</v>
-      </c>
-      <c r="L25" t="s">
-        <v>32</v>
-      </c>
-      <c r="M25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" t="s">
-        <v>32</v>
-      </c>
-      <c r="H26" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J26" t="s">
-        <v>32</v>
-      </c>
-      <c r="K26" t="s">
-        <v>32</v>
-      </c>
-      <c r="L26" t="s">
-        <v>32</v>
-      </c>
-      <c r="M26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" t="s">
-        <v>32</v>
-      </c>
-      <c r="H27" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" t="s">
-        <v>32</v>
-      </c>
-      <c r="J27" t="s">
-        <v>32</v>
-      </c>
-      <c r="K27" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" t="s">
-        <v>32</v>
-      </c>
-      <c r="M27" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" t="s">
-        <v>32</v>
-      </c>
-      <c r="H28" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" t="s">
-        <v>32</v>
-      </c>
-      <c r="J28" t="s">
-        <v>32</v>
-      </c>
-      <c r="K28" t="s">
-        <v>32</v>
-      </c>
-      <c r="L28" t="s">
-        <v>32</v>
-      </c>
-      <c r="M28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>99</v>
-      </c>
-      <c r="B29" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29" t="s">
-        <v>32</v>
-      </c>
-      <c r="G29" t="s">
-        <v>32</v>
-      </c>
-      <c r="H29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" t="s">
-        <v>32</v>
-      </c>
-      <c r="J29" t="s">
-        <v>32</v>
-      </c>
-      <c r="K29" t="s">
-        <v>32</v>
-      </c>
-      <c r="L29" t="s">
-        <v>32</v>
-      </c>
-      <c r="M29" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" t="s">
-        <v>32</v>
-      </c>
-      <c r="H30" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" t="s">
-        <v>32</v>
-      </c>
-      <c r="J30" t="s">
-        <v>32</v>
-      </c>
-      <c r="K30" t="s">
-        <v>32</v>
-      </c>
-      <c r="L30" t="s">
-        <v>32</v>
-      </c>
-      <c r="M30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>101</v>
-      </c>
-      <c r="B31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" t="s">
-        <v>32</v>
-      </c>
-      <c r="G31" t="s">
-        <v>32</v>
-      </c>
-      <c r="H31" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" t="s">
-        <v>32</v>
-      </c>
-      <c r="J31" t="s">
-        <v>32</v>
-      </c>
-      <c r="K31" t="s">
-        <v>32</v>
-      </c>
-      <c r="L31" t="s">
-        <v>32</v>
-      </c>
-      <c r="M31" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" t="s">
-        <v>32</v>
-      </c>
-      <c r="G32" t="s">
-        <v>32</v>
-      </c>
-      <c r="H32" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" t="s">
-        <v>32</v>
-      </c>
-      <c r="J32" t="s">
-        <v>32</v>
-      </c>
-      <c r="K32" t="s">
-        <v>32</v>
-      </c>
-      <c r="L32" t="s">
-        <v>32</v>
-      </c>
-      <c r="M32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>103</v>
-      </c>
-      <c r="B33" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" t="s">
-        <v>32</v>
-      </c>
-      <c r="F33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G33" t="s">
-        <v>32</v>
-      </c>
-      <c r="H33" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" t="s">
-        <v>32</v>
-      </c>
-      <c r="J33" t="s">
-        <v>32</v>
-      </c>
-      <c r="K33" t="s">
-        <v>32</v>
-      </c>
-      <c r="L33" t="s">
-        <v>32</v>
-      </c>
-      <c r="M33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" t="s">
-        <v>32</v>
-      </c>
-      <c r="E34" t="s">
-        <v>32</v>
-      </c>
-      <c r="F34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G34" t="s">
-        <v>32</v>
-      </c>
-      <c r="H34" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" t="s">
-        <v>32</v>
-      </c>
-      <c r="J34" t="s">
-        <v>32</v>
-      </c>
-      <c r="K34" t="s">
-        <v>32</v>
-      </c>
-      <c r="L34" t="s">
-        <v>32</v>
-      </c>
-      <c r="M34" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>106</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" t="s">
-        <v>32</v>
-      </c>
-      <c r="F35" t="s">
-        <v>32</v>
-      </c>
-      <c r="G35" t="s">
-        <v>32</v>
-      </c>
-      <c r="H35" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" t="s">
-        <v>32</v>
-      </c>
-      <c r="J35" t="s">
-        <v>32</v>
-      </c>
-      <c r="K35" t="s">
-        <v>32</v>
-      </c>
-      <c r="L35" t="s">
-        <v>32</v>
-      </c>
-      <c r="M35" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>107</v>
-      </c>
-      <c r="B36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" t="s">
-        <v>32</v>
-      </c>
-      <c r="F36" t="s">
-        <v>32</v>
-      </c>
-      <c r="G36" t="s">
-        <v>32</v>
-      </c>
-      <c r="H36" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" t="s">
-        <v>32</v>
-      </c>
-      <c r="J36" t="s">
-        <v>32</v>
-      </c>
-      <c r="K36" t="s">
-        <v>32</v>
-      </c>
-      <c r="L36" t="s">
-        <v>32</v>
-      </c>
-      <c r="M36" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>108</v>
-      </c>
-      <c r="B37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" t="s">
-        <v>32</v>
-      </c>
-      <c r="E37" t="s">
-        <v>32</v>
-      </c>
-      <c r="F37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" t="s">
-        <v>32</v>
-      </c>
-      <c r="H37" t="s">
-        <v>32</v>
-      </c>
-      <c r="I37" t="s">
-        <v>32</v>
-      </c>
-      <c r="J37" t="s">
-        <v>32</v>
-      </c>
-      <c r="K37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L37" t="s">
-        <v>32</v>
-      </c>
-      <c r="M37" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>109</v>
-      </c>
-      <c r="B38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" t="s">
-        <v>32</v>
-      </c>
-      <c r="E38" t="s">
-        <v>32</v>
-      </c>
-      <c r="F38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H38" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" t="s">
-        <v>32</v>
-      </c>
-      <c r="J38" t="s">
-        <v>32</v>
-      </c>
-      <c r="K38" t="s">
-        <v>32</v>
-      </c>
-      <c r="L38" t="s">
-        <v>32</v>
-      </c>
-      <c r="M38" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>110</v>
-      </c>
-      <c r="B39" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" t="s">
-        <v>32</v>
-      </c>
-      <c r="E39" t="s">
-        <v>32</v>
-      </c>
-      <c r="F39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" t="s">
-        <v>32</v>
-      </c>
-      <c r="H39" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" t="s">
-        <v>32</v>
-      </c>
-      <c r="J39" t="s">
-        <v>32</v>
-      </c>
-      <c r="K39" t="s">
-        <v>32</v>
-      </c>
-      <c r="L39" t="s">
-        <v>32</v>
-      </c>
-      <c r="M39" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>111</v>
-      </c>
-      <c r="B40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" t="s">
-        <v>32</v>
-      </c>
-      <c r="E40" t="s">
-        <v>32</v>
-      </c>
-      <c r="F40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G40" t="s">
-        <v>32</v>
-      </c>
-      <c r="H40" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J40" t="s">
-        <v>32</v>
-      </c>
-      <c r="K40" t="s">
-        <v>32</v>
-      </c>
-      <c r="L40" t="s">
-        <v>32</v>
-      </c>
-      <c r="M40" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>112</v>
-      </c>
-      <c r="B41" t="s">
-        <v>32</v>
-      </c>
-      <c r="C41" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" t="s">
-        <v>32</v>
-      </c>
-      <c r="E41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H41" t="s">
-        <v>32</v>
-      </c>
-      <c r="I41" t="s">
-        <v>32</v>
-      </c>
-      <c r="J41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K41" t="s">
-        <v>32</v>
-      </c>
-      <c r="L41" t="s">
-        <v>32</v>
-      </c>
-      <c r="M41" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>113</v>
-      </c>
-      <c r="B42" t="s">
-        <v>32</v>
-      </c>
-      <c r="C42" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" t="s">
-        <v>32</v>
-      </c>
-      <c r="E42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F42" t="s">
-        <v>32</v>
-      </c>
-      <c r="G42" t="s">
-        <v>32</v>
-      </c>
-      <c r="H42" t="s">
-        <v>32</v>
-      </c>
-      <c r="I42" t="s">
-        <v>32</v>
-      </c>
-      <c r="J42" t="s">
-        <v>32</v>
-      </c>
-      <c r="K42" t="s">
-        <v>32</v>
-      </c>
-      <c r="L42" t="s">
-        <v>32</v>
-      </c>
-      <c r="M42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B43" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" t="s">
-        <v>32</v>
-      </c>
-      <c r="D43" t="s">
-        <v>32</v>
-      </c>
-      <c r="E43" t="s">
-        <v>32</v>
-      </c>
-      <c r="F43" t="s">
-        <v>32</v>
-      </c>
-      <c r="G43" t="s">
-        <v>32</v>
-      </c>
-      <c r="H43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I43" t="s">
-        <v>32</v>
-      </c>
-      <c r="J43" t="s">
-        <v>32</v>
-      </c>
-      <c r="K43" t="s">
-        <v>32</v>
-      </c>
-      <c r="L43" t="s">
-        <v>32</v>
-      </c>
-      <c r="M43" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>115</v>
-      </c>
-      <c r="B44" t="s">
-        <v>32</v>
-      </c>
-      <c r="C44" t="s">
-        <v>32</v>
-      </c>
-      <c r="D44" t="s">
-        <v>32</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H44" t="s">
-        <v>32</v>
-      </c>
-      <c r="I44" t="s">
-        <v>32</v>
-      </c>
-      <c r="J44" t="s">
-        <v>32</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>116</v>
-      </c>
-      <c r="B45" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" t="s">
-        <v>32</v>
-      </c>
-      <c r="D45" t="s">
-        <v>32</v>
-      </c>
-      <c r="E45" t="s">
-        <v>32</v>
-      </c>
-      <c r="F45" t="s">
-        <v>32</v>
-      </c>
-      <c r="G45" t="s">
-        <v>32</v>
-      </c>
-      <c r="H45" t="s">
-        <v>32</v>
-      </c>
-      <c r="I45" t="s">
-        <v>32</v>
-      </c>
-      <c r="J45" t="s">
-        <v>32</v>
-      </c>
-      <c r="K45" t="s">
-        <v>32</v>
-      </c>
-      <c r="L45" t="s">
-        <v>32</v>
-      </c>
-      <c r="M45" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>117</v>
-      </c>
-      <c r="B46" t="s">
-        <v>32</v>
-      </c>
-      <c r="C46" t="s">
-        <v>32</v>
-      </c>
-      <c r="D46" t="s">
-        <v>32</v>
-      </c>
-      <c r="E46" t="s">
-        <v>32</v>
-      </c>
-      <c r="F46" t="s">
-        <v>32</v>
-      </c>
-      <c r="G46" t="s">
-        <v>32</v>
-      </c>
-      <c r="H46" t="s">
-        <v>32</v>
-      </c>
-      <c r="I46" t="s">
-        <v>32</v>
-      </c>
-      <c r="J46" t="s">
-        <v>32</v>
-      </c>
-      <c r="K46" t="s">
-        <v>32</v>
-      </c>
-      <c r="L46" t="s">
-        <v>32</v>
-      </c>
-      <c r="M46" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>118</v>
-      </c>
-      <c r="B47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" t="s">
-        <v>32</v>
-      </c>
-      <c r="D47" t="s">
-        <v>32</v>
-      </c>
-      <c r="E47" t="s">
-        <v>32</v>
-      </c>
-      <c r="F47" t="s">
-        <v>32</v>
-      </c>
-      <c r="G47" t="s">
-        <v>32</v>
-      </c>
-      <c r="H47" t="s">
-        <v>32</v>
-      </c>
-      <c r="I47" t="s">
-        <v>32</v>
-      </c>
-      <c r="J47" t="s">
-        <v>32</v>
-      </c>
-      <c r="K47" t="s">
-        <v>32</v>
-      </c>
-      <c r="L47" t="s">
-        <v>32</v>
-      </c>
-      <c r="M47" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>119</v>
-      </c>
-      <c r="B48" t="s">
-        <v>32</v>
-      </c>
-      <c r="C48" t="s">
-        <v>32</v>
-      </c>
-      <c r="D48" t="s">
-        <v>32</v>
-      </c>
-      <c r="E48" t="s">
-        <v>32</v>
-      </c>
-      <c r="F48" t="s">
-        <v>32</v>
-      </c>
-      <c r="G48" t="s">
-        <v>32</v>
-      </c>
-      <c r="H48" t="s">
-        <v>32</v>
-      </c>
-      <c r="I48" t="s">
-        <v>32</v>
-      </c>
-      <c r="J48" t="s">
-        <v>32</v>
-      </c>
-      <c r="K48" t="s">
-        <v>32</v>
-      </c>
-      <c r="L48" t="s">
-        <v>32</v>
-      </c>
-      <c r="M48" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>120</v>
-      </c>
-      <c r="B49" t="s">
-        <v>32</v>
-      </c>
-      <c r="C49" t="s">
-        <v>32</v>
-      </c>
-      <c r="D49" t="s">
-        <v>32</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H49" t="s">
-        <v>32</v>
-      </c>
-      <c r="I49" t="s">
-        <v>32</v>
-      </c>
-      <c r="J49" t="s">
-        <v>32</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>121</v>
-      </c>
-      <c r="B50" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" t="s">
-        <v>52</v>
-      </c>
-      <c r="D50" t="s">
-        <v>32</v>
-      </c>
-      <c r="E50" t="s">
-        <v>32</v>
-      </c>
-      <c r="F50" t="s">
-        <v>32</v>
-      </c>
-      <c r="G50" t="s">
-        <v>32</v>
-      </c>
-      <c r="H50" t="s">
-        <v>32</v>
-      </c>
-      <c r="I50" t="s">
-        <v>32</v>
-      </c>
-      <c r="J50" t="s">
-        <v>32</v>
-      </c>
-      <c r="K50" t="s">
-        <v>32</v>
-      </c>
-      <c r="L50" t="s">
-        <v>32</v>
-      </c>
-      <c r="M50" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -11,11 +11,11 @@
     <sheet name="Rooms" r:id="rId5" sheetId="3"/>
     <sheet name="Speakers" r:id="rId6" sheetId="4"/>
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
-    <sheet name="Room view" r:id="rId8" sheetId="6"/>
-    <sheet name="Speaker view" r:id="rId9" sheetId="7"/>
-    <sheet name="Theme view" r:id="rId10" sheetId="8"/>
-    <sheet name="Sector view" r:id="rId11" sheetId="9"/>
-    <sheet name="Content view" r:id="rId12" sheetId="10"/>
+    <sheet name="Rooms view" r:id="rId8" sheetId="6"/>
+    <sheet name="Speakers view" r:id="rId9" sheetId="7"/>
+    <sheet name="Theme tracks view" r:id="rId10" sheetId="8"/>
+    <sheet name="Sectors view" r:id="rId11" sheetId="9"/>
+    <sheet name="Contents view" r:id="rId12" sheetId="10"/>
   </sheets>
 </workbook>
 </file>
@@ -38,10 +38,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Theme conflict</t>
-  </si>
-  <si>
-    <t>Soft penalty per common theme of 2 talks that have an overlapping timeslot</t>
+    <t>Theme track conflict</t>
+  </si>
+  <si>
+    <t>Soft penalty per common theme track of 2 talks that have an overlapping timeslot</t>
   </si>
   <si>
     <t>Sector conflict</t>
@@ -185,618 +185,618 @@
     <t>Large, Recorded</t>
   </si>
   <si>
+    <t>R 2</t>
+  </si>
+  <si>
+    <t>R 3</t>
+  </si>
+  <si>
+    <t>Recorded</t>
+  </si>
+  <si>
+    <t>R 4</t>
+  </si>
+  <si>
+    <t>R 5</t>
+  </si>
+  <si>
+    <t>Lab_room, Large, Recorded</t>
+  </si>
+  <si>
+    <t>R 6</t>
+  </si>
+  <si>
+    <t>R 7</t>
+  </si>
+  <si>
+    <t>R 8</t>
+  </si>
+  <si>
+    <t>R 9</t>
+  </si>
+  <si>
+    <t>R 10</t>
+  </si>
+  <si>
+    <t>Lab_room</t>
+  </si>
+  <si>
+    <t>Required timeslot tags</t>
+  </si>
+  <si>
+    <t>Preferred timeslot tags</t>
+  </si>
+  <si>
+    <t>Prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t>Undesired timeslot tags</t>
+  </si>
+  <si>
+    <t>Required room tags</t>
+  </si>
+  <si>
+    <t>Preferred room tags</t>
+  </si>
+  <si>
+    <t>Prohibited room tags</t>
+  </si>
+  <si>
+    <t>Undesired room tags</t>
+  </si>
+  <si>
+    <t>Amy Cole</t>
+  </si>
+  <si>
+    <t>Beth Fox</t>
+  </si>
+  <si>
+    <t>Chad Green</t>
+  </si>
+  <si>
+    <t>Dan Jones</t>
+  </si>
+  <si>
+    <t>Elsa King</t>
+  </si>
+  <si>
+    <t>Flo Li</t>
+  </si>
+  <si>
+    <t>Gus Poe</t>
+  </si>
+  <si>
+    <t>Hugo Rye</t>
+  </si>
+  <si>
+    <t>Ivy Smith</t>
+  </si>
+  <si>
+    <t>Jay Watt</t>
+  </si>
+  <si>
+    <t>Amy Fox</t>
+  </si>
+  <si>
+    <t>Beth Green</t>
+  </si>
+  <si>
+    <t>Chad Jones</t>
+  </si>
+  <si>
+    <t>Dan King</t>
+  </si>
+  <si>
+    <t>Elsa Li</t>
+  </si>
+  <si>
+    <t>Flo Poe</t>
+  </si>
+  <si>
+    <t>Gus Rye</t>
+  </si>
+  <si>
+    <t>Hugo Smith</t>
+  </si>
+  <si>
+    <t>Ivy Watt</t>
+  </si>
+  <si>
+    <t>Jay Cole</t>
+  </si>
+  <si>
+    <t>Amy Green</t>
+  </si>
+  <si>
+    <t>Beth Jones</t>
+  </si>
+  <si>
+    <t>Chad King</t>
+  </si>
+  <si>
+    <t>Dan Li</t>
+  </si>
+  <si>
+    <t>Elsa Poe</t>
+  </si>
+  <si>
+    <t>Flo Rye</t>
+  </si>
+  <si>
+    <t>Gus Smith</t>
+  </si>
+  <si>
+    <t>Hugo Watt</t>
+  </si>
+  <si>
+    <t>Ivy Cole</t>
+  </si>
+  <si>
+    <t>Jay Fox</t>
+  </si>
+  <si>
+    <t>Amy Jones</t>
+  </si>
+  <si>
+    <t>Beth King</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>Chad Li</t>
+  </si>
+  <si>
+    <t>Dan Poe</t>
+  </si>
+  <si>
+    <t>Elsa Rye</t>
+  </si>
+  <si>
+    <t>Flo Smith</t>
+  </si>
+  <si>
+    <t>Gus Watt</t>
+  </si>
+  <si>
+    <t>Hugo Cole</t>
+  </si>
+  <si>
+    <t>Ivy Fox</t>
+  </si>
+  <si>
+    <t>Jay Green</t>
+  </si>
+  <si>
+    <t>Amy King</t>
+  </si>
+  <si>
+    <t>Beth Li</t>
+  </si>
+  <si>
+    <t>Chad Poe</t>
+  </si>
+  <si>
+    <t>Dan Rye</t>
+  </si>
+  <si>
+    <t>Elsa Smith</t>
+  </si>
+  <si>
+    <t>Flo Watt</t>
+  </si>
+  <si>
+    <t>Gus Cole</t>
+  </si>
+  <si>
+    <t>Hugo Fox</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Speakers</t>
+  </si>
+  <si>
+    <t>Theme track tags</t>
+  </si>
+  <si>
+    <t>Sector tags</t>
+  </si>
+  <si>
+    <t>Audience level</t>
+  </si>
+  <si>
+    <t>Content tags</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Pinned by user</t>
+  </si>
+  <si>
+    <t>Timeslot day</t>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>S00</t>
+  </si>
+  <si>
+    <t>Hands on real-time OpenShift</t>
+  </si>
+  <si>
+    <t>Amy Cole, Beth Fox</t>
+  </si>
+  <si>
+    <t>IoT</t>
+  </si>
+  <si>
+    <t>OpenShift, Kubernetes</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>S01</t>
+  </si>
+  <si>
+    <t>Advanced containerized WildFly</t>
+  </si>
+  <si>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>Telecommunications</t>
+  </si>
+  <si>
+    <t>WildFly</t>
+  </si>
+  <si>
+    <t>S02</t>
+  </si>
+  <si>
+    <t>Learn virtualized Spring</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>S03</t>
+  </si>
+  <si>
+    <t>Intro to serverless Drools</t>
+  </si>
+  <si>
+    <t>Modern Web</t>
+  </si>
+  <si>
+    <t>Financial services</t>
+  </si>
+  <si>
+    <t>Drools</t>
+  </si>
+  <si>
+    <t>S04</t>
+  </si>
+  <si>
+    <t>Discover AI-driven OptaPlanner</t>
+  </si>
+  <si>
+    <t>OptaPlanner</t>
+  </si>
+  <si>
+    <t>S05</t>
+  </si>
+  <si>
+    <t>Mastering machine learning jBPM</t>
+  </si>
+  <si>
+    <t>Gus Poe, Hugo Rye</t>
+  </si>
+  <si>
+    <t>jBPM</t>
+  </si>
+  <si>
+    <t>S06</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Camel</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>S07</t>
+  </si>
+  <si>
+    <t>Building deep learning XStream</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>XStream</t>
+  </si>
+  <si>
+    <t>S08</t>
+  </si>
+  <si>
+    <t>Securing scalable Docker</t>
+  </si>
+  <si>
+    <t>Mobile, Big Data</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
+    <t>S09</t>
+  </si>
+  <si>
+    <t>Debug enterprise Hibernate</t>
+  </si>
+  <si>
+    <t>Culture, Big Data</t>
+  </si>
+  <si>
+    <t>Hibernate</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>Prepare for streaming GWT</t>
+  </si>
+  <si>
+    <t>Chad Jones, Dan King</t>
+  </si>
+  <si>
+    <t>Security, Big Data</t>
+  </si>
+  <si>
+    <t>GWT</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>Understand mobile Errai</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Errai</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>Applying modern Angular</t>
+  </si>
+  <si>
+    <t>Flo Poe, Gus Rye</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>Grok distributed Weld</t>
+  </si>
+  <si>
+    <t>Hugo Smith, Ivy Watt</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Culture</t>
+  </si>
+  <si>
+    <t>Weld</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable RestEasy</t>
+  </si>
+  <si>
+    <t>IoT, Big Data</t>
+  </si>
+  <si>
+    <t>RestEasy</t>
+  </si>
+  <si>
+    <t>S15</t>
+  </si>
+  <si>
+    <t>Using secure Android</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>Deliver stable Tensorflow</t>
+  </si>
+  <si>
+    <t>Middleware</t>
+  </si>
+  <si>
+    <t>Tensorflow</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>Implement platform-independent VertX</t>
+  </si>
+  <si>
+    <t>IoT, Security</t>
+  </si>
+  <si>
+    <t>VertX</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>Program flexible JUnit</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>JUnit</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>Hack modularized Keycloak</t>
+  </si>
+  <si>
+    <t>Elsa Poe, Flo Rye</t>
+  </si>
+  <si>
+    <t>Keycloak</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>Hands on real-time WildFly</t>
+  </si>
+  <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>Advanced containerized Spring</t>
+  </si>
+  <si>
+    <t>Modern Web, Culture</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>Learn virtualized Drools</t>
+  </si>
+  <si>
+    <t>Ivy Cole, Jay Fox</t>
+  </si>
+  <si>
+    <t>S23</t>
+  </si>
+  <si>
+    <t>Intro to serverless OptaPlanner</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>Discover AI-driven jBPM</t>
+  </si>
+  <si>
+    <t>S25</t>
+  </si>
+  <si>
+    <t>Mastering machine learning Camel</t>
+  </si>
+  <si>
+    <t>S26</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven XStream</t>
+  </si>
+  <si>
+    <t>S27</t>
+  </si>
+  <si>
+    <t>Building deep learning Docker</t>
+  </si>
+  <si>
+    <t>Elsa Rye, Flo Smith</t>
+  </si>
+  <si>
+    <t>Cloud, Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>S28</t>
+  </si>
+  <si>
+    <t>Securing scalable Hibernate</t>
+  </si>
+  <si>
+    <t>S29</t>
+  </si>
+  <si>
+    <t>Debug enterprise GWT</t>
+  </si>
+  <si>
+    <t>S30</t>
+  </si>
+  <si>
+    <t>Prepare for streaming Errai</t>
+  </si>
+  <si>
+    <t>Ivy Fox, Jay Green</t>
+  </si>
+  <si>
+    <t>Culture, Security</t>
+  </si>
+  <si>
+    <t>S31</t>
+  </si>
+  <si>
+    <t>Understand mobile Angular</t>
+  </si>
+  <si>
+    <t>Amy King, Beth Li</t>
+  </si>
+  <si>
+    <t>S32</t>
+  </si>
+  <si>
+    <t>Applying modern Weld</t>
+  </si>
+  <si>
+    <t>Chad Poe, Dan Rye, Elsa Smith</t>
+  </si>
+  <si>
+    <t>S33</t>
+  </si>
+  <si>
+    <t>Grok distributed RestEasy</t>
+  </si>
+  <si>
+    <t>Flo Watt, Gus Cole</t>
+  </si>
+  <si>
     <t>S34</t>
   </si>
   <si>
-    <t>R 2</t>
-  </si>
-  <si>
-    <t>R 3</t>
-  </si>
-  <si>
-    <t>Recorded</t>
-  </si>
-  <si>
-    <t>R 4</t>
-  </si>
-  <si>
-    <t>R 5</t>
-  </si>
-  <si>
-    <t>Lab_room, Large, Recorded</t>
-  </si>
-  <si>
-    <t>R 6</t>
-  </si>
-  <si>
-    <t>R 7</t>
-  </si>
-  <si>
-    <t>R 8</t>
-  </si>
-  <si>
-    <t>R 9</t>
-  </si>
-  <si>
-    <t>R 10</t>
-  </si>
-  <si>
-    <t>Lab_room</t>
-  </si>
-  <si>
-    <t>Required timeslot tags</t>
-  </si>
-  <si>
-    <t>Preferred timeslot tags</t>
-  </si>
-  <si>
-    <t>Prohibited timeslot tags</t>
-  </si>
-  <si>
-    <t>Undesired timeslot tags</t>
-  </si>
-  <si>
-    <t>Required room tags</t>
-  </si>
-  <si>
-    <t>Preferred room tags</t>
-  </si>
-  <si>
-    <t>Prohibited room tags</t>
-  </si>
-  <si>
-    <t>Undesired room tags</t>
-  </si>
-  <si>
-    <t>Amy Cole</t>
-  </si>
-  <si>
-    <t>Beth Fox</t>
-  </si>
-  <si>
-    <t>Chad Green</t>
-  </si>
-  <si>
-    <t>Dan Jones</t>
-  </si>
-  <si>
-    <t>Elsa King</t>
-  </si>
-  <si>
-    <t>Flo Li</t>
-  </si>
-  <si>
-    <t>Gus Poe</t>
-  </si>
-  <si>
-    <t>Hugo Rye</t>
-  </si>
-  <si>
-    <t>Ivy Smith</t>
-  </si>
-  <si>
-    <t>Jay Watt</t>
-  </si>
-  <si>
-    <t>Amy Fox</t>
-  </si>
-  <si>
-    <t>Beth Green</t>
-  </si>
-  <si>
-    <t>Chad Jones</t>
-  </si>
-  <si>
-    <t>Dan King</t>
-  </si>
-  <si>
-    <t>Elsa Li</t>
-  </si>
-  <si>
-    <t>Flo Poe</t>
-  </si>
-  <si>
-    <t>Gus Rye</t>
-  </si>
-  <si>
-    <t>Hugo Smith</t>
-  </si>
-  <si>
-    <t>Ivy Watt</t>
-  </si>
-  <si>
-    <t>Jay Cole</t>
-  </si>
-  <si>
-    <t>Amy Green</t>
-  </si>
-  <si>
-    <t>Beth Jones</t>
-  </si>
-  <si>
-    <t>Chad King</t>
-  </si>
-  <si>
-    <t>Dan Li</t>
-  </si>
-  <si>
-    <t>Elsa Poe</t>
-  </si>
-  <si>
-    <t>Flo Rye</t>
-  </si>
-  <si>
-    <t>Gus Smith</t>
-  </si>
-  <si>
-    <t>Hugo Watt</t>
-  </si>
-  <si>
-    <t>Ivy Cole</t>
-  </si>
-  <si>
-    <t>Jay Fox</t>
-  </si>
-  <si>
-    <t>Amy Jones</t>
-  </si>
-  <si>
-    <t>Beth King</t>
-  </si>
-  <si>
-    <t>Large</t>
-  </si>
-  <si>
-    <t>Chad Li</t>
-  </si>
-  <si>
-    <t>Dan Poe</t>
-  </si>
-  <si>
-    <t>Elsa Rye</t>
-  </si>
-  <si>
-    <t>Flo Smith</t>
-  </si>
-  <si>
-    <t>Gus Watt</t>
-  </si>
-  <si>
-    <t>Hugo Cole</t>
-  </si>
-  <si>
-    <t>Ivy Fox</t>
-  </si>
-  <si>
-    <t>Jay Green</t>
-  </si>
-  <si>
-    <t>Amy King</t>
-  </si>
-  <si>
-    <t>Beth Li</t>
-  </si>
-  <si>
-    <t>Chad Poe</t>
-  </si>
-  <si>
-    <t>Dan Rye</t>
-  </si>
-  <si>
-    <t>Elsa Smith</t>
-  </si>
-  <si>
-    <t>Flo Watt</t>
-  </si>
-  <si>
-    <t>Gus Cole</t>
-  </si>
-  <si>
-    <t>Hugo Fox</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Speakers</t>
-  </si>
-  <si>
-    <t>Theme tags</t>
-  </si>
-  <si>
-    <t>Sector tags</t>
-  </si>
-  <si>
-    <t>Audience level</t>
-  </si>
-  <si>
-    <t>Content tags</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>Pinned by user</t>
-  </si>
-  <si>
-    <t>Timeslot day</t>
-  </si>
-  <si>
-    <t>Room</t>
-  </si>
-  <si>
-    <t>S00</t>
-  </si>
-  <si>
-    <t>Hands on real-time OpenShift</t>
-  </si>
-  <si>
-    <t>Amy Cole, Beth Fox</t>
-  </si>
-  <si>
-    <t>IoT</t>
-  </si>
-  <si>
-    <t>OpenShift, Kubernetes</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>S01</t>
-  </si>
-  <si>
-    <t>Advanced containerized WildFly</t>
-  </si>
-  <si>
-    <t>Culture</t>
-  </si>
-  <si>
-    <t>Telecommunications</t>
-  </si>
-  <si>
-    <t>WildFly</t>
-  </si>
-  <si>
-    <t>S02</t>
-  </si>
-  <si>
-    <t>Learn virtualized Spring</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>Spring</t>
-  </si>
-  <si>
-    <t>S03</t>
-  </si>
-  <si>
-    <t>Intro to serverless Drools</t>
-  </si>
-  <si>
-    <t>Modern Web</t>
-  </si>
-  <si>
-    <t>Financial services</t>
-  </si>
-  <si>
-    <t>Drools</t>
-  </si>
-  <si>
-    <t>S04</t>
-  </si>
-  <si>
-    <t>Discover AI-driven OptaPlanner</t>
-  </si>
-  <si>
-    <t>OptaPlanner</t>
-  </si>
-  <si>
-    <t>S05</t>
-  </si>
-  <si>
-    <t>Mastering machine learning jBPM</t>
-  </si>
-  <si>
-    <t>Gus Poe, Hugo Rye</t>
-  </si>
-  <si>
-    <t>jBPM</t>
-  </si>
-  <si>
-    <t>S06</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Camel</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>Camel</t>
-  </si>
-  <si>
-    <t>S07</t>
-  </si>
-  <si>
-    <t>Building deep learning XStream</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>XStream</t>
-  </si>
-  <si>
-    <t>S08</t>
-  </si>
-  <si>
-    <t>Securing scalable Docker</t>
-  </si>
-  <si>
-    <t>Mobile, Big Data</t>
-  </si>
-  <si>
-    <t>Docker</t>
-  </si>
-  <si>
-    <t>S09</t>
-  </si>
-  <si>
-    <t>Debug enterprise Hibernate</t>
-  </si>
-  <si>
-    <t>Culture, Big Data</t>
-  </si>
-  <si>
-    <t>Hibernate</t>
-  </si>
-  <si>
-    <t>S10</t>
-  </si>
-  <si>
-    <t>Prepare for streaming GWT</t>
-  </si>
-  <si>
-    <t>Chad Jones, Dan King</t>
-  </si>
-  <si>
-    <t>Security, Big Data</t>
-  </si>
-  <si>
-    <t>GWT</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>Understand mobile Errai</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Errai</t>
-  </si>
-  <si>
-    <t>S12</t>
-  </si>
-  <si>
-    <t>Applying modern Angular</t>
-  </si>
-  <si>
-    <t>Flo Poe, Gus Rye</t>
-  </si>
-  <si>
-    <t>Angular</t>
-  </si>
-  <si>
-    <t>S13</t>
-  </si>
-  <si>
-    <t>Grok distributed Weld</t>
-  </si>
-  <si>
-    <t>Hugo Smith, Ivy Watt</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence, Culture</t>
-  </si>
-  <si>
-    <t>Weld</t>
-  </si>
-  <si>
-    <t>S14</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable RestEasy</t>
-  </si>
-  <si>
-    <t>IoT, Big Data</t>
-  </si>
-  <si>
-    <t>RestEasy</t>
-  </si>
-  <si>
-    <t>S15</t>
-  </si>
-  <si>
-    <t>Using secure Android</t>
-  </si>
-  <si>
-    <t>Android</t>
-  </si>
-  <si>
-    <t>S16</t>
-  </si>
-  <si>
-    <t>Deliver stable Tensorflow</t>
-  </si>
-  <si>
-    <t>Middleware</t>
-  </si>
-  <si>
-    <t>Tensorflow</t>
-  </si>
-  <si>
-    <t>S17</t>
-  </si>
-  <si>
-    <t>Implement platform-independent VertX</t>
-  </si>
-  <si>
-    <t>IoT, Security</t>
-  </si>
-  <si>
-    <t>VertX</t>
-  </si>
-  <si>
-    <t>S18</t>
-  </si>
-  <si>
-    <t>Program flexible JUnit</t>
-  </si>
-  <si>
-    <t>Cloud</t>
-  </si>
-  <si>
-    <t>JUnit</t>
-  </si>
-  <si>
-    <t>S19</t>
-  </si>
-  <si>
-    <t>Hack modularized Keycloak</t>
-  </si>
-  <si>
-    <t>Elsa Poe, Flo Rye</t>
-  </si>
-  <si>
-    <t>Keycloak</t>
-  </si>
-  <si>
-    <t>S20</t>
-  </si>
-  <si>
-    <t>Hands on real-time WildFly</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
-    <t>S21</t>
-  </si>
-  <si>
-    <t>Advanced containerized Spring</t>
-  </si>
-  <si>
-    <t>Modern Web, Culture</t>
-  </si>
-  <si>
-    <t>S22</t>
-  </si>
-  <si>
-    <t>Learn virtualized Drools</t>
-  </si>
-  <si>
-    <t>Ivy Cole, Jay Fox</t>
-  </si>
-  <si>
-    <t>S23</t>
-  </si>
-  <si>
-    <t>Intro to serverless OptaPlanner</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>Discover AI-driven jBPM</t>
-  </si>
-  <si>
-    <t>S25</t>
-  </si>
-  <si>
-    <t>Mastering machine learning Camel</t>
-  </si>
-  <si>
-    <t>S26</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven XStream</t>
-  </si>
-  <si>
-    <t>S27</t>
-  </si>
-  <si>
-    <t>Building deep learning Docker</t>
-  </si>
-  <si>
-    <t>Elsa Rye, Flo Smith</t>
-  </si>
-  <si>
-    <t>Cloud, Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>S28</t>
-  </si>
-  <si>
-    <t>Securing scalable Hibernate</t>
-  </si>
-  <si>
-    <t>S29</t>
-  </si>
-  <si>
-    <t>Debug enterprise GWT</t>
-  </si>
-  <si>
-    <t>S30</t>
-  </si>
-  <si>
-    <t>Prepare for streaming Errai</t>
-  </si>
-  <si>
-    <t>Ivy Fox, Jay Green</t>
-  </si>
-  <si>
-    <t>Culture, Security</t>
-  </si>
-  <si>
-    <t>S31</t>
-  </si>
-  <si>
-    <t>Understand mobile Angular</t>
-  </si>
-  <si>
-    <t>Amy King, Beth Li</t>
-  </si>
-  <si>
-    <t>S32</t>
-  </si>
-  <si>
-    <t>Applying modern Weld</t>
-  </si>
-  <si>
-    <t>Chad Poe, Dan Rye, Elsa Smith</t>
-  </si>
-  <si>
-    <t>S33</t>
-  </si>
-  <si>
-    <t>Grok distributed RestEasy</t>
-  </si>
-  <si>
-    <t>Flo Watt, Gus Cole</t>
-  </si>
-  <si>
     <t>Troubleshooting reliable Android</t>
   </si>
   <si>
@@ -1088,7 +1088,7 @@
     <t>Speaker</t>
   </si>
   <si>
-    <t>Theme tag</t>
+    <t>Theme track tag</t>
   </si>
   <si>
     <t>Sector tag</t>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
@@ -1870,8 +1870,8 @@
       <c r="C3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>54</v>
+      <c r="D3" t="s">
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
@@ -1950,10 +1950,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
         <v>56</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>34</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>34</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
         <v>59</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
@@ -2082,10 +2082,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>34</v>
@@ -2126,7 +2126,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
@@ -2170,10 +2170,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>34</v>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
         <v>65</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
       </c>
       <c r="C12" t="s">
         <v>34</v>
@@ -2408,28 +2408,28 @@
         <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>46</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
@@ -2488,7 +2488,7 @@
         <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H3" t="s">
         <v>34</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
         <v>34</v>
@@ -2665,7 +2665,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
@@ -2748,7 +2748,7 @@
         <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H7" t="s">
         <v>34</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
@@ -2925,7 +2925,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
@@ -2943,7 +2943,7 @@
         <v>34</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H10" t="s">
         <v>34</v>
@@ -2990,7 +2990,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
@@ -3055,7 +3055,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -3185,7 +3185,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -3380,7 +3380,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -3445,7 +3445,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -3770,7 +3770,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" t="s">
         <v>34</v>
@@ -3835,7 +3835,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
@@ -3900,7 +3900,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -3965,7 +3965,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -4030,7 +4030,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
@@ -4095,7 +4095,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -4160,7 +4160,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
@@ -4225,7 +4225,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
@@ -4290,7 +4290,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
@@ -4355,7 +4355,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B32" t="s">
         <v>34</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
@@ -4485,22 +4485,22 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>105</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" t="s">
+        <v>34</v>
+      </c>
+      <c r="F34" t="s">
         <v>106</v>
-      </c>
-      <c r="B34" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D34" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" t="s">
-        <v>107</v>
       </c>
       <c r="G34" t="s">
         <v>34</v>
@@ -4550,7 +4550,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
@@ -4615,7 +4615,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" t="s">
         <v>34</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B37" t="s">
         <v>34</v>
@@ -4745,7 +4745,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
         <v>34</v>
@@ -4810,7 +4810,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
         <v>34</v>
@@ -4875,7 +4875,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B40" t="s">
         <v>34</v>
@@ -4940,7 +4940,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
         <v>34</v>
@@ -5005,7 +5005,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
         <v>34</v>
@@ -5070,7 +5070,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
         <v>34</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B44" t="s">
         <v>34</v>
@@ -5200,7 +5200,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B45" t="s">
         <v>34</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
         <v>34</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
         <v>34</v>
@@ -5348,7 +5348,7 @@
         <v>34</v>
       </c>
       <c r="G47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H47" t="s">
         <v>34</v>
@@ -5395,7 +5395,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s">
         <v>34</v>
@@ -5460,7 +5460,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
         <v>34</v>
@@ -5525,7 +5525,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B50" t="s">
         <v>34</v>
@@ -5555,7 +5555,7 @@
         <v>34</v>
       </c>
       <c r="K50" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="L50" t="s">
         <v>34</v>
@@ -5629,61 +5629,61 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>26</v>
@@ -5692,24 +5692,24 @@
         <v>27</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" t="s">
         <v>135</v>
-      </c>
-      <c r="B2" t="s">
-        <v>136</v>
       </c>
       <c r="C2" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" t="s">
         <v>137</v>
-      </c>
-      <c r="E2" t="s">
-        <v>138</v>
       </c>
       <c r="F2" t="s">
         <v>34</v>
@@ -5718,11 +5718,11 @@
         <v>3.0</v>
       </c>
       <c r="H2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I2" t="s">
         <v>139</v>
       </c>
-      <c r="I2" t="s">
-        <v>140</v>
-      </c>
       <c r="J2" t="s">
         <v>34</v>
       </c>
@@ -5736,7 +5736,7 @@
         <v>34</v>
       </c>
       <c r="N2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O2" t="s">
         <v>34</v>
@@ -5765,31 +5765,31 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" t="s">
         <v>141</v>
-      </c>
-      <c r="B3" t="s">
-        <v>142</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F3" t="s">
         <v>143</v>
-      </c>
-      <c r="F3" t="s">
-        <v>144</v>
       </c>
       <c r="G3" t="n">
         <v>2.0</v>
       </c>
       <c r="H3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J3" t="s">
         <v>34</v>
@@ -5804,7 +5804,7 @@
         <v>34</v>
       </c>
       <c r="N3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O3" t="s">
         <v>34</v>
@@ -5833,31 +5833,31 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" t="s">
         <v>146</v>
-      </c>
-      <c r="B4" t="s">
-        <v>147</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" t="s">
         <v>148</v>
-      </c>
-      <c r="F4" t="s">
-        <v>149</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
       </c>
       <c r="H4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J4" t="s">
         <v>34</v>
@@ -5872,7 +5872,7 @@
         <v>34</v>
       </c>
       <c r="N4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O4" t="s">
         <v>34</v>
@@ -5901,31 +5901,31 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" t="s">
         <v>151</v>
-      </c>
-      <c r="B5" t="s">
-        <v>152</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F5" t="s">
         <v>153</v>
-      </c>
-      <c r="F5" t="s">
-        <v>154</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
       </c>
       <c r="H5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J5" t="s">
         <v>34</v>
@@ -5940,7 +5940,7 @@
         <v>34</v>
       </c>
       <c r="N5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O5" t="s">
         <v>34</v>
@@ -5969,19 +5969,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" t="s">
         <v>156</v>
-      </c>
-      <c r="B6" t="s">
-        <v>157</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F6" t="s">
         <v>34</v>
@@ -5990,10 +5990,10 @@
         <v>1.0</v>
       </c>
       <c r="H6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J6" t="s">
         <v>34</v>
@@ -6008,7 +6008,7 @@
         <v>34</v>
       </c>
       <c r="N6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O6" t="s">
         <v>34</v>
@@ -6037,19 +6037,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" t="s">
         <v>159</v>
-      </c>
-      <c r="B7" t="s">
-        <v>160</v>
       </c>
       <c r="C7" t="s">
         <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F7" t="s">
         <v>34</v>
@@ -6058,10 +6058,10 @@
         <v>2.0</v>
       </c>
       <c r="H7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J7" t="s">
         <v>34</v>
@@ -6076,7 +6076,7 @@
         <v>34</v>
       </c>
       <c r="N7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O7" t="s">
         <v>34</v>
@@ -6105,19 +6105,19 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" t="s">
         <v>163</v>
-      </c>
-      <c r="B8" t="s">
-        <v>164</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -6126,10 +6126,10 @@
         <v>1.0</v>
       </c>
       <c r="H8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J8" t="s">
         <v>34</v>
@@ -6144,7 +6144,7 @@
         <v>34</v>
       </c>
       <c r="N8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O8" t="s">
         <v>34</v>
@@ -6173,19 +6173,19 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" t="s">
         <v>167</v>
-      </c>
-      <c r="B9" t="s">
-        <v>168</v>
       </c>
       <c r="C9" t="s">
         <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -6194,10 +6194,10 @@
         <v>3.0</v>
       </c>
       <c r="H9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J9" t="s">
         <v>34</v>
@@ -6212,7 +6212,7 @@
         <v>34</v>
       </c>
       <c r="N9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O9" t="s">
         <v>34</v>
@@ -6241,19 +6241,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B10" t="s">
         <v>171</v>
-      </c>
-      <c r="B10" t="s">
-        <v>172</v>
       </c>
       <c r="C10" t="s">
         <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F10" t="s">
         <v>34</v>
@@ -6262,10 +6262,10 @@
         <v>3.0</v>
       </c>
       <c r="H10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J10" t="s">
         <v>34</v>
@@ -6309,19 +6309,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11" t="s">
         <v>175</v>
-      </c>
-      <c r="B11" t="s">
-        <v>176</v>
       </c>
       <c r="C11" t="s">
         <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F11" t="s">
         <v>34</v>
@@ -6330,10 +6330,10 @@
         <v>3.0</v>
       </c>
       <c r="H11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J11" t="s">
         <v>34</v>
@@ -6377,19 +6377,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" t="s">
         <v>179</v>
-      </c>
-      <c r="B12" t="s">
-        <v>180</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
       </c>
       <c r="D12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E12" t="s">
         <v>181</v>
-      </c>
-      <c r="E12" t="s">
-        <v>182</v>
       </c>
       <c r="F12" t="s">
         <v>34</v>
@@ -6398,10 +6398,10 @@
         <v>3.0</v>
       </c>
       <c r="H12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J12" t="s">
         <v>34</v>
@@ -6445,31 +6445,31 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" t="s">
         <v>184</v>
-      </c>
-      <c r="B13" t="s">
-        <v>185</v>
       </c>
       <c r="C13" t="s">
         <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G13" t="n">
         <v>3.0</v>
       </c>
       <c r="H13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J13" t="s">
         <v>34</v>
@@ -6513,19 +6513,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B14" t="s">
         <v>188</v>
-      </c>
-      <c r="B14" t="s">
-        <v>189</v>
       </c>
       <c r="C14" t="s">
         <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F14" t="s">
         <v>34</v>
@@ -6534,10 +6534,10 @@
         <v>3.0</v>
       </c>
       <c r="H14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J14" t="s">
         <v>34</v>
@@ -6581,19 +6581,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" t="s">
         <v>192</v>
-      </c>
-      <c r="B15" t="s">
-        <v>193</v>
       </c>
       <c r="C15" t="s">
         <v>36</v>
       </c>
       <c r="D15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" t="s">
         <v>194</v>
-      </c>
-      <c r="E15" t="s">
-        <v>195</v>
       </c>
       <c r="F15" t="s">
         <v>34</v>
@@ -6602,10 +6602,10 @@
         <v>1.0</v>
       </c>
       <c r="H15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J15" t="s">
         <v>34</v>
@@ -6649,19 +6649,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" t="s">
         <v>197</v>
-      </c>
-      <c r="B16" t="s">
-        <v>198</v>
       </c>
       <c r="C16" t="s">
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F16" t="s">
         <v>34</v>
@@ -6670,10 +6670,10 @@
         <v>3.0</v>
       </c>
       <c r="H16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J16" t="s">
         <v>34</v>
@@ -6717,19 +6717,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>200</v>
+      </c>
+      <c r="B17" t="s">
         <v>201</v>
-      </c>
-      <c r="B17" t="s">
-        <v>202</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -6738,10 +6738,10 @@
         <v>3.0</v>
       </c>
       <c r="H17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J17" t="s">
         <v>34</v>
@@ -6785,19 +6785,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B18" t="s">
         <v>204</v>
-      </c>
-      <c r="B18" t="s">
-        <v>205</v>
       </c>
       <c r="C18" t="s">
         <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F18" t="s">
         <v>34</v>
@@ -6806,10 +6806,10 @@
         <v>1.0</v>
       </c>
       <c r="H18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J18" t="s">
         <v>34</v>
@@ -6853,31 +6853,31 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" t="s">
         <v>208</v>
-      </c>
-      <c r="B19" t="s">
-        <v>209</v>
       </c>
       <c r="C19" t="s">
         <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G19" t="n">
         <v>2.0</v>
       </c>
       <c r="H19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J19" t="s">
         <v>34</v>
@@ -6921,19 +6921,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>211</v>
+      </c>
+      <c r="B20" t="s">
         <v>212</v>
-      </c>
-      <c r="B20" t="s">
-        <v>213</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E20" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F20" t="s">
         <v>34</v>
@@ -6942,10 +6942,10 @@
         <v>3.0</v>
       </c>
       <c r="H20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J20" t="s">
         <v>34</v>
@@ -6989,31 +6989,31 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>215</v>
+      </c>
+      <c r="B21" t="s">
         <v>216</v>
-      </c>
-      <c r="B21" t="s">
-        <v>217</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G21" t="n">
         <v>1.0</v>
       </c>
       <c r="H21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J21" t="s">
         <v>34</v>
@@ -7057,31 +7057,31 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>219</v>
+      </c>
+      <c r="B22" t="s">
         <v>220</v>
-      </c>
-      <c r="B22" t="s">
-        <v>221</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G22" t="n">
         <v>3.0</v>
       </c>
       <c r="H22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J22" t="s">
         <v>34</v>
@@ -7125,19 +7125,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>222</v>
+      </c>
+      <c r="B23" t="s">
         <v>223</v>
-      </c>
-      <c r="B23" t="s">
-        <v>224</v>
       </c>
       <c r="C23" t="s">
         <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
@@ -7146,10 +7146,10 @@
         <v>3.0</v>
       </c>
       <c r="H23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J23" t="s">
         <v>34</v>
@@ -7193,19 +7193,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>225</v>
+      </c>
+      <c r="B24" t="s">
         <v>226</v>
-      </c>
-      <c r="B24" t="s">
-        <v>227</v>
       </c>
       <c r="C24" t="s">
         <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F24" t="s">
         <v>34</v>
@@ -7214,10 +7214,10 @@
         <v>3.0</v>
       </c>
       <c r="H24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J24" t="s">
         <v>34</v>
@@ -7261,19 +7261,19 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>228</v>
+      </c>
+      <c r="B25" t="s">
         <v>229</v>
-      </c>
-      <c r="B25" t="s">
-        <v>230</v>
       </c>
       <c r="C25" t="s">
         <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -7282,10 +7282,10 @@
         <v>2.0</v>
       </c>
       <c r="H25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J25" t="s">
         <v>34</v>
@@ -7329,31 +7329,31 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>230</v>
+      </c>
+      <c r="B26" t="s">
         <v>231</v>
-      </c>
-      <c r="B26" t="s">
-        <v>232</v>
       </c>
       <c r="C26" t="s">
         <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G26" t="n">
         <v>2.0</v>
       </c>
       <c r="H26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J26" t="s">
         <v>34</v>
@@ -7397,19 +7397,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>232</v>
+      </c>
+      <c r="B27" t="s">
         <v>233</v>
-      </c>
-      <c r="B27" t="s">
-        <v>234</v>
       </c>
       <c r="C27" t="s">
         <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E27" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F27" t="s">
         <v>34</v>
@@ -7418,10 +7418,10 @@
         <v>2.0</v>
       </c>
       <c r="H27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J27" t="s">
         <v>34</v>
@@ -7465,19 +7465,19 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>234</v>
+      </c>
+      <c r="B28" t="s">
         <v>235</v>
-      </c>
-      <c r="B28" t="s">
-        <v>236</v>
       </c>
       <c r="C28" t="s">
         <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F28" t="s">
         <v>34</v>
@@ -7486,10 +7486,10 @@
         <v>1.0</v>
       </c>
       <c r="H28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J28" t="s">
         <v>34</v>
@@ -7533,19 +7533,19 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>236</v>
+      </c>
+      <c r="B29" t="s">
         <v>237</v>
-      </c>
-      <c r="B29" t="s">
-        <v>238</v>
       </c>
       <c r="C29" t="s">
         <v>36</v>
       </c>
       <c r="D29" t="s">
+        <v>238</v>
+      </c>
+      <c r="E29" t="s">
         <v>239</v>
-      </c>
-      <c r="E29" t="s">
-        <v>240</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -7554,10 +7554,10 @@
         <v>3.0</v>
       </c>
       <c r="H29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J29" t="s">
         <v>34</v>
@@ -7601,19 +7601,19 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>240</v>
+      </c>
+      <c r="B30" t="s">
         <v>241</v>
-      </c>
-      <c r="B30" t="s">
-        <v>242</v>
       </c>
       <c r="C30" t="s">
         <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F30" t="s">
         <v>34</v>
@@ -7622,10 +7622,10 @@
         <v>1.0</v>
       </c>
       <c r="H30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J30" t="s">
         <v>34</v>
@@ -7669,19 +7669,19 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>242</v>
+      </c>
+      <c r="B31" t="s">
         <v>243</v>
-      </c>
-      <c r="B31" t="s">
-        <v>244</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F31" t="s">
         <v>34</v>
@@ -7690,10 +7690,10 @@
         <v>2.0</v>
       </c>
       <c r="H31" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J31" t="s">
         <v>34</v>
@@ -7737,19 +7737,19 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>244</v>
+      </c>
+      <c r="B32" t="s">
         <v>245</v>
-      </c>
-      <c r="B32" t="s">
-        <v>246</v>
       </c>
       <c r="C32" t="s">
         <v>36</v>
       </c>
       <c r="D32" t="s">
+        <v>246</v>
+      </c>
+      <c r="E32" t="s">
         <v>247</v>
-      </c>
-      <c r="E32" t="s">
-        <v>248</v>
       </c>
       <c r="F32" t="s">
         <v>34</v>
@@ -7758,10 +7758,10 @@
         <v>2.0</v>
       </c>
       <c r="H32" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J32" t="s">
         <v>34</v>
@@ -7805,19 +7805,19 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>248</v>
+      </c>
+      <c r="B33" t="s">
         <v>249</v>
-      </c>
-      <c r="B33" t="s">
-        <v>250</v>
       </c>
       <c r="C33" t="s">
         <v>36</v>
       </c>
       <c r="D33" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F33" t="s">
         <v>34</v>
@@ -7826,10 +7826,10 @@
         <v>3.0</v>
       </c>
       <c r="H33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J33" t="s">
         <v>34</v>
@@ -7873,19 +7873,19 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>251</v>
+      </c>
+      <c r="B34" t="s">
         <v>252</v>
-      </c>
-      <c r="B34" t="s">
-        <v>253</v>
       </c>
       <c r="C34" t="s">
         <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E34" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F34" t="s">
         <v>34</v>
@@ -7894,10 +7894,10 @@
         <v>1.0</v>
       </c>
       <c r="H34" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J34" t="s">
         <v>34</v>
@@ -7941,31 +7941,31 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>254</v>
+      </c>
+      <c r="B35" t="s">
         <v>255</v>
-      </c>
-      <c r="B35" t="s">
-        <v>256</v>
       </c>
       <c r="C35" t="s">
         <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E35" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F35" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G35" t="n">
         <v>1.0</v>
       </c>
       <c r="H35" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J35" t="s">
         <v>34</v>
@@ -8009,7 +8009,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>257</v>
       </c>
       <c r="B36" t="s">
         <v>258</v>
@@ -8018,10 +8018,10 @@
         <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F36" t="s">
         <v>34</v>
@@ -8030,10 +8030,10 @@
         <v>2.0</v>
       </c>
       <c r="H36" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I36" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J36" t="s">
         <v>34</v>
@@ -8086,10 +8086,10 @@
         <v>36</v>
       </c>
       <c r="D37" t="s">
+        <v>136</v>
+      </c>
+      <c r="E37" t="s">
         <v>137</v>
-      </c>
-      <c r="E37" t="s">
-        <v>138</v>
       </c>
       <c r="F37" t="s">
         <v>34</v>
@@ -8098,10 +8098,10 @@
         <v>1.0</v>
       </c>
       <c r="H37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I37" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J37" t="s">
         <v>34</v>
@@ -8157,7 +8157,7 @@
         <v>263</v>
       </c>
       <c r="E38" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F38" t="s">
         <v>34</v>
@@ -8166,10 +8166,10 @@
         <v>1.0</v>
       </c>
       <c r="H38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I38" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J38" t="s">
         <v>34</v>
@@ -8225,7 +8225,7 @@
         <v>266</v>
       </c>
       <c r="E39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -8234,10 +8234,10 @@
         <v>3.0</v>
       </c>
       <c r="H39" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J39" t="s">
         <v>34</v>
@@ -8290,10 +8290,10 @@
         <v>36</v>
       </c>
       <c r="D40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F40" t="s">
         <v>34</v>
@@ -8302,10 +8302,10 @@
         <v>3.0</v>
       </c>
       <c r="H40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I40" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J40" t="s">
         <v>34</v>
@@ -8358,10 +8358,10 @@
         <v>36</v>
       </c>
       <c r="D41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F41" t="s">
         <v>34</v>
@@ -8373,7 +8373,7 @@
         <v>271</v>
       </c>
       <c r="I41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J41" t="s">
         <v>34</v>
@@ -8426,10 +8426,10 @@
         <v>36</v>
       </c>
       <c r="D42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F42" t="s">
         <v>34</v>
@@ -8438,10 +8438,10 @@
         <v>2.0</v>
       </c>
       <c r="H42" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J42" t="s">
         <v>34</v>
@@ -8497,7 +8497,7 @@
         <v>276</v>
       </c>
       <c r="E43" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -8506,10 +8506,10 @@
         <v>1.0</v>
       </c>
       <c r="H43" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J43" t="s">
         <v>34</v>
@@ -8562,22 +8562,22 @@
         <v>36</v>
       </c>
       <c r="D44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F44" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G44" t="n">
         <v>1.0</v>
       </c>
       <c r="H44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J44" t="s">
         <v>34</v>
@@ -8630,10 +8630,10 @@
         <v>36</v>
       </c>
       <c r="D45" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E45" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F45" t="s">
         <v>34</v>
@@ -8642,10 +8642,10 @@
         <v>3.0</v>
       </c>
       <c r="H45" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J45" t="s">
         <v>34</v>
@@ -8701,7 +8701,7 @@
         <v>283</v>
       </c>
       <c r="E46" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F46" t="s">
         <v>34</v>
@@ -8710,10 +8710,10 @@
         <v>1.0</v>
       </c>
       <c r="H46" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J46" t="s">
         <v>34</v>
@@ -8766,10 +8766,10 @@
         <v>36</v>
       </c>
       <c r="D47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F47" t="s">
         <v>286</v>
@@ -8778,10 +8778,10 @@
         <v>2.0</v>
       </c>
       <c r="H47" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J47" t="s">
         <v>34</v>
@@ -8834,10 +8834,10 @@
         <v>36</v>
       </c>
       <c r="D48" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E48" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F48" t="s">
         <v>34</v>
@@ -8849,7 +8849,7 @@
         <v>289</v>
       </c>
       <c r="I48" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J48" t="s">
         <v>34</v>
@@ -8902,22 +8902,22 @@
         <v>36</v>
       </c>
       <c r="D49" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E49" t="s">
         <v>292</v>
       </c>
       <c r="F49" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G49" t="n">
         <v>1.0</v>
       </c>
       <c r="H49" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I49" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J49" t="s">
         <v>34</v>
@@ -8970,7 +8970,7 @@
         <v>36</v>
       </c>
       <c r="D50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E50" t="s">
         <v>295</v>
@@ -8982,10 +8982,10 @@
         <v>3.0</v>
       </c>
       <c r="H50" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J50" t="s">
         <v>34</v>
@@ -9038,22 +9038,22 @@
         <v>36</v>
       </c>
       <c r="D51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E51" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F51" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G51" t="n">
         <v>1.0</v>
       </c>
       <c r="H51" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I51" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J51" t="s">
         <v>34</v>
@@ -9106,22 +9106,22 @@
         <v>36</v>
       </c>
       <c r="D52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E52" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F52" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G52" t="n">
         <v>3.0</v>
       </c>
       <c r="H52" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I52" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J52" t="s">
         <v>34</v>
@@ -9177,7 +9177,7 @@
         <v>302</v>
       </c>
       <c r="E53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F53" t="s">
         <v>34</v>
@@ -9186,10 +9186,10 @@
         <v>2.0</v>
       </c>
       <c r="H53" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I53" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J53" t="s">
         <v>34</v>
@@ -9242,10 +9242,10 @@
         <v>36</v>
       </c>
       <c r="D54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F54" t="s">
         <v>34</v>
@@ -9254,10 +9254,10 @@
         <v>2.0</v>
       </c>
       <c r="H54" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I54" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J54" t="s">
         <v>34</v>
@@ -9313,7 +9313,7 @@
         <v>307</v>
       </c>
       <c r="E55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -9322,10 +9322,10 @@
         <v>2.0</v>
       </c>
       <c r="H55" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I55" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J55" t="s">
         <v>34</v>
@@ -9381,19 +9381,19 @@
         <v>310</v>
       </c>
       <c r="E56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F56" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G56" t="n">
         <v>2.0</v>
       </c>
       <c r="H56" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I56" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J56" t="s">
         <v>34</v>
@@ -9446,10 +9446,10 @@
         <v>36</v>
       </c>
       <c r="D57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E57" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F57" t="s">
         <v>34</v>
@@ -9458,10 +9458,10 @@
         <v>1.0</v>
       </c>
       <c r="H57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I57" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J57" t="s">
         <v>34</v>
@@ -9526,10 +9526,10 @@
         <v>1.0</v>
       </c>
       <c r="H58" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I58" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J58" t="s">
         <v>34</v>
@@ -9582,7 +9582,7 @@
         <v>36</v>
       </c>
       <c r="D59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E59" t="s">
         <v>319</v>
@@ -9594,10 +9594,10 @@
         <v>3.0</v>
       </c>
       <c r="H59" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I59" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J59" t="s">
         <v>34</v>
@@ -9650,13 +9650,13 @@
         <v>36</v>
       </c>
       <c r="D60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E60" t="s">
         <v>322</v>
       </c>
       <c r="F60" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G60" t="n">
         <v>1.0</v>
@@ -9665,7 +9665,7 @@
         <v>271</v>
       </c>
       <c r="I60" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J60" t="s">
         <v>34</v>
@@ -9718,10 +9718,10 @@
         <v>36</v>
       </c>
       <c r="D61" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F61" t="s">
         <v>34</v>
@@ -9730,10 +9730,10 @@
         <v>2.0</v>
       </c>
       <c r="H61" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I61" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J61" t="s">
         <v>34</v>
@@ -9789,7 +9789,7 @@
         <v>327</v>
       </c>
       <c r="E62" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F62" t="s">
         <v>34</v>
@@ -9798,10 +9798,10 @@
         <v>1.0</v>
       </c>
       <c r="H62" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I62" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J62" t="s">
         <v>34</v>
@@ -9854,7 +9854,7 @@
         <v>36</v>
       </c>
       <c r="D63" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E63" t="s">
         <v>330</v>
@@ -9866,10 +9866,10 @@
         <v>1.0</v>
       </c>
       <c r="H63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I63" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J63" t="s">
         <v>34</v>
@@ -9922,7 +9922,7 @@
         <v>36</v>
       </c>
       <c r="D64" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E64" t="s">
         <v>295</v>
@@ -9934,10 +9934,10 @@
         <v>2.0</v>
       </c>
       <c r="H64" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J64" t="s">
         <v>34</v>
@@ -9990,10 +9990,10 @@
         <v>36</v>
       </c>
       <c r="D65" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F65" t="s">
         <v>34</v>
@@ -10002,10 +10002,10 @@
         <v>3.0</v>
       </c>
       <c r="H65" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I65" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J65" t="s">
         <v>34</v>
@@ -10058,7 +10058,7 @@
         <v>36</v>
       </c>
       <c r="D66" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E66" t="s">
         <v>337</v>
@@ -10070,10 +10070,10 @@
         <v>1.0</v>
       </c>
       <c r="H66" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I66" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J66" t="s">
         <v>34</v>
@@ -10126,10 +10126,10 @@
         <v>36</v>
       </c>
       <c r="D67" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E67" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F67" t="s">
         <v>34</v>
@@ -10141,7 +10141,7 @@
         <v>289</v>
       </c>
       <c r="I67" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J67" t="s">
         <v>34</v>
@@ -10197,19 +10197,19 @@
         <v>342</v>
       </c>
       <c r="E68" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F68" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G68" t="n">
         <v>2.0</v>
       </c>
       <c r="H68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I68" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J68" t="s">
         <v>34</v>
@@ -10265,7 +10265,7 @@
         <v>345</v>
       </c>
       <c r="E69" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -10274,10 +10274,10 @@
         <v>2.0</v>
       </c>
       <c r="H69" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I69" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J69" t="s">
         <v>34</v>
@@ -10330,10 +10330,10 @@
         <v>36</v>
       </c>
       <c r="D70" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E70" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F70" t="s">
         <v>34</v>
@@ -10342,10 +10342,10 @@
         <v>1.0</v>
       </c>
       <c r="H70" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I70" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J70" t="s">
         <v>34</v>
@@ -10398,10 +10398,10 @@
         <v>36</v>
       </c>
       <c r="D71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E71" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F71" t="s">
         <v>34</v>
@@ -10410,10 +10410,10 @@
         <v>1.0</v>
       </c>
       <c r="H71" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I71" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J71" t="s">
         <v>34</v>
@@ -10466,10 +10466,10 @@
         <v>36</v>
       </c>
       <c r="D72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F72" t="s">
         <v>34</v>
@@ -10478,10 +10478,10 @@
         <v>2.0</v>
       </c>
       <c r="H72" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I72" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J72" t="s">
         <v>34</v>
@@ -10534,10 +10534,10 @@
         <v>36</v>
       </c>
       <c r="D73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E73" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F73" t="s">
         <v>34</v>
@@ -10546,10 +10546,10 @@
         <v>2.0</v>
       </c>
       <c r="H73" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J73" t="s">
         <v>34</v>
@@ -10660,7 +10660,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>46</v>
@@ -10706,8 +10706,8 @@
       <c r="B3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
-        <v>54</v>
+      <c r="C3" s="3" t="s">
+        <v>257</v>
       </c>
       <c r="D3" t="s">
         <v>34</v>
@@ -10742,7 +10742,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>34</v>
@@ -10783,7 +10783,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>34</v>
@@ -10824,7 +10824,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>34</v>
@@ -10865,7 +10865,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
@@ -10906,7 +10906,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>34</v>
@@ -10947,7 +10947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>34</v>
@@ -10988,7 +10988,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>34</v>
@@ -11029,7 +11029,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>34</v>
@@ -11070,7 +11070,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -11223,7 +11223,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
@@ -11264,7 +11264,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
@@ -11305,7 +11305,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
         <v>34</v>
@@ -11346,7 +11346,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
@@ -11387,7 +11387,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
@@ -11428,7 +11428,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
@@ -11469,7 +11469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>34</v>
@@ -11510,7 +11510,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
@@ -11551,7 +11551,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
@@ -11592,7 +11592,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -11633,7 +11633,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -11674,7 +11674,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -11715,7 +11715,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -11797,7 +11797,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -11838,7 +11838,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -11879,7 +11879,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -11920,7 +11920,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -11961,7 +11961,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -12002,7 +12002,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -12043,7 +12043,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" t="s">
         <v>34</v>
@@ -12084,7 +12084,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
@@ -12125,7 +12125,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -12166,7 +12166,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -12207,7 +12207,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
@@ -12248,7 +12248,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -12289,7 +12289,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
@@ -12330,7 +12330,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
@@ -12371,7 +12371,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
@@ -12412,7 +12412,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B32" t="s">
         <v>34</v>
@@ -12453,7 +12453,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
@@ -12494,7 +12494,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B34" t="s">
         <v>34</v>
@@ -12535,7 +12535,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>34</v>
@@ -12576,7 +12576,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" t="s">
         <v>34</v>
@@ -12617,7 +12617,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B37" t="s">
         <v>34</v>
@@ -12658,7 +12658,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
         <v>34</v>
@@ -12699,7 +12699,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
         <v>34</v>
@@ -12740,7 +12740,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B40" t="s">
         <v>34</v>
@@ -12781,7 +12781,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
         <v>34</v>
@@ -12822,7 +12822,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
         <v>34</v>
@@ -12863,7 +12863,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
         <v>34</v>
@@ -12904,7 +12904,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B44" t="s">
         <v>34</v>
@@ -12945,7 +12945,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B45" t="s">
         <v>34</v>
@@ -12986,7 +12986,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
         <v>34</v>
@@ -13027,7 +13027,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
         <v>34</v>
@@ -13068,7 +13068,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s">
         <v>34</v>
@@ -13109,7 +13109,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
         <v>34</v>
@@ -13150,13 +13150,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B50" t="s">
         <v>34</v>
       </c>
       <c r="C50" t="s">
-        <v>54</v>
+        <v>257</v>
       </c>
       <c r="D50" t="s">
         <v>34</v>
@@ -13204,7 +13204,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="13.19140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="15.82421875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
@@ -13303,11 +13303,11 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>257</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -20,8 +20,76 @@
 </workbook>
 </file>
 
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S34: Troubleshooting reliable Android
+  Hugo Fox
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S34: Troubleshooting reliable Android
+  Hugo Fox
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C50" authorId="0">
+      <text>
+        <t>S34: Troubleshooting reliable Android
+  Hugo Fox
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S34: Troubleshooting reliable Android
+  Hugo Fox
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3664" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3686" uniqueCount="362">
   <si>
     <t>Conference name</t>
   </si>
@@ -1419,6 +1487,9 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -1523,20 +1594,42 @@
       <c r="A3" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="D3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -1545,6 +1638,7 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -10635,6 +10729,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -11165,11 +11262,15 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -13245,11 +13346,15 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -13354,20 +13459,42 @@
       <c r="A3" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="D3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -13376,11 +13503,15 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3882" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3882" uniqueCount="398">
   <si>
     <t>Conference name</t>
   </si>
@@ -304,295 +304,298 @@
     <t>End</t>
   </si>
   <si>
+    <t>Talk types</t>
+  </si>
+  <si>
+    <t>Tags</t>
+  </si>
+  <si>
+    <t>Mon 2018-10-01</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>Lab</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>Breakout</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>Tue 2018-10-02</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>10:15-12:15</t>
+  </si>
+  <si>
+    <t>10:15-11:00</t>
+  </si>
+  <si>
+    <t>11:30-12:15</t>
+  </si>
+  <si>
+    <t>13:00-15:00</t>
+  </si>
+  <si>
+    <t>15:30-16:15</t>
+  </si>
+  <si>
+    <t>16:30-17:15</t>
+  </si>
+  <si>
+    <t>R 1</t>
+  </si>
+  <si>
+    <t>Large, Recorded</t>
+  </si>
+  <si>
+    <t>R 2</t>
+  </si>
+  <si>
+    <t>R 3</t>
+  </si>
+  <si>
+    <t>Recorded</t>
+  </si>
+  <si>
+    <t>R 4</t>
+  </si>
+  <si>
+    <t>R 5</t>
+  </si>
+  <si>
+    <t>Lab_room, Large, Recorded</t>
+  </si>
+  <si>
+    <t>R 6</t>
+  </si>
+  <si>
+    <t>R 7</t>
+  </si>
+  <si>
+    <t>R 8</t>
+  </si>
+  <si>
+    <t>R 9</t>
+  </si>
+  <si>
+    <t>R 10</t>
+  </si>
+  <si>
+    <t>Lab_room</t>
+  </si>
+  <si>
+    <t>Required timeslot tags</t>
+  </si>
+  <si>
+    <t>Preferred timeslot tags</t>
+  </si>
+  <si>
+    <t>Prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t>Undesired timeslot tags</t>
+  </si>
+  <si>
+    <t>Required room tags</t>
+  </si>
+  <si>
+    <t>Preferred room tags</t>
+  </si>
+  <si>
+    <t>Prohibited room tags</t>
+  </si>
+  <si>
+    <t>Undesired room tags</t>
+  </si>
+  <si>
+    <t>Amy Cole</t>
+  </si>
+  <si>
+    <t>Beth Fox</t>
+  </si>
+  <si>
+    <t>Chad Green</t>
+  </si>
+  <si>
+    <t>Dan Jones</t>
+  </si>
+  <si>
+    <t>Elsa King</t>
+  </si>
+  <si>
+    <t>Flo Li</t>
+  </si>
+  <si>
+    <t>Gus Poe</t>
+  </si>
+  <si>
+    <t>Hugo Rye</t>
+  </si>
+  <si>
+    <t>Ivy Smith</t>
+  </si>
+  <si>
+    <t>Jay Watt</t>
+  </si>
+  <si>
+    <t>Amy Fox</t>
+  </si>
+  <si>
+    <t>Beth Green</t>
+  </si>
+  <si>
+    <t>Chad Jones</t>
+  </si>
+  <si>
+    <t>Dan King</t>
+  </si>
+  <si>
+    <t>Elsa Li</t>
+  </si>
+  <si>
+    <t>Flo Poe</t>
+  </si>
+  <si>
+    <t>Gus Rye</t>
+  </si>
+  <si>
+    <t>Hugo Smith</t>
+  </si>
+  <si>
+    <t>Ivy Watt</t>
+  </si>
+  <si>
+    <t>Jay Cole</t>
+  </si>
+  <si>
+    <t>Amy Green</t>
+  </si>
+  <si>
+    <t>Beth Jones</t>
+  </si>
+  <si>
+    <t>Chad King</t>
+  </si>
+  <si>
+    <t>Dan Li</t>
+  </si>
+  <si>
+    <t>Elsa Poe</t>
+  </si>
+  <si>
+    <t>Flo Rye</t>
+  </si>
+  <si>
+    <t>Gus Smith</t>
+  </si>
+  <si>
+    <t>Hugo Watt</t>
+  </si>
+  <si>
+    <t>Ivy Cole</t>
+  </si>
+  <si>
+    <t>Jay Fox</t>
+  </si>
+  <si>
+    <t>Amy Jones</t>
+  </si>
+  <si>
+    <t>Beth King</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>Chad Li</t>
+  </si>
+  <si>
+    <t>Dan Poe</t>
+  </si>
+  <si>
+    <t>Elsa Rye</t>
+  </si>
+  <si>
+    <t>Flo Smith</t>
+  </si>
+  <si>
+    <t>Gus Watt</t>
+  </si>
+  <si>
+    <t>Hugo Cole</t>
+  </si>
+  <si>
+    <t>Ivy Fox</t>
+  </si>
+  <si>
+    <t>Jay Green</t>
+  </si>
+  <si>
+    <t>Amy King</t>
+  </si>
+  <si>
+    <t>Beth Li</t>
+  </si>
+  <si>
+    <t>Chad Poe</t>
+  </si>
+  <si>
+    <t>Dan Rye</t>
+  </si>
+  <si>
+    <t>Elsa Smith</t>
+  </si>
+  <si>
+    <t>Flo Watt</t>
+  </si>
+  <si>
+    <t>Gus Cole</t>
+  </si>
+  <si>
+    <t>Hugo Fox</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
     <t>Talk type</t>
-  </si>
-  <si>
-    <t>Tags</t>
-  </si>
-  <si>
-    <t>Mon 2018-10-01</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>Lab</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>Breakout</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>Tue 2018-10-02</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>10:15-12:15</t>
-  </si>
-  <si>
-    <t>10:15-11:00</t>
-  </si>
-  <si>
-    <t>11:30-12:15</t>
-  </si>
-  <si>
-    <t>13:00-15:00</t>
-  </si>
-  <si>
-    <t>15:30-16:15</t>
-  </si>
-  <si>
-    <t>16:30-17:15</t>
-  </si>
-  <si>
-    <t>R 1</t>
-  </si>
-  <si>
-    <t>Large, Recorded</t>
-  </si>
-  <si>
-    <t>R 2</t>
-  </si>
-  <si>
-    <t>R 3</t>
-  </si>
-  <si>
-    <t>Recorded</t>
-  </si>
-  <si>
-    <t>R 4</t>
-  </si>
-  <si>
-    <t>R 5</t>
-  </si>
-  <si>
-    <t>Lab_room, Large, Recorded</t>
-  </si>
-  <si>
-    <t>R 6</t>
-  </si>
-  <si>
-    <t>R 7</t>
-  </si>
-  <si>
-    <t>R 8</t>
-  </si>
-  <si>
-    <t>R 9</t>
-  </si>
-  <si>
-    <t>R 10</t>
-  </si>
-  <si>
-    <t>Lab_room</t>
-  </si>
-  <si>
-    <t>Required timeslot tags</t>
-  </si>
-  <si>
-    <t>Preferred timeslot tags</t>
-  </si>
-  <si>
-    <t>Prohibited timeslot tags</t>
-  </si>
-  <si>
-    <t>Undesired timeslot tags</t>
-  </si>
-  <si>
-    <t>Required room tags</t>
-  </si>
-  <si>
-    <t>Preferred room tags</t>
-  </si>
-  <si>
-    <t>Prohibited room tags</t>
-  </si>
-  <si>
-    <t>Undesired room tags</t>
-  </si>
-  <si>
-    <t>Amy Cole</t>
-  </si>
-  <si>
-    <t>Beth Fox</t>
-  </si>
-  <si>
-    <t>Chad Green</t>
-  </si>
-  <si>
-    <t>Dan Jones</t>
-  </si>
-  <si>
-    <t>Elsa King</t>
-  </si>
-  <si>
-    <t>Flo Li</t>
-  </si>
-  <si>
-    <t>Gus Poe</t>
-  </si>
-  <si>
-    <t>Hugo Rye</t>
-  </si>
-  <si>
-    <t>Ivy Smith</t>
-  </si>
-  <si>
-    <t>Jay Watt</t>
-  </si>
-  <si>
-    <t>Amy Fox</t>
-  </si>
-  <si>
-    <t>Beth Green</t>
-  </si>
-  <si>
-    <t>Chad Jones</t>
-  </si>
-  <si>
-    <t>Dan King</t>
-  </si>
-  <si>
-    <t>Elsa Li</t>
-  </si>
-  <si>
-    <t>Flo Poe</t>
-  </si>
-  <si>
-    <t>Gus Rye</t>
-  </si>
-  <si>
-    <t>Hugo Smith</t>
-  </si>
-  <si>
-    <t>Ivy Watt</t>
-  </si>
-  <si>
-    <t>Jay Cole</t>
-  </si>
-  <si>
-    <t>Amy Green</t>
-  </si>
-  <si>
-    <t>Beth Jones</t>
-  </si>
-  <si>
-    <t>Chad King</t>
-  </si>
-  <si>
-    <t>Dan Li</t>
-  </si>
-  <si>
-    <t>Elsa Poe</t>
-  </si>
-  <si>
-    <t>Flo Rye</t>
-  </si>
-  <si>
-    <t>Gus Smith</t>
-  </si>
-  <si>
-    <t>Hugo Watt</t>
-  </si>
-  <si>
-    <t>Ivy Cole</t>
-  </si>
-  <si>
-    <t>Jay Fox</t>
-  </si>
-  <si>
-    <t>Amy Jones</t>
-  </si>
-  <si>
-    <t>Beth King</t>
-  </si>
-  <si>
-    <t>Large</t>
-  </si>
-  <si>
-    <t>Chad Li</t>
-  </si>
-  <si>
-    <t>Dan Poe</t>
-  </si>
-  <si>
-    <t>Elsa Rye</t>
-  </si>
-  <si>
-    <t>Flo Smith</t>
-  </si>
-  <si>
-    <t>Gus Watt</t>
-  </si>
-  <si>
-    <t>Hugo Cole</t>
-  </si>
-  <si>
-    <t>Ivy Fox</t>
-  </si>
-  <si>
-    <t>Jay Green</t>
-  </si>
-  <si>
-    <t>Amy King</t>
-  </si>
-  <si>
-    <t>Beth Li</t>
-  </si>
-  <si>
-    <t>Chad Poe</t>
-  </si>
-  <si>
-    <t>Dan Rye</t>
-  </si>
-  <si>
-    <t>Elsa Smith</t>
-  </si>
-  <si>
-    <t>Flo Watt</t>
-  </si>
-  <si>
-    <t>Gus Cole</t>
-  </si>
-  <si>
-    <t>Hugo Fox</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Title</t>
   </si>
   <si>
     <t>Speakers</t>
@@ -1878,7 +1881,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -1919,13 +1922,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2035,7 +2038,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -2076,13 +2079,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2192,7 +2195,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -2233,13 +2236,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2291,7 +2294,7 @@
     <col min="1" max="1" width="15.99609375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="6.0859375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="6.0859375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="9.41796875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="10.29296875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="5.1484375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -6407,28 +6410,28 @@
         <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>97</v>
@@ -6455,10 +6458,10 @@
         <v>104</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>57</v>
@@ -6467,39 +6470,39 @@
         <v>58</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>65</v>
@@ -6543,34 +6546,34 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>65</v>
@@ -6614,34 +6617,34 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>65</v>
@@ -6685,10 +6688,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>64</v>
@@ -6697,22 +6700,22 @@
         <v>111</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>65</v>
@@ -6756,34 +6759,34 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>65</v>
@@ -6827,34 +6830,34 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>65</v>
@@ -6898,34 +6901,34 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>65</v>
@@ -6969,34 +6972,34 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>65</v>
@@ -7040,10 +7043,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>67</v>
@@ -7052,22 +7055,22 @@
         <v>121</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>65</v>
@@ -7111,10 +7114,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>67</v>
@@ -7123,22 +7126,22 @@
         <v>122</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>65</v>
@@ -7182,34 +7185,34 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>65</v>
@@ -7253,34 +7256,34 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>65</v>
@@ -7324,34 +7327,34 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>65</v>
@@ -7395,34 +7398,34 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>65</v>
@@ -7466,10 +7469,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>67</v>
@@ -7478,22 +7481,22 @@
         <v>131</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>65</v>
@@ -7537,10 +7540,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>67</v>
@@ -7549,22 +7552,22 @@
         <v>132</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>65</v>
@@ -7608,10 +7611,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>67</v>
@@ -7620,22 +7623,22 @@
         <v>133</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -7679,34 +7682,34 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>65</v>
@@ -7750,10 +7753,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>67</v>
@@ -7762,22 +7765,22 @@
         <v>136</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>65</v>
@@ -7821,10 +7824,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>67</v>
@@ -7833,22 +7836,22 @@
         <v>138</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>65</v>
@@ -7892,34 +7895,34 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>65</v>
@@ -7963,10 +7966,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>67</v>
@@ -7975,22 +7978,22 @@
         <v>141</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>65</v>
@@ -8034,34 +8037,34 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>65</v>
@@ -8105,10 +8108,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>67</v>
@@ -8117,22 +8120,22 @@
         <v>144</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>65</v>
@@ -8176,10 +8179,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>67</v>
@@ -8188,22 +8191,22 @@
         <v>145</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>65</v>
@@ -8247,10 +8250,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>67</v>
@@ -8259,22 +8262,22 @@
         <v>146</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>65</v>
@@ -8318,34 +8321,34 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>65</v>
@@ -8389,10 +8392,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>67</v>
@@ -8401,22 +8404,22 @@
         <v>151</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>65</v>
@@ -8460,10 +8463,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>67</v>
@@ -8472,22 +8475,22 @@
         <v>152</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>65</v>
@@ -8531,34 +8534,34 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>65</v>
@@ -8602,10 +8605,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>67</v>
@@ -8614,22 +8617,22 @@
         <v>106</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>65</v>
@@ -8673,10 +8676,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>67</v>
@@ -8685,22 +8688,22 @@
         <v>107</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>65</v>
@@ -8744,10 +8747,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>67</v>
@@ -8756,22 +8759,22 @@
         <v>108</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>65</v>
@@ -8815,10 +8818,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>67</v>
@@ -8827,22 +8830,22 @@
         <v>109</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>65</v>
@@ -8886,10 +8889,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>67</v>
@@ -8898,22 +8901,22 @@
         <v>110</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>65</v>
@@ -8957,34 +8960,34 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>65</v>
@@ -9028,10 +9031,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>67</v>
@@ -9040,22 +9043,22 @@
         <v>113</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>65</v>
@@ -9099,10 +9102,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>67</v>
@@ -9111,22 +9114,22 @@
         <v>114</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>65</v>
@@ -9170,10 +9173,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>67</v>
@@ -9182,22 +9185,22 @@
         <v>115</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>65</v>
@@ -9241,34 +9244,34 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>65</v>
@@ -9312,34 +9315,34 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>65</v>
@@ -9383,34 +9386,34 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>65</v>
@@ -9454,34 +9457,34 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>65</v>
@@ -9525,10 +9528,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>67</v>
@@ -9537,22 +9540,22 @@
         <v>126</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>65</v>
@@ -9596,10 +9599,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>67</v>
@@ -9608,22 +9611,22 @@
         <v>127</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>65</v>
@@ -9667,10 +9670,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>67</v>
@@ -9679,22 +9682,22 @@
         <v>128</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>65</v>
@@ -9738,34 +9741,34 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>65</v>
@@ -9809,10 +9812,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>67</v>
@@ -9821,22 +9824,22 @@
         <v>131</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>65</v>
@@ -9880,34 +9883,34 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>65</v>
@@ -9951,10 +9954,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>67</v>
@@ -9963,22 +9966,22 @@
         <v>134</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>65</v>
@@ -10022,10 +10025,10 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>67</v>
@@ -10034,22 +10037,22 @@
         <v>135</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>65</v>
@@ -10093,10 +10096,10 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>67</v>
@@ -10105,22 +10108,22 @@
         <v>136</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>65</v>
@@ -10164,10 +10167,10 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>67</v>
@@ -10176,22 +10179,22 @@
         <v>138</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>65</v>
@@ -10235,10 +10238,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>67</v>
@@ -10247,22 +10250,22 @@
         <v>139</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>65</v>
@@ -10306,34 +10309,34 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>65</v>
@@ -10377,10 +10380,10 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>67</v>
@@ -10389,22 +10392,22 @@
         <v>142</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>65</v>
@@ -10448,34 +10451,34 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>65</v>
@@ -10519,10 +10522,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>67</v>
@@ -10531,22 +10534,22 @@
         <v>145</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>65</v>
@@ -10590,10 +10593,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>67</v>
@@ -10602,22 +10605,22 @@
         <v>146</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>65</v>
@@ -10661,10 +10664,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>67</v>
@@ -10673,22 +10676,22 @@
         <v>147</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>65</v>
@@ -10732,34 +10735,34 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>65</v>
@@ -10803,10 +10806,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>67</v>
@@ -10815,22 +10818,22 @@
         <v>150</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>65</v>
@@ -10874,10 +10877,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>67</v>
@@ -10886,22 +10889,22 @@
         <v>151</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>65</v>
@@ -10945,10 +10948,10 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>67</v>
@@ -10957,22 +10960,22 @@
         <v>152</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>65</v>
@@ -11016,10 +11019,10 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>67</v>
@@ -11028,22 +11031,22 @@
         <v>153</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>65</v>
@@ -11087,10 +11090,10 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>67</v>
@@ -11099,22 +11102,22 @@
         <v>105</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>65</v>
@@ -11158,10 +11161,10 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>67</v>
@@ -11170,22 +11173,22 @@
         <v>106</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>65</v>
@@ -11229,10 +11232,10 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>67</v>
@@ -11241,22 +11244,22 @@
         <v>107</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>65</v>
@@ -11300,10 +11303,10 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>67</v>
@@ -11312,22 +11315,22 @@
         <v>108</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>65</v>
@@ -11371,10 +11374,10 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>67</v>
@@ -11383,22 +11386,22 @@
         <v>109</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>65</v>
@@ -11442,10 +11445,10 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>67</v>
@@ -11454,22 +11457,22 @@
         <v>110</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>65</v>
@@ -11513,34 +11516,34 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>65</v>
@@ -11667,7 +11670,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -11714,7 +11717,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -12193,7 +12196,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -12445,7 +12448,7 @@
         <v>65</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>65</v>
@@ -14277,7 +14280,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -14318,13 +14321,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -14434,7 +14437,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -11,32 +11,16 @@
     <sheet name="Rooms" r:id="rId5" sheetId="3"/>
     <sheet name="Speakers" r:id="rId6" sheetId="4"/>
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
-    <sheet name="Rooms view" r:id="rId8" sheetId="6"/>
-    <sheet name="Speakers view" r:id="rId9" sheetId="7"/>
-    <sheet name="Theme tracks view" r:id="rId10" sheetId="8"/>
-    <sheet name="Sectors view" r:id="rId11" sheetId="9"/>
-    <sheet name="Audience type view" r:id="rId12" sheetId="10"/>
-    <sheet name="Audience level view" r:id="rId13" sheetId="11"/>
-    <sheet name="Contents view" r:id="rId14" sheetId="12"/>
+    <sheet name="Score view" r:id="rId8" sheetId="6"/>
+    <sheet name="Rooms view" r:id="rId9" sheetId="7"/>
+    <sheet name="Speakers view" r:id="rId10" sheetId="8"/>
+    <sheet name="Theme tracks view" r:id="rId11" sheetId="9"/>
+    <sheet name="Sectors view" r:id="rId12" sheetId="10"/>
+    <sheet name="Audience type view" r:id="rId13" sheetId="11"/>
+    <sheet name="Audience level view" r:id="rId14" sheetId="12"/>
+    <sheet name="Contents view" r:id="rId15" sheetId="13"/>
   </sheets>
 </workbook>
-</file>
-
-<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
-    <comment ref="C3" authorId="0">
-      <text>
-        <t>S70: Prepare for streaming Weld
-  Flo Li
-  PINNED BY USER</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
@@ -73,7 +57,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments13.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
@@ -96,6 +80,23 @@
     <author/>
   </authors>
   <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S70: Prepare for streaming Weld
+  Flo Li
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
     <comment ref="C8" authorId="0">
       <text>
         <t>S70: Prepare for streaming Weld
@@ -107,7 +108,7 @@
 </comments>
 </file>
 
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
@@ -125,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3882" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3903" uniqueCount="402">
   <si>
     <t>Conference name</t>
   </si>
@@ -397,9 +398,6 @@
     <t>R 5</t>
   </si>
   <si>
-    <t>Lab_room, Large, Recorded</t>
-  </si>
-  <si>
     <t>R 6</t>
   </si>
   <si>
@@ -415,9 +413,6 @@
     <t>R 10</t>
   </si>
   <si>
-    <t>Lab_room</t>
-  </si>
-  <si>
     <t>Required timeslot tags</t>
   </si>
   <si>
@@ -1295,6 +1290,24 @@
   </si>
   <si>
     <t>Understand mobile RestEasy</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>-142init</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Usable timeslots</t>
+  </si>
+  <si>
+    <t>Usable rooms</t>
+  </si>
+  <si>
+    <t>Usable sessions</t>
   </si>
   <si>
     <t>S70: Prepare for streaming Weld
@@ -1427,6 +1440,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
@@ -1823,6 +1840,121 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
+    <col min="1" max="1" width="10.23828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
     <col min="1" max="1" width="14.1953125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
@@ -1881,7 +2013,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -1922,13 +2054,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -1972,7 +2104,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -2038,7 +2170,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -2079,13 +2211,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2129,7 +2261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -2195,7 +2327,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -2236,13 +2368,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2531,8 +2663,8 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="6.48828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="25.6328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="10.29296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="15.51171875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
@@ -2544,6 +2676,7 @@
     <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2554,11 +2687,11 @@
         <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="E1" s="1" t="s">
         <v>65</v>
       </c>
@@ -2572,11 +2705,11 @@
         <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="K1" s="1" t="s">
         <v>65</v>
       </c>
@@ -2587,6 +2720,9 @@
         <v>65</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2595,42 +2731,45 @@
         <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2639,42 +2778,45 @@
         <v>83</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="I3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="L3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2683,42 +2825,45 @@
         <v>85</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="I4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M4" s="2" t="s">
+      <c r="L4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2727,42 +2872,45 @@
         <v>86</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="I5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M5" s="2" t="s">
+      <c r="L5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O5" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2771,42 +2919,45 @@
         <v>88</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="I6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M6" s="2" t="s">
+      <c r="L6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2815,269 +2966,287 @@
         <v>89</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="F7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="I7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M7" s="3" t="s">
+      <c r="L7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M8" s="2" t="s">
+      <c r="L8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="I9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M9" s="2" t="s">
+      <c r="L9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="I10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10" s="2" t="s">
+      <c r="L10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11" s="2" t="s">
+      <c r="I11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11" s="2" t="s">
+      <c r="L11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O11" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="F12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J12" s="3" t="s">
+      <c r="I12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12" s="3" t="s">
+      <c r="L12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12" s="3" t="s">
         <v>65</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="J1:O1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
@@ -3182,28 +3351,28 @@
         <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>77</v>
@@ -3244,7 +3413,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>65</v>
@@ -3309,7 +3478,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>65</v>
@@ -3374,7 +3543,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>65</v>
@@ -3439,7 +3608,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>65</v>
@@ -3504,7 +3673,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>65</v>
@@ -3569,7 +3738,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>65</v>
@@ -3634,7 +3803,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -3699,7 +3868,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -3764,7 +3933,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>65</v>
@@ -3829,7 +3998,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>65</v>
@@ -3894,7 +4063,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>65</v>
@@ -3959,7 +4128,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>65</v>
@@ -4024,7 +4193,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>65</v>
@@ -4089,7 +4258,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>65</v>
@@ -4154,7 +4323,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>65</v>
@@ -4219,7 +4388,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>65</v>
@@ -4284,7 +4453,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>65</v>
@@ -4349,7 +4518,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>65</v>
@@ -4414,7 +4583,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>65</v>
@@ -4479,7 +4648,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>65</v>
@@ -4544,7 +4713,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>65</v>
@@ -4609,7 +4778,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>65</v>
@@ -4674,7 +4843,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>65</v>
@@ -4739,7 +4908,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
@@ -4804,7 +4973,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>65</v>
@@ -4869,7 +5038,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>65</v>
@@ -4934,7 +5103,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>65</v>
@@ -4999,7 +5168,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>65</v>
@@ -5064,7 +5233,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>65</v>
@@ -5129,7 +5298,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>65</v>
@@ -5194,7 +5363,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>65</v>
@@ -5259,7 +5428,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>65</v>
@@ -5274,7 +5443,7 @@
         <v>65</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>65</v>
@@ -5324,7 +5493,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>65</v>
@@ -5389,7 +5558,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>65</v>
@@ -5454,7 +5623,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>65</v>
@@ -5519,7 +5688,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>65</v>
@@ -5584,7 +5753,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>65</v>
@@ -5649,7 +5818,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>65</v>
@@ -5714,7 +5883,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>65</v>
@@ -5779,7 +5948,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>65</v>
@@ -5844,7 +6013,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>65</v>
@@ -5909,7 +6078,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>65</v>
@@ -5974,7 +6143,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>65</v>
@@ -6039,7 +6208,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>65</v>
@@ -6104,7 +6273,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>65</v>
@@ -6169,7 +6338,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>65</v>
@@ -6234,7 +6403,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>65</v>
@@ -6299,7 +6468,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>65</v>
@@ -6404,64 +6573,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>57</v>
@@ -6470,39 +6639,39 @@
         <v>58</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>65</v>
@@ -6517,7 +6686,7 @@
         <v>65</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>65</v>
@@ -6546,34 +6715,34 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>65</v>
@@ -6588,7 +6757,7 @@
         <v>65</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>65</v>
@@ -6617,34 +6786,34 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>65</v>
@@ -6659,7 +6828,7 @@
         <v>65</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>65</v>
@@ -6688,34 +6857,34 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>65</v>
@@ -6730,7 +6899,7 @@
         <v>65</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>65</v>
@@ -6759,34 +6928,34 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>65</v>
@@ -6801,7 +6970,7 @@
         <v>65</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>65</v>
@@ -6830,34 +6999,34 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>65</v>
@@ -6872,7 +7041,7 @@
         <v>65</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>65</v>
@@ -6901,34 +7070,34 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>65</v>
@@ -6943,7 +7112,7 @@
         <v>65</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>65</v>
@@ -6972,34 +7141,34 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>65</v>
@@ -7014,7 +7183,7 @@
         <v>65</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>65</v>
@@ -7043,34 +7212,34 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>65</v>
@@ -7114,34 +7283,34 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>65</v>
@@ -7185,34 +7354,34 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>65</v>
@@ -7256,34 +7425,34 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>65</v>
@@ -7327,34 +7496,34 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>65</v>
@@ -7398,34 +7567,34 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>65</v>
@@ -7469,34 +7638,34 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>65</v>
@@ -7540,34 +7709,34 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>65</v>
@@ -7611,34 +7780,34 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -7682,34 +7851,34 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>65</v>
@@ -7753,34 +7922,34 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>65</v>
@@ -7824,34 +7993,34 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>65</v>
@@ -7895,34 +8064,34 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>65</v>
@@ -7966,34 +8135,34 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>65</v>
@@ -8037,34 +8206,34 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>65</v>
@@ -8108,34 +8277,34 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>65</v>
@@ -8179,34 +8348,34 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>65</v>
@@ -8250,34 +8419,34 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>65</v>
@@ -8321,34 +8490,34 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>65</v>
@@ -8392,34 +8561,34 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>65</v>
@@ -8463,34 +8632,34 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>65</v>
@@ -8534,34 +8703,34 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>65</v>
@@ -8605,34 +8774,34 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>65</v>
@@ -8676,34 +8845,34 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>65</v>
@@ -8747,34 +8916,34 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>65</v>
@@ -8818,34 +8987,34 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>65</v>
@@ -8889,34 +9058,34 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>65</v>
@@ -8960,34 +9129,34 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>65</v>
@@ -9031,34 +9200,34 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>65</v>
@@ -9102,34 +9271,34 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>65</v>
@@ -9173,34 +9342,34 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>65</v>
@@ -9244,34 +9413,34 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>65</v>
@@ -9315,34 +9484,34 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>65</v>
@@ -9386,34 +9555,34 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>65</v>
@@ -9457,34 +9626,34 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>65</v>
@@ -9528,34 +9697,34 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>65</v>
@@ -9599,34 +9768,34 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>65</v>
@@ -9670,34 +9839,34 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>65</v>
@@ -9741,34 +9910,34 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>65</v>
@@ -9812,34 +9981,34 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>65</v>
@@ -9883,34 +10052,34 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>65</v>
@@ -9954,34 +10123,34 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>65</v>
@@ -10025,34 +10194,34 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>65</v>
@@ -10096,34 +10265,34 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>65</v>
@@ -10167,34 +10336,34 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>65</v>
@@ -10238,34 +10407,34 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>65</v>
@@ -10309,34 +10478,34 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>65</v>
@@ -10380,34 +10549,34 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>65</v>
@@ -10451,34 +10620,34 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>65</v>
@@ -10522,34 +10691,34 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>65</v>
@@ -10593,34 +10762,34 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>65</v>
@@ -10664,34 +10833,34 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>65</v>
@@ -10735,34 +10904,34 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>65</v>
@@ -10806,34 +10975,34 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>65</v>
@@ -10877,34 +11046,34 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>65</v>
@@ -10948,34 +11117,34 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>65</v>
@@ -11019,34 +11188,34 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>65</v>
@@ -11090,34 +11259,34 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>65</v>
@@ -11161,34 +11330,34 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>65</v>
@@ -11232,34 +11401,34 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>65</v>
@@ -11303,34 +11472,34 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>65</v>
@@ -11374,34 +11543,34 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>65</v>
@@ -11445,34 +11614,34 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>65</v>
@@ -11516,34 +11685,34 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>65</v>
@@ -11592,6 +11761,87 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="9.4453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="7.95703125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.22265625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="13.59375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="15.30078125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>64.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -11670,7 +11920,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -11717,7 +11967,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -11916,7 +12166,7 @@
     </row>
     <row r="8" ht="60.0" customHeight="true">
       <c r="A8" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>65</v>
@@ -11957,7 +12207,7 @@
     </row>
     <row r="9" ht="60.0" customHeight="true">
       <c r="A9" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>65</v>
@@ -11998,7 +12248,7 @@
     </row>
     <row r="10" ht="60.0" customHeight="true">
       <c r="A10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>65</v>
@@ -12039,7 +12289,7 @@
     </row>
     <row r="11" ht="60.0" customHeight="true">
       <c r="A11" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>65</v>
@@ -12080,7 +12330,7 @@
     </row>
     <row r="12" ht="60.0" customHeight="true">
       <c r="A12" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>65</v>
@@ -12130,7 +12380,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -12196,7 +12446,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -12237,7 +12487,7 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
@@ -12278,7 +12528,7 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>65</v>
@@ -12319,7 +12569,7 @@
     </row>
     <row r="5" ht="15.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>65</v>
@@ -12360,7 +12610,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>65</v>
@@ -12401,7 +12651,7 @@
     </row>
     <row r="7" ht="15.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>65</v>
@@ -12442,13 +12692,13 @@
     </row>
     <row r="8" ht="15.0" customHeight="true">
       <c r="A8" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>65</v>
@@ -12483,7 +12733,7 @@
     </row>
     <row r="9" ht="15.0" customHeight="true">
       <c r="A9" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>65</v>
@@ -12524,7 +12774,7 @@
     </row>
     <row r="10" ht="15.0" customHeight="true">
       <c r="A10" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>65</v>
@@ -12565,7 +12815,7 @@
     </row>
     <row r="11" ht="15.0" customHeight="true">
       <c r="A11" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>65</v>
@@ -12606,7 +12856,7 @@
     </row>
     <row r="12" ht="15.0" customHeight="true">
       <c r="A12" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>65</v>
@@ -12647,7 +12897,7 @@
     </row>
     <row r="13" ht="15.0" customHeight="true">
       <c r="A13" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>65</v>
@@ -12688,7 +12938,7 @@
     </row>
     <row r="14" ht="15.0" customHeight="true">
       <c r="A14" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>65</v>
@@ -12729,7 +12979,7 @@
     </row>
     <row r="15" ht="15.0" customHeight="true">
       <c r="A15" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>65</v>
@@ -12770,7 +13020,7 @@
     </row>
     <row r="16" ht="15.0" customHeight="true">
       <c r="A16" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>65</v>
@@ -12811,7 +13061,7 @@
     </row>
     <row r="17" ht="15.0" customHeight="true">
       <c r="A17" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>65</v>
@@ -12852,7 +13102,7 @@
     </row>
     <row r="18" ht="15.0" customHeight="true">
       <c r="A18" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>65</v>
@@ -12893,7 +13143,7 @@
     </row>
     <row r="19" ht="15.0" customHeight="true">
       <c r="A19" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>65</v>
@@ -12934,7 +13184,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="true">
       <c r="A20" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>65</v>
@@ -12975,7 +13225,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="true">
       <c r="A21" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>65</v>
@@ -13016,7 +13266,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="true">
       <c r="A22" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>65</v>
@@ -13057,7 +13307,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="true">
       <c r="A23" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>65</v>
@@ -13098,7 +13348,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="true">
       <c r="A24" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>65</v>
@@ -13139,7 +13389,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="true">
       <c r="A25" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>65</v>
@@ -13180,7 +13430,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="true">
       <c r="A26" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>65</v>
@@ -13221,7 +13471,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="true">
       <c r="A27" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>65</v>
@@ -13262,7 +13512,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="true">
       <c r="A28" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>65</v>
@@ -13303,7 +13553,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="true">
       <c r="A29" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>65</v>
@@ -13344,7 +13594,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="true">
       <c r="A30" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>65</v>
@@ -13385,7 +13635,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="true">
       <c r="A31" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>65</v>
@@ -13426,7 +13676,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="true">
       <c r="A32" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>65</v>
@@ -13467,7 +13717,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="true">
       <c r="A33" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>65</v>
@@ -13508,7 +13758,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="true">
       <c r="A34" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>65</v>
@@ -13549,7 +13799,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="true">
       <c r="A35" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>65</v>
@@ -13590,7 +13840,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="true">
       <c r="A36" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>65</v>
@@ -13631,7 +13881,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="true">
       <c r="A37" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>65</v>
@@ -13672,7 +13922,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="true">
       <c r="A38" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>65</v>
@@ -13713,7 +13963,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="true">
       <c r="A39" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>65</v>
@@ -13754,7 +14004,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="true">
       <c r="A40" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>65</v>
@@ -13795,7 +14045,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="true">
       <c r="A41" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>65</v>
@@ -13836,7 +14086,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="true">
       <c r="A42" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>65</v>
@@ -13877,7 +14127,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="true">
       <c r="A43" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>65</v>
@@ -13918,7 +14168,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="true">
       <c r="A44" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>65</v>
@@ -13959,7 +14209,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="true">
       <c r="A45" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>65</v>
@@ -14000,7 +14250,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="true">
       <c r="A46" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>65</v>
@@ -14041,7 +14291,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="true">
       <c r="A47" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>65</v>
@@ -14082,7 +14332,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="true">
       <c r="A48" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>65</v>
@@ -14123,7 +14373,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="true">
       <c r="A49" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>65</v>
@@ -14164,7 +14414,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="true">
       <c r="A50" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>65</v>
@@ -14214,7 +14464,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -14280,7 +14530,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -14321,13 +14571,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -14369,119 +14619,4 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <tabColor rgb="FCE94F"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="10.23828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:M1"/>
-  </mergeCells>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3903" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3904" uniqueCount="404">
   <si>
     <t>Conference name</t>
   </si>
@@ -602,7 +602,7 @@
     <t>Sector tags</t>
   </si>
   <si>
-    <t>Audience type</t>
+    <t>Audience types</t>
   </si>
   <si>
     <t>Audience level</t>
@@ -1308,6 +1308,9 @@
   </si>
   <si>
     <t>Usable sessions</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
   <si>
     <t>S70: Prepare for streaming Weld
@@ -1324,6 +1327,9 @@
   </si>
   <si>
     <t>Sector tag</t>
+  </si>
+  <si>
+    <t>Audience type</t>
   </si>
   <si>
     <t>2</t>
@@ -1898,7 +1904,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -2013,7 +2019,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>158</v>
+        <v>400</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -2060,7 +2066,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2211,13 +2217,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2327,7 +2333,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -2374,7 +2380,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -11833,6 +11839,24 @@
       </c>
       <c r="E5" s="2" t="n">
         <v>64.0</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>72.0</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>120.0</v>
       </c>
     </row>
   </sheetData>
@@ -11967,7 +11991,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -12446,7 +12470,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -12698,7 +12722,7 @@
         <v>65</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>65</v>
@@ -14530,7 +14554,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>77</v>
@@ -14577,7 +14601,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -2789,7 +2789,7 @@
       <c r="C3" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -2798,7 +2798,7 @@
       <c r="F3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -2807,7 +2807,7 @@
       <c r="I3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K3" s="2" t="s">
@@ -2816,7 +2816,7 @@
       <c r="L3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N3" s="2" t="s">
@@ -2836,7 +2836,7 @@
       <c r="C4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -2845,7 +2845,7 @@
       <c r="F4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -2854,7 +2854,7 @@
       <c r="I4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K4" s="2" t="s">
@@ -2863,7 +2863,7 @@
       <c r="L4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N4" s="2" t="s">
@@ -2883,7 +2883,7 @@
       <c r="C5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -2892,7 +2892,7 @@
       <c r="F5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -2901,7 +2901,7 @@
       <c r="I5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K5" s="2" t="s">
@@ -2910,7 +2910,7 @@
       <c r="L5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N5" s="2" t="s">
@@ -2930,7 +2930,7 @@
       <c r="C6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -2939,7 +2939,7 @@
       <c r="F6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -2948,7 +2948,7 @@
       <c r="I6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K6" s="2" t="s">
@@ -2957,7 +2957,7 @@
       <c r="L6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N6" s="2" t="s">
@@ -2980,37 +2980,37 @@
       <c r="D7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="H7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L7" s="3" t="s">
+      <c r="K7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="O7" s="3" t="s">
+      <c r="N7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       <c r="C8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -3033,7 +3033,7 @@
       <c r="F8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -3042,7 +3042,7 @@
       <c r="I8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K8" s="2" t="s">
@@ -3051,7 +3051,7 @@
       <c r="L8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N8" s="2" t="s">
@@ -3071,7 +3071,7 @@
       <c r="C9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -3080,7 +3080,7 @@
       <c r="F9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -3089,7 +3089,7 @@
       <c r="I9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K9" s="2" t="s">
@@ -3098,7 +3098,7 @@
       <c r="L9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="M9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N9" s="2" t="s">
@@ -3118,7 +3118,7 @@
       <c r="C10" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -3127,7 +3127,7 @@
       <c r="F10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H10" s="2" t="s">
@@ -3136,7 +3136,7 @@
       <c r="I10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K10" s="2" t="s">
@@ -3145,7 +3145,7 @@
       <c r="L10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="M10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N10" s="2" t="s">
@@ -3165,7 +3165,7 @@
       <c r="C11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -3174,7 +3174,7 @@
       <c r="F11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H11" s="2" t="s">
@@ -3183,7 +3183,7 @@
       <c r="I11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K11" s="2" t="s">
@@ -3192,7 +3192,7 @@
       <c r="L11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="M11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N11" s="2" t="s">
@@ -3215,37 +3215,37 @@
       <c r="D12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="H12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L12" s="3" t="s">
+      <c r="K12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="O12" s="3" t="s">
+      <c r="N12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12" s="2" t="s">
         <v>65</v>
       </c>
     </row>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -1539,7 +1539,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
@@ -1561,7 +1561,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -1583,7 +1583,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -1605,7 +1605,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>22</v>
@@ -1616,7 +1616,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>24</v>
@@ -1627,7 +1627,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>22</v>
@@ -1638,7 +1638,7 @@
         <v>26</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>24</v>
@@ -1649,7 +1649,7 @@
         <v>27</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>30</v>
@@ -1671,7 +1671,7 @@
         <v>31</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -1682,7 +1682,7 @@
         <v>32</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>30</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -11,14 +11,16 @@
     <sheet name="Rooms" r:id="rId5" sheetId="3"/>
     <sheet name="Speakers" r:id="rId6" sheetId="4"/>
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
-    <sheet name="Score view" r:id="rId8" sheetId="6"/>
+    <sheet name="Infeasible view" r:id="rId8" sheetId="6"/>
     <sheet name="Rooms view" r:id="rId9" sheetId="7"/>
     <sheet name="Speakers view" r:id="rId10" sheetId="8"/>
     <sheet name="Theme tracks view" r:id="rId11" sheetId="9"/>
     <sheet name="Sectors view" r:id="rId12" sheetId="10"/>
-    <sheet name="Audience type view" r:id="rId13" sheetId="11"/>
-    <sheet name="Audience level view" r:id="rId14" sheetId="12"/>
+    <sheet name="Audience types view" r:id="rId13" sheetId="11"/>
+    <sheet name="Audience levels view" r:id="rId14" sheetId="12"/>
     <sheet name="Contents view" r:id="rId15" sheetId="13"/>
+    <sheet name="Languages view" r:id="rId16" sheetId="14"/>
+    <sheet name="Score view" r:id="rId17" sheetId="15"/>
   </sheets>
 </workbook>
 </file>
@@ -31,9 +33,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S70: Prepare for streaming Weld
-  Flo Li
-  PINNED BY USER</t>
+        <t xml:space="preserve">S70: Prepare for streaming Weld
+    Flo Li
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -48,9 +51,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S70: Prepare for streaming Weld
-  Flo Li
-  PINNED BY USER</t>
+        <t xml:space="preserve">S70: Prepare for streaming Weld
+    Flo Li
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -65,9 +69,28 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S70: Prepare for streaming Weld
-  Flo Li
-  PINNED BY USER</t>
+        <t xml:space="preserve">S70: Prepare for streaming Weld
+    Flo Li
+PINNED BY USER
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t xml:space="preserve">S70: Prepare for streaming Weld
+    Flo Li
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -82,9 +105,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S70: Prepare for streaming Weld
-  Flo Li
-  PINNED BY USER</t>
+        <t xml:space="preserve">S70: Prepare for streaming Weld
+    Flo Li
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -99,9 +123,10 @@
   <commentList>
     <comment ref="C8" authorId="0">
       <text>
-        <t>S70: Prepare for streaming Weld
-  Flo Li
-  PINNED BY USER</t>
+        <t xml:space="preserve">S70: Prepare for streaming Weld
+    Flo Li
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -116,9 +141,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S70: Prepare for streaming Weld
-  Flo Li
-  PINNED BY USER</t>
+        <t xml:space="preserve">S70: Prepare for streaming Weld
+    Flo Li
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -126,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3904" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="407">
   <si>
     <t>Conference name</t>
   </si>
@@ -1339,6 +1365,15 @@
   </si>
   <si>
     <t>S70 (level 2)</t>
+  </si>
+  <si>
+    <t>Constraint match</t>
+  </si>
+  <si>
+    <t>Match score</t>
+  </si>
+  <si>
+    <t>Total score</t>
   </si>
 </sst>
 </file>
@@ -1450,6 +1485,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
@@ -2424,6 +2467,200 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" ht="15.0" customHeight="true">
+      <c r="A3" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="16.8125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="12.296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.08203125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
@@ -11856,7 +12093,7 @@
         <v>10.0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>120.0</v>
+        <v>72.0</v>
       </c>
     </row>
   </sheetData>
@@ -11983,7 +12220,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" ht="60.0" customHeight="true">
+    <row r="3" ht="45.0" customHeight="true">
       <c r="A3" s="2" t="s">
         <v>83</v>
       </c>
@@ -12024,7 +12261,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" ht="60.0" customHeight="true">
+    <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
         <v>85</v>
       </c>
@@ -12065,7 +12302,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" ht="60.0" customHeight="true">
+    <row r="5" ht="45.0" customHeight="true">
       <c r="A5" s="2" t="s">
         <v>86</v>
       </c>
@@ -12106,7 +12343,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" ht="60.0" customHeight="true">
+    <row r="6" ht="45.0" customHeight="true">
       <c r="A6" s="2" t="s">
         <v>88</v>
       </c>
@@ -12147,7 +12384,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" ht="60.0" customHeight="true">
+    <row r="7" ht="45.0" customHeight="true">
       <c r="A7" s="2" t="s">
         <v>89</v>
       </c>
@@ -12188,7 +12425,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" ht="60.0" customHeight="true">
+    <row r="8" ht="45.0" customHeight="true">
       <c r="A8" s="2" t="s">
         <v>90</v>
       </c>
@@ -12229,7 +12466,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" ht="60.0" customHeight="true">
+    <row r="9" ht="45.0" customHeight="true">
       <c r="A9" s="2" t="s">
         <v>91</v>
       </c>
@@ -12270,7 +12507,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" ht="60.0" customHeight="true">
+    <row r="10" ht="45.0" customHeight="true">
       <c r="A10" s="2" t="s">
         <v>92</v>
       </c>
@@ -12311,7 +12548,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" ht="60.0" customHeight="true">
+    <row r="11" ht="45.0" customHeight="true">
       <c r="A11" s="2" t="s">
         <v>93</v>
       </c>
@@ -12352,7 +12589,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" ht="60.0" customHeight="true">
+    <row r="12" ht="45.0" customHeight="true">
       <c r="A12" s="2" t="s">
         <v>94</v>
       </c>
@@ -12413,18 +12650,31 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="20.0" customWidth="true"/>
+    <col min="3" max="3" width="20.0" customWidth="true"/>
+    <col min="4" max="4" width="20.0" customWidth="true"/>
+    <col min="5" max="5" width="20.0" customWidth="true"/>
+    <col min="6" max="6" width="20.0" customWidth="true"/>
+    <col min="7" max="7" width="20.0" customWidth="true"/>
+    <col min="8" max="8" width="20.0" customWidth="true"/>
+    <col min="9" max="9" width="20.0" customWidth="true"/>
+    <col min="10" max="10" width="20.0" customWidth="true"/>
+    <col min="11" max="11" width="20.0" customWidth="true"/>
+    <col min="12" max="12" width="20.0" customWidth="true"/>
+    <col min="13" max="13" width="20.0" customWidth="true"/>
+    <col min="14" max="14" width="20.0" customWidth="true"/>
+    <col min="15" max="15" width="20.0" customWidth="true"/>
+    <col min="16" max="16" width="20.0" customWidth="true"/>
+    <col min="17" max="17" width="20.0" customWidth="true"/>
+    <col min="18" max="18" width="20.0" customWidth="true"/>
+    <col min="19" max="19" width="20.0" customWidth="true"/>
+    <col min="20" max="20" width="20.0" customWidth="true"/>
+    <col min="21" max="21" width="20.0" customWidth="true"/>
+    <col min="22" max="22" width="20.0" customWidth="true"/>
+    <col min="23" max="23" width="20.0" customWidth="true"/>
+    <col min="24" max="24" width="20.0" customWidth="true"/>
+    <col min="25" max="25" width="20.0" customWidth="true"/>
+    <col min="26" max="26" width="20.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -33,8 +33,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S70: Prepare for streaming Weld
-    Flo Li
+        <t xml:space="preserve">S64: Discover AI-driven XStream
+    Jay Green
 PINNED BY USER
 </t>
       </text>
@@ -51,8 +51,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S70: Prepare for streaming Weld
-    Flo Li
+        <t xml:space="preserve">S64: Discover AI-driven XStream
+    Jay Green
 PINNED BY USER
 </t>
       </text>
@@ -69,8 +69,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S70: Prepare for streaming Weld
-    Flo Li
+        <t xml:space="preserve">S64: Discover AI-driven XStream
+    Jay Green
 PINNED BY USER
 </t>
       </text>
@@ -87,8 +87,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S70: Prepare for streaming Weld
-    Flo Li
+        <t xml:space="preserve">S64: Discover AI-driven XStream
+    Jay Green
 PINNED BY USER
 </t>
       </text>
@@ -105,8 +105,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S70: Prepare for streaming Weld
-    Flo Li
+        <t xml:space="preserve">S64: Discover AI-driven XStream
+    Jay Green
 PINNED BY USER
 </t>
       </text>
@@ -121,10 +121,10 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="C8" authorId="0">
+    <comment ref="C42" authorId="0">
       <text>
-        <t xml:space="preserve">S70: Prepare for streaming Weld
-    Flo Li
+        <t xml:space="preserve">S64: Discover AI-driven XStream
+    Jay Green
 PINNED BY USER
 </t>
       </text>
@@ -141,8 +141,16 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S70: Prepare for streaming Weld
-    Flo Li
+        <t xml:space="preserve">S64: Discover AI-driven XStream
+    Jay Green
+PINNED BY USER
+</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0">
+      <text>
+        <t xml:space="preserve">S64: Discover AI-driven XStream
+    Jay Green
 PINNED BY USER
 </t>
       </text>
@@ -152,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4089" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4104" uniqueCount="409">
   <si>
     <t>Conference name</t>
   </si>
@@ -667,6 +675,12 @@
     <t>Prerequisite talks codes</t>
   </si>
   <si>
+    <t>Number of likes</t>
+  </si>
+  <si>
+    <t>Crowd control risk</t>
+  </si>
+  <si>
     <t>Pinned by user</t>
   </si>
   <si>
@@ -703,603 +717,576 @@
     <t>Advanced containerized WildFly</t>
   </si>
   <si>
-    <t>Chad Green, Dan Jones</t>
+    <t>Modern Web</t>
+  </si>
+  <si>
+    <t>WildFly</t>
+  </si>
+  <si>
+    <t>S02</t>
+  </si>
+  <si>
+    <t>Learn virtualized Spring</t>
+  </si>
+  <si>
+    <t>Dan Jones, Elsa King</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Business analysts</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>S03</t>
+  </si>
+  <si>
+    <t>Intro to serverless Drools</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Programmers</t>
+  </si>
+  <si>
+    <t>Drools</t>
+  </si>
+  <si>
+    <t>S04</t>
+  </si>
+  <si>
+    <t>Discover AI-driven OptaPlanner</t>
+  </si>
+  <si>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>OptaPlanner</t>
+  </si>
+  <si>
+    <t>S05</t>
+  </si>
+  <si>
+    <t>Mastering machine learning jBPM</t>
+  </si>
+  <si>
+    <t>Hugo Rye, Ivy Smith</t>
+  </si>
+  <si>
+    <t>Big Data</t>
+  </si>
+  <si>
+    <t>jBPM</t>
+  </si>
+  <si>
+    <t>S06</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Camel</t>
+  </si>
+  <si>
+    <t>Jay Watt, Amy Fox, Beth Green</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>S07</t>
+  </si>
+  <si>
+    <t>Building deep learning XStream</t>
+  </si>
+  <si>
+    <t>Chad Jones, Dan King</t>
   </si>
   <si>
     <t>Middleware</t>
   </si>
   <si>
-    <t>Business analysts</t>
-  </si>
-  <si>
-    <t>WildFly</t>
-  </si>
-  <si>
-    <t>S02</t>
-  </si>
-  <si>
-    <t>Learn virtualized Spring</t>
-  </si>
-  <si>
-    <t>Elsa King, Flo Li</t>
-  </si>
-  <si>
-    <t>Security, Culture</t>
-  </si>
-  <si>
-    <t>Spring</t>
-  </si>
-  <si>
-    <t>S03</t>
-  </si>
-  <si>
-    <t>Intro to serverless Drools</t>
-  </si>
-  <si>
-    <t>Mobile, Cloud</t>
+    <t>XStream</t>
+  </si>
+  <si>
+    <t>S08</t>
+  </si>
+  <si>
+    <t>Securing scalable Docker</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
+    <t>S09</t>
+  </si>
+  <si>
+    <t>Debug enterprise Hibernate</t>
+  </si>
+  <si>
+    <t>Flo Poe, Gus Rye</t>
+  </si>
+  <si>
+    <t>Hibernate</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>Prepare for streaming GWT</t>
+  </si>
+  <si>
+    <t>GWT</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>Understand mobile Errai</t>
+  </si>
+  <si>
+    <t>Ivy Watt, Jay Cole</t>
+  </si>
+  <si>
+    <t>Errai</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>Applying modern Angular</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>Grok distributed Weld</t>
   </si>
   <si>
     <t>Transportation</t>
   </si>
   <si>
-    <t>Drools</t>
-  </si>
-  <si>
-    <t>S04</t>
-  </si>
-  <si>
-    <t>Discover AI-driven OptaPlanner</t>
-  </si>
-  <si>
-    <t>Hugo Rye, Ivy Smith</t>
-  </si>
-  <si>
-    <t>Cloud</t>
-  </si>
-  <si>
-    <t>Programmers</t>
-  </si>
-  <si>
-    <t>OptaPlanner</t>
-  </si>
-  <si>
-    <t>S05</t>
-  </si>
-  <si>
-    <t>Mastering machine learning jBPM</t>
+    <t>Weld</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable RestEasy</t>
+  </si>
+  <si>
+    <t>RestEasy</t>
+  </si>
+  <si>
+    <t>S15</t>
+  </si>
+  <si>
+    <t>Using secure Android</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>Deliver stable Tensorflow</t>
+  </si>
+  <si>
+    <t>Elsa Poe, Flo Rye, Gus Smith</t>
+  </si>
+  <si>
+    <t>Tensorflow</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>Implement platform-independent VertX</t>
+  </si>
+  <si>
+    <t>Hugo Watt, Ivy Cole</t>
+  </si>
+  <si>
+    <t>VertX</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>Program flexible JUnit</t>
+  </si>
+  <si>
+    <t>Big Data, Mobile</t>
+  </si>
+  <si>
+    <t>JUnit</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>Hack modularized Keycloak</t>
+  </si>
+  <si>
+    <t>Amy Jones, Beth King</t>
+  </si>
+  <si>
+    <t>Keycloak</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>Hands on real-time WildFly</t>
+  </si>
+  <si>
+    <t>Chad Li, Dan Poe</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>Advanced containerized Spring</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>Learn virtualized Drools</t>
+  </si>
+  <si>
+    <t>Flo Smith, Gus Watt</t>
+  </si>
+  <si>
+    <t>S23</t>
+  </si>
+  <si>
+    <t>Intro to serverless OptaPlanner</t>
+  </si>
+  <si>
+    <t>Cloud, Culture</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>Discover AI-driven jBPM</t>
+  </si>
+  <si>
+    <t>S25</t>
+  </si>
+  <si>
+    <t>Mastering machine learning Camel</t>
+  </si>
+  <si>
+    <t>S26</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven XStream</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>S27</t>
+  </si>
+  <si>
+    <t>Building deep learning Docker</t>
+  </si>
+  <si>
+    <t>Beth Li, Chad Poe</t>
+  </si>
+  <si>
+    <t>S28</t>
+  </si>
+  <si>
+    <t>Securing scalable Hibernate</t>
+  </si>
+  <si>
+    <t>Modern Web, Mobile</t>
+  </si>
+  <si>
+    <t>S29</t>
+  </si>
+  <si>
+    <t>Debug enterprise GWT</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>S30</t>
+  </si>
+  <si>
+    <t>Prepare for streaming Errai</t>
+  </si>
+  <si>
+    <t>S31</t>
+  </si>
+  <si>
+    <t>Understand mobile Angular</t>
+  </si>
+  <si>
+    <t>Gus Cole, Hugo Fox</t>
+  </si>
+  <si>
+    <t>S32</t>
+  </si>
+  <si>
+    <t>Applying modern Weld</t>
+  </si>
+  <si>
+    <t>Security, Mobile</t>
+  </si>
+  <si>
+    <t>S33</t>
+  </si>
+  <si>
+    <t>Grok distributed RestEasy</t>
+  </si>
+  <si>
+    <t>Telecommunications</t>
+  </si>
+  <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable Android</t>
+  </si>
+  <si>
+    <t>S35</t>
+  </si>
+  <si>
+    <t>Using secure Tensorflow</t>
+  </si>
+  <si>
+    <t>S36</t>
+  </si>
+  <si>
+    <t>Deliver stable VertX</t>
+  </si>
+  <si>
+    <t>S37</t>
+  </si>
+  <si>
+    <t>Implement platform-independent JUnit</t>
+  </si>
+  <si>
+    <t>S38</t>
+  </si>
+  <si>
+    <t>Program flexible Keycloak</t>
+  </si>
+  <si>
+    <t>S39</t>
+  </si>
+  <si>
+    <t>Hack modularized OpenShift</t>
+  </si>
+  <si>
+    <t>S40</t>
+  </si>
+  <si>
+    <t>Hands on real-time Spring</t>
   </si>
   <si>
     <t>Jay Watt, Amy Fox</t>
   </si>
   <si>
-    <t>jBPM</t>
-  </si>
-  <si>
-    <t>S06</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Camel</t>
-  </si>
-  <si>
-    <t>Beth Green, Chad Jones</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>Camel</t>
-  </si>
-  <si>
-    <t>S07</t>
-  </si>
-  <si>
-    <t>Building deep learning XStream</t>
-  </si>
-  <si>
-    <t>Dan King, Elsa Li, Flo Poe</t>
-  </si>
-  <si>
-    <t>Modern Web</t>
-  </si>
-  <si>
-    <t>XStream</t>
-  </si>
-  <si>
-    <t>S08</t>
-  </si>
-  <si>
-    <t>Securing scalable Docker</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>Docker, Kubernetes</t>
-  </si>
-  <si>
-    <t>S09</t>
-  </si>
-  <si>
-    <t>Debug enterprise Hibernate</t>
-  </si>
-  <si>
-    <t>Hibernate</t>
-  </si>
-  <si>
-    <t>S10</t>
-  </si>
-  <si>
-    <t>Prepare for streaming GWT</t>
-  </si>
-  <si>
-    <t>Ivy Watt, Jay Cole</t>
-  </si>
-  <si>
-    <t>Middleware, Cloud</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>GWT</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>Understand mobile Errai</t>
-  </si>
-  <si>
-    <t>Amy Green, Beth Jones</t>
-  </si>
-  <si>
-    <t>Errai</t>
-  </si>
-  <si>
-    <t>S12</t>
-  </si>
-  <si>
-    <t>Applying modern Angular</t>
-  </si>
-  <si>
-    <t>Chad King, Dan Li</t>
-  </si>
-  <si>
-    <t>Culture</t>
-  </si>
-  <si>
-    <t>Angular</t>
-  </si>
-  <si>
-    <t>S13</t>
-  </si>
-  <si>
-    <t>Grok distributed Weld</t>
+    <t>S41</t>
+  </si>
+  <si>
+    <t>Advanced containerized Drools</t>
+  </si>
+  <si>
+    <t>S42</t>
+  </si>
+  <si>
+    <t>Learn virtualized OptaPlanner</t>
+  </si>
+  <si>
+    <t>Financial services</t>
+  </si>
+  <si>
+    <t>S43</t>
+  </si>
+  <si>
+    <t>Intro to serverless jBPM</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Cloud</t>
+  </si>
+  <si>
+    <t>S44</t>
+  </si>
+  <si>
+    <t>Discover AI-driven Camel</t>
+  </si>
+  <si>
+    <t>Elsa Li, Flo Poe</t>
+  </si>
+  <si>
+    <t>Security, Modern Web</t>
+  </si>
+  <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>S45</t>
+  </si>
+  <si>
+    <t>Mastering machine learning XStream</t>
+  </si>
+  <si>
+    <t>S46</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Docker</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>S47</t>
+  </si>
+  <si>
+    <t>Building deep learning Hibernate</t>
+  </si>
+  <si>
+    <t>S48</t>
+  </si>
+  <si>
+    <t>Securing scalable GWT</t>
+  </si>
+  <si>
+    <t>S49</t>
+  </si>
+  <si>
+    <t>Debug enterprise Errai</t>
+  </si>
+  <si>
+    <t>S50</t>
+  </si>
+  <si>
+    <t>Prepare for streaming Angular</t>
+  </si>
+  <si>
+    <t>IoT, Mobile</t>
+  </si>
+  <si>
+    <t>S51</t>
+  </si>
+  <si>
+    <t>Understand mobile Weld</t>
+  </si>
+  <si>
+    <t>Cloud, Middleware</t>
+  </si>
+  <si>
+    <t>S52</t>
+  </si>
+  <si>
+    <t>Applying modern RestEasy</t>
+  </si>
+  <si>
+    <t>S53</t>
+  </si>
+  <si>
+    <t>Grok distributed Android</t>
   </si>
   <si>
     <t>Elsa Poe, Flo Rye</t>
   </si>
   <si>
-    <t>Weld</t>
-  </si>
-  <si>
-    <t>S14</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable RestEasy</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>RestEasy</t>
-  </si>
-  <si>
-    <t>S15</t>
-  </si>
-  <si>
-    <t>Using secure Android</t>
-  </si>
-  <si>
-    <t>Android</t>
-  </si>
-  <si>
-    <t>S16</t>
-  </si>
-  <si>
-    <t>Deliver stable Tensorflow</t>
-  </si>
-  <si>
-    <t>IoT, Big Data</t>
-  </si>
-  <si>
-    <t>Tensorflow</t>
-  </si>
-  <si>
-    <t>S17</t>
-  </si>
-  <si>
-    <t>Implement platform-independent VertX</t>
-  </si>
-  <si>
-    <t>Jay Fox, Amy Jones</t>
-  </si>
-  <si>
-    <t>VertX</t>
-  </si>
-  <si>
-    <t>S18</t>
-  </si>
-  <si>
-    <t>Program flexible JUnit</t>
-  </si>
-  <si>
-    <t>JUnit</t>
-  </si>
-  <si>
-    <t>S19</t>
-  </si>
-  <si>
-    <t>Hack modularized Keycloak</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Keycloak</t>
-  </si>
-  <si>
-    <t>S20</t>
-  </si>
-  <si>
-    <t>Hands on real-time WildFly</t>
-  </si>
-  <si>
-    <t>Dan Poe, Elsa Rye</t>
-  </si>
-  <si>
-    <t>S21</t>
-  </si>
-  <si>
-    <t>Advanced containerized Spring</t>
-  </si>
-  <si>
-    <t>Big Data, Mobile</t>
-  </si>
-  <si>
-    <t>S22</t>
-  </si>
-  <si>
-    <t>Learn virtualized Drools</t>
-  </si>
-  <si>
-    <t>Gus Watt, Hugo Cole</t>
+    <t>S54</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable Tensorflow</t>
+  </si>
+  <si>
+    <t>S55</t>
+  </si>
+  <si>
+    <t>Using secure VertX</t>
+  </si>
+  <si>
+    <t>S56</t>
+  </si>
+  <si>
+    <t>Deliver stable JUnit</t>
+  </si>
+  <si>
+    <t>S57</t>
+  </si>
+  <si>
+    <t>Implement platform-independent Keycloak</t>
+  </si>
+  <si>
+    <t>Security, Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>S58</t>
+  </si>
+  <si>
+    <t>Program flexible OpenShift</t>
+  </si>
+  <si>
+    <t>Beth King, Chad Li</t>
+  </si>
+  <si>
+    <t>S59</t>
+  </si>
+  <si>
+    <t>Hack modularized WildFly</t>
+  </si>
+  <si>
+    <t>S60</t>
+  </si>
+  <si>
+    <t>Hands on real-time Drools</t>
+  </si>
+  <si>
+    <t>S61</t>
+  </si>
+  <si>
+    <t>Advanced containerized OptaPlanner</t>
+  </si>
+  <si>
+    <t>S62</t>
+  </si>
+  <si>
+    <t>Learn virtualized jBPM</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Mobile</t>
+  </si>
+  <si>
+    <t>S63</t>
+  </si>
+  <si>
+    <t>Intro to serverless Camel</t>
+  </si>
+  <si>
+    <t>Hugo Cole, Ivy Fox</t>
+  </si>
+  <si>
+    <t>S64</t>
+  </si>
+  <si>
+    <t>Discover AI-driven XStream</t>
   </si>
   <si>
     <t>Big Data, Middleware</t>
   </si>
   <si>
-    <t>S23</t>
-  </si>
-  <si>
-    <t>Intro to serverless OptaPlanner</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>Discover AI-driven jBPM</t>
-  </si>
-  <si>
-    <t>S25</t>
-  </si>
-  <si>
-    <t>Mastering machine learning Camel</t>
-  </si>
-  <si>
-    <t>Big Data</t>
-  </si>
-  <si>
-    <t>S26</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven XStream</t>
-  </si>
-  <si>
-    <t>Beth Li, Chad Poe, Dan Rye, Elsa Smith</t>
-  </si>
-  <si>
-    <t>S27</t>
-  </si>
-  <si>
-    <t>Building deep learning Docker</t>
-  </si>
-  <si>
-    <t>Cloud, Culture</t>
-  </si>
-  <si>
-    <t>S28</t>
-  </si>
-  <si>
-    <t>Securing scalable Hibernate</t>
-  </si>
-  <si>
-    <t>S29</t>
-  </si>
-  <si>
-    <t>Debug enterprise GWT</t>
-  </si>
-  <si>
-    <t>Hugo Fox, Amy Cole</t>
-  </si>
-  <si>
-    <t>S30</t>
-  </si>
-  <si>
-    <t>Prepare for streaming Errai</t>
-  </si>
-  <si>
-    <t>S31</t>
-  </si>
-  <si>
-    <t>Understand mobile Angular</t>
-  </si>
-  <si>
-    <t>S32</t>
-  </si>
-  <si>
-    <t>Applying modern Weld</t>
-  </si>
-  <si>
-    <t>Middleware, Culture</t>
-  </si>
-  <si>
-    <t>S33</t>
-  </si>
-  <si>
-    <t>Grok distributed RestEasy</t>
-  </si>
-  <si>
-    <t>Modern Web, Mobile</t>
-  </si>
-  <si>
-    <t>S34</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable Android</t>
-  </si>
-  <si>
-    <t>S35</t>
-  </si>
-  <si>
-    <t>Using secure Tensorflow</t>
-  </si>
-  <si>
-    <t>Gus Poe, Hugo Rye</t>
-  </si>
-  <si>
-    <t>S36</t>
-  </si>
-  <si>
-    <t>Deliver stable VertX</t>
-  </si>
-  <si>
-    <t>S37</t>
-  </si>
-  <si>
-    <t>Implement platform-independent JUnit</t>
-  </si>
-  <si>
-    <t>S38</t>
-  </si>
-  <si>
-    <t>Program flexible Keycloak</t>
-  </si>
-  <si>
-    <t>Security, Mobile</t>
-  </si>
-  <si>
-    <t>S39</t>
-  </si>
-  <si>
-    <t>Hack modularized OpenShift</t>
-  </si>
-  <si>
-    <t>S40</t>
-  </si>
-  <si>
-    <t>Hands on real-time Spring</t>
-  </si>
-  <si>
-    <t>Dan King, Elsa Li, Flo Poe, Gus Rye</t>
-  </si>
-  <si>
-    <t>S41</t>
-  </si>
-  <si>
-    <t>Advanced containerized Drools</t>
-  </si>
-  <si>
-    <t>Hugo Smith, Ivy Watt</t>
-  </si>
-  <si>
-    <t>Big Data, IoT</t>
-  </si>
-  <si>
-    <t>S42</t>
-  </si>
-  <si>
-    <t>Learn virtualized OptaPlanner</t>
-  </si>
-  <si>
-    <t>Jay Cole, Amy Green</t>
-  </si>
-  <si>
-    <t>S43</t>
-  </si>
-  <si>
-    <t>Intro to serverless jBPM</t>
-  </si>
-  <si>
-    <t>Culture, Mobile</t>
-  </si>
-  <si>
-    <t>S44</t>
-  </si>
-  <si>
-    <t>Discover AI-driven Camel</t>
-  </si>
-  <si>
-    <t>Cloud, Middleware</t>
-  </si>
-  <si>
-    <t>S45</t>
-  </si>
-  <si>
-    <t>Mastering machine learning XStream</t>
-  </si>
-  <si>
-    <t>S46</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Docker</t>
-  </si>
-  <si>
-    <t>Docker</t>
-  </si>
-  <si>
-    <t>S47</t>
-  </si>
-  <si>
-    <t>Building deep learning Hibernate</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence, Middleware</t>
-  </si>
-  <si>
-    <t>S48</t>
-  </si>
-  <si>
-    <t>Securing scalable GWT</t>
-  </si>
-  <si>
-    <t>Hugo Watt, Ivy Cole</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
-    <t>S49</t>
-  </si>
-  <si>
-    <t>Debug enterprise Errai</t>
-  </si>
-  <si>
-    <t>S50</t>
-  </si>
-  <si>
-    <t>Prepare for streaming Angular</t>
-  </si>
-  <si>
-    <t>S51</t>
-  </si>
-  <si>
-    <t>Understand mobile Weld</t>
-  </si>
-  <si>
-    <t>S52</t>
-  </si>
-  <si>
-    <t>Applying modern RestEasy</t>
-  </si>
-  <si>
-    <t>Telecommunications</t>
-  </si>
-  <si>
-    <t>S53</t>
-  </si>
-  <si>
-    <t>Grok distributed Android</t>
-  </si>
-  <si>
-    <t>S54</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable Tensorflow</t>
-  </si>
-  <si>
-    <t>Elsa Rye, Flo Smith</t>
-  </si>
-  <si>
-    <t>S55</t>
-  </si>
-  <si>
-    <t>Using secure VertX</t>
-  </si>
-  <si>
-    <t>S56</t>
-  </si>
-  <si>
-    <t>Deliver stable JUnit</t>
-  </si>
-  <si>
-    <t>Hugo Cole, Ivy Fox</t>
-  </si>
-  <si>
-    <t>S57</t>
-  </si>
-  <si>
-    <t>Implement platform-independent Keycloak</t>
-  </si>
-  <si>
-    <t>S58</t>
-  </si>
-  <si>
-    <t>Program flexible OpenShift</t>
-  </si>
-  <si>
-    <t>OpenShift, Kubernetes</t>
-  </si>
-  <si>
-    <t>S59</t>
-  </si>
-  <si>
-    <t>Hack modularized WildFly</t>
-  </si>
-  <si>
-    <t>S60</t>
-  </si>
-  <si>
-    <t>Hands on real-time Drools</t>
-  </si>
-  <si>
-    <t>Chad Poe, Dan Rye</t>
-  </si>
-  <si>
-    <t>S61</t>
-  </si>
-  <si>
-    <t>Advanced containerized OptaPlanner</t>
-  </si>
-  <si>
-    <t>S62</t>
-  </si>
-  <si>
-    <t>Learn virtualized jBPM</t>
-  </si>
-  <si>
-    <t>S63</t>
-  </si>
-  <si>
-    <t>Intro to serverless Camel</t>
-  </si>
-  <si>
-    <t>S64</t>
-  </si>
-  <si>
-    <t>Discover AI-driven XStream</t>
-  </si>
-  <si>
     <t>S65</t>
   </si>
   <si>
@@ -1312,9 +1299,6 @@
     <t>Tuning IOT-driven Hibernate</t>
   </si>
   <si>
-    <t>Security, Artificial Intelligence</t>
-  </si>
-  <si>
     <t>S67</t>
   </si>
   <si>
@@ -1327,6 +1311,9 @@
     <t>Securing scalable Errai</t>
   </si>
   <si>
+    <t>Dan Rye, Elsa Smith</t>
+  </si>
+  <si>
     <t>S69</t>
   </si>
   <si>
@@ -1366,14 +1353,14 @@
     <t>Total</t>
   </si>
   <si>
-    <t>S70: Prepare for streaming Weld
-  Flo Li</t>
+    <t>S64: Discover AI-driven XStream
+  Jay Green</t>
   </si>
   <si>
     <t>Speaker</t>
   </si>
   <si>
-    <t>S70 @ R 1</t>
+    <t>S64 @ R 1</t>
   </si>
   <si>
     <t>Theme track tag</t>
@@ -1385,13 +1372,13 @@
     <t>Audience type</t>
   </si>
   <si>
-    <t>2</t>
+    <t>3</t>
   </si>
   <si>
     <t>Content tag</t>
   </si>
   <si>
-    <t>S70 (level 2)</t>
+    <t>S64 (level 3)</t>
   </si>
   <si>
     <t>Constraint match</t>
@@ -2026,7 +2013,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>84</v>
@@ -2141,7 +2128,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>84</v>
@@ -2182,13 +2169,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -2339,13 +2326,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -2455,7 +2442,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>84</v>
@@ -2496,13 +2483,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -2653,13 +2640,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -2692,10 +2679,10 @@
         <v>72</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -2725,13 +2712,13 @@
     <row r="1"/>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -6871,12 +6858,12 @@
     <col min="1" max="1" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.44140625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.78515625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="37.0234375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="31.55859375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="29.48828125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="28.52734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="20.05859375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="17.34375" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="16.3046875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="21.8046875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="14.55078125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="11.3046875" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="24.85546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="25.390625" customWidth="true" bestFit="true"/>
@@ -6888,11 +6875,13 @@
     <col min="18" max="18" width="22.84375" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="31.2734375" customWidth="true" bestFit="true"/>
     <col min="20" max="20" width="26.23046875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="16.65234375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.14453125" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="6.3984375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="6.32421875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="7.02734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="17.5390625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="20.140625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.65234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.14453125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="6.3984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="6.32421875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="7.02734375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6963,45 +6952,51 @@
         <v>172</v>
       </c>
       <c r="W1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>173</v>
+      <c r="AA1" s="1" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>72</v>
@@ -7033,43 +7028,49 @@
       <c r="T2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U2" s="2" t="b">
+      <c r="U2" s="2" t="n">
+        <v>166.0</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W2" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X2" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA2" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3.0</v>
@@ -7078,7 +7079,7 @@
         <v>186</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>72</v>
@@ -7110,19 +7111,25 @@
       <c r="T3" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U3" s="2" t="b">
+      <c r="U3" s="2" t="n">
+        <v>915.0</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W3" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X3" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA3" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7146,16 +7153,16 @@
         <v>72</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>72</v>
@@ -7187,52 +7194,58 @@
       <c r="T4" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U4" s="2" t="b">
+      <c r="U4" s="2" t="n">
+        <v>790.0</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X4" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA4" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>72</v>
@@ -7264,34 +7277,40 @@
       <c r="T5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U5" s="2" t="b">
+      <c r="U5" s="2" t="n">
+        <v>540.0</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X5" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA5" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>199</v>
+        <v>116</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>200</v>
@@ -7300,16 +7319,16 @@
         <v>72</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>72</v>
@@ -7341,43 +7360,49 @@
       <c r="T6" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U6" s="2" t="b">
+      <c r="U6" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W6" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X6" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA6" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="F7" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>2.0</v>
@@ -7386,7 +7411,7 @@
         <v>206</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>72</v>
@@ -7418,19 +7443,25 @@
       <c r="T7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U7" s="2" t="b">
+      <c r="U7" s="2" t="n">
+        <v>522.0</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W7" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA7" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7448,99 +7479,105 @@
         <v>209</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H8" s="2" t="n">
+      <c r="J8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>349.0</v>
+      </c>
+      <c r="V8" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U8" s="2" t="b">
+      <c r="W8" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X8" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA8" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="F9" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>72</v>
@@ -7572,120 +7609,132 @@
       <c r="T9" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U9" s="2" t="b">
+      <c r="U9" s="2" t="n">
+        <v>217.0</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W9" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X9" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA9" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="H10" s="2" t="n">
+      <c r="J10" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>802.0</v>
+      </c>
+      <c r="V10" s="2" t="n">
         <v>3.0</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U10" s="2" t="b">
+      <c r="W10" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X10" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA10" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>127</v>
+        <v>222</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1.0</v>
@@ -7694,7 +7743,7 @@
         <v>223</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>72</v>
@@ -7726,19 +7775,25 @@
       <c r="T11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U11" s="2" t="b">
+      <c r="U11" s="2" t="n">
+        <v>718.0</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W11" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X11" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA11" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -7753,25 +7808,25 @@
         <v>74</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="J12" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>72</v>
@@ -7803,52 +7858,58 @@
       <c r="T12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U12" s="2" t="b">
+      <c r="U12" s="2" t="n">
+        <v>348.0</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W12" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X12" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA12" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>72</v>
@@ -7880,52 +7941,58 @@
       <c r="T13" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U13" s="2" t="b">
+      <c r="U13" s="2" t="n">
+        <v>299.0</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W13" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X13" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA13" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>236</v>
+        <v>130</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>72</v>
@@ -7957,52 +8024,58 @@
       <c r="T14" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U14" s="2" t="b">
+      <c r="U14" s="2" t="n">
+        <v>529.0</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W14" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X14" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA14" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>241</v>
+        <v>131</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>72</v>
@@ -8034,52 +8107,58 @@
       <c r="T15" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U15" s="2" t="b">
+      <c r="U15" s="2" t="n">
+        <v>486.0</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W15" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W15" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X15" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA15" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>72</v>
@@ -8111,52 +8190,58 @@
       <c r="T16" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U16" s="2" t="b">
+      <c r="U16" s="2" t="n">
+        <v>295.0</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W16" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X16" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA16" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>72</v>
@@ -8188,52 +8273,58 @@
       <c r="T17" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U17" s="2" t="b">
+      <c r="U17" s="2" t="n">
+        <v>596.0</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W17" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V17" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W17" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X17" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA17" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>138</v>
+        <v>246</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>252</v>
+        <v>205</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>72</v>
@@ -8265,52 +8356,58 @@
       <c r="T18" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U18" s="2" t="b">
+      <c r="U18" s="2" t="n">
+        <v>313.0</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W18" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X18" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA18" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>72</v>
@@ -8342,52 +8439,58 @@
       <c r="T19" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U19" s="2" t="b">
+      <c r="U19" s="2" t="n">
+        <v>926.0</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W19" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V19" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W19" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X19" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA19" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>72</v>
@@ -8419,129 +8522,141 @@
       <c r="T20" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U20" s="2" t="b">
+      <c r="U20" s="2" t="n">
+        <v>550.0</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W20" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W20" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X20" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA20" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>143</v>
+        <v>258</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>263</v>
+        <v>72</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H21" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>466.0</v>
+      </c>
+      <c r="V21" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U21" s="2" t="b">
+      <c r="W21" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W21" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X21" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA21" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>186</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>72</v>
@@ -8573,52 +8688,58 @@
       <c r="T22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U22" s="2" t="b">
+      <c r="U22" s="2" t="n">
+        <v>274.0</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W22" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V22" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W22" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X22" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA22" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>270</v>
+        <v>214</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>72</v>
@@ -8650,52 +8771,58 @@
       <c r="T23" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U23" s="2" t="b">
+      <c r="U23" s="2" t="n">
+        <v>591.0</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W23" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W23" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X23" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA23" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>274</v>
+        <v>200</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>72</v>
@@ -8727,129 +8854,141 @@
       <c r="T24" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U24" s="2" t="b">
+      <c r="U24" s="2" t="n">
+        <v>130.0</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W24" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V24" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W24" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X24" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA24" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>184</v>
+        <v>270</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>72</v>
+        <v>236</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="H25" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>868.0</v>
+      </c>
+      <c r="V25" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U25" s="2" t="b">
+      <c r="W25" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W25" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X25" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA25" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>206</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>72</v>
@@ -8881,129 +9020,141 @@
       <c r="T26" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U26" s="2" t="b">
+      <c r="U26" s="2" t="n">
+        <v>560.0</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W26" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V26" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W26" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X26" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA26" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>281</v>
+        <v>214</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H27" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>454.0</v>
+      </c>
+      <c r="V27" s="2" t="n">
         <v>3.0</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U27" s="2" t="b">
+      <c r="W27" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W27" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X27" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA27" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>284</v>
+        <v>151</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>72</v>
@@ -9035,52 +9186,58 @@
       <c r="T28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U28" s="2" t="b">
+      <c r="U28" s="2" t="n">
+        <v>768.0</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W28" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V28" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W28" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X28" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA28" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>156</v>
+        <v>280</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>287</v>
+        <v>214</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>72</v>
@@ -9112,43 +9269,49 @@
       <c r="T29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U29" s="2" t="b">
+      <c r="U29" s="2" t="n">
+        <v>952.0</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W29" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X29" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA29" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>200</v>
+        <v>283</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>3.0</v>
@@ -9157,7 +9320,7 @@
         <v>223</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>72</v>
@@ -9189,129 +9352,141 @@
       <c r="T30" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U30" s="2" t="b">
+      <c r="U30" s="2" t="n">
+        <v>295.0</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W30" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X30" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA30" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>292</v>
+        <v>155</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>72</v>
+        <v>286</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="H31" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>926.0</v>
+      </c>
+      <c r="V31" s="2" t="n">
         <v>2.0</v>
       </c>
-      <c r="I31" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U31" s="2" t="b">
+      <c r="W31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W31" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X31" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA31" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>215</v>
+        <v>277</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>72</v>
@@ -9343,52 +9518,58 @@
       <c r="T32" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U32" s="2" t="b">
+      <c r="U32" s="2" t="n">
+        <v>135.0</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V32" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W32" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X32" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA32" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>112</v>
+        <v>291</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>281</v>
+        <v>185</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>72</v>
@@ -9420,52 +9601,58 @@
       <c r="T33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U33" s="2" t="b">
+      <c r="U33" s="2" t="n">
+        <v>454.0</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W33" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V33" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W33" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X33" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y33" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z33" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA33" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>72</v>
@@ -9497,52 +9684,58 @@
       <c r="T34" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U34" s="2" t="b">
+      <c r="U34" s="2" t="n">
+        <v>969.0</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W34" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V34" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W34" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X34" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA34" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>302</v>
+        <v>190</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>72</v>
+        <v>297</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>72</v>
@@ -9574,52 +9767,58 @@
       <c r="T35" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U35" s="2" t="b">
+      <c r="U35" s="2" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W35" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V35" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W35" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X35" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA35" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>245</v>
+        <v>190</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>72</v>
+        <v>297</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>72</v>
@@ -9651,52 +9850,58 @@
       <c r="T36" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U36" s="2" t="b">
+      <c r="U36" s="2" t="n">
+        <v>618.0</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W36" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V36" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W36" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X36" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA36" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>307</v>
+        <v>113</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>72</v>
@@ -9728,52 +9933,58 @@
       <c r="T37" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U37" s="2" t="b">
+      <c r="U37" s="2" t="n">
+        <v>506.0</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W37" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V37" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W37" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X37" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y37" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z37" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA37" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>177</v>
+        <v>277</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>72</v>
@@ -9805,52 +10016,58 @@
       <c r="T38" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U38" s="2" t="b">
+      <c r="U38" s="2" t="n">
+        <v>947.0</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W38" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y38" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA38" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>72</v>
@@ -9882,52 +10099,58 @@
       <c r="T39" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U39" s="2" t="b">
+      <c r="U39" s="2" t="n">
+        <v>428.0</v>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W39" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V39" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W39" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X39" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y39" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z39" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA39" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>314</v>
+        <v>190</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>72</v>
+        <v>297</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>72</v>
@@ -9959,52 +10182,58 @@
       <c r="T40" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U40" s="2" t="b">
+      <c r="U40" s="2" t="n">
+        <v>450.0</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W40" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V40" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W40" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X40" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y40" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z40" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA40" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>252</v>
+        <v>205</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>72</v>
@@ -10036,52 +10265,58 @@
       <c r="T41" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U41" s="2" t="b">
+      <c r="U41" s="2" t="n">
+        <v>707.0</v>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W41" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V41" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W41" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X41" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y41" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z41" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA41" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>72</v>
@@ -10113,52 +10348,58 @@
       <c r="T42" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U42" s="2" t="b">
+      <c r="U42" s="2" t="n">
+        <v>188.0</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W42" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V42" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W42" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X42" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA42" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>322</v>
+        <v>121</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>323</v>
+        <v>179</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>72</v>
@@ -10190,52 +10431,58 @@
       <c r="T43" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U43" s="2" t="b">
+      <c r="U43" s="2" t="n">
+        <v>454.0</v>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W43" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V43" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W43" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X43" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y43" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z43" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA43" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>326</v>
+        <v>122</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>72</v>
+        <v>317</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>72</v>
@@ -10267,43 +10514,49 @@
       <c r="T44" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U44" s="2" t="b">
+      <c r="U44" s="2" t="n">
+        <v>989.0</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W44" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V44" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W44" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X44" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA44" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>1.0</v>
@@ -10312,7 +10565,7 @@
         <v>206</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>72</v>
@@ -10344,52 +10597,58 @@
       <c r="T45" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U45" s="2" t="b">
+      <c r="U45" s="2" t="n">
+        <v>959.0</v>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W45" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V45" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W45" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X45" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y45" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z45" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA45" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>132</v>
+        <v>323</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>72</v>
+        <v>325</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>72</v>
@@ -10421,52 +10680,58 @@
       <c r="T46" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U46" s="2" t="b">
+      <c r="U46" s="2" t="n">
+        <v>995.0</v>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W46" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V46" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W46" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X46" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y46" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z46" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA46" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>332</v>
+        <v>179</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>72</v>
@@ -10498,52 +10763,58 @@
       <c r="T47" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U47" s="2" t="b">
+      <c r="U47" s="2" t="n">
+        <v>327.0</v>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W47" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V47" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W47" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X47" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y47" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z47" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA47" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>241</v>
+        <v>127</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>281</v>
+        <v>200</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>72</v>
+        <v>330</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>337</v>
+        <v>219</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>72</v>
@@ -10575,43 +10846,49 @@
       <c r="T48" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U48" s="2" t="b">
+      <c r="U48" s="2" t="n">
+        <v>864.0</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W48" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V48" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W48" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X48" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y48" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z48" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA48" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>340</v>
+        <v>195</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>2.0</v>
@@ -10620,7 +10897,7 @@
         <v>223</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>72</v>
@@ -10652,52 +10929,58 @@
       <c r="T49" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U49" s="2" t="b">
+      <c r="U49" s="2" t="n">
+        <v>277.0</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W49" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W49" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X49" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA49" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>343</v>
+        <v>129</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>344</v>
+        <v>72</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>72</v>
@@ -10729,129 +11012,141 @@
       <c r="T50" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U50" s="2" t="b">
+      <c r="U50" s="2" t="n">
+        <v>928.0</v>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W50" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V50" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W50" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X50" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y50" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z50" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA50" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>281</v>
+        <v>200</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H51" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U51" s="2" t="n">
+        <v>659.0</v>
+      </c>
+      <c r="V51" s="2" t="n">
         <v>2.0</v>
       </c>
-      <c r="I51" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U51" s="2" t="b">
+      <c r="W51" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W51" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X51" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA51" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>200</v>
+        <v>339</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>72</v>
@@ -10883,52 +11178,58 @@
       <c r="T52" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U52" s="2" t="b">
+      <c r="U52" s="2" t="n">
+        <v>402.0</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W52" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W52" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X52" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA52" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>219</v>
+        <v>342</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>72</v>
@@ -10960,52 +11261,58 @@
       <c r="T53" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U53" s="2" t="b">
+      <c r="U53" s="2" t="n">
+        <v>648.0</v>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W53" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V53" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W53" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X53" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA53" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>200</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>353</v>
+        <v>72</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>72</v>
@@ -11037,52 +11344,58 @@
       <c r="T54" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U54" s="2" t="b">
+      <c r="U54" s="2" t="n">
+        <v>900.0</v>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W54" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V54" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W54" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X54" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y54" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z54" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA54" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>144</v>
+        <v>347</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>72</v>
@@ -11114,129 +11427,141 @@
       <c r="T55" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U55" s="2" t="b">
+      <c r="U55" s="2" t="n">
+        <v>283.0</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W55" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W55" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X55" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA55" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>358</v>
+        <v>136</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H56" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U56" s="2" t="n">
+        <v>514.0</v>
+      </c>
+      <c r="V56" s="2" t="n">
         <v>2.0</v>
       </c>
-      <c r="I56" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U56" s="2" t="b">
+      <c r="W56" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W56" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X56" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA56" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>147</v>
+        <v>250</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>299</v>
+        <v>179</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>72</v>
@@ -11268,52 +11593,58 @@
       <c r="T57" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U57" s="2" t="b">
+      <c r="U57" s="2" t="n">
+        <v>601.0</v>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W57" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V57" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W57" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X57" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y57" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z57" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA57" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>363</v>
+        <v>139</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>219</v>
+        <v>277</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>72</v>
@@ -11345,52 +11676,58 @@
       <c r="T58" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U58" s="2" t="b">
+      <c r="U58" s="2" t="n">
+        <v>307.0</v>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W58" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V58" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W58" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X58" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y58" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z58" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA58" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>237</v>
+        <v>356</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>72</v>
@@ -11422,52 +11759,58 @@
       <c r="T59" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U59" s="2" t="b">
+      <c r="U59" s="2" t="n">
+        <v>525.0</v>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W59" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V59" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W59" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X59" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y59" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z59" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA59" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>151</v>
+        <v>359</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>368</v>
+        <v>181</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>72</v>
@@ -11499,52 +11842,58 @@
       <c r="T60" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U60" s="2" t="b">
+      <c r="U60" s="2" t="n">
+        <v>898.0</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W60" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V60" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W60" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X60" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA60" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>72</v>
+        <v>325</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>186</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>72</v>
@@ -11576,52 +11925,58 @@
       <c r="T61" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U61" s="2" t="b">
+      <c r="U61" s="2" t="n">
+        <v>621.0</v>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W61" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V61" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W61" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X61" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y61" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z61" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA61" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>373</v>
+        <v>145</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>72</v>
@@ -11653,52 +12008,58 @@
       <c r="T62" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U62" s="2" t="b">
+      <c r="U62" s="2" t="n">
+        <v>993.0</v>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W62" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V62" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W62" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X62" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y62" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z62" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA62" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>332</v>
+        <v>185</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>72</v>
@@ -11730,52 +12091,58 @@
       <c r="T63" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U63" s="2" t="b">
+      <c r="U63" s="2" t="n">
+        <v>404.0</v>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W63" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V63" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W63" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X63" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y63" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z63" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA63" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>245</v>
+        <v>368</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>206</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>72</v>
@@ -11807,52 +12174,58 @@
       <c r="T64" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U64" s="2" t="b">
+      <c r="U64" s="2" t="n">
+        <v>125.0</v>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W64" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V64" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W64" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X64" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y64" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z64" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA64" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>157</v>
+        <v>371</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>72</v>
@@ -11884,52 +12257,58 @@
       <c r="T65" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U65" s="2" t="b">
+      <c r="U65" s="2" t="n">
+        <v>591.0</v>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W65" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V65" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W65" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X65" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y65" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z65" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA65" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>210</v>
+        <v>374</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>72</v>
@@ -11961,52 +12340,58 @@
       <c r="T66" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U66" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V66" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W66" s="2" t="s">
-        <v>72</v>
+      <c r="U66" s="2" t="n">
+        <v>778.0</v>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W66" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
+      </c>
+      <c r="Z66" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA66" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>72</v>
@@ -12038,52 +12423,58 @@
       <c r="T67" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U67" s="2" t="b">
+      <c r="U67" s="2" t="n">
+        <v>552.0</v>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="W67" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V67" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W67" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X67" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y67" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z67" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA67" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>386</v>
+        <v>195</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>223</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>72</v>
@@ -12115,129 +12506,141 @@
       <c r="T68" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U68" s="2" t="b">
+      <c r="U68" s="2" t="n">
+        <v>658.0</v>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W68" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V68" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W68" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X68" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA68" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="H69" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U69" s="2" t="n">
+        <v>564.0</v>
+      </c>
+      <c r="V69" s="2" t="n">
         <v>3.0</v>
       </c>
-      <c r="I69" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J69" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U69" s="2" t="b">
+      <c r="W69" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W69" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X69" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA69" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>113</v>
+        <v>383</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>386</v>
+        <v>185</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>72</v>
@@ -12269,52 +12672,58 @@
       <c r="T70" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U70" s="2" t="b">
+      <c r="U70" s="2" t="n">
+        <v>357.0</v>
+      </c>
+      <c r="V70" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W70" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V70" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W70" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X70" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y70" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z70" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA70" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>72</v>
@@ -12346,52 +12755,58 @@
       <c r="T71" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U71" s="2" t="b">
+      <c r="U71" s="2" t="n">
+        <v>97.0</v>
+      </c>
+      <c r="V71" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="W71" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V71" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W71" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X71" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y71" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z71" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA71" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>72</v>
@@ -12423,96 +12838,108 @@
       <c r="T72" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U72" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="V72" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="W72" s="2" t="s">
-        <v>69</v>
+      <c r="U72" s="2" t="n">
+        <v>626.0</v>
+      </c>
+      <c r="V72" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W72" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="X72" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Y72" s="2" t="s">
-        <v>90</v>
+        <v>72</v>
+      </c>
+      <c r="Z72" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA72" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>307</v>
+        <v>158</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="H73" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U73" s="2" t="n">
+        <v>231.0</v>
+      </c>
+      <c r="V73" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="I73" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="J73" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="K73" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L73" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M73" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N73" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O73" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P73" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q73" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R73" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S73" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T73" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U73" s="2" t="b">
+      <c r="W73" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V73" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W73" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="X73" s="2" t="s">
         <v>72</v>
       </c>
       <c r="Y73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA73" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -12539,10 +12966,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2"/>
@@ -12551,16 +12978,16 @@
         <v>161</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4">
@@ -12600,7 +13027,7 @@
     <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>72.0</v>
@@ -12700,7 +13127,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>84</v>
@@ -12747,7 +13174,7 @@
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -13239,7 +13666,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>84</v>
@@ -13490,8 +13917,8 @@
       <c r="B8" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>406</v>
+      <c r="C8" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>72</v>
@@ -14884,8 +15311,8 @@
       <c r="B42" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>72</v>
+      <c r="C42" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>72</v>
@@ -15323,7 +15750,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>84</v>
@@ -15364,13 +15791,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>72</v>
@@ -15400,6 +15827,47 @@
         <v>72</v>
       </c>
       <c r="M3" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" ht="15.0" customHeight="true">
+      <c r="A4" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="M4" s="8" t="s">
         <v>72</v>
       </c>
     </row>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -25,6 +25,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t xml:space="preserve">S35: Using secure Tensorflow
+    Beth Fox
+PINNED BY USER
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -33,8 +51,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S64: Discover AI-driven XStream
-    Jay Green
+        <t xml:space="preserve">S35: Using secure Tensorflow
+    Beth Fox
 PINNED BY USER
 </t>
       </text>
@@ -51,8 +69,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S64: Discover AI-driven XStream
-    Jay Green
+        <t xml:space="preserve">S35: Using secure Tensorflow
+    Beth Fox
 PINNED BY USER
 </t>
       </text>
@@ -69,8 +87,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S64: Discover AI-driven XStream
-    Jay Green
+        <t xml:space="preserve">S35: Using secure Tensorflow
+    Beth Fox
 PINNED BY USER
 </t>
       </text>
@@ -87,8 +105,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S64: Discover AI-driven XStream
-    Jay Green
+        <t xml:space="preserve">S35: Using secure Tensorflow
+    Beth Fox
 PINNED BY USER
 </t>
       </text>
@@ -105,8 +123,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S64: Discover AI-driven XStream
-    Jay Green
+        <t xml:space="preserve">S35: Using secure Tensorflow
+    Beth Fox
 PINNED BY USER
 </t>
       </text>
@@ -121,10 +139,10 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="C42" authorId="0">
+    <comment ref="C4" authorId="0">
       <text>
-        <t xml:space="preserve">S64: Discover AI-driven XStream
-    Jay Green
+        <t xml:space="preserve">S35: Using secure Tensorflow
+    Beth Fox
 PINNED BY USER
 </t>
       </text>
@@ -141,16 +159,8 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S64: Discover AI-driven XStream
-    Jay Green
-PINNED BY USER
-</t>
-      </text>
-    </comment>
-    <comment ref="C4" authorId="0">
-      <text>
-        <t xml:space="preserve">S64: Discover AI-driven XStream
-    Jay Green
+        <t xml:space="preserve">S35: Using secure Tensorflow
+    Beth Fox
 PINNED BY USER
 </t>
       </text>
@@ -160,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4104" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4105" uniqueCount="409">
   <si>
     <t>Conference name</t>
   </si>
@@ -414,6 +424,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Capacity</t>
+  </si>
+  <si>
     <t>10:15-12:15</t>
   </si>
   <si>
@@ -444,12 +457,12 @@
     <t>R 3</t>
   </si>
   <si>
+    <t>R 4</t>
+  </si>
+  <si>
     <t>Recorded</t>
   </si>
   <si>
-    <t>R 4</t>
-  </si>
-  <si>
     <t>R 5</t>
   </si>
   <si>
@@ -585,12 +598,12 @@
     <t>Amy Jones</t>
   </si>
   <si>
+    <t>Large</t>
+  </si>
+  <si>
     <t>Beth King</t>
   </si>
   <si>
-    <t>Large</t>
-  </si>
-  <si>
     <t>Chad Li</t>
   </si>
   <si>
@@ -696,450 +709,450 @@
     <t>Hands on real-time OpenShift</t>
   </si>
   <si>
-    <t>Amy Cole, Beth Fox</t>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>Telecommunications</t>
+  </si>
+  <si>
+    <t>Business analysts</t>
+  </si>
+  <si>
+    <t>OpenShift, Kubernetes</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>S01</t>
+  </si>
+  <si>
+    <t>Advanced containerized WildFly</t>
+  </si>
+  <si>
+    <t>Beth Fox, Chad Green</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>WildFly</t>
+  </si>
+  <si>
+    <t>S02</t>
+  </si>
+  <si>
+    <t>Learn virtualized Spring</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Programmers</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>S03</t>
+  </si>
+  <si>
+    <t>Intro to serverless Drools</t>
+  </si>
+  <si>
+    <t>Drools</t>
+  </si>
+  <si>
+    <t>S04</t>
+  </si>
+  <si>
+    <t>Discover AI-driven OptaPlanner</t>
+  </si>
+  <si>
+    <t>Flo Li, Gus Poe</t>
+  </si>
+  <si>
+    <t>Big Data</t>
+  </si>
+  <si>
+    <t>Managers</t>
+  </si>
+  <si>
+    <t>OptaPlanner</t>
+  </si>
+  <si>
+    <t>S05</t>
+  </si>
+  <si>
+    <t>Mastering machine learning jBPM</t>
+  </si>
+  <si>
+    <t>Hugo Rye, Ivy Smith, Jay Watt</t>
+  </si>
+  <si>
+    <t>Modern Web</t>
+  </si>
+  <si>
+    <t>jBPM</t>
+  </si>
+  <si>
+    <t>S06</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Camel</t>
+  </si>
+  <si>
+    <t>Amy Fox, Beth Green</t>
+  </si>
+  <si>
+    <t>Middleware</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>S07</t>
+  </si>
+  <si>
+    <t>Building deep learning XStream</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>XStream</t>
+  </si>
+  <si>
+    <t>S08</t>
+  </si>
+  <si>
+    <t>Securing scalable Docker</t>
+  </si>
+  <si>
+    <t>Culture, Security</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
+    <t>S09</t>
+  </si>
+  <si>
+    <t>Debug enterprise Hibernate</t>
+  </si>
+  <si>
+    <t>Elsa Li, Flo Poe</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Culture</t>
+  </si>
+  <si>
+    <t>Hibernate</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>Prepare for streaming GWT</t>
+  </si>
+  <si>
+    <t>Gus Rye, Hugo Smith</t>
+  </si>
+  <si>
+    <t>GWT</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>Understand mobile Errai</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Errai</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>Applying modern Angular</t>
+  </si>
+  <si>
+    <t>Jay Cole, Amy Green</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>Grok distributed Weld</t>
+  </si>
+  <si>
+    <t>Beth Jones, Chad King</t>
+  </si>
+  <si>
+    <t>Weld</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable RestEasy</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>RestEasy</t>
+  </si>
+  <si>
+    <t>S15</t>
+  </si>
+  <si>
+    <t>Using secure Android</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>Deliver stable Tensorflow</t>
+  </si>
+  <si>
+    <t>Flo Rye, Gus Smith</t>
+  </si>
+  <si>
+    <t>Security, Mobile</t>
+  </si>
+  <si>
+    <t>Tensorflow</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>Implement platform-independent VertX</t>
+  </si>
+  <si>
+    <t>VertX</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>Program flexible JUnit</t>
+  </si>
+  <si>
+    <t>JUnit</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>Hack modularized Keycloak</t>
   </si>
   <si>
     <t>IoT</t>
   </si>
   <si>
-    <t>Managers</t>
+    <t>Keycloak</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>Hands on real-time WildFly</t>
+  </si>
+  <si>
+    <t>Amy Jones, Beth King</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>Advanced containerized Spring</t>
+  </si>
+  <si>
+    <t>Chad Li, Dan Poe</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>Learn virtualized Drools</t>
+  </si>
+  <si>
+    <t>Elsa Rye, Flo Smith</t>
+  </si>
+  <si>
+    <t>S23</t>
+  </si>
+  <si>
+    <t>Intro to serverless OptaPlanner</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>Discover AI-driven jBPM</t>
+  </si>
+  <si>
+    <t>S25</t>
+  </si>
+  <si>
+    <t>Mastering machine learning Camel</t>
+  </si>
+  <si>
+    <t>S26</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven XStream</t>
+  </si>
+  <si>
+    <t>Middleware, Culture</t>
+  </si>
+  <si>
+    <t>S27</t>
+  </si>
+  <si>
+    <t>Building deep learning Docker</t>
+  </si>
+  <si>
+    <t>Amy King, Beth Li</t>
+  </si>
+  <si>
+    <t>Docker, Kubernetes</t>
+  </si>
+  <si>
+    <t>S28</t>
+  </si>
+  <si>
+    <t>Securing scalable Hibernate</t>
+  </si>
+  <si>
+    <t>S29</t>
+  </si>
+  <si>
+    <t>Debug enterprise GWT</t>
+  </si>
+  <si>
+    <t>S30</t>
+  </si>
+  <si>
+    <t>Prepare for streaming Errai</t>
+  </si>
+  <si>
+    <t>S31</t>
+  </si>
+  <si>
+    <t>Understand mobile Angular</t>
+  </si>
+  <si>
+    <t>Mobile, Culture</t>
+  </si>
+  <si>
+    <t>S32</t>
+  </si>
+  <si>
+    <t>Applying modern Weld</t>
+  </si>
+  <si>
+    <t>Modern Web, Middleware</t>
+  </si>
+  <si>
+    <t>S33</t>
+  </si>
+  <si>
+    <t>Grok distributed RestEasy</t>
+  </si>
+  <si>
+    <t>Modern Web, Cloud</t>
+  </si>
+  <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable Android</t>
+  </si>
+  <si>
+    <t>S35</t>
+  </si>
+  <si>
+    <t>Using secure Tensorflow</t>
+  </si>
+  <si>
+    <t>S36</t>
+  </si>
+  <si>
+    <t>Deliver stable VertX</t>
+  </si>
+  <si>
+    <t>Cloud, Middleware</t>
+  </si>
+  <si>
+    <t>S37</t>
+  </si>
+  <si>
+    <t>Implement platform-independent JUnit</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>S38</t>
+  </si>
+  <si>
+    <t>Program flexible Keycloak</t>
+  </si>
+  <si>
+    <t>S39</t>
+  </si>
+  <si>
+    <t>Hack modularized OpenShift</t>
   </si>
   <si>
     <t>OpenShift</t>
   </si>
   <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>S01</t>
-  </si>
-  <si>
-    <t>Advanced containerized WildFly</t>
-  </si>
-  <si>
-    <t>Modern Web</t>
-  </si>
-  <si>
-    <t>WildFly</t>
-  </si>
-  <si>
-    <t>S02</t>
-  </si>
-  <si>
-    <t>Learn virtualized Spring</t>
-  </si>
-  <si>
-    <t>Dan Jones, Elsa King</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>Business analysts</t>
-  </si>
-  <si>
-    <t>Spring</t>
-  </si>
-  <si>
-    <t>S03</t>
-  </si>
-  <si>
-    <t>Intro to serverless Drools</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Programmers</t>
-  </si>
-  <si>
-    <t>Drools</t>
-  </si>
-  <si>
-    <t>S04</t>
-  </si>
-  <si>
-    <t>Discover AI-driven OptaPlanner</t>
-  </si>
-  <si>
-    <t>Culture</t>
-  </si>
-  <si>
-    <t>OptaPlanner</t>
-  </si>
-  <si>
-    <t>S05</t>
-  </si>
-  <si>
-    <t>Mastering machine learning jBPM</t>
-  </si>
-  <si>
-    <t>Hugo Rye, Ivy Smith</t>
-  </si>
-  <si>
-    <t>Big Data</t>
-  </si>
-  <si>
-    <t>jBPM</t>
-  </si>
-  <si>
-    <t>S06</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Camel</t>
-  </si>
-  <si>
-    <t>Jay Watt, Amy Fox, Beth Green</t>
-  </si>
-  <si>
-    <t>Camel</t>
-  </si>
-  <si>
-    <t>S07</t>
-  </si>
-  <si>
-    <t>Building deep learning XStream</t>
-  </si>
-  <si>
-    <t>Chad Jones, Dan King</t>
-  </si>
-  <si>
-    <t>Middleware</t>
-  </si>
-  <si>
-    <t>XStream</t>
-  </si>
-  <si>
-    <t>S08</t>
-  </si>
-  <si>
-    <t>Securing scalable Docker</t>
-  </si>
-  <si>
-    <t>Cloud</t>
-  </si>
-  <si>
-    <t>Docker</t>
-  </si>
-  <si>
-    <t>S09</t>
-  </si>
-  <si>
-    <t>Debug enterprise Hibernate</t>
-  </si>
-  <si>
-    <t>Flo Poe, Gus Rye</t>
-  </si>
-  <si>
-    <t>Hibernate</t>
-  </si>
-  <si>
-    <t>S10</t>
-  </si>
-  <si>
-    <t>Prepare for streaming GWT</t>
-  </si>
-  <si>
-    <t>GWT</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>Understand mobile Errai</t>
-  </si>
-  <si>
-    <t>Ivy Watt, Jay Cole</t>
-  </si>
-  <si>
-    <t>Errai</t>
-  </si>
-  <si>
-    <t>S12</t>
-  </si>
-  <si>
-    <t>Applying modern Angular</t>
-  </si>
-  <si>
-    <t>Angular</t>
-  </si>
-  <si>
-    <t>S13</t>
-  </si>
-  <si>
-    <t>Grok distributed Weld</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>Weld</t>
-  </si>
-  <si>
-    <t>S14</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable RestEasy</t>
-  </si>
-  <si>
-    <t>RestEasy</t>
-  </si>
-  <si>
-    <t>S15</t>
-  </si>
-  <si>
-    <t>Using secure Android</t>
-  </si>
-  <si>
-    <t>Android</t>
-  </si>
-  <si>
-    <t>S16</t>
-  </si>
-  <si>
-    <t>Deliver stable Tensorflow</t>
-  </si>
-  <si>
-    <t>Elsa Poe, Flo Rye, Gus Smith</t>
-  </si>
-  <si>
-    <t>Tensorflow</t>
-  </si>
-  <si>
-    <t>S17</t>
-  </si>
-  <si>
-    <t>Implement platform-independent VertX</t>
-  </si>
-  <si>
-    <t>Hugo Watt, Ivy Cole</t>
-  </si>
-  <si>
-    <t>VertX</t>
-  </si>
-  <si>
-    <t>S18</t>
-  </si>
-  <si>
-    <t>Program flexible JUnit</t>
-  </si>
-  <si>
-    <t>Big Data, Mobile</t>
-  </si>
-  <si>
-    <t>JUnit</t>
-  </si>
-  <si>
-    <t>S19</t>
-  </si>
-  <si>
-    <t>Hack modularized Keycloak</t>
-  </si>
-  <si>
-    <t>Amy Jones, Beth King</t>
-  </si>
-  <si>
-    <t>Keycloak</t>
-  </si>
-  <si>
-    <t>S20</t>
-  </si>
-  <si>
-    <t>Hands on real-time WildFly</t>
-  </si>
-  <si>
-    <t>Chad Li, Dan Poe</t>
-  </si>
-  <si>
-    <t>S21</t>
-  </si>
-  <si>
-    <t>Advanced containerized Spring</t>
-  </si>
-  <si>
-    <t>S22</t>
-  </si>
-  <si>
-    <t>Learn virtualized Drools</t>
-  </si>
-  <si>
-    <t>Flo Smith, Gus Watt</t>
-  </si>
-  <si>
-    <t>S23</t>
-  </si>
-  <si>
-    <t>Intro to serverless OptaPlanner</t>
-  </si>
-  <si>
-    <t>Cloud, Culture</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>Discover AI-driven jBPM</t>
-  </si>
-  <si>
-    <t>S25</t>
-  </si>
-  <si>
-    <t>Mastering machine learning Camel</t>
-  </si>
-  <si>
-    <t>S26</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven XStream</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>S27</t>
-  </si>
-  <si>
-    <t>Building deep learning Docker</t>
-  </si>
-  <si>
-    <t>Beth Li, Chad Poe</t>
-  </si>
-  <si>
-    <t>S28</t>
-  </si>
-  <si>
-    <t>Securing scalable Hibernate</t>
-  </si>
-  <si>
-    <t>Modern Web, Mobile</t>
-  </si>
-  <si>
-    <t>S29</t>
-  </si>
-  <si>
-    <t>Debug enterprise GWT</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>S30</t>
-  </si>
-  <si>
-    <t>Prepare for streaming Errai</t>
-  </si>
-  <si>
-    <t>S31</t>
-  </si>
-  <si>
-    <t>Understand mobile Angular</t>
-  </si>
-  <si>
-    <t>Gus Cole, Hugo Fox</t>
-  </si>
-  <si>
-    <t>S32</t>
-  </si>
-  <si>
-    <t>Applying modern Weld</t>
-  </si>
-  <si>
-    <t>Security, Mobile</t>
-  </si>
-  <si>
-    <t>S33</t>
-  </si>
-  <si>
-    <t>Grok distributed RestEasy</t>
-  </si>
-  <si>
-    <t>Telecommunications</t>
-  </si>
-  <si>
-    <t>S34</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable Android</t>
-  </si>
-  <si>
-    <t>S35</t>
-  </si>
-  <si>
-    <t>Using secure Tensorflow</t>
-  </si>
-  <si>
-    <t>S36</t>
-  </si>
-  <si>
-    <t>Deliver stable VertX</t>
-  </si>
-  <si>
-    <t>S37</t>
-  </si>
-  <si>
-    <t>Implement platform-independent JUnit</t>
-  </si>
-  <si>
-    <t>S38</t>
-  </si>
-  <si>
-    <t>Program flexible Keycloak</t>
-  </si>
-  <si>
-    <t>S39</t>
-  </si>
-  <si>
-    <t>Hack modularized OpenShift</t>
-  </si>
-  <si>
     <t>S40</t>
   </si>
   <si>
     <t>Hands on real-time Spring</t>
   </si>
   <si>
+    <t>S41</t>
+  </si>
+  <si>
+    <t>Advanced containerized Drools</t>
+  </si>
+  <si>
+    <t>S42</t>
+  </si>
+  <si>
+    <t>Learn virtualized OptaPlanner</t>
+  </si>
+  <si>
     <t>Jay Watt, Amy Fox</t>
   </si>
   <si>
-    <t>S41</t>
-  </si>
-  <si>
-    <t>Advanced containerized Drools</t>
-  </si>
-  <si>
-    <t>S42</t>
-  </si>
-  <si>
-    <t>Learn virtualized OptaPlanner</t>
-  </si>
-  <si>
-    <t>Financial services</t>
-  </si>
-  <si>
     <t>S43</t>
   </si>
   <si>
     <t>Intro to serverless jBPM</t>
   </si>
   <si>
-    <t>Artificial Intelligence, Cloud</t>
-  </si>
-  <si>
     <t>S44</t>
   </si>
   <si>
     <t>Discover AI-driven Camel</t>
   </si>
   <si>
-    <t>Elsa Li, Flo Poe</t>
-  </si>
-  <si>
-    <t>Security, Modern Web</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
     <t>S45</t>
   </si>
   <si>
@@ -1152,9 +1165,6 @@
     <t>Tuning IOT-driven Docker</t>
   </si>
   <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
     <t>S47</t>
   </si>
   <si>
@@ -1173,24 +1183,21 @@
     <t>Debug enterprise Errai</t>
   </si>
   <si>
+    <t>IoT, Mobile</t>
+  </si>
+  <si>
     <t>S50</t>
   </si>
   <si>
     <t>Prepare for streaming Angular</t>
   </si>
   <si>
-    <t>IoT, Mobile</t>
-  </si>
-  <si>
     <t>S51</t>
   </si>
   <si>
     <t>Understand mobile Weld</t>
   </si>
   <si>
-    <t>Cloud, Middleware</t>
-  </si>
-  <si>
     <t>S52</t>
   </si>
   <si>
@@ -1203,15 +1210,15 @@
     <t>Grok distributed Android</t>
   </si>
   <si>
+    <t>S54</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable Tensorflow</t>
+  </si>
+  <si>
     <t>Elsa Poe, Flo Rye</t>
   </si>
   <si>
-    <t>S54</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable Tensorflow</t>
-  </si>
-  <si>
     <t>S55</t>
   </si>
   <si>
@@ -1224,13 +1231,16 @@
     <t>Deliver stable JUnit</t>
   </si>
   <si>
+    <t>Security, Artificial Intelligence</t>
+  </si>
+  <si>
     <t>S57</t>
   </si>
   <si>
     <t>Implement platform-independent Keycloak</t>
   </si>
   <si>
-    <t>Security, Artificial Intelligence</t>
+    <t>Ivy Cole, Jay Fox</t>
   </si>
   <si>
     <t>S58</t>
@@ -1239,7 +1249,7 @@
     <t>Program flexible OpenShift</t>
   </si>
   <si>
-    <t>Beth King, Chad Li</t>
+    <t>Amy Jones, Beth King, Chad Li</t>
   </si>
   <si>
     <t>S59</t>
@@ -1260,13 +1270,16 @@
     <t>Advanced containerized OptaPlanner</t>
   </si>
   <si>
+    <t>Artificial Intelligence, Mobile</t>
+  </si>
+  <si>
     <t>S62</t>
   </si>
   <si>
     <t>Learn virtualized jBPM</t>
   </si>
   <si>
-    <t>Artificial Intelligence, Mobile</t>
+    <t>Gus Watt, Hugo Cole</t>
   </si>
   <si>
     <t>S63</t>
@@ -1275,7 +1288,7 @@
     <t>Intro to serverless Camel</t>
   </si>
   <si>
-    <t>Hugo Cole, Ivy Fox</t>
+    <t>Big Data, Middleware</t>
   </si>
   <si>
     <t>S64</t>
@@ -1284,9 +1297,6 @@
     <t>Discover AI-driven XStream</t>
   </si>
   <si>
-    <t>Big Data, Middleware</t>
-  </si>
-  <si>
     <t>S65</t>
   </si>
   <si>
@@ -1305,15 +1315,15 @@
     <t>Building deep learning GWT</t>
   </si>
   <si>
+    <t>Chad Poe, Dan Rye</t>
+  </si>
+  <si>
     <t>S68</t>
   </si>
   <si>
     <t>Securing scalable Errai</t>
   </si>
   <si>
-    <t>Dan Rye, Elsa Smith</t>
-  </si>
-  <si>
     <t>S69</t>
   </si>
   <si>
@@ -1353,14 +1363,14 @@
     <t>Total</t>
   </si>
   <si>
-    <t>S64: Discover AI-driven XStream
-  Jay Green</t>
+    <t>S35: Using secure Tensorflow
+  Beth Fox</t>
   </si>
   <si>
     <t>Speaker</t>
   </si>
   <si>
-    <t>S64 @ R 1</t>
+    <t>S35 @ R 1</t>
   </si>
   <si>
     <t>Theme track tag</t>
@@ -1378,7 +1388,7 @@
     <t>Content tag</t>
   </si>
   <si>
-    <t>S64 (level 3)</t>
+    <t>S35 (level 3)</t>
   </si>
   <si>
     <t>Constraint match</t>
@@ -1955,7 +1965,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.94140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.6328125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
@@ -2016,40 +2026,81 @@
         <v>401</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" ht="15.0" customHeight="true">
+      <c r="A3" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2059,6 +2110,7 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2070,7 +2122,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="15.99609375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="19.640625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
@@ -2131,45 +2183,45 @@
         <v>402</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
@@ -2285,43 +2337,43 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
@@ -2445,45 +2497,45 @@
         <v>404</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
@@ -2599,48 +2651,48 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
@@ -2972,9 +3024,9 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.87890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.140625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="10.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.87890625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="16.140625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="13.6171875" customWidth="true" bestFit="true"/>
@@ -2986,6 +3038,7 @@
     <col min="13" max="13" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="13.6171875" customWidth="true" bestFit="true"/>
     <col min="15" max="15" width="13.6171875" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="13.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3040,13 +3093,13 @@
         <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>85</v>
@@ -3064,7 +3117,7 @@
         <v>89</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>85</v>
@@ -3081,19 +3134,22 @@
       <c r="O2" s="1" t="s">
         <v>89</v>
       </c>
+      <c r="P2" s="1" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>72</v>
@@ -3126,19 +3182,22 @@
         <v>72</v>
       </c>
       <c r="O3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="D4" s="2" t="s">
         <v>72</v>
       </c>
@@ -3173,21 +3232,24 @@
         <v>72</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>630.0</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>72</v>
@@ -3220,6 +3282,9 @@
         <v>72</v>
       </c>
       <c r="O5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3227,14 +3292,14 @@
       <c r="A6" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="2" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>72</v>
@@ -3267,21 +3332,24 @@
         <v>72</v>
       </c>
       <c r="O6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>490.0</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>72</v>
@@ -3314,19 +3382,22 @@
         <v>72</v>
       </c>
       <c r="O7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>320.0</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="D8" s="2" t="s">
         <v>72</v>
       </c>
@@ -3361,21 +3432,24 @@
         <v>72</v>
       </c>
       <c r="O8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>410.0</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>72</v>
@@ -3408,19 +3482,22 @@
         <v>72</v>
       </c>
       <c r="O9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>360.0</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="D10" s="2" t="s">
         <v>72</v>
       </c>
@@ -3455,19 +3532,22 @@
         <v>72</v>
       </c>
       <c r="O10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P10" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>160.0</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="D11" s="2" t="s">
         <v>72</v>
       </c>
@@ -3502,21 +3582,24 @@
         <v>72</v>
       </c>
       <c r="O11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>750.0</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>72</v>
@@ -3549,6 +3632,9 @@
         <v>72</v>
       </c>
       <c r="O12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3660,69 +3746,69 @@
         <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="U2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>72</v>
@@ -3740,7 +3826,7 @@
         <v>72</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>72</v>
@@ -3787,7 +3873,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>72</v>
@@ -3852,7 +3938,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>72</v>
@@ -3917,7 +4003,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>72</v>
@@ -3935,7 +4021,7 @@
         <v>72</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>72</v>
@@ -3982,7 +4068,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>72</v>
@@ -4000,7 +4086,7 @@
         <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>72</v>
@@ -4047,7 +4133,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>72</v>
@@ -4073,13 +4159,13 @@
       <c r="I8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L8" s="2" t="s">
+      <c r="J8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>72</v>
       </c>
       <c r="M8" s="2" t="s">
@@ -4091,13 +4177,13 @@
       <c r="O8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R8" s="2" t="s">
+      <c r="P8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="R8" s="3" t="s">
         <v>72</v>
       </c>
       <c r="S8" s="2" t="s">
@@ -4112,7 +4198,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>72</v>
@@ -4130,7 +4216,7 @@
         <v>72</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>72</v>
@@ -4138,13 +4224,13 @@
       <c r="I9" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="3" t="s">
+      <c r="J9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>72</v>
       </c>
       <c r="M9" s="2" t="s">
@@ -4156,13 +4242,13 @@
       <c r="O9" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="R9" s="3" t="s">
+      <c r="P9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>72</v>
       </c>
       <c r="S9" s="2" t="s">
@@ -4177,7 +4263,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>72</v>
@@ -4195,7 +4281,7 @@
         <v>72</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>72</v>
@@ -4242,7 +4328,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>72</v>
@@ -4307,7 +4393,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>72</v>
@@ -4372,7 +4458,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>72</v>
@@ -4437,7 +4523,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>72</v>
@@ -4502,7 +4588,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>72</v>
@@ -4567,7 +4653,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>72</v>
@@ -4632,7 +4718,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>72</v>
@@ -4697,7 +4783,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>72</v>
@@ -4762,7 +4848,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>72</v>
@@ -4794,16 +4880,16 @@
       <c r="K19" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="L19" s="3" t="s">
         <v>72</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="N19" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O19" s="2" t="s">
+      <c r="N19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>72</v>
       </c>
       <c r="P19" s="2" t="s">
@@ -4827,7 +4913,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>72</v>
@@ -4856,19 +4942,19 @@
       <c r="J20" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L20" s="3" t="s">
+      <c r="K20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L20" s="2" t="s">
         <v>72</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="O20" s="3" t="s">
+      <c r="N20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O20" s="2" t="s">
         <v>72</v>
       </c>
       <c r="P20" s="2" t="s">
@@ -4892,7 +4978,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>72</v>
@@ -4921,7 +5007,7 @@
       <c r="J21" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="K21" s="2" t="s">
         <v>72</v>
       </c>
       <c r="L21" s="2" t="s">
@@ -4957,7 +5043,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>72</v>
@@ -5022,7 +5108,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>72</v>
@@ -5087,7 +5173,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>72</v>
@@ -5152,7 +5238,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>72</v>
@@ -5217,7 +5303,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>72</v>
@@ -5282,7 +5368,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>72</v>
@@ -5347,7 +5433,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>72</v>
@@ -5412,7 +5498,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>72</v>
@@ -5477,7 +5563,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>72</v>
@@ -5542,7 +5628,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>72</v>
@@ -5607,7 +5693,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>72</v>
@@ -5672,7 +5758,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>72</v>
@@ -5687,7 +5773,7 @@
         <v>72</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>72</v>
@@ -5737,7 +5823,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>72</v>
@@ -5752,7 +5838,7 @@
         <v>72</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>72</v>
@@ -5763,7 +5849,7 @@
       <c r="I34" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="J34" s="3" t="s">
         <v>72</v>
       </c>
       <c r="K34" s="2" t="s">
@@ -5802,7 +5888,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>72</v>
@@ -5828,7 +5914,7 @@
       <c r="I35" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="J35" s="2" t="s">
         <v>72</v>
       </c>
       <c r="K35" s="2" t="s">
@@ -5867,7 +5953,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>72</v>
@@ -5932,7 +6018,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>72</v>
@@ -5997,7 +6083,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>72</v>
@@ -6062,7 +6148,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>72</v>
@@ -6127,7 +6213,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>72</v>
@@ -6192,7 +6278,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>72</v>
@@ -6257,7 +6343,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>72</v>
@@ -6322,7 +6408,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>72</v>
@@ -6357,13 +6443,13 @@
       <c r="L43" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M43" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O43" s="2" t="s">
+      <c r="M43" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O43" s="3" t="s">
         <v>72</v>
       </c>
       <c r="P43" s="2" t="s">
@@ -6375,19 +6461,19 @@
       <c r="R43" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="S43" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T43" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U43" s="2" t="s">
+      <c r="S43" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="U43" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>72</v>
@@ -6422,13 +6508,13 @@
       <c r="L44" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="O44" s="3" t="s">
+      <c r="M44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O44" s="2" t="s">
         <v>72</v>
       </c>
       <c r="P44" s="2" t="s">
@@ -6440,19 +6526,19 @@
       <c r="R44" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="U44" s="3" t="s">
+      <c r="S44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U44" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>72</v>
@@ -6517,7 +6603,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>72</v>
@@ -6535,7 +6621,7 @@
         <v>72</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>72</v>
@@ -6582,7 +6668,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>72</v>
@@ -6600,7 +6686,7 @@
         <v>72</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>72</v>
@@ -6647,7 +6733,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>72</v>
@@ -6682,13 +6768,13 @@
       <c r="L48" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M48" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O48" s="2" t="s">
+      <c r="M48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O48" s="3" t="s">
         <v>72</v>
       </c>
       <c r="P48" s="2" t="s">
@@ -6700,19 +6786,19 @@
       <c r="R48" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="S48" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T48" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U48" s="2" t="s">
+      <c r="S48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="U48" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>72</v>
@@ -6747,13 +6833,13 @@
       <c r="L49" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="O49" s="3" t="s">
+      <c r="M49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O49" s="2" t="s">
         <v>72</v>
       </c>
       <c r="P49" s="2" t="s">
@@ -6765,19 +6851,19 @@
       <c r="R49" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="U49" s="3" t="s">
+      <c r="S49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U49" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>72</v>
@@ -6858,12 +6944,12 @@
     <col min="1" max="1" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.44140625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.78515625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="29.48828125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="28.71875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="28.52734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="20.05859375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="17.34375" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="16.3046875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="14.55078125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="21.8046875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="11.3046875" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="24.85546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="25.390625" customWidth="true" bestFit="true"/>
@@ -6886,76 +6972,76 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>64</v>
@@ -6964,39 +7050,39 @@
         <v>65</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>179</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>72</v>
@@ -7029,10 +7115,10 @@
         <v>72</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>166.0</v>
+        <v>915.0</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W2" s="2" t="b">
         <v>0</v>
@@ -7052,34 +7138,34 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>72</v>
@@ -7112,7 +7198,7 @@
         <v>72</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>915.0</v>
+        <v>790.0</v>
       </c>
       <c r="V3" s="2" t="n">
         <v>3.0</v>
@@ -7135,34 +7221,34 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>72</v>
@@ -7195,10 +7281,10 @@
         <v>72</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>790.0</v>
+        <v>540.0</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="W4" s="2" t="b">
         <v>0</v>
@@ -7218,10 +7304,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>71</v>
@@ -7230,22 +7316,22 @@
         <v>115</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>72</v>
@@ -7278,10 +7364,10 @@
         <v>72</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>540.0</v>
+        <v>240.0</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W5" s="2" t="b">
         <v>0</v>
@@ -7301,16 +7387,16 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>116</v>
+        <v>199</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>200</v>
@@ -7319,16 +7405,16 @@
         <v>72</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>72</v>
@@ -7361,10 +7447,10 @@
         <v>72</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>240.0</v>
+        <v>522.0</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="W6" s="2" t="b">
         <v>0</v>
@@ -7384,34 +7470,34 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>72</v>
@@ -7444,7 +7530,7 @@
         <v>72</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>522.0</v>
+        <v>349.0</v>
       </c>
       <c r="V7" s="2" t="n">
         <v>1.0</v>
@@ -7467,34 +7553,34 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>72</v>
@@ -7527,7 +7613,7 @@
         <v>72</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>349.0</v>
+        <v>217.0</v>
       </c>
       <c r="V8" s="2" t="n">
         <v>1.0</v>
@@ -7550,34 +7636,34 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>213</v>
+        <v>123</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>72</v>
@@ -7610,10 +7696,10 @@
         <v>72</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>217.0</v>
+        <v>630.0</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="W9" s="2" t="b">
         <v>0</v>
@@ -7633,10 +7719,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>74</v>
@@ -7645,58 +7731,58 @@
         <v>124</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="H10" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>295.0</v>
+      </c>
+      <c r="V10" s="2" t="n">
         <v>2.0</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>802.0</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>3.0</v>
       </c>
       <c r="W10" s="2" t="b">
         <v>0</v>
@@ -7716,70 +7802,70 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H11" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>711.0</v>
+      </c>
+      <c r="V11" s="2" t="n">
         <v>1.0</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U11" s="2" t="n">
-        <v>718.0</v>
-      </c>
-      <c r="V11" s="2" t="n">
-        <v>0.0</v>
       </c>
       <c r="W11" s="2" t="b">
         <v>0</v>
@@ -7799,34 +7885,34 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>127</v>
+        <v>228</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>72</v>
@@ -7859,10 +7945,10 @@
         <v>72</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>348.0</v>
+        <v>534.0</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W12" s="2" t="b">
         <v>0</v>
@@ -7882,34 +7968,34 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>229</v>
+        <v>129</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>72</v>
+        <v>232</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>72</v>
@@ -7942,7 +8028,7 @@
         <v>72</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>299.0</v>
+        <v>529.0</v>
       </c>
       <c r="V13" s="2" t="n">
         <v>3.0</v>
@@ -7965,34 +8051,34 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>72</v>
@@ -8025,10 +8111,10 @@
         <v>72</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>529.0</v>
+        <v>194.0</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W14" s="2" t="b">
         <v>0</v>
@@ -8048,34 +8134,34 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>131</v>
+        <v>240</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>236</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>72</v>
@@ -8108,10 +8194,10 @@
         <v>72</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>486.0</v>
+        <v>653.0</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W15" s="2" t="b">
         <v>0</v>
@@ -8131,34 +8217,34 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>72</v>
@@ -8191,10 +8277,10 @@
         <v>72</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>295.0</v>
+        <v>682.0</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="W16" s="2" t="b">
         <v>0</v>
@@ -8214,34 +8300,34 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>72</v>
@@ -8274,10 +8360,10 @@
         <v>72</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>596.0</v>
+        <v>610.0</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="W17" s="2" t="b">
         <v>0</v>
@@ -8297,34 +8383,34 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>72</v>
@@ -8357,7 +8443,7 @@
         <v>72</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>313.0</v>
+        <v>88.0</v>
       </c>
       <c r="V18" s="2" t="n">
         <v>0.0</v>
@@ -8380,34 +8466,34 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>250</v>
+        <v>138</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>72</v>
@@ -8440,10 +8526,10 @@
         <v>72</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>926.0</v>
+        <v>935.0</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W19" s="2" t="b">
         <v>0</v>
@@ -8463,10 +8549,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>74</v>
@@ -8475,22 +8561,22 @@
         <v>139</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>254</v>
+        <v>215</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>72</v>
@@ -8523,10 +8609,10 @@
         <v>72</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>550.0</v>
+        <v>309.0</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W20" s="2" t="b">
         <v>0</v>
@@ -8546,70 +8632,70 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>258</v>
+        <v>140</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>190</v>
+        <v>262</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H21" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>736.0</v>
+      </c>
+      <c r="V21" s="2" t="n">
         <v>3.0</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U21" s="2" t="n">
-        <v>466.0</v>
-      </c>
-      <c r="V21" s="2" t="n">
-        <v>1.0</v>
       </c>
       <c r="W21" s="2" t="b">
         <v>0</v>
@@ -8629,34 +8715,34 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>72</v>
@@ -8689,7 +8775,7 @@
         <v>72</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>274.0</v>
+        <v>946.0</v>
       </c>
       <c r="V22" s="2" t="n">
         <v>0.0</v>
@@ -8712,34 +8798,34 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>72</v>
@@ -8772,7 +8858,7 @@
         <v>72</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>591.0</v>
+        <v>726.0</v>
       </c>
       <c r="V23" s="2" t="n">
         <v>0.0</v>
@@ -8795,34 +8881,34 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>72</v>
@@ -8855,10 +8941,10 @@
         <v>72</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>130.0</v>
+        <v>435.0</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W24" s="2" t="b">
         <v>0</v>
@@ -8878,10 +8964,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>74</v>
@@ -8890,22 +8976,22 @@
         <v>148</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>72</v>
@@ -8938,10 +9024,10 @@
         <v>72</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>868.0</v>
+        <v>87.0</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="W25" s="2" t="b">
         <v>0</v>
@@ -8961,10 +9047,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>74</v>
@@ -8973,22 +9059,22 @@
         <v>149</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>72</v>
@@ -9021,10 +9107,10 @@
         <v>72</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>560.0</v>
+        <v>968.0</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W26" s="2" t="b">
         <v>0</v>
@@ -9044,10 +9130,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>74</v>
@@ -9056,22 +9142,22 @@
         <v>150</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>72</v>
@@ -9104,10 +9190,10 @@
         <v>72</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>454.0</v>
+        <v>141.0</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="W27" s="2" t="b">
         <v>0</v>
@@ -9127,10 +9213,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>74</v>
@@ -9139,22 +9225,22 @@
         <v>151</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>72</v>
@@ -9187,7 +9273,7 @@
         <v>72</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>768.0</v>
+        <v>268.0</v>
       </c>
       <c r="V28" s="2" t="n">
         <v>0.0</v>
@@ -9210,34 +9296,34 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>219</v>
+        <v>285</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>72</v>
@@ -9270,7 +9356,7 @@
         <v>72</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>952.0</v>
+        <v>820.0</v>
       </c>
       <c r="V29" s="2" t="n">
         <v>3.0</v>
@@ -9293,10 +9379,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>74</v>
@@ -9305,22 +9391,22 @@
         <v>154</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>72</v>
@@ -9353,10 +9439,10 @@
         <v>72</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>295.0</v>
+        <v>258.0</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="W30" s="2" t="b">
         <v>0</v>
@@ -9376,10 +9462,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>74</v>
@@ -9388,22 +9474,22 @@
         <v>155</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>286</v>
+        <v>72</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>72</v>
@@ -9436,10 +9522,10 @@
         <v>72</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>926.0</v>
+        <v>312.0</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="W31" s="2" t="b">
         <v>0</v>
@@ -9459,10 +9545,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>74</v>
@@ -9471,22 +9557,22 @@
         <v>156</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>72</v>
@@ -9519,10 +9605,10 @@
         <v>72</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>135.0</v>
+        <v>774.0</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="W32" s="2" t="b">
         <v>0</v>
@@ -9542,34 +9628,34 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>291</v>
+        <v>157</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>185</v>
+        <v>294</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>72</v>
@@ -9602,10 +9688,10 @@
         <v>72</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>454.0</v>
+        <v>161.0</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="W33" s="2" t="b">
         <v>0</v>
@@ -9625,34 +9711,34 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>72</v>
@@ -9685,10 +9771,10 @@
         <v>72</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>969.0</v>
+        <v>377.0</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W34" s="2" t="b">
         <v>0</v>
@@ -9708,34 +9794,34 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>297</v>
+        <v>72</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>72</v>
@@ -9768,10 +9854,10 @@
         <v>72</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>63.0</v>
+        <v>208.0</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="W35" s="2" t="b">
         <v>0</v>
@@ -9791,34 +9877,34 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>297</v>
+        <v>72</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>72</v>
@@ -9851,10 +9937,10 @@
         <v>72</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>618.0</v>
+        <v>156.0</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="W36" s="2" t="b">
         <v>0</v>
@@ -9874,34 +9960,34 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>195</v>
+        <v>262</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>72</v>
+        <v>232</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>72</v>
@@ -9934,57 +10020,57 @@
         <v>72</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>506.0</v>
+        <v>617.0</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="W37" s="2" t="b">
-        <v>0</v>
+        <v>2.0</v>
+      </c>
+      <c r="W37" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA37" s="2" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>72</v>
@@ -10017,10 +10103,10 @@
         <v>72</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>947.0</v>
+        <v>572.0</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W38" s="2" t="b">
         <v>0</v>
@@ -10040,34 +10126,34 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>179</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>72</v>
+        <v>310</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>72</v>
@@ -10100,10 +10186,10 @@
         <v>72</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>428.0</v>
+        <v>618.0</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="W39" s="2" t="b">
         <v>0</v>
@@ -10123,34 +10209,34 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>297</v>
+        <v>72</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>72</v>
@@ -10183,10 +10269,10 @@
         <v>72</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>450.0</v>
+        <v>642.0</v>
       </c>
       <c r="V40" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="W40" s="2" t="b">
         <v>0</v>
@@ -10206,34 +10292,34 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>181</v>
+        <v>315</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>72</v>
@@ -10266,10 +10352,10 @@
         <v>72</v>
       </c>
       <c r="U41" s="2" t="n">
-        <v>707.0</v>
+        <v>158.0</v>
       </c>
       <c r="V41" s="2" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="W41" s="2" t="b">
         <v>0</v>
@@ -10289,70 +10375,70 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>312</v>
+        <v>118</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H42" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>493.0</v>
+      </c>
+      <c r="V42" s="2" t="n">
         <v>2.0</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R42" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S42" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T42" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U42" s="2" t="n">
-        <v>188.0</v>
-      </c>
-      <c r="V42" s="2" t="n">
-        <v>0.0</v>
       </c>
       <c r="W42" s="2" t="b">
         <v>0</v>
@@ -10372,34 +10458,34 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>72</v>
@@ -10432,7 +10518,7 @@
         <v>72</v>
       </c>
       <c r="U43" s="2" t="n">
-        <v>454.0</v>
+        <v>569.0</v>
       </c>
       <c r="V43" s="2" t="n">
         <v>3.0</v>
@@ -10455,34 +10541,34 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>122</v>
+        <v>322</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>317</v>
+        <v>72</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>72</v>
@@ -10515,10 +10601,10 @@
         <v>72</v>
       </c>
       <c r="U44" s="2" t="n">
-        <v>989.0</v>
+        <v>718.0</v>
       </c>
       <c r="V44" s="2" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="W44" s="2" t="b">
         <v>0</v>
@@ -10538,34 +10624,34 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>320</v>
+        <v>215</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>72</v>
@@ -10598,10 +10684,10 @@
         <v>72</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>959.0</v>
+        <v>995.0</v>
       </c>
       <c r="V45" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W45" s="2" t="b">
         <v>0</v>
@@ -10621,34 +10707,34 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>323</v>
+        <v>123</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>325</v>
+        <v>72</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>72</v>
@@ -10681,7 +10767,7 @@
         <v>72</v>
       </c>
       <c r="U46" s="2" t="n">
-        <v>995.0</v>
+        <v>327.0</v>
       </c>
       <c r="V46" s="2" t="n">
         <v>0.0</v>
@@ -10704,34 +10790,34 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>179</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>72</v>
+        <v>310</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>72</v>
@@ -10764,10 +10850,10 @@
         <v>72</v>
       </c>
       <c r="U47" s="2" t="n">
-        <v>327.0</v>
+        <v>588.0</v>
       </c>
       <c r="V47" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W47" s="2" t="b">
         <v>0</v>
@@ -10787,34 +10873,34 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>127</v>
+        <v>223</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>330</v>
+        <v>72</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>72</v>
@@ -10847,10 +10933,10 @@
         <v>72</v>
       </c>
       <c r="U48" s="2" t="n">
-        <v>864.0</v>
+        <v>277.0</v>
       </c>
       <c r="V48" s="2" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="W48" s="2" t="b">
         <v>0</v>
@@ -10879,61 +10965,61 @@
         <v>74</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="H49" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>928.0</v>
+      </c>
+      <c r="V49" s="2" t="n">
         <v>2.0</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U49" s="2" t="n">
-        <v>277.0</v>
-      </c>
-      <c r="V49" s="2" t="n">
-        <v>4.0</v>
       </c>
       <c r="W49" s="2" t="b">
         <v>0</v>
@@ -10962,25 +11048,25 @@
         <v>74</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>72</v>
@@ -11013,7 +11099,7 @@
         <v>72</v>
       </c>
       <c r="U50" s="2" t="n">
-        <v>928.0</v>
+        <v>659.0</v>
       </c>
       <c r="V50" s="2" t="n">
         <v>2.0</v>
@@ -11045,25 +11131,25 @@
         <v>74</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>200</v>
+        <v>337</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>72</v>
@@ -11096,10 +11182,10 @@
         <v>72</v>
       </c>
       <c r="U51" s="2" t="n">
-        <v>659.0</v>
+        <v>402.0</v>
       </c>
       <c r="V51" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W51" s="2" t="b">
         <v>0</v>
@@ -11119,70 +11205,70 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>339</v>
+        <v>307</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="H52" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T52" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>648.0</v>
+      </c>
+      <c r="V52" s="2" t="n">
         <v>2.0</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U52" s="2" t="n">
-        <v>402.0</v>
-      </c>
-      <c r="V52" s="2" t="n">
-        <v>3.0</v>
       </c>
       <c r="W52" s="2" t="b">
         <v>0</v>
@@ -11211,25 +11297,25 @@
         <v>74</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>342</v>
+        <v>179</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>72</v>
@@ -11262,10 +11348,10 @@
         <v>72</v>
       </c>
       <c r="U53" s="2" t="n">
-        <v>648.0</v>
+        <v>900.0</v>
       </c>
       <c r="V53" s="2" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="W53" s="2" t="b">
         <v>0</v>
@@ -11285,34 +11371,34 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>72</v>
@@ -11345,7 +11431,7 @@
         <v>72</v>
       </c>
       <c r="U54" s="2" t="n">
-        <v>900.0</v>
+        <v>283.0</v>
       </c>
       <c r="V54" s="2" t="n">
         <v>4.0</v>
@@ -11368,70 +11454,70 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>347</v>
+        <v>134</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="H55" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>514.0</v>
+      </c>
+      <c r="V55" s="2" t="n">
         <v>2.0</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U55" s="2" t="n">
-        <v>283.0</v>
-      </c>
-      <c r="V55" s="2" t="n">
-        <v>4.0</v>
       </c>
       <c r="W55" s="2" t="b">
         <v>0</v>
@@ -11451,34 +11537,34 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>136</v>
+        <v>348</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>195</v>
+        <v>262</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>72</v>
@@ -11511,10 +11597,10 @@
         <v>72</v>
       </c>
       <c r="U56" s="2" t="n">
-        <v>514.0</v>
+        <v>601.0</v>
       </c>
       <c r="V56" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="W56" s="2" t="b">
         <v>0</v>
@@ -11534,34 +11620,34 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>250</v>
+        <v>137</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>179</v>
+        <v>244</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>72</v>
@@ -11594,10 +11680,10 @@
         <v>72</v>
       </c>
       <c r="U57" s="2" t="n">
-        <v>601.0</v>
+        <v>307.0</v>
       </c>
       <c r="V57" s="2" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="W57" s="2" t="b">
         <v>0</v>
@@ -11617,34 +11703,34 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>353</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>277</v>
+        <v>353</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>72</v>
@@ -11677,7 +11763,7 @@
         <v>72</v>
       </c>
       <c r="U58" s="2" t="n">
-        <v>307.0</v>
+        <v>525.0</v>
       </c>
       <c r="V58" s="2" t="n">
         <v>4.0</v>
@@ -11709,25 +11795,25 @@
         <v>74</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>140</v>
+        <v>356</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>356</v>
+        <v>191</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>72</v>
@@ -11760,10 +11846,10 @@
         <v>72</v>
       </c>
       <c r="U59" s="2" t="n">
-        <v>525.0</v>
+        <v>968.0</v>
       </c>
       <c r="V59" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W59" s="2" t="b">
         <v>0</v>
@@ -11795,58 +11881,58 @@
         <v>359</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>195</v>
+        <v>262</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H60" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U60" s="2" t="n">
+        <v>356.0</v>
+      </c>
+      <c r="V60" s="2" t="n">
         <v>1.0</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N60" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O60" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P60" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q60" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R60" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S60" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T60" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U60" s="2" t="n">
-        <v>898.0</v>
-      </c>
-      <c r="V60" s="2" t="n">
-        <v>0.0</v>
       </c>
       <c r="W60" s="2" t="b">
         <v>0</v>
@@ -11875,25 +11961,25 @@
         <v>74</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>325</v>
+        <v>72</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>72</v>
@@ -11926,10 +12012,10 @@
         <v>72</v>
       </c>
       <c r="U61" s="2" t="n">
-        <v>621.0</v>
+        <v>125.0</v>
       </c>
       <c r="V61" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W61" s="2" t="b">
         <v>0</v>
@@ -11958,25 +12044,25 @@
         <v>74</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G62" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I62" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="H62" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="J62" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>72</v>
@@ -12009,10 +12095,10 @@
         <v>72</v>
       </c>
       <c r="U62" s="2" t="n">
-        <v>993.0</v>
+        <v>404.0</v>
       </c>
       <c r="V62" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W62" s="2" t="b">
         <v>0</v>
@@ -12041,25 +12127,25 @@
         <v>74</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>185</v>
+        <v>366</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>72</v>
@@ -12092,10 +12178,10 @@
         <v>72</v>
       </c>
       <c r="U63" s="2" t="n">
-        <v>404.0</v>
+        <v>125.0</v>
       </c>
       <c r="V63" s="2" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="W63" s="2" t="b">
         <v>0</v>
@@ -12115,34 +12201,34 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>147</v>
+        <v>369</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>368</v>
+        <v>211</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>72</v>
@@ -12175,10 +12261,10 @@
         <v>72</v>
       </c>
       <c r="U64" s="2" t="n">
-        <v>125.0</v>
+        <v>591.0</v>
       </c>
       <c r="V64" s="2" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="W64" s="2" t="b">
         <v>0</v>
@@ -12198,34 +12284,34 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>371</v>
+        <v>150</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>214</v>
+        <v>372</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>72</v>
@@ -12258,7 +12344,7 @@
         <v>72</v>
       </c>
       <c r="U65" s="2" t="n">
-        <v>591.0</v>
+        <v>778.0</v>
       </c>
       <c r="V65" s="2" t="n">
         <v>3.0</v>
@@ -12281,34 +12367,34 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>374</v>
+        <v>200</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>72</v>
@@ -12341,25 +12427,25 @@
         <v>72</v>
       </c>
       <c r="U66" s="2" t="n">
-        <v>778.0</v>
+        <v>310.0</v>
       </c>
       <c r="V66" s="2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="W66" s="4" t="b">
-        <v>1</v>
+        <v>1.0</v>
+      </c>
+      <c r="W66" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Z66" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AA66" s="2" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67">
@@ -12373,25 +12459,25 @@
         <v>74</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>72</v>
@@ -12424,10 +12510,10 @@
         <v>72</v>
       </c>
       <c r="U67" s="2" t="n">
-        <v>552.0</v>
+        <v>658.0</v>
       </c>
       <c r="V67" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="W67" s="2" t="b">
         <v>0</v>
@@ -12456,61 +12542,61 @@
         <v>74</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H68" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U68" s="2" t="n">
+        <v>564.0</v>
+      </c>
+      <c r="V68" s="2" t="n">
         <v>3.0</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N68" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O68" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P68" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q68" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R68" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S68" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T68" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U68" s="2" t="n">
-        <v>658.0</v>
-      </c>
-      <c r="V68" s="2" t="n">
-        <v>2.0</v>
       </c>
       <c r="W68" s="2" t="b">
         <v>0</v>
@@ -12539,25 +12625,25 @@
         <v>74</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>153</v>
+        <v>381</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>72</v>
@@ -12590,10 +12676,10 @@
         <v>72</v>
       </c>
       <c r="U69" s="2" t="n">
-        <v>564.0</v>
+        <v>357.0</v>
       </c>
       <c r="V69" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W69" s="2" t="b">
         <v>0</v>
@@ -12613,34 +12699,34 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>383</v>
+        <v>156</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>72</v>
@@ -12673,10 +12759,10 @@
         <v>72</v>
       </c>
       <c r="U70" s="2" t="n">
-        <v>357.0</v>
+        <v>97.0</v>
       </c>
       <c r="V70" s="2" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="W70" s="2" t="b">
         <v>0</v>
@@ -12705,25 +12791,25 @@
         <v>74</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>72</v>
@@ -12756,10 +12842,10 @@
         <v>72</v>
       </c>
       <c r="U71" s="2" t="n">
-        <v>97.0</v>
+        <v>626.0</v>
       </c>
       <c r="V71" s="2" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="W71" s="2" t="b">
         <v>0</v>
@@ -12788,25 +12874,25 @@
         <v>74</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>200</v>
+        <v>262</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>72</v>
@@ -12839,7 +12925,7 @@
         <v>72</v>
       </c>
       <c r="U72" s="2" t="n">
-        <v>626.0</v>
+        <v>231.0</v>
       </c>
       <c r="V72" s="2" t="n">
         <v>1.0</v>
@@ -12871,25 +12957,25 @@
         <v>74</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>72</v>
@@ -12922,10 +13008,10 @@
         <v>72</v>
       </c>
       <c r="U73" s="2" t="n">
-        <v>231.0</v>
+        <v>548.0</v>
       </c>
       <c r="V73" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="W73" s="2" t="b">
         <v>0</v>
@@ -12975,7 +13061,7 @@
     <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>392</v>
@@ -13127,48 +13213,48 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="45.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>72</v>
@@ -13209,7 +13295,7 @@
     </row>
     <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>72</v>
@@ -13250,7 +13336,7 @@
     </row>
     <row r="5" ht="45.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>72</v>
@@ -13332,7 +13418,7 @@
     </row>
     <row r="7" ht="45.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>72</v>
@@ -13373,7 +13459,7 @@
     </row>
     <row r="8" ht="45.0" customHeight="true">
       <c r="A8" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>72</v>
@@ -13414,7 +13500,7 @@
     </row>
     <row r="9" ht="45.0" customHeight="true">
       <c r="A9" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>72</v>
@@ -13455,7 +13541,7 @@
     </row>
     <row r="10" ht="45.0" customHeight="true">
       <c r="A10" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>72</v>
@@ -13496,7 +13582,7 @@
     </row>
     <row r="11" ht="45.0" customHeight="true">
       <c r="A11" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>72</v>
@@ -13537,7 +13623,7 @@
     </row>
     <row r="12" ht="45.0" customHeight="true">
       <c r="A12" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>72</v>
@@ -13669,45 +13755,45 @@
         <v>398</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
@@ -13748,13 +13834,13 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>72</v>
+      <c r="C4" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>72</v>
@@ -13789,7 +13875,7 @@
     </row>
     <row r="5" ht="15.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>72</v>
@@ -13830,7 +13916,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>72</v>
@@ -13871,7 +13957,7 @@
     </row>
     <row r="7" ht="15.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>72</v>
@@ -13912,15 +13998,15 @@
     </row>
     <row r="8" ht="15.0" customHeight="true">
       <c r="A8" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>72</v>
       </c>
       <c r="E8" s="8" t="s">
@@ -13932,13 +14018,13 @@
       <c r="G8" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="H8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>72</v>
       </c>
       <c r="K8" s="8" t="s">
@@ -13953,15 +14039,15 @@
     </row>
     <row r="9" ht="15.0" customHeight="true">
       <c r="A9" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>72</v>
       </c>
       <c r="E9" s="8" t="s">
@@ -13973,13 +14059,13 @@
       <c r="G9" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J9" s="3" t="s">
+      <c r="H9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>72</v>
       </c>
       <c r="K9" s="8" t="s">
@@ -13994,7 +14080,7 @@
     </row>
     <row r="10" ht="15.0" customHeight="true">
       <c r="A10" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>72</v>
@@ -14035,7 +14121,7 @@
     </row>
     <row r="11" ht="15.0" customHeight="true">
       <c r="A11" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>72</v>
@@ -14076,7 +14162,7 @@
     </row>
     <row r="12" ht="15.0" customHeight="true">
       <c r="A12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>72</v>
@@ -14117,7 +14203,7 @@
     </row>
     <row r="13" ht="15.0" customHeight="true">
       <c r="A13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>72</v>
@@ -14158,7 +14244,7 @@
     </row>
     <row r="14" ht="15.0" customHeight="true">
       <c r="A14" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>72</v>
@@ -14199,7 +14285,7 @@
     </row>
     <row r="15" ht="15.0" customHeight="true">
       <c r="A15" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>72</v>
@@ -14240,7 +14326,7 @@
     </row>
     <row r="16" ht="15.0" customHeight="true">
       <c r="A16" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>72</v>
@@ -14281,7 +14367,7 @@
     </row>
     <row r="17" ht="15.0" customHeight="true">
       <c r="A17" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>72</v>
@@ -14322,7 +14408,7 @@
     </row>
     <row r="18" ht="15.0" customHeight="true">
       <c r="A18" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>72</v>
@@ -14363,7 +14449,7 @@
     </row>
     <row r="19" ht="15.0" customHeight="true">
       <c r="A19" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>72</v>
@@ -14371,16 +14457,16 @@
       <c r="C19" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="3" t="s">
         <v>72</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19" s="8" t="s">
+      <c r="F19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>72</v>
       </c>
       <c r="H19" s="8" t="s">
@@ -14404,24 +14490,24 @@
     </row>
     <row r="20" ht="15.0" customHeight="true">
       <c r="A20" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>72</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="F20" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" s="8" t="s">
         <v>72</v>
       </c>
       <c r="H20" s="8" t="s">
@@ -14445,12 +14531,12 @@
     </row>
     <row r="21" ht="15.0" customHeight="true">
       <c r="A21" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="8" t="s">
         <v>72</v>
       </c>
       <c r="D21" s="8" t="s">
@@ -14486,7 +14572,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="true">
       <c r="A22" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>72</v>
@@ -14527,7 +14613,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="true">
       <c r="A23" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>72</v>
@@ -14568,7 +14654,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="true">
       <c r="A24" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>72</v>
@@ -14609,7 +14695,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="true">
       <c r="A25" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>72</v>
@@ -14650,7 +14736,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="true">
       <c r="A26" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>72</v>
@@ -14691,7 +14777,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="true">
       <c r="A27" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>72</v>
@@ -14732,7 +14818,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="true">
       <c r="A28" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>72</v>
@@ -14773,7 +14859,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="true">
       <c r="A29" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>72</v>
@@ -14814,7 +14900,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="true">
       <c r="A30" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>72</v>
@@ -14855,7 +14941,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="true">
       <c r="A31" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>72</v>
@@ -14896,7 +14982,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="true">
       <c r="A32" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>72</v>
@@ -14937,7 +15023,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="true">
       <c r="A33" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>72</v>
@@ -14978,9 +15064,9 @@
     </row>
     <row r="34" ht="15.0" customHeight="true">
       <c r="A34" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B34" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C34" s="8" t="s">
@@ -15019,9 +15105,9 @@
     </row>
     <row r="35" ht="15.0" customHeight="true">
       <c r="A35" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B35" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C35" s="8" t="s">
@@ -15060,7 +15146,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="true">
       <c r="A36" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>72</v>
@@ -15101,7 +15187,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="true">
       <c r="A37" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>72</v>
@@ -15142,7 +15228,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="true">
       <c r="A38" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>72</v>
@@ -15183,7 +15269,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="true">
       <c r="A39" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>72</v>
@@ -15224,7 +15310,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="true">
       <c r="A40" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>72</v>
@@ -15265,7 +15351,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="true">
       <c r="A41" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>72</v>
@@ -15306,13 +15392,13 @@
     </row>
     <row r="42" ht="15.0" customHeight="true">
       <c r="A42" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>399</v>
+      <c r="C42" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>72</v>
@@ -15347,7 +15433,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="true">
       <c r="A43" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>72</v>
@@ -15358,13 +15444,13 @@
       <c r="D43" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E43" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G43" s="8" t="s">
+      <c r="E43" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G43" s="3" t="s">
         <v>72</v>
       </c>
       <c r="H43" s="8" t="s">
@@ -15376,19 +15462,19 @@
       <c r="J43" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="K43" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="L43" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="M43" s="8" t="s">
+      <c r="K43" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M43" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="44" ht="15.0" customHeight="true">
       <c r="A44" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>72</v>
@@ -15399,13 +15485,13 @@
       <c r="D44" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G44" s="3" t="s">
+      <c r="E44" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G44" s="8" t="s">
         <v>72</v>
       </c>
       <c r="H44" s="8" t="s">
@@ -15417,19 +15503,19 @@
       <c r="J44" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="M44" s="3" t="s">
+      <c r="K44" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="M44" s="8" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="true">
       <c r="A45" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>72</v>
@@ -15470,7 +15556,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="true">
       <c r="A46" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>72</v>
@@ -15511,7 +15597,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="true">
       <c r="A47" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>72</v>
@@ -15552,7 +15638,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="true">
       <c r="A48" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>72</v>
@@ -15563,13 +15649,13 @@
       <c r="D48" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E48" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G48" s="8" t="s">
+      <c r="E48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G48" s="3" t="s">
         <v>72</v>
       </c>
       <c r="H48" s="8" t="s">
@@ -15581,19 +15667,19 @@
       <c r="J48" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="K48" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="L48" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="M48" s="8" t="s">
+      <c r="K48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M48" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="49" ht="15.0" customHeight="true">
       <c r="A49" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>72</v>
@@ -15604,13 +15690,13 @@
       <c r="D49" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G49" s="3" t="s">
+      <c r="E49" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G49" s="8" t="s">
         <v>72</v>
       </c>
       <c r="H49" s="8" t="s">
@@ -15622,19 +15708,19 @@
       <c r="J49" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="M49" s="3" t="s">
+      <c r="K49" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="M49" s="8" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="50" ht="15.0" customHeight="true">
       <c r="A50" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>72</v>
@@ -15753,45 +15839,45 @@
         <v>400</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>205</v>
+        <v>262</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>72</v>
@@ -15827,47 +15913,6 @@
         <v>72</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" ht="15.0" customHeight="true">
-      <c r="A4" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="M4" s="8" t="s">
         <v>72</v>
       </c>
     </row>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -235,40 +235,40 @@
     <t>Soft reward per 2 talks that have the same timeslot and a different language</t>
   </si>
   <si>
-    <t>Speaker preferred timeslot tag</t>
+    <t>Speaker preferred timeslot tags</t>
   </si>
   <si>
     <t>Soft penalty per missing preferred tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Speaker undesired timeslot tag</t>
+    <t>Speaker undesired timeslot tags</t>
   </si>
   <si>
     <t>Soft penalty per undesired tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Talk preferred timeslot tag</t>
-  </si>
-  <si>
-    <t>Talk undesired timeslot tag</t>
-  </si>
-  <si>
-    <t>Speaker preferred room tag</t>
+    <t>Talk preferred timeslot tags</t>
+  </si>
+  <si>
+    <t>Talk undesired timeslot tags</t>
+  </si>
+  <si>
+    <t>Speaker preferred room tags</t>
   </si>
   <si>
     <t>Soft penalty per missing preferred tag in a talk's room</t>
   </si>
   <si>
-    <t>Speaker undesired room tag</t>
+    <t>Speaker undesired room tags</t>
   </si>
   <si>
     <t>Soft penalty per undesired tag in a talk's room</t>
   </si>
   <si>
-    <t>Talk preferred room tag</t>
-  </si>
-  <si>
-    <t>Talk undesired room tag</t>
+    <t>Talk preferred room tags</t>
+  </si>
+  <si>
+    <t>Talk undesired room tags</t>
   </si>
   <si>
     <t>Same day talks</t>
@@ -319,43 +319,43 @@
     <t>Hard penalty per pair of talks with the same speaker in overlapping timeslots</t>
   </si>
   <si>
-    <t>Speaker required timeslot tag</t>
+    <t>Speaker required timeslot tags</t>
   </si>
   <si>
     <t>Hard penalty per missing required tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Speaker prohibited timeslot tag</t>
+    <t>Speaker prohibited timeslot tags</t>
   </si>
   <si>
     <t>Hard penalty per prohibited tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Talk required timeslot tag</t>
-  </si>
-  <si>
-    <t>Talk prohibited timeslot tag</t>
-  </si>
-  <si>
-    <t>Speaker required room tag</t>
+    <t>Talk required timeslot tags</t>
+  </si>
+  <si>
+    <t>Talk prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t>Speaker required room tags</t>
   </si>
   <si>
     <t>Hard penalty per missing required tag in a talk's room</t>
   </si>
   <si>
-    <t>Speaker prohibited room tag</t>
+    <t>Speaker prohibited room tags</t>
   </si>
   <si>
     <t>Hard penalty per prohibited tag in a talk's room</t>
   </si>
   <si>
-    <t>Talk required room tag</t>
-  </si>
-  <si>
-    <t>Talk prohibited room tag</t>
-  </si>
-  <si>
-    <t>Talk mutually-exclusive-talks tag</t>
+    <t>Talk required room tags</t>
+  </si>
+  <si>
+    <t>Talk prohibited room tags</t>
+  </si>
+  <si>
+    <t>Talk mutually-exclusive-talks tags</t>
   </si>
   <si>
     <t>Hard penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -296,7 +296,7 @@
     <t>Popular talks</t>
   </si>
   <si>
-    <t>Soft penalty per 2 talks where the less popular one (has lower number of likes) is assigned a larger room than the more popular talk</t>
+    <t>Soft penalty per 2 talks where the less popular one (has lower favorite count) is assigned a larger room than the more popular talk</t>
   </si>
   <si>
     <t>Crowd control</t>
@@ -716,7 +716,7 @@
     <t>Prerequisite talks codes</t>
   </si>
   <si>
-    <t>Number of likes</t>
+    <t>Favorite count</t>
   </si>
   <si>
     <t>Crowd control risk</t>
@@ -7039,7 +7039,7 @@
     <col min="18" max="18" width="22.84375" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="31.2734375" customWidth="true" bestFit="true"/>
     <col min="20" max="20" width="26.23046875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.5390625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="16.25390625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="20.140625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.65234375" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.14453125" customWidth="true" bestFit="true"/>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -21,6 +21,8 @@
     <sheet name="Contents view" r:id="rId15" sheetId="13"/>
     <sheet name="Languages view" r:id="rId16" sheetId="14"/>
     <sheet name="Score view" r:id="rId17" sheetId="15"/>
+    <sheet name="Mon 2018-10-01" r:id="rId18" sheetId="16"/>
+    <sheet name="Tue 2018-10-02" r:id="rId19" sheetId="17"/>
   </sheets>
 </workbook>
 </file>
@@ -33,11 +35,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S35: Using secure Tensorflow
+        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
     Beth Fox
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -53,11 +54,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S35: Using secure Tensorflow
+        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
     Beth Fox
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -73,11 +73,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S35: Using secure Tensorflow
+        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
     Beth Fox
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -93,11 +92,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S35: Using secure Tensorflow
+        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
     Beth Fox
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -113,7 +111,26 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S35: Using secure Tensorflow
+        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
+    Beth Fox
+PINNED BY USER
+-10soft total
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments16.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="B3" authorId="0">
+      <text>
+        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
     Beth Fox
 PINNED BY USER
 -10soft total
@@ -133,7 +150,7 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S35: Using secure Tensorflow
+        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
     Beth Fox
 PINNED BY USER
 -10soft total
@@ -153,11 +170,10 @@
   <commentList>
     <comment ref="C4" authorId="0">
       <text>
-        <t xml:space="preserve">S35: Using secure Tensorflow
+        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
     Beth Fox
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -173,11 +189,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S35: Using secure Tensorflow
+        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
     Beth Fox
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -186,7 +201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4114" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4135" uniqueCount="416">
   <si>
     <t>Conference name</t>
   </si>
@@ -305,6 +320,12 @@
     <t>Soft penalty per talks with crowd control risk greater than zero that are not in pairs</t>
   </si>
   <si>
+    <t>Talk mutually-exclusive-talks tags</t>
+  </si>
+  <si>
+    <t>Medium penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>
+  </si>
+  <si>
     <t>Talk type of timeslot</t>
   </si>
   <si>
@@ -375,12 +396,6 @@
   </si>
   <si>
     <t>Talk prohibited room tags</t>
-  </si>
-  <si>
-    <t>Talk mutually-exclusive-talks tags</t>
-  </si>
-  <si>
-    <t>Hard penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>
   </si>
   <si>
     <t>Talk prerequisite talks</t>
@@ -1432,6 +1447,10 @@
   </si>
   <si>
     <t xml:space="preserve">    S35</t>
+  </si>
+  <si>
+    <t>Using secure Tensorflow
+Beth Fox</t>
   </si>
 </sst>
 </file>
@@ -1453,7 +1472,7 @@
       <b val="true"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1488,6 +1507,46 @@
         <fgColor rgb="FCAF3E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="8AE234"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FCE94F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="729FCF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="E9B96E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="73D216"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="EDD400"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="3465A4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="C17D11"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1501,7 +1560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true">
       <alignment wrapText="true" vertical="center"/>
@@ -1525,6 +1584,33 @@
       <alignment wrapText="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1556,6 +1642,14 @@
 </file>
 
 <file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
@@ -1593,7 +1687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.66796875" customWidth="true" bestFit="true"/>
@@ -1836,109 +1930,99 @@
         <v>39</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>10000.0</v>
+        <v>1.0</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>10000.0</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>10000.0</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>10.0</v>
+        <v>10000.0</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1.0</v>
+        <v>10000.0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
@@ -1949,40 +2033,40 @@
         <v>1.0</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38">
@@ -1993,17 +2077,28 @@
         <v>1.0</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2018,7 +2113,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.6328125" customWidth="true" bestFit="true"/>
@@ -2175,7 +2270,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.640625" customWidth="true" bestFit="true"/>
@@ -2332,7 +2427,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.3046875" customWidth="true" bestFit="true"/>
@@ -2489,7 +2584,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="13.4609375" customWidth="true" bestFit="true"/>
@@ -2646,7 +2741,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.3046875" customWidth="true" bestFit="true"/>
@@ -2786,12 +2881,6 @@
       <c r="M3" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>395</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -2809,44 +2898,179 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.0703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.73828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="15.15625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>412</v>
-      </c>
-    </row>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="4">
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="17.94140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="15.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" ht="45.0" customHeight="true">
+      <c r="A2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" ht="45.0" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" ht="45.0" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" ht="45.0" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" ht="45.0" customHeight="true">
+      <c r="A7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="17.3515625" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" ht="45.0" customHeight="true">
+      <c r="A2" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" ht="45.0" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" ht="45.0" customHeight="true">
+      <c r="A4" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" ht="45.0" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" ht="45.0" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" ht="45.0" customHeight="true">
+      <c r="A7" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2856,7 +3080,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.14453125" customWidth="true" bestFit="true"/>
@@ -3095,7 +3319,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.109375" customWidth="true" bestFit="true"/>
@@ -3728,7 +3952,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:V50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.9453125" customWidth="true" bestFit="true"/>
@@ -7016,7 +7240,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AB73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="6.34765625" customWidth="true" bestFit="true"/>
@@ -13118,7 +13342,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="10.78515625" customWidth="true" bestFit="true"/>
@@ -13217,7 +13441,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.02734375" customWidth="true" bestFit="true"/>
@@ -13756,7 +13980,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.9453125" customWidth="true" bestFit="true"/>
@@ -15853,7 +16077,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.1640625" customWidth="true" bestFit="true"/>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -27,25 +27,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
-    <comment ref="C3" authorId="0">
-      <text>
-        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
-    Beth Fox
-PINNED BY USER
--45hard total
-</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -54,10 +35,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
-    Beth Fox
+        <t xml:space="preserve">S54-Culture: Troubleshooting reliable Tensorflow
+    Jay Fox, Amy Jones
 PINNED BY USER
--45hard total
 </t>
       </text>
     </comment>
@@ -73,10 +53,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
-    Beth Fox
+        <t xml:space="preserve">S54-Culture: Troubleshooting reliable Tensorflow
+    Jay Fox, Amy Jones
 PINNED BY USER
--45hard total
 </t>
       </text>
     </comment>
@@ -92,10 +71,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
-    Beth Fox
+        <t xml:space="preserve">S54-Culture: Troubleshooting reliable Tensorflow
+    Jay Fox, Amy Jones
 PINNED BY USER
--45hard total
 </t>
       </text>
     </comment>
@@ -111,10 +89,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
-    Beth Fox
+        <t xml:space="preserve">S54-Culture: Troubleshooting reliable Tensorflow
+    Jay Fox, Amy Jones
 PINNED BY USER
--45hard total
 </t>
       </text>
     </comment>
@@ -130,11 +107,9 @@
   <commentList>
     <comment ref="B3" authorId="0">
       <text>
-        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
-    Beth Fox
+        <t xml:space="preserve">S54-Culture: Troubleshooting reliable Tensorflow
+    Jay Fox, Amy Jones
 PINNED BY USER
--45hard total
-    -45hard for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -150,11 +125,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
-    Beth Fox
+        <t xml:space="preserve">S54-Culture: Troubleshooting reliable Tensorflow
+    Jay Fox, Amy Jones
 PINNED BY USER
--45hard total
-    -45hard for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -168,12 +141,19 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0">
+    <comment ref="C32" authorId="0">
       <text>
-        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
-    Beth Fox
+        <t xml:space="preserve">S54-Culture: Troubleshooting reliable Tensorflow
+    Jay Fox, Amy Jones
 PINNED BY USER
--45hard total
+</t>
+      </text>
+    </comment>
+    <comment ref="C33" authorId="0">
+      <text>
+        <t xml:space="preserve">S54-Culture: Troubleshooting reliable Tensorflow
+    Jay Fox, Amy Jones
+PINNED BY USER
 </t>
       </text>
     </comment>
@@ -189,10 +169,9 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S35-IoT: Using secure Tensorflow
-    Beth Fox
+        <t xml:space="preserve">S54-Culture: Troubleshooting reliable Tensorflow
+    Jay Fox, Amy Jones
 PINNED BY USER
--45hard total
 </t>
       </text>
     </comment>
@@ -201,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4695" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4680" uniqueCount="454">
   <si>
     <t>Conference name</t>
   </si>
@@ -692,9 +671,6 @@
     <t>Amy Jones</t>
   </si>
   <si>
-    <t>Large</t>
-  </si>
-  <si>
     <t>Beth King</t>
   </si>
   <si>
@@ -815,588 +791,603 @@
     <t>Hands on real-time OpenShift</t>
   </si>
   <si>
+    <t>Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Business analysts</t>
+  </si>
+  <si>
+    <t>OpenShift, Kubernetes</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>S01</t>
+  </si>
+  <si>
+    <t>Advanced containerized WildFly</t>
+  </si>
+  <si>
+    <t>Beth Fox, Chad Green</t>
+  </si>
+  <si>
+    <t>Middleware</t>
+  </si>
+  <si>
+    <t>Programmers</t>
+  </si>
+  <si>
+    <t>WildFly</t>
+  </si>
+  <si>
+    <t>S02</t>
+  </si>
+  <si>
+    <t>Learn virtualized Spring</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>S03</t>
+  </si>
+  <si>
+    <t>Intro to serverless Drools</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Managers</t>
+  </si>
+  <si>
+    <t>Drools</t>
+  </si>
+  <si>
+    <t>S04</t>
+  </si>
+  <si>
+    <t>Discover AI-driven OptaPlanner</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Mobile</t>
+  </si>
+  <si>
+    <t>OptaPlanner</t>
+  </si>
+  <si>
+    <t>S05</t>
+  </si>
+  <si>
+    <t>Mastering machine learning jBPM</t>
+  </si>
+  <si>
+    <t>Modern Web</t>
+  </si>
+  <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>jBPM</t>
+  </si>
+  <si>
+    <t>S06</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Camel</t>
+  </si>
+  <si>
+    <t>Hugo Rye, Ivy Smith</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>S07</t>
+  </si>
+  <si>
+    <t>Building deep learning XStream</t>
+  </si>
+  <si>
+    <t>Big Data</t>
+  </si>
+  <si>
+    <t>XStream</t>
+  </si>
+  <si>
+    <t>S08</t>
+  </si>
+  <si>
+    <t>Securing scalable Docker</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
+    <t>S09</t>
+  </si>
+  <si>
+    <t>Debug enterprise Hibernate</t>
+  </si>
+  <si>
+    <t>Beth Green, Chad Jones</t>
+  </si>
+  <si>
+    <t>Hibernate</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>Prepare for streaming GWT</t>
+  </si>
+  <si>
+    <t>Dan King, Elsa Li</t>
+  </si>
+  <si>
+    <t>GWT</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>Understand mobile Errai</t>
+  </si>
+  <si>
+    <t>Flo Poe, Gus Rye</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Errai</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>Applying modern Angular</t>
+  </si>
+  <si>
+    <t>Hugo Smith, Ivy Watt</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>Grok distributed Weld</t>
+  </si>
+  <si>
+    <t>IoT</t>
+  </si>
+  <si>
+    <t>Weld</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable RestEasy</t>
+  </si>
+  <si>
+    <t>Amy Green, Beth Jones</t>
+  </si>
+  <si>
+    <t>Telecommunications</t>
+  </si>
+  <si>
+    <t>RestEasy</t>
+  </si>
+  <si>
+    <t>S15</t>
+  </si>
+  <si>
+    <t>Using secure Android</t>
+  </si>
+  <si>
+    <t>Chad King, Dan Li</t>
+  </si>
+  <si>
     <t>Culture</t>
   </si>
   <si>
-    <t>Telecommunications</t>
-  </si>
-  <si>
-    <t>Business analysts</t>
-  </si>
-  <si>
-    <t>OpenShift, Kubernetes</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>S01</t>
-  </si>
-  <si>
-    <t>Advanced containerized WildFly</t>
-  </si>
-  <si>
-    <t>Beth Fox, Chad Green</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>WildFly</t>
-  </si>
-  <si>
-    <t>S02</t>
-  </si>
-  <si>
-    <t>Learn virtualized Spring</t>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>Deliver stable Tensorflow</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Tensorflow</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>Implement platform-independent VertX</t>
+  </si>
+  <si>
+    <t>IoT, Big Data</t>
+  </si>
+  <si>
+    <t>VertX</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>Program flexible JUnit</t>
+  </si>
+  <si>
+    <t>JUnit</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>Hack modularized Keycloak</t>
+  </si>
+  <si>
+    <t>Keycloak</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>Hands on real-time WildFly</t>
+  </si>
+  <si>
+    <t>Ivy Cole, Jay Fox</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>Advanced containerized Spring</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Cloud</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>Learn virtualized Drools</t>
+  </si>
+  <si>
+    <t>S23</t>
+  </si>
+  <si>
+    <t>Intro to serverless OptaPlanner</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>Discover AI-driven jBPM</t>
+  </si>
+  <si>
+    <t>Dan Poe, Elsa Rye, Flo Smith, Gus Watt</t>
+  </si>
+  <si>
+    <t>S25</t>
+  </si>
+  <si>
+    <t>Mastering machine learning Camel</t>
+  </si>
+  <si>
+    <t>Security, Middleware</t>
+  </si>
+  <si>
+    <t>S26</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven XStream</t>
+  </si>
+  <si>
+    <t>S27</t>
+  </si>
+  <si>
+    <t>Building deep learning Docker</t>
+  </si>
+  <si>
+    <t>Docker, Kubernetes</t>
+  </si>
+  <si>
+    <t>S28</t>
+  </si>
+  <si>
+    <t>Securing scalable Hibernate</t>
+  </si>
+  <si>
+    <t>S29</t>
+  </si>
+  <si>
+    <t>Debug enterprise GWT</t>
+  </si>
+  <si>
+    <t>Beth Li, Chad Poe</t>
+  </si>
+  <si>
+    <t>S30</t>
+  </si>
+  <si>
+    <t>Prepare for streaming Errai</t>
+  </si>
+  <si>
+    <t>S31</t>
+  </si>
+  <si>
+    <t>Understand mobile Angular</t>
+  </si>
+  <si>
+    <t>Elsa Smith, Flo Watt</t>
+  </si>
+  <si>
+    <t>S32</t>
+  </si>
+  <si>
+    <t>Applying modern Weld</t>
+  </si>
+  <si>
+    <t>Gus Cole, Hugo Fox</t>
+  </si>
+  <si>
+    <t>S33</t>
+  </si>
+  <si>
+    <t>Grok distributed RestEasy</t>
+  </si>
+  <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable Android</t>
+  </si>
+  <si>
+    <t>S35</t>
+  </si>
+  <si>
+    <t>Using secure Tensorflow</t>
+  </si>
+  <si>
+    <t>Chad Green, Dan Jones</t>
+  </si>
+  <si>
+    <t>S36</t>
+  </si>
+  <si>
+    <t>Deliver stable VertX</t>
+  </si>
+  <si>
+    <t>Elsa King, Flo Li</t>
+  </si>
+  <si>
+    <t>S37</t>
+  </si>
+  <si>
+    <t>Implement platform-independent JUnit</t>
+  </si>
+  <si>
+    <t>S38</t>
+  </si>
+  <si>
+    <t>Program flexible Keycloak</t>
+  </si>
+  <si>
+    <t>S39</t>
+  </si>
+  <si>
+    <t>Hack modularized OpenShift</t>
+  </si>
+  <si>
+    <t>OpenShift</t>
+  </si>
+  <si>
+    <t>S40</t>
+  </si>
+  <si>
+    <t>Hands on real-time Spring</t>
+  </si>
+  <si>
+    <t>Jay Watt, Amy Fox</t>
   </si>
   <si>
     <t>Security</t>
   </si>
   <si>
-    <t>Programmers</t>
-  </si>
-  <si>
-    <t>Spring</t>
-  </si>
-  <si>
-    <t>S03</t>
-  </si>
-  <si>
-    <t>Intro to serverless Drools</t>
-  </si>
-  <si>
-    <t>Drools</t>
-  </si>
-  <si>
-    <t>S04</t>
-  </si>
-  <si>
-    <t>Discover AI-driven OptaPlanner</t>
-  </si>
-  <si>
-    <t>Flo Li, Gus Poe</t>
-  </si>
-  <si>
-    <t>Big Data</t>
-  </si>
-  <si>
-    <t>Managers</t>
-  </si>
-  <si>
-    <t>OptaPlanner</t>
-  </si>
-  <si>
-    <t>S05</t>
-  </si>
-  <si>
-    <t>Mastering machine learning jBPM</t>
-  </si>
-  <si>
-    <t>Hugo Rye, Ivy Smith, Jay Watt</t>
-  </si>
-  <si>
-    <t>Modern Web</t>
-  </si>
-  <si>
-    <t>jBPM</t>
-  </si>
-  <si>
-    <t>S06</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Camel</t>
-  </si>
-  <si>
-    <t>Amy Fox, Beth Green</t>
-  </si>
-  <si>
-    <t>Middleware</t>
-  </si>
-  <si>
-    <t>Camel</t>
-  </si>
-  <si>
-    <t>S07</t>
-  </si>
-  <si>
-    <t>Building deep learning XStream</t>
-  </si>
-  <si>
-    <t>Cloud</t>
-  </si>
-  <si>
-    <t>XStream</t>
-  </si>
-  <si>
-    <t>S08</t>
-  </si>
-  <si>
-    <t>Securing scalable Docker</t>
-  </si>
-  <si>
-    <t>Culture, Security</t>
-  </si>
-  <si>
-    <t>Docker</t>
-  </si>
-  <si>
-    <t>S09</t>
-  </si>
-  <si>
-    <t>Debug enterprise Hibernate</t>
-  </si>
-  <si>
-    <t>Elsa Li, Flo Poe</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence, Culture</t>
-  </si>
-  <si>
-    <t>Hibernate</t>
-  </si>
-  <si>
-    <t>S10</t>
-  </si>
-  <si>
-    <t>Prepare for streaming GWT</t>
-  </si>
-  <si>
-    <t>Gus Rye, Hugo Smith</t>
-  </si>
-  <si>
-    <t>GWT</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>Understand mobile Errai</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>Errai</t>
-  </si>
-  <si>
-    <t>S12</t>
-  </si>
-  <si>
-    <t>Applying modern Angular</t>
-  </si>
-  <si>
-    <t>Jay Cole, Amy Green</t>
-  </si>
-  <si>
-    <t>Angular</t>
-  </si>
-  <si>
-    <t>S13</t>
-  </si>
-  <si>
-    <t>Grok distributed Weld</t>
-  </si>
-  <si>
-    <t>Beth Jones, Chad King</t>
-  </si>
-  <si>
-    <t>Weld</t>
-  </si>
-  <si>
-    <t>S14</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable RestEasy</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>RestEasy</t>
-  </si>
-  <si>
-    <t>S15</t>
-  </si>
-  <si>
-    <t>Using secure Android</t>
-  </si>
-  <si>
-    <t>Android</t>
-  </si>
-  <si>
-    <t>S16</t>
-  </si>
-  <si>
-    <t>Deliver stable Tensorflow</t>
-  </si>
-  <si>
-    <t>Flo Rye, Gus Smith</t>
-  </si>
-  <si>
-    <t>Security, Mobile</t>
-  </si>
-  <si>
-    <t>Tensorflow</t>
-  </si>
-  <si>
-    <t>S17</t>
-  </si>
-  <si>
-    <t>Implement platform-independent VertX</t>
-  </si>
-  <si>
-    <t>VertX</t>
-  </si>
-  <si>
-    <t>S18</t>
-  </si>
-  <si>
-    <t>Program flexible JUnit</t>
-  </si>
-  <si>
-    <t>JUnit</t>
-  </si>
-  <si>
-    <t>S19</t>
-  </si>
-  <si>
-    <t>Hack modularized Keycloak</t>
-  </si>
-  <si>
-    <t>IoT</t>
-  </si>
-  <si>
-    <t>Keycloak</t>
-  </si>
-  <si>
-    <t>S20</t>
-  </si>
-  <si>
-    <t>Hands on real-time WildFly</t>
-  </si>
-  <si>
-    <t>Amy Jones, Beth King</t>
-  </si>
-  <si>
-    <t>S21</t>
-  </si>
-  <si>
-    <t>Advanced containerized Spring</t>
-  </si>
-  <si>
-    <t>Chad Li, Dan Poe</t>
-  </si>
-  <si>
-    <t>S22</t>
-  </si>
-  <si>
-    <t>Learn virtualized Drools</t>
-  </si>
-  <si>
-    <t>Elsa Rye, Flo Smith</t>
-  </si>
-  <si>
-    <t>S23</t>
-  </si>
-  <si>
-    <t>Intro to serverless OptaPlanner</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>Discover AI-driven jBPM</t>
-  </si>
-  <si>
-    <t>S25</t>
-  </si>
-  <si>
-    <t>Mastering machine learning Camel</t>
-  </si>
-  <si>
-    <t>S26</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven XStream</t>
-  </si>
-  <si>
-    <t>Middleware, Culture</t>
-  </si>
-  <si>
-    <t>S27</t>
-  </si>
-  <si>
-    <t>Building deep learning Docker</t>
+    <t>S41</t>
+  </si>
+  <si>
+    <t>Advanced containerized Drools</t>
+  </si>
+  <si>
+    <t>S42</t>
+  </si>
+  <si>
+    <t>Learn virtualized OptaPlanner</t>
+  </si>
+  <si>
+    <t>Modern Web, IoT</t>
+  </si>
+  <si>
+    <t>S43</t>
+  </si>
+  <si>
+    <t>Intro to serverless jBPM</t>
+  </si>
+  <si>
+    <t>S44</t>
+  </si>
+  <si>
+    <t>Discover AI-driven Camel</t>
+  </si>
+  <si>
+    <t>S45</t>
+  </si>
+  <si>
+    <t>Mastering machine learning XStream</t>
+  </si>
+  <si>
+    <t>Culture, Mobile</t>
+  </si>
+  <si>
+    <t>S46</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Docker</t>
+  </si>
+  <si>
+    <t>Ivy Watt, Jay Cole</t>
+  </si>
+  <si>
+    <t>Modern Web, Security</t>
+  </si>
+  <si>
+    <t>S47</t>
+  </si>
+  <si>
+    <t>Building deep learning Hibernate</t>
+  </si>
+  <si>
+    <t>Security, IoT</t>
+  </si>
+  <si>
+    <t>S48</t>
+  </si>
+  <si>
+    <t>Securing scalable GWT</t>
+  </si>
+  <si>
+    <t>S49</t>
+  </si>
+  <si>
+    <t>Debug enterprise Errai</t>
+  </si>
+  <si>
+    <t>S50</t>
+  </si>
+  <si>
+    <t>Prepare for streaming Angular</t>
+  </si>
+  <si>
+    <t>Elsa Poe, Flo Rye</t>
+  </si>
+  <si>
+    <t>S51</t>
+  </si>
+  <si>
+    <t>Understand mobile Weld</t>
+  </si>
+  <si>
+    <t>Financial services</t>
+  </si>
+  <si>
+    <t>S52</t>
+  </si>
+  <si>
+    <t>Applying modern RestEasy</t>
+  </si>
+  <si>
+    <t>S53</t>
+  </si>
+  <si>
+    <t>Grok distributed Android</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Security</t>
+  </si>
+  <si>
+    <t>S54</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable Tensorflow</t>
+  </si>
+  <si>
+    <t>Jay Fox, Amy Jones</t>
+  </si>
+  <si>
+    <t>S55</t>
+  </si>
+  <si>
+    <t>Using secure VertX</t>
+  </si>
+  <si>
+    <t>Beth King, Chad Li</t>
+  </si>
+  <si>
+    <t>S56</t>
+  </si>
+  <si>
+    <t>Deliver stable JUnit</t>
+  </si>
+  <si>
+    <t>Dan Poe, Elsa Rye</t>
+  </si>
+  <si>
+    <t>S57</t>
+  </si>
+  <si>
+    <t>Implement platform-independent Keycloak</t>
+  </si>
+  <si>
+    <t>S58</t>
+  </si>
+  <si>
+    <t>Program flexible OpenShift</t>
+  </si>
+  <si>
+    <t>S59</t>
+  </si>
+  <si>
+    <t>Hack modularized WildFly</t>
+  </si>
+  <si>
+    <t>Hugo Cole, Ivy Fox</t>
+  </si>
+  <si>
+    <t>S60</t>
+  </si>
+  <si>
+    <t>Hands on real-time Drools</t>
+  </si>
+  <si>
+    <t>IoT, Mobile</t>
+  </si>
+  <si>
+    <t>S61</t>
+  </si>
+  <si>
+    <t>Advanced containerized OptaPlanner</t>
   </si>
   <si>
     <t>Amy King, Beth Li</t>
   </si>
   <si>
-    <t>Docker, Kubernetes</t>
-  </si>
-  <si>
-    <t>S28</t>
-  </si>
-  <si>
-    <t>Securing scalable Hibernate</t>
-  </si>
-  <si>
-    <t>S29</t>
-  </si>
-  <si>
-    <t>Debug enterprise GWT</t>
-  </si>
-  <si>
-    <t>S30</t>
-  </si>
-  <si>
-    <t>Prepare for streaming Errai</t>
-  </si>
-  <si>
-    <t>S31</t>
-  </si>
-  <si>
-    <t>Understand mobile Angular</t>
-  </si>
-  <si>
-    <t>Mobile, Culture</t>
-  </si>
-  <si>
-    <t>S32</t>
-  </si>
-  <si>
-    <t>Applying modern Weld</t>
-  </si>
-  <si>
-    <t>Modern Web, Middleware</t>
-  </si>
-  <si>
-    <t>S33</t>
-  </si>
-  <si>
-    <t>Grok distributed RestEasy</t>
-  </si>
-  <si>
-    <t>Modern Web, Cloud</t>
-  </si>
-  <si>
-    <t>S34</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable Android</t>
-  </si>
-  <si>
-    <t>S35</t>
-  </si>
-  <si>
-    <t>Using secure Tensorflow</t>
-  </si>
-  <si>
-    <t>S36</t>
-  </si>
-  <si>
-    <t>Deliver stable VertX</t>
-  </si>
-  <si>
-    <t>Cloud, Middleware</t>
-  </si>
-  <si>
-    <t>S37</t>
-  </si>
-  <si>
-    <t>Implement platform-independent JUnit</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>S38</t>
-  </si>
-  <si>
-    <t>Program flexible Keycloak</t>
-  </si>
-  <si>
-    <t>S39</t>
-  </si>
-  <si>
-    <t>Hack modularized OpenShift</t>
-  </si>
-  <si>
-    <t>OpenShift</t>
-  </si>
-  <si>
-    <t>S40</t>
-  </si>
-  <si>
-    <t>Hands on real-time Spring</t>
-  </si>
-  <si>
-    <t>S41</t>
-  </si>
-  <si>
-    <t>Advanced containerized Drools</t>
-  </si>
-  <si>
-    <t>S42</t>
-  </si>
-  <si>
-    <t>Learn virtualized OptaPlanner</t>
-  </si>
-  <si>
-    <t>Jay Watt, Amy Fox</t>
-  </si>
-  <si>
-    <t>S43</t>
-  </si>
-  <si>
-    <t>Intro to serverless jBPM</t>
-  </si>
-  <si>
-    <t>S44</t>
-  </si>
-  <si>
-    <t>Discover AI-driven Camel</t>
-  </si>
-  <si>
-    <t>S45</t>
-  </si>
-  <si>
-    <t>Mastering machine learning XStream</t>
-  </si>
-  <si>
-    <t>S46</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Docker</t>
-  </si>
-  <si>
-    <t>S47</t>
-  </si>
-  <si>
-    <t>Building deep learning Hibernate</t>
-  </si>
-  <si>
-    <t>S48</t>
-  </si>
-  <si>
-    <t>Securing scalable GWT</t>
-  </si>
-  <si>
-    <t>S49</t>
-  </si>
-  <si>
-    <t>Debug enterprise Errai</t>
-  </si>
-  <si>
-    <t>IoT, Mobile</t>
-  </si>
-  <si>
-    <t>S50</t>
-  </si>
-  <si>
-    <t>Prepare for streaming Angular</t>
-  </si>
-  <si>
-    <t>S51</t>
-  </si>
-  <si>
-    <t>Understand mobile Weld</t>
-  </si>
-  <si>
-    <t>S52</t>
-  </si>
-  <si>
-    <t>Applying modern RestEasy</t>
-  </si>
-  <si>
-    <t>S53</t>
-  </si>
-  <si>
-    <t>Grok distributed Android</t>
-  </si>
-  <si>
-    <t>S54</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable Tensorflow</t>
-  </si>
-  <si>
-    <t>Elsa Poe, Flo Rye</t>
-  </si>
-  <si>
-    <t>S55</t>
-  </si>
-  <si>
-    <t>Using secure VertX</t>
-  </si>
-  <si>
-    <t>S56</t>
-  </si>
-  <si>
-    <t>Deliver stable JUnit</t>
-  </si>
-  <si>
-    <t>Security, Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>S57</t>
-  </si>
-  <si>
-    <t>Implement platform-independent Keycloak</t>
-  </si>
-  <si>
-    <t>Ivy Cole, Jay Fox</t>
-  </si>
-  <si>
-    <t>S58</t>
-  </si>
-  <si>
-    <t>Program flexible OpenShift</t>
-  </si>
-  <si>
-    <t>Amy Jones, Beth King, Chad Li</t>
-  </si>
-  <si>
-    <t>S59</t>
-  </si>
-  <si>
-    <t>Hack modularized WildFly</t>
-  </si>
-  <si>
-    <t>S60</t>
-  </si>
-  <si>
-    <t>Hands on real-time Drools</t>
-  </si>
-  <si>
-    <t>S61</t>
-  </si>
-  <si>
-    <t>Advanced containerized OptaPlanner</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence, Mobile</t>
-  </si>
-  <si>
     <t>S62</t>
   </si>
   <si>
     <t>Learn virtualized jBPM</t>
   </si>
   <si>
-    <t>Gus Watt, Hugo Cole</t>
-  </si>
-  <si>
     <t>S63</t>
   </si>
   <si>
     <t>Intro to serverless Camel</t>
   </si>
   <si>
-    <t>Big Data, Middleware</t>
-  </si>
-  <si>
     <t>S64</t>
   </si>
   <si>
@@ -1421,7 +1412,7 @@
     <t>Building deep learning GWT</t>
   </si>
   <si>
-    <t>Chad Poe, Dan Rye</t>
+    <t>Amy Cole, Beth Fox</t>
   </si>
   <si>
     <t>S68</t>
@@ -1430,6 +1421,9 @@
     <t>Securing scalable Errai</t>
   </si>
   <si>
+    <t>Chad Green, Dan Jones, Elsa King, Flo Li</t>
+  </si>
+  <si>
     <t>S69</t>
   </si>
   <si>
@@ -1451,7 +1445,7 @@
     <t>Score</t>
   </si>
   <si>
-    <t>-142init/-45hard</t>
+    <t>-142init</t>
   </si>
   <si>
     <t>Count</t>
@@ -1469,14 +1463,14 @@
     <t>Total</t>
   </si>
   <si>
-    <t>S35: Using secure Tensorflow
-  Beth Fox</t>
+    <t>S54: Troubleshooting reliable Tensorflow
+  Jay Fox, Amy Jones</t>
   </si>
   <si>
     <t>Speaker</t>
   </si>
   <si>
-    <t>S35 @ R 1</t>
+    <t>S54 @ R 1</t>
   </si>
   <si>
     <t>Theme track tag</t>
@@ -1494,7 +1488,7 @@
     <t>Content tag</t>
   </si>
   <si>
-    <t>S35 (level 3)</t>
+    <t>S54 (level 3)</t>
   </si>
   <si>
     <t>Constraint name</t>
@@ -1533,9 +1527,6 @@
     <t>1hard</t>
   </si>
   <si>
-    <t>-45hard</t>
-  </si>
-  <si>
     <t>1medium</t>
   </si>
   <si>
@@ -1551,8 +1542,8 @@
     <t>1soft</t>
   </si>
   <si>
-    <t>Using secure Tensorflow
-Beth Fox</t>
+    <t>Troubleshooting reliable Tensorflow
+Jay Fox, Amy Jones</t>
   </si>
 </sst>
 </file>
@@ -2267,10 +2258,10 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="14.73046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.23828125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
@@ -2328,7 +2319,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -2365,47 +2356,6 @@
       </c>
       <c r="M2" s="1" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="3" ht="15.0" customHeight="true">
-      <c r="A3" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2415,7 +2365,6 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2485,7 +2434,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -2526,13 +2475,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -2642,7 +2591,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -2683,13 +2632,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -2799,7 +2748,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -2840,13 +2789,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -2956,7 +2905,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -2997,13 +2946,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -3052,13 +3001,13 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="17.34375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.65234375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="8.0703125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="6.0859375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="1.0546875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="12.296875" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="12.9296875" customWidth="true" bestFit="true"/>
@@ -3066,39 +3015,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3111,13 +3060,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6">
@@ -3125,13 +3074,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7">
@@ -3139,13 +3088,13 @@
         <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8">
@@ -3153,13 +3102,13 @@
         <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -3167,13 +3116,13 @@
         <v>19</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10">
@@ -3181,13 +3130,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="11">
@@ -3195,10 +3144,10 @@
         <v>26</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>443</v>
@@ -3209,13 +3158,13 @@
         <v>36</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13">
@@ -3223,13 +3172,13 @@
         <v>30</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14">
@@ -3237,13 +3186,13 @@
         <v>34</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15">
@@ -3251,13 +3200,13 @@
         <v>28</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16">
@@ -3265,13 +3214,13 @@
         <v>21</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="17">
@@ -3279,13 +3228,13 @@
         <v>39</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="18">
@@ -3293,13 +3242,13 @@
         <v>33</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19">
@@ -3307,13 +3256,13 @@
         <v>38</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20">
@@ -3321,13 +3270,13 @@
         <v>32</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21">
@@ -3335,13 +3284,13 @@
         <v>40</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="22">
@@ -3349,13 +3298,13 @@
         <v>62</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="23">
@@ -3363,13 +3312,13 @@
         <v>78</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="24">
@@ -3377,13 +3326,13 @@
         <v>71</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25">
@@ -3391,13 +3340,13 @@
         <v>80</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="26">
@@ -3405,13 +3354,13 @@
         <v>74</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="27">
@@ -3419,13 +3368,13 @@
         <v>82</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="28">
@@ -3433,13 +3382,13 @@
         <v>76</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="29">
@@ -3447,13 +3396,13 @@
         <v>83</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="30">
@@ -3461,13 +3410,13 @@
         <v>77</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31">
@@ -3475,13 +3424,13 @@
         <v>60</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="32">
@@ -3489,13 +3438,13 @@
         <v>65</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="33">
@@ -3503,13 +3452,13 @@
         <v>69</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="34">
@@ -3517,13 +3466,13 @@
         <v>43</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="35">
@@ -3531,13 +3480,13 @@
         <v>67</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="36">
@@ -3545,13 +3494,13 @@
         <v>50</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="37">
@@ -3559,13 +3508,13 @@
         <v>46</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="38">
@@ -3573,13 +3522,13 @@
         <v>48</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="39">
@@ -3587,13 +3536,13 @@
         <v>58</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="40">
@@ -3601,13 +3550,13 @@
         <v>52</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="41">
@@ -3615,103 +3564,104 @@
         <v>55</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="42"/>
     <row r="43"/>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="3" t="s">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>447</v>
@@ -3720,68 +3670,68 @@
         <v>0.0</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>444</v>
@@ -3790,236 +3740,236 @@
         <v>0.0</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>446</v>
@@ -4028,133 +3978,119 @@
         <v>0.0</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -4195,8 +4131,8 @@
       <c r="A3" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>449</v>
+      <c r="B3" s="19" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="4" ht="45.0" customHeight="true">
@@ -6394,7 +6330,7 @@
       <c r="K19" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="L19" s="5" t="s">
+      <c r="L19" s="2" t="s">
         <v>93</v>
       </c>
       <c r="M19" s="2" t="s">
@@ -6403,13 +6339,13 @@
       <c r="N19" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="O19" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q19" s="2" t="s">
+      <c r="O19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="P19" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q19" s="5" t="s">
         <v>93</v>
       </c>
       <c r="R19" s="2" t="s">
@@ -6456,7 +6392,7 @@
       <c r="J20" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="K20" s="2" t="s">
         <v>93</v>
       </c>
       <c r="L20" s="2" t="s">
@@ -6796,22 +6732,22 @@
       <c r="O25" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="P25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="U25" s="2" t="s">
+      <c r="P25" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="R25" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="S25" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="T25" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="U25" s="5" t="s">
         <v>93</v>
       </c>
     </row>
@@ -7092,7 +7028,7 @@
         <v>93</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>93</v>
@@ -7160,7 +7096,7 @@
         <v>93</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>93</v>
@@ -7287,7 +7223,7 @@
         <v>93</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>163</v>
+        <v>93</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>93</v>
@@ -7337,7 +7273,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>93</v>
@@ -7363,7 +7299,7 @@
       <c r="I34" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="J34" s="2" t="s">
         <v>93</v>
       </c>
       <c r="K34" s="2" t="s">
@@ -7402,7 +7338,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>93</v>
@@ -7467,7 +7403,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>93</v>
@@ -7532,7 +7468,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>93</v>
@@ -7597,7 +7533,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>93</v>
@@ -7662,7 +7598,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>93</v>
@@ -7727,7 +7663,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>93</v>
@@ -7792,7 +7728,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>93</v>
@@ -7818,13 +7754,13 @@
       <c r="I41" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="J41" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="L41" s="2" t="s">
+      <c r="J41" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L41" s="5" t="s">
         <v>93</v>
       </c>
       <c r="M41" s="2" t="s">
@@ -7836,13 +7772,13 @@
       <c r="O41" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="P41" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q41" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="R41" s="2" t="s">
+      <c r="P41" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q41" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="R41" s="5" t="s">
         <v>93</v>
       </c>
       <c r="S41" s="2" t="s">
@@ -7857,7 +7793,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>93</v>
@@ -7922,7 +7858,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>93</v>
@@ -7957,13 +7893,13 @@
       <c r="L43" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M43" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="N43" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="O43" s="5" t="s">
+      <c r="M43" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="O43" s="2" t="s">
         <v>93</v>
       </c>
       <c r="P43" s="2" t="s">
@@ -7975,19 +7911,19 @@
       <c r="R43" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="S43" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="T43" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="U43" s="5" t="s">
+      <c r="S43" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="T43" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="U43" s="2" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>93</v>
@@ -8052,7 +7988,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>93</v>
@@ -8070,7 +8006,7 @@
         <v>93</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>93</v>
@@ -8117,7 +8053,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>93</v>
@@ -8135,7 +8071,7 @@
         <v>93</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>93</v>
@@ -8182,7 +8118,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>93</v>
@@ -8247,7 +8183,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>93</v>
@@ -8282,13 +8218,13 @@
       <c r="L48" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M48" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="N48" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="O48" s="5" t="s">
+      <c r="M48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="O48" s="2" t="s">
         <v>93</v>
       </c>
       <c r="P48" s="2" t="s">
@@ -8300,19 +8236,19 @@
       <c r="R48" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="S48" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="T48" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="U48" s="5" t="s">
+      <c r="S48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="T48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="U48" s="2" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>93</v>
@@ -8377,7 +8313,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>93</v>
@@ -8458,7 +8394,7 @@
     <col min="1" max="1" width="5.69140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="39.66796875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.41796875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="27.609375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="36.17578125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="27.59375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="19.625" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="16.4453125" customWidth="true" bestFit="true"/>
@@ -8490,34 +8426,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>124</v>
@@ -8544,22 +8480,22 @@
         <v>131</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>85</v>
@@ -8568,27 +8504,27 @@
         <v>86</v>
       </c>
       <c r="AA1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>92</v>
@@ -8597,23 +8533,23 @@
         <v>132</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K2" s="2" t="s">
         <v>93</v>
       </c>
@@ -8645,10 +8581,10 @@
         <v>93</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>915.0</v>
+        <v>435.0</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W2" s="2" t="b">
         <v>0</v>
@@ -8680,35 +8616,35 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K3" s="2" t="s">
         <v>93</v>
       </c>
@@ -8740,10 +8676,10 @@
         <v>93</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>790.0</v>
+        <v>322.0</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W3" s="2" t="b">
         <v>0</v>
@@ -8775,10 +8711,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>92</v>
@@ -8787,22 +8723,22 @@
         <v>135</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="J4" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>93</v>
@@ -8835,10 +8771,10 @@
         <v>93</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>540.0</v>
+        <v>558.0</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W4" s="2" t="b">
         <v>0</v>
@@ -8870,10 +8806,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>92</v>
@@ -8882,13 +8818,13 @@
         <v>136</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>93</v>
+        <v>219</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>2.0</v>
@@ -8897,7 +8833,7 @@
         <v>221</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>93</v>
@@ -8930,10 +8866,10 @@
         <v>93</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>240.0</v>
+        <v>119.0</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W5" s="2" t="b">
         <v>0</v>
@@ -8974,25 +8910,25 @@
         <v>92</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>93</v>
@@ -9025,10 +8961,10 @@
         <v>93</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>522.0</v>
+        <v>838.0</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W6" s="2" t="b">
         <v>0</v>
@@ -9060,34 +8996,34 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="J7" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>93</v>
@@ -9120,10 +9056,10 @@
         <v>93</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>349.0</v>
+        <v>734.0</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W7" s="2" t="b">
         <v>0</v>
@@ -9155,34 +9091,34 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>93</v>
@@ -9215,10 +9151,10 @@
         <v>93</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>217.0</v>
+        <v>946.0</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W8" s="2" t="b">
         <v>0</v>
@@ -9250,34 +9186,34 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>93</v>
+        <v>219</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>93</v>
@@ -9310,10 +9246,10 @@
         <v>93</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>630.0</v>
+        <v>685.0</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W9" s="2" t="b">
         <v>0</v>
@@ -9345,34 +9281,34 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>93</v>
@@ -9405,10 +9341,10 @@
         <v>93</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>295.0</v>
+        <v>236.0</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W10" s="2" t="b">
         <v>0</v>
@@ -9440,34 +9376,34 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>93</v>
@@ -9500,10 +9436,10 @@
         <v>93</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>711.0</v>
+        <v>539.0</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W11" s="2" t="b">
         <v>0</v>
@@ -9535,34 +9471,34 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>93</v>
@@ -9595,10 +9531,10 @@
         <v>93</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>534.0</v>
+        <v>313.0</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W12" s="2" t="b">
         <v>0</v>
@@ -9630,34 +9566,34 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>150</v>
+        <v>252</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>257</v>
+        <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>93</v>
@@ -9690,10 +9626,10 @@
         <v>93</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>529.0</v>
+        <v>740.0</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W13" s="2" t="b">
         <v>0</v>
@@ -9725,35 +9661,35 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>205</v>
+        <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K14" s="2" t="s">
         <v>93</v>
       </c>
@@ -9785,7 +9721,7 @@
         <v>93</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>194.0</v>
+        <v>282.0</v>
       </c>
       <c r="V14" s="2" t="n">
         <v>0.0</v>
@@ -9820,35 +9756,35 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>265</v>
+        <v>151</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K15" s="2" t="s">
         <v>93</v>
       </c>
@@ -9880,7 +9816,7 @@
         <v>93</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>653.0</v>
+        <v>898.0</v>
       </c>
       <c r="V15" s="2" t="n">
         <v>0.0</v>
@@ -9915,34 +9851,34 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>155</v>
+        <v>265</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>93</v>
+        <v>266</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>93</v>
@@ -9975,10 +9911,10 @@
         <v>93</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>682.0</v>
+        <v>243.0</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W16" s="2" t="b">
         <v>0</v>
@@ -10010,34 +9946,34 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>156</v>
+        <v>270</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>93</v>
@@ -10070,10 +10006,10 @@
         <v>93</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>610.0</v>
+        <v>718.0</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W17" s="2" t="b">
         <v>0</v>
@@ -10105,34 +10041,34 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>276</v>
+        <v>156</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>277</v>
+        <v>210</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>93</v>
+        <v>275</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>93</v>
@@ -10165,7 +10101,7 @@
         <v>93</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>88.0</v>
+        <v>348.0</v>
       </c>
       <c r="V18" s="2" t="n">
         <v>0.0</v>
@@ -10200,34 +10136,34 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>240</v>
+        <v>279</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>93</v>
@@ -10260,7 +10196,7 @@
         <v>93</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>935.0</v>
+        <v>299.0</v>
       </c>
       <c r="V19" s="2" t="n">
         <v>0.0</v>
@@ -10295,34 +10231,34 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>93</v>
@@ -10355,7 +10291,7 @@
         <v>93</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>309.0</v>
+        <v>444.0</v>
       </c>
       <c r="V20" s="2" t="n">
         <v>0.0</v>
@@ -10390,34 +10326,34 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>93</v>
@@ -10450,10 +10386,10 @@
         <v>93</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>736.0</v>
+        <v>813.0</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W21" s="2" t="b">
         <v>0</v>
@@ -10485,34 +10421,34 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>93</v>
@@ -10545,7 +10481,7 @@
         <v>93</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>946.0</v>
+        <v>536.0</v>
       </c>
       <c r="V22" s="2" t="n">
         <v>0.0</v>
@@ -10580,34 +10516,34 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>294</v>
+        <v>162</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>93</v>
@@ -10640,7 +10576,7 @@
         <v>93</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>726.0</v>
+        <v>453.0</v>
       </c>
       <c r="V23" s="2" t="n">
         <v>0.0</v>
@@ -10675,34 +10611,34 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>297</v>
+        <v>163</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>93</v>
+        <v>229</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>221</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>93</v>
@@ -10735,7 +10671,7 @@
         <v>93</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>435.0</v>
+        <v>881.0</v>
       </c>
       <c r="V24" s="2" t="n">
         <v>0.0</v>
@@ -10770,35 +10706,35 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G25" s="2" t="s">
+      <c r="J25" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H25" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K25" s="2" t="s">
         <v>93</v>
       </c>
@@ -10830,10 +10766,10 @@
         <v>93</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>87.0</v>
+        <v>75.0</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W25" s="2" t="b">
         <v>0</v>
@@ -10865,34 +10801,34 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>170</v>
+        <v>299</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>93</v>
@@ -10925,7 +10861,7 @@
         <v>93</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>968.0</v>
+        <v>198.0</v>
       </c>
       <c r="V26" s="2" t="n">
         <v>0.0</v>
@@ -10960,34 +10896,34 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>93</v>
@@ -11020,10 +10956,10 @@
         <v>93</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>141.0</v>
+        <v>713.0</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W27" s="2" t="b">
         <v>0</v>
@@ -11055,34 +10991,34 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>93</v>
@@ -11115,7 +11051,7 @@
         <v>93</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>268.0</v>
+        <v>615.0</v>
       </c>
       <c r="V28" s="2" t="n">
         <v>0.0</v>
@@ -11150,34 +11086,34 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>309</v>
+        <v>171</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>93</v>
@@ -11210,10 +11146,10 @@
         <v>93</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>820.0</v>
+        <v>333.0</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W29" s="2" t="b">
         <v>0</v>
@@ -11245,34 +11181,34 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>93</v>
@@ -11305,10 +11241,10 @@
         <v>93</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>258.0</v>
+        <v>480.0</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W30" s="2" t="b">
         <v>0</v>
@@ -11340,34 +11276,34 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>176</v>
+        <v>312</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>93</v>
@@ -11400,10 +11336,10 @@
         <v>93</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>312.0</v>
+        <v>726.0</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W31" s="2" t="b">
         <v>0</v>
@@ -11435,34 +11371,34 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>93</v>
@@ -11495,10 +11431,10 @@
         <v>93</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>774.0</v>
+        <v>868.0</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W32" s="2" t="b">
         <v>0</v>
@@ -11530,35 +11466,35 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>178</v>
+        <v>317</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>319</v>
+        <v>271</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G33" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="J33" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H33" s="2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K33" s="2" t="s">
         <v>93</v>
       </c>
@@ -11590,10 +11526,10 @@
         <v>93</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>161.0</v>
+        <v>679.0</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W33" s="2" t="b">
         <v>0</v>
@@ -11625,34 +11561,34 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>179</v>
+        <v>320</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>322</v>
+        <v>228</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>93</v>
@@ -11685,7 +11621,7 @@
         <v>93</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>377.0</v>
+        <v>655.0</v>
       </c>
       <c r="V34" s="2" t="n">
         <v>0.0</v>
@@ -11720,35 +11656,35 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>325</v>
+        <v>253</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G35" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="J35" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H35" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K35" s="2" t="s">
         <v>93</v>
       </c>
@@ -11780,10 +11716,10 @@
         <v>93</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>208.0</v>
+        <v>735.0</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W35" s="2" t="b">
         <v>0</v>
@@ -11815,34 +11751,34 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>269</v>
+        <v>210</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>93</v>
@@ -11875,10 +11811,10 @@
         <v>93</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>156.0</v>
+        <v>191.0</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W36" s="2" t="b">
         <v>0</v>
@@ -11910,35 +11846,35 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>133</v>
+        <v>327</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>257</v>
+        <v>93</v>
       </c>
       <c r="G37" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="J37" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H37" s="2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K37" s="2" t="s">
         <v>93</v>
       </c>
@@ -11970,25 +11906,25 @@
         <v>93</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>617.0</v>
+        <v>266.0</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="W37" s="6" t="b">
-        <v>1</v>
+        <v>0.0</v>
+      </c>
+      <c r="W37" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA37" s="2" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="AB37" s="2" t="s">
         <v>93</v>
@@ -12005,34 +11941,34 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>134</v>
+        <v>330</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>332</v>
+        <v>253</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>93</v>
@@ -12065,7 +12001,7 @@
         <v>93</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>572.0</v>
+        <v>460.0</v>
       </c>
       <c r="V38" s="2" t="n">
         <v>0.0</v>
@@ -12100,35 +12036,35 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>204</v>
+        <v>271</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>335</v>
+        <v>93</v>
       </c>
       <c r="G39" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="J39" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H39" s="2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K39" s="2" t="s">
         <v>93</v>
       </c>
@@ -12160,10 +12096,10 @@
         <v>93</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>618.0</v>
+        <v>926.0</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W39" s="2" t="b">
         <v>0</v>
@@ -12195,35 +12131,35 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G40" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J40" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H40" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K40" s="2" t="s">
         <v>93</v>
       </c>
@@ -12255,10 +12191,10 @@
         <v>93</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>642.0</v>
+        <v>193.0</v>
       </c>
       <c r="V40" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W40" s="2" t="b">
         <v>0</v>
@@ -12290,34 +12226,34 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>224</v>
+        <v>140</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>205</v>
+        <v>93</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>93</v>
@@ -12350,10 +12286,10 @@
         <v>93</v>
       </c>
       <c r="U41" s="2" t="n">
-        <v>158.0</v>
+        <v>454.0</v>
       </c>
       <c r="V41" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W41" s="2" t="b">
         <v>0</v>
@@ -12385,34 +12321,34 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>139</v>
+        <v>340</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>216</v>
+        <v>341</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>93</v>
@@ -12445,10 +12381,10 @@
         <v>93</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>493.0</v>
+        <v>291.0</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W42" s="2" t="b">
         <v>0</v>
@@ -12480,34 +12416,34 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>221</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>93</v>
@@ -12540,10 +12476,10 @@
         <v>93</v>
       </c>
       <c r="U43" s="2" t="n">
-        <v>569.0</v>
+        <v>272.0</v>
       </c>
       <c r="V43" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W43" s="2" t="b">
         <v>0</v>
@@ -12575,35 +12511,35 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>347</v>
+        <v>144</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>240</v>
+        <v>346</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G44" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J44" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H44" s="2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K44" s="2" t="s">
         <v>93</v>
       </c>
@@ -12635,10 +12571,10 @@
         <v>93</v>
       </c>
       <c r="U44" s="2" t="n">
-        <v>718.0</v>
+        <v>964.0</v>
       </c>
       <c r="V44" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W44" s="2" t="b">
         <v>0</v>
@@ -12670,35 +12606,35 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>349</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>143</v>
+        <v>248</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G45" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J45" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H45" s="2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K45" s="2" t="s">
         <v>93</v>
       </c>
@@ -12730,7 +12666,7 @@
         <v>93</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>995.0</v>
+        <v>530.0</v>
       </c>
       <c r="V45" s="2" t="n">
         <v>0.0</v>
@@ -12765,34 +12701,34 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>144</v>
+        <v>252</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>93</v>
+        <v>229</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>93</v>
@@ -12825,7 +12761,7 @@
         <v>93</v>
       </c>
       <c r="U46" s="2" t="n">
-        <v>327.0</v>
+        <v>228.0</v>
       </c>
       <c r="V46" s="2" t="n">
         <v>0.0</v>
@@ -12860,34 +12796,34 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>353</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>204</v>
+        <v>353</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>335</v>
+        <v>93</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>93</v>
@@ -12920,10 +12856,10 @@
         <v>93</v>
       </c>
       <c r="U47" s="2" t="n">
-        <v>588.0</v>
+        <v>318.0</v>
       </c>
       <c r="V47" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W47" s="2" t="b">
         <v>0</v>
@@ -12964,25 +12900,25 @@
         <v>95</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>248</v>
+        <v>356</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>212</v>
+        <v>357</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>93</v>
@@ -13015,10 +12951,10 @@
         <v>93</v>
       </c>
       <c r="U48" s="2" t="n">
-        <v>277.0</v>
+        <v>454.0</v>
       </c>
       <c r="V48" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W48" s="2" t="b">
         <v>0</v>
@@ -13050,35 +12986,35 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>204</v>
+        <v>360</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G49" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J49" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H49" s="2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K49" s="2" t="s">
         <v>93</v>
       </c>
@@ -13110,10 +13046,10 @@
         <v>93</v>
       </c>
       <c r="U49" s="2" t="n">
-        <v>928.0</v>
+        <v>903.0</v>
       </c>
       <c r="V49" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W49" s="2" t="b">
         <v>0</v>
@@ -13145,34 +13081,34 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E50" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>93</v>
@@ -13205,10 +13141,10 @@
         <v>93</v>
       </c>
       <c r="U50" s="2" t="n">
-        <v>659.0</v>
+        <v>837.0</v>
       </c>
       <c r="V50" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W50" s="2" t="b">
         <v>0</v>
@@ -13240,34 +13176,34 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>93</v>
+        <v>266</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>93</v>
@@ -13300,10 +13236,10 @@
         <v>93</v>
       </c>
       <c r="U51" s="2" t="n">
-        <v>402.0</v>
+        <v>571.0</v>
       </c>
       <c r="V51" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W51" s="2" t="b">
         <v>0</v>
@@ -13335,35 +13271,35 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>151</v>
+        <v>367</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>332</v>
+        <v>237</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G52" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="J52" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H52" s="2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K52" s="2" t="s">
         <v>93</v>
       </c>
@@ -13395,10 +13331,10 @@
         <v>93</v>
       </c>
       <c r="U52" s="2" t="n">
-        <v>648.0</v>
+        <v>113.0</v>
       </c>
       <c r="V52" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W52" s="2" t="b">
         <v>0</v>
@@ -13430,34 +13366,34 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>226</v>
-      </c>
       <c r="H53" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>93</v>
@@ -13490,10 +13426,10 @@
         <v>93</v>
       </c>
       <c r="U53" s="2" t="n">
-        <v>900.0</v>
+        <v>989.0</v>
       </c>
       <c r="V53" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W53" s="2" t="b">
         <v>0</v>
@@ -13525,34 +13461,34 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>265</v>
+        <v>159</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>240</v>
+        <v>341</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>93</v>
@@ -13585,10 +13521,10 @@
         <v>93</v>
       </c>
       <c r="U54" s="2" t="n">
-        <v>283.0</v>
+        <v>853.0</v>
       </c>
       <c r="V54" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W54" s="2" t="b">
         <v>0</v>
@@ -13620,35 +13556,35 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>216</v>
+        <v>375</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>93</v>
+        <v>266</v>
       </c>
       <c r="G55" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="J55" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H55" s="2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K55" s="2" t="s">
         <v>93</v>
       </c>
@@ -13680,10 +13616,10 @@
         <v>93</v>
       </c>
       <c r="U55" s="2" t="n">
-        <v>514.0</v>
+        <v>884.0</v>
       </c>
       <c r="V55" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W55" s="2" t="b">
         <v>0</v>
@@ -13715,34 +13651,34 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>93</v>
@@ -13775,25 +13711,25 @@
         <v>93</v>
       </c>
       <c r="U56" s="2" t="n">
-        <v>601.0</v>
+        <v>938.0</v>
       </c>
       <c r="V56" s="2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="W56" s="2" t="b">
-        <v>0</v>
+        <v>0.0</v>
+      </c>
+      <c r="W56" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="Z56" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AA56" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="AB56" s="2" t="s">
         <v>93</v>
@@ -13810,34 +13746,34 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>158</v>
+        <v>381</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>269</v>
+        <v>203</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>93</v>
@@ -13870,10 +13806,10 @@
         <v>93</v>
       </c>
       <c r="U57" s="2" t="n">
-        <v>307.0</v>
+        <v>991.0</v>
       </c>
       <c r="V57" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W57" s="2" t="b">
         <v>0</v>
@@ -13905,34 +13841,34 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>159</v>
+        <v>384</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>378</v>
+        <v>271</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>93</v>
@@ -13965,10 +13901,10 @@
         <v>93</v>
       </c>
       <c r="U58" s="2" t="n">
-        <v>525.0</v>
+        <v>530.0</v>
       </c>
       <c r="V58" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W58" s="2" t="b">
         <v>0</v>
@@ -14000,34 +13936,34 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>381</v>
+        <v>167</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>93</v>
@@ -14060,7 +13996,7 @@
         <v>93</v>
       </c>
       <c r="U59" s="2" t="n">
-        <v>968.0</v>
+        <v>364.0</v>
       </c>
       <c r="V59" s="2" t="n">
         <v>0.0</v>
@@ -14095,35 +14031,35 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>384</v>
+        <v>168</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G60" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="J60" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H60" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K60" s="2" t="s">
         <v>93</v>
       </c>
@@ -14155,10 +14091,10 @@
         <v>93</v>
       </c>
       <c r="U60" s="2" t="n">
-        <v>356.0</v>
+        <v>768.0</v>
       </c>
       <c r="V60" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W60" s="2" t="b">
         <v>0</v>
@@ -14190,34 +14126,34 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>166</v>
+        <v>391</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>93</v>
@@ -14250,10 +14186,10 @@
         <v>93</v>
       </c>
       <c r="U61" s="2" t="n">
-        <v>125.0</v>
+        <v>877.0</v>
       </c>
       <c r="V61" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W61" s="2" t="b">
         <v>0</v>
@@ -14285,34 +14221,34 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>244</v>
+        <v>394</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>221</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>93</v>
@@ -14345,7 +14281,7 @@
         <v>93</v>
       </c>
       <c r="U62" s="2" t="n">
-        <v>404.0</v>
+        <v>402.0</v>
       </c>
       <c r="V62" s="2" t="n">
         <v>0.0</v>
@@ -14380,34 +14316,34 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>168</v>
+        <v>397</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>391</v>
+        <v>237</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>93</v>
@@ -14440,10 +14376,10 @@
         <v>93</v>
       </c>
       <c r="U63" s="2" t="n">
-        <v>125.0</v>
+        <v>703.0</v>
       </c>
       <c r="V63" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W63" s="2" t="b">
         <v>0</v>
@@ -14475,34 +14411,34 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>394</v>
+        <v>174</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>93</v>
@@ -14535,10 +14471,10 @@
         <v>93</v>
       </c>
       <c r="U64" s="2" t="n">
-        <v>591.0</v>
+        <v>150.0</v>
       </c>
       <c r="V64" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W64" s="2" t="b">
         <v>0</v>
@@ -14570,34 +14506,34 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>397</v>
+        <v>253</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>93</v>
@@ -14633,7 +14569,7 @@
         <v>778.0</v>
       </c>
       <c r="V65" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W65" s="2" t="b">
         <v>0</v>
@@ -14665,34 +14601,34 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>93</v>
@@ -14725,10 +14661,10 @@
         <v>93</v>
       </c>
       <c r="U66" s="2" t="n">
-        <v>310.0</v>
+        <v>362.0</v>
       </c>
       <c r="V66" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W66" s="2" t="b">
         <v>0</v>
@@ -14760,34 +14696,34 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>93</v>
@@ -14820,10 +14756,10 @@
         <v>93</v>
       </c>
       <c r="U67" s="2" t="n">
-        <v>658.0</v>
+        <v>194.0</v>
       </c>
       <c r="V67" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W67" s="2" t="b">
         <v>0</v>
@@ -14855,34 +14791,34 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>174</v>
+        <v>320</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>93</v>
@@ -14915,10 +14851,10 @@
         <v>93</v>
       </c>
       <c r="U68" s="2" t="n">
-        <v>564.0</v>
+        <v>251.0</v>
       </c>
       <c r="V68" s="2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="W68" s="2" t="b">
         <v>0</v>
@@ -14950,34 +14886,34 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>231</v>
+        <v>341</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>93</v>
@@ -15010,7 +14946,7 @@
         <v>93</v>
       </c>
       <c r="U69" s="2" t="n">
-        <v>357.0</v>
+        <v>759.0</v>
       </c>
       <c r="V69" s="2" t="n">
         <v>0.0</v>
@@ -15045,34 +14981,34 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>177</v>
+        <v>413</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>93</v>
+        <v>370</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>93</v>
@@ -15105,10 +15041,10 @@
         <v>93</v>
       </c>
       <c r="U70" s="2" t="n">
-        <v>97.0</v>
+        <v>239.0</v>
       </c>
       <c r="V70" s="2" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="W70" s="2" t="b">
         <v>0</v>
@@ -15140,34 +15076,34 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>204</v>
+        <v>271</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>93</v>
@@ -15200,10 +15136,10 @@
         <v>93</v>
       </c>
       <c r="U71" s="2" t="n">
-        <v>626.0</v>
+        <v>310.0</v>
       </c>
       <c r="V71" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W71" s="2" t="b">
         <v>0</v>
@@ -15235,34 +15171,34 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>287</v>
+        <v>215</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>93</v>
+        <v>229</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>93</v>
@@ -15295,10 +15231,10 @@
         <v>93</v>
       </c>
       <c r="U72" s="2" t="n">
-        <v>231.0</v>
+        <v>621.0</v>
       </c>
       <c r="V72" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="W72" s="2" t="b">
         <v>0</v>
@@ -15330,34 +15266,34 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>93</v>
@@ -15390,10 +15326,10 @@
         <v>93</v>
       </c>
       <c r="U73" s="2" t="n">
-        <v>548.0</v>
+        <v>125.0</v>
       </c>
       <c r="V73" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="W73" s="2" t="b">
         <v>0</v>
@@ -15438,7 +15374,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.4453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="15.84375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="7.95703125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.22265625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="13.59375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="15.30078125" customWidth="true" bestFit="true"/>
@@ -15446,28 +15382,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4">
@@ -15507,7 +15443,7 @@
     <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>72.0</v>
@@ -15607,7 +15543,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -15654,7 +15590,7 @@
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -16146,7 +16082,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -16233,8 +16169,8 @@
       <c r="B4" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>424</v>
+      <c r="C4" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>93</v>
@@ -16851,7 +16787,7 @@
       <c r="C19" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="10" t="s">
         <v>93</v>
       </c>
       <c r="E19" s="10" t="s">
@@ -16860,13 +16796,13 @@
       <c r="F19" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="I19" s="10" t="s">
+      <c r="G19" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>93</v>
       </c>
       <c r="J19" s="10" t="s">
@@ -16889,7 +16825,7 @@
       <c r="B20" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="10" t="s">
         <v>93</v>
       </c>
       <c r="D20" s="10" t="s">
@@ -17109,22 +17045,22 @@
       <c r="G25" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="H25" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="M25" s="10" t="s">
+      <c r="H25" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="M25" s="5" t="s">
         <v>93</v>
       </c>
     </row>
@@ -17381,8 +17317,8 @@
       <c r="B32" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>93</v>
+      <c r="C32" s="6" t="s">
+        <v>429</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>93</v>
@@ -17422,8 +17358,8 @@
       <c r="B33" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>93</v>
+      <c r="C33" s="6" t="s">
+        <v>429</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>93</v>
@@ -17458,9 +17394,9 @@
     </row>
     <row r="34" ht="15.0" customHeight="true">
       <c r="A34" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B34" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B34" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C34" s="10" t="s">
@@ -17499,7 +17435,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="true">
       <c r="A35" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>93</v>
@@ -17540,7 +17476,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="true">
       <c r="A36" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>93</v>
@@ -17581,7 +17517,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="true">
       <c r="A37" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>93</v>
@@ -17622,7 +17558,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="true">
       <c r="A38" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>93</v>
@@ -17663,7 +17599,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="true">
       <c r="A39" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>93</v>
@@ -17704,7 +17640,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="true">
       <c r="A40" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>93</v>
@@ -17745,15 +17681,15 @@
     </row>
     <row r="41" ht="15.0" customHeight="true">
       <c r="A41" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D41" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E41" s="10" t="s">
@@ -17765,13 +17701,13 @@
       <c r="G41" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="H41" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="J41" s="10" t="s">
+      <c r="H41" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J41" s="5" t="s">
         <v>93</v>
       </c>
       <c r="K41" s="10" t="s">
@@ -17786,7 +17722,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="true">
       <c r="A42" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>93</v>
@@ -17827,7 +17763,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="true">
       <c r="A43" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>93</v>
@@ -17838,13 +17774,13 @@
       <c r="D43" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G43" s="5" t="s">
+      <c r="E43" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>93</v>
       </c>
       <c r="H43" s="10" t="s">
@@ -17856,19 +17792,19 @@
       <c r="J43" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="K43" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="L43" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="M43" s="5" t="s">
+      <c r="K43" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="M43" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="44" ht="15.0" customHeight="true">
       <c r="A44" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>93</v>
@@ -17909,7 +17845,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="true">
       <c r="A45" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>93</v>
@@ -17950,7 +17886,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="true">
       <c r="A46" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>93</v>
@@ -17991,7 +17927,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="true">
       <c r="A47" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>93</v>
@@ -18032,7 +17968,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="true">
       <c r="A48" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>93</v>
@@ -18043,13 +17979,13 @@
       <c r="D48" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G48" s="5" t="s">
+      <c r="E48" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G48" s="10" t="s">
         <v>93</v>
       </c>
       <c r="H48" s="10" t="s">
@@ -18061,19 +17997,19 @@
       <c r="J48" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="K48" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="L48" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="M48" s="5" t="s">
+      <c r="K48" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="L48" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="M48" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="49" ht="15.0" customHeight="true">
       <c r="A49" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>93</v>
@@ -18114,7 +18050,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="true">
       <c r="A50" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>93</v>
@@ -18230,7 +18166,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -18271,13 +18207,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/72talks-12timeslots-10rooms.xlsx
@@ -235,7 +235,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4731" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4731" uniqueCount="460">
   <si>
     <t>Conference name</t>
   </si>
@@ -877,9 +877,6 @@
   </si>
   <si>
     <t>WildFly</t>
-  </si>
-  <si>
-    <t>Large, Recorded</t>
   </si>
   <si>
     <t>S02</t>
@@ -2397,7 +2394,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>107</v>
@@ -2512,7 +2509,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>107</v>
@@ -2559,7 +2556,7 @@
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -2597,7 +2594,7 @@
         <v>212</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>93</v>
@@ -2751,10 +2748,10 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>93</v>
@@ -2792,13 +2789,13 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>93</v>
@@ -2908,7 +2905,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>107</v>
@@ -2949,13 +2946,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -2990,10 +2987,10 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>93</v>
@@ -3150,10 +3147,10 @@
         <v>208</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -3216,39 +3213,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3261,13 +3258,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="6">
@@ -3275,13 +3272,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7">
@@ -3289,13 +3286,13 @@
         <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8">
@@ -3303,13 +3300,13 @@
         <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -3317,13 +3314,13 @@
         <v>19</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10">
@@ -3331,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11">
@@ -3345,13 +3342,13 @@
         <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12">
@@ -3359,13 +3356,13 @@
         <v>31</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="13">
@@ -3373,13 +3370,13 @@
         <v>35</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14">
@@ -3387,13 +3384,13 @@
         <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="15">
@@ -3401,13 +3398,13 @@
         <v>21</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16">
@@ -3415,13 +3412,13 @@
         <v>40</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="17">
@@ -3429,13 +3426,13 @@
         <v>34</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18">
@@ -3443,13 +3440,13 @@
         <v>39</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19">
@@ -3457,13 +3454,13 @@
         <v>33</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20">
@@ -3471,13 +3468,13 @@
         <v>41</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="21">
@@ -3485,13 +3482,13 @@
         <v>62</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22">
@@ -3499,13 +3496,13 @@
         <v>78</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="23">
@@ -3513,13 +3510,13 @@
         <v>71</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="24">
@@ -3527,13 +3524,13 @@
         <v>80</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="25">
@@ -3541,13 +3538,13 @@
         <v>74</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26">
@@ -3555,13 +3552,13 @@
         <v>82</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="27">
@@ -3569,13 +3566,13 @@
         <v>76</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="28">
@@ -3583,13 +3580,13 @@
         <v>83</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="29">
@@ -3597,13 +3594,13 @@
         <v>77</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="30">
@@ -3611,13 +3608,13 @@
         <v>60</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="31">
@@ -3625,13 +3622,13 @@
         <v>65</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="32">
@@ -3639,13 +3636,13 @@
         <v>69</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="33">
@@ -3653,13 +3650,13 @@
         <v>44</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="34">
@@ -3667,13 +3664,13 @@
         <v>67</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="35">
@@ -3681,13 +3678,13 @@
         <v>51</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="36">
@@ -3695,13 +3692,13 @@
         <v>47</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="37">
@@ -3709,13 +3706,13 @@
         <v>49</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="38">
@@ -3723,13 +3720,13 @@
         <v>58</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="39">
@@ -3737,13 +3734,13 @@
         <v>53</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="40">
@@ -3751,13 +3748,13 @@
         <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="41">
@@ -3765,13 +3762,13 @@
         <v>26</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="42"/>
@@ -3781,13 +3778,13 @@
         <v>58</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="45">
@@ -3795,13 +3792,13 @@
         <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="46">
@@ -3809,13 +3806,13 @@
         <v>56</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="47">
@@ -3823,13 +3820,13 @@
         <v>24</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="48">
@@ -3837,13 +3834,13 @@
         <v>60</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="49">
@@ -3851,13 +3848,13 @@
         <v>62</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="50">
@@ -3865,13 +3862,13 @@
         <v>26</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="51">
@@ -3879,13 +3876,13 @@
         <v>65</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="52">
@@ -3893,13 +3890,13 @@
         <v>69</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="53">
@@ -3907,13 +3904,13 @@
         <v>44</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="54">
@@ -3921,13 +3918,13 @@
         <v>41</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="55">
@@ -3935,13 +3932,13 @@
         <v>10</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="56">
@@ -3949,13 +3946,13 @@
         <v>7</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="57">
@@ -3963,13 +3960,13 @@
         <v>67</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="58">
@@ -3977,13 +3974,13 @@
         <v>51</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="59">
@@ -3991,13 +3988,13 @@
         <v>16</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="60">
@@ -4005,13 +4002,13 @@
         <v>78</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="61">
@@ -4019,13 +4016,13 @@
         <v>71</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="62">
@@ -4033,13 +4030,13 @@
         <v>37</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="63">
@@ -4047,13 +4044,13 @@
         <v>31</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="64">
@@ -4061,13 +4058,13 @@
         <v>35</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="65">
@@ -4075,13 +4072,13 @@
         <v>29</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="66">
@@ -4089,13 +4086,13 @@
         <v>13</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="67">
@@ -4103,13 +4100,13 @@
         <v>80</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="68">
@@ -4117,13 +4114,13 @@
         <v>74</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="69">
@@ -4131,13 +4128,13 @@
         <v>21</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="70">
@@ -4145,13 +4142,13 @@
         <v>82</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="71">
@@ -4159,13 +4156,13 @@
         <v>76</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="72">
@@ -4173,13 +4170,13 @@
         <v>19</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="73">
@@ -4187,13 +4184,13 @@
         <v>40</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="74">
@@ -4201,13 +4198,13 @@
         <v>34</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="75">
@@ -4215,13 +4212,13 @@
         <v>39</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="76">
@@ -4229,13 +4226,13 @@
         <v>33</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="77">
@@ -4243,13 +4240,13 @@
         <v>83</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="78">
@@ -4257,13 +4254,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="79">
@@ -4271,13 +4268,13 @@
         <v>47</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="80">
@@ -4285,13 +4282,13 @@
         <v>49</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -4332,7 +4329,7 @@
         <v>93</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" ht="45.0" customHeight="true">
@@ -4340,7 +4337,7 @@
         <v>108</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C3" s="2"/>
     </row>
@@ -8883,7 +8880,7 @@
         <v>93</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>214</v>
+        <v>93</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>93</v>
@@ -8933,10 +8930,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>92</v>
@@ -8945,19 +8942,19 @@
         <v>136</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>208</v>
@@ -8978,7 +8975,7 @@
         <v>93</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>93</v>
@@ -9028,31 +9025,31 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>205</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>208</v>
@@ -9073,7 +9070,7 @@
         <v>93</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>93</v>
@@ -9123,19 +9120,19 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -9147,7 +9144,7 @@
         <v>1.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>208</v>
@@ -9168,7 +9165,7 @@
         <v>93</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>93</v>
@@ -9218,10 +9215,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>92</v>
@@ -9230,7 +9227,7 @@
         <v>142</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -9242,7 +9239,7 @@
         <v>3.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>208</v>
@@ -9263,7 +9260,7 @@
         <v>93</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>93</v>
@@ -9313,10 +9310,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>92</v>
@@ -9325,10 +9322,10 @@
         <v>143</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>206</v>
@@ -9337,7 +9334,7 @@
         <v>1.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>208</v>
@@ -9408,19 +9405,19 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>241</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -9432,7 +9429,7 @@
         <v>1.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>208</v>
@@ -9453,7 +9450,7 @@
         <v>93</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>93</v>
@@ -9503,10 +9500,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>95</v>
@@ -9515,19 +9512,19 @@
         <v>146</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="G10" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>208</v>
@@ -9548,7 +9545,7 @@
         <v>93</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>93</v>
@@ -9598,10 +9595,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>95</v>
@@ -9610,7 +9607,7 @@
         <v>147</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -9622,7 +9619,7 @@
         <v>1.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>208</v>
@@ -9643,16 +9640,16 @@
         <v>93</v>
       </c>
       <c r="P11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="Q11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="S11" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>93</v>
@@ -9693,19 +9690,19 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -9717,7 +9714,7 @@
         <v>1.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>208</v>
@@ -9788,31 +9785,31 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>208</v>
@@ -9833,7 +9830,7 @@
         <v>93</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>214</v>
+        <v>93</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>93</v>
@@ -9883,31 +9880,31 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>265</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>208</v>
@@ -9928,7 +9925,7 @@
         <v>93</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>93</v>
@@ -9978,31 +9975,31 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>208</v>
@@ -10023,7 +10020,7 @@
         <v>93</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>93</v>
@@ -10073,19 +10070,19 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -10097,7 +10094,7 @@
         <v>2.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>208</v>
@@ -10127,7 +10124,7 @@
         <v>93</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T16" s="2" t="s">
         <v>93</v>
@@ -10168,16 +10165,16 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>277</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>205</v>
@@ -10186,13 +10183,13 @@
         <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>208</v>
@@ -10213,7 +10210,7 @@
         <v>93</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>93</v>
@@ -10263,10 +10260,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>95</v>
@@ -10275,7 +10272,7 @@
         <v>160</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -10287,7 +10284,7 @@
         <v>1.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>208</v>
@@ -10358,31 +10355,31 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>208</v>
@@ -10453,10 +10450,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>95</v>
@@ -10465,19 +10462,19 @@
         <v>163</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>208</v>
@@ -10548,16 +10545,16 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>205</v>
@@ -10572,7 +10569,7 @@
         <v>1.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>208</v>
@@ -10593,13 +10590,13 @@
         <v>93</v>
       </c>
       <c r="P21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R21" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>93</v>
@@ -10643,10 +10640,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>95</v>
@@ -10655,13 +10652,13 @@
         <v>166</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>298</v>
-      </c>
       <c r="G22" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>2.0</v>
@@ -10688,7 +10685,7 @@
         <v>93</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>93</v>
@@ -10738,10 +10735,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>95</v>
@@ -10750,7 +10747,7 @@
         <v>167</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
@@ -10762,7 +10759,7 @@
         <v>1.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>208</v>
@@ -10783,7 +10780,7 @@
         <v>93</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>214</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="2" t="s">
         <v>93</v>
@@ -10833,10 +10830,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>303</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>95</v>
@@ -10845,7 +10842,7 @@
         <v>168</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -10857,7 +10854,7 @@
         <v>1.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>208</v>
@@ -10878,7 +10875,7 @@
         <v>93</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q24" s="2" t="s">
         <v>93</v>
@@ -10928,10 +10925,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>95</v>
@@ -10940,7 +10937,7 @@
         <v>169</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
@@ -10952,7 +10949,7 @@
         <v>3.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>208</v>
@@ -10973,7 +10970,7 @@
         <v>93</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q25" s="2" t="s">
         <v>93</v>
@@ -11023,10 +11020,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>95</v>
@@ -11035,7 +11032,7 @@
         <v>170</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -11047,7 +11044,7 @@
         <v>2.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>208</v>
@@ -11118,10 +11115,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>95</v>
@@ -11130,7 +11127,7 @@
         <v>171</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
@@ -11142,7 +11139,7 @@
         <v>3.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>208</v>
@@ -11175,7 +11172,7 @@
         <v>93</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="U27" s="2" t="n">
         <v>971.0</v>
@@ -11213,19 +11210,19 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
@@ -11237,7 +11234,7 @@
         <v>3.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>208</v>
@@ -11308,19 +11305,19 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
@@ -11332,7 +11329,7 @@
         <v>1.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>208</v>
@@ -11403,10 +11400,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>95</v>
@@ -11415,19 +11412,19 @@
         <v>176</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>208</v>
@@ -11448,7 +11445,7 @@
         <v>93</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q30" s="2" t="s">
         <v>93</v>
@@ -11498,10 +11495,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>95</v>
@@ -11510,7 +11507,7 @@
         <v>177</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>93</v>
@@ -11522,7 +11519,7 @@
         <v>2.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>208</v>
@@ -11593,10 +11590,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>321</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>95</v>
@@ -11605,7 +11602,7 @@
         <v>178</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>93</v>
@@ -11617,7 +11614,7 @@
         <v>1.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>208</v>
@@ -11635,16 +11632,16 @@
         <v>93</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q32" s="2" t="s">
         <v>93</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="S32" s="2" t="s">
         <v>93</v>
@@ -11688,10 +11685,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>323</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>95</v>
@@ -11700,19 +11697,19 @@
         <v>179</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>208</v>
@@ -11783,10 +11780,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>326</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>95</v>
@@ -11795,7 +11792,7 @@
         <v>180</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>93</v>
@@ -11807,7 +11804,7 @@
         <v>3.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>208</v>
@@ -11878,10 +11875,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>328</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>95</v>
@@ -11890,7 +11887,7 @@
         <v>181</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>93</v>
@@ -11902,7 +11899,7 @@
         <v>1.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>208</v>
@@ -11973,10 +11970,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>95</v>
@@ -11985,7 +11982,7 @@
         <v>133</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>93</v>
@@ -11997,7 +11994,7 @@
         <v>1.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>208</v>
@@ -12018,7 +12015,7 @@
         <v>93</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="Q36" s="2" t="s">
         <v>93</v>
@@ -12068,10 +12065,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>95</v>
@@ -12080,7 +12077,7 @@
         <v>134</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>93</v>
@@ -12092,7 +12089,7 @@
         <v>3.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>208</v>
@@ -12163,10 +12160,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>95</v>
@@ -12175,7 +12172,7 @@
         <v>135</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>93</v>
@@ -12187,7 +12184,7 @@
         <v>2.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>208</v>
@@ -12258,10 +12255,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>95</v>
@@ -12270,7 +12267,7 @@
         <v>136</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>93</v>
@@ -12282,7 +12279,7 @@
         <v>3.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>208</v>
@@ -12353,10 +12350,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>95</v>
@@ -12365,7 +12362,7 @@
         <v>137</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>93</v>
@@ -12377,7 +12374,7 @@
         <v>1.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>208</v>
@@ -12448,10 +12445,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>95</v>
@@ -12460,7 +12457,7 @@
         <v>138</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>93</v>
@@ -12543,10 +12540,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>95</v>
@@ -12567,7 +12564,7 @@
         <v>3.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>208</v>
@@ -12638,31 +12635,31 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>208</v>
@@ -12695,7 +12692,7 @@
         <v>93</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="U43" s="2" t="n">
         <v>894.0</v>
@@ -12733,10 +12730,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>95</v>
@@ -12745,7 +12742,7 @@
         <v>143</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>93</v>
@@ -12757,7 +12754,7 @@
         <v>2.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>208</v>
@@ -12828,31 +12825,31 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>208</v>
@@ -12923,10 +12920,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>352</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>95</v>
@@ -12935,7 +12932,7 @@
         <v>146</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>93</v>
@@ -12947,7 +12944,7 @@
         <v>1.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>208</v>
@@ -12968,7 +12965,7 @@
         <v>93</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q46" s="2" t="s">
         <v>93</v>
@@ -13018,10 +13015,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>355</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>95</v>
@@ -13030,7 +13027,7 @@
         <v>147</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>93</v>
@@ -13042,7 +13039,7 @@
         <v>3.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>208</v>
@@ -13072,7 +13069,7 @@
         <v>93</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T47" s="2" t="s">
         <v>93</v>
@@ -13113,10 +13110,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>95</v>
@@ -13125,7 +13122,7 @@
         <v>148</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>93</v>
@@ -13137,7 +13134,7 @@
         <v>2.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>208</v>
@@ -13208,10 +13205,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>95</v>
@@ -13220,7 +13217,7 @@
         <v>149</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>93</v>
@@ -13232,7 +13229,7 @@
         <v>2.0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>208</v>
@@ -13253,7 +13250,7 @@
         <v>93</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q49" s="2" t="s">
         <v>93</v>
@@ -13262,7 +13259,7 @@
         <v>93</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T49" s="2" t="s">
         <v>93</v>
@@ -13303,31 +13300,31 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>208</v>
@@ -13398,10 +13395,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>95</v>
@@ -13422,7 +13419,7 @@
         <v>2.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>208</v>
@@ -13443,7 +13440,7 @@
         <v>93</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q51" s="2" t="s">
         <v>93</v>
@@ -13493,19 +13490,19 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>93</v>
@@ -13517,7 +13514,7 @@
         <v>1.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>208</v>
@@ -13538,7 +13535,7 @@
         <v>93</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q52" s="2" t="s">
         <v>93</v>
@@ -13588,10 +13585,10 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>95</v>
@@ -13600,10 +13597,10 @@
         <v>155</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>212</v>
@@ -13612,7 +13609,7 @@
         <v>1.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>208</v>
@@ -13630,7 +13627,7 @@
         <v>93</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>93</v>
@@ -13639,7 +13636,7 @@
         <v>93</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="S53" s="2" t="s">
         <v>93</v>
@@ -13683,10 +13680,10 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>95</v>
@@ -13707,7 +13704,7 @@
         <v>3.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>208</v>
@@ -13778,10 +13775,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>95</v>
@@ -13790,7 +13787,7 @@
         <v>157</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>93</v>
@@ -13802,7 +13799,7 @@
         <v>1.0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>208</v>
@@ -13823,13 +13820,13 @@
         <v>93</v>
       </c>
       <c r="P55" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R55" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="Q55" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="R55" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="S55" s="2" t="s">
         <v>93</v>
@@ -13873,10 +13870,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>95</v>
@@ -13885,7 +13882,7 @@
         <v>158</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>93</v>
@@ -13897,7 +13894,7 @@
         <v>2.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>208</v>
@@ -13918,7 +13915,7 @@
         <v>93</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="Q56" s="2" t="s">
         <v>93</v>
@@ -13968,10 +13965,10 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>95</v>
@@ -13980,10 +13977,10 @@
         <v>159</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>206</v>
@@ -13992,7 +13989,7 @@
         <v>1.0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>208</v>
@@ -14063,31 +14060,31 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>208</v>
@@ -14158,19 +14155,19 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>93</v>
@@ -14182,7 +14179,7 @@
         <v>1.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>208</v>
@@ -14253,25 +14250,25 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>2.0</v>
@@ -14298,7 +14295,7 @@
         <v>93</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="Q60" s="2" t="s">
         <v>93</v>
@@ -14348,22 +14345,22 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>212</v>
@@ -14393,7 +14390,7 @@
         <v>93</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>214</v>
+        <v>93</v>
       </c>
       <c r="Q61" s="2" t="s">
         <v>93</v>
@@ -14405,7 +14402,7 @@
         <v>93</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="U61" s="2" t="n">
         <v>307.0</v>
@@ -14443,10 +14440,10 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>393</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>95</v>
@@ -14455,7 +14452,7 @@
         <v>168</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>93</v>
@@ -14467,7 +14464,7 @@
         <v>3.0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>208</v>
@@ -14538,19 +14535,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>93</v>
@@ -14562,7 +14559,7 @@
         <v>3.0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>208</v>
@@ -14583,7 +14580,7 @@
         <v>93</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q63" s="2" t="s">
         <v>93</v>
@@ -14633,19 +14630,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>398</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>93</v>
@@ -14657,7 +14654,7 @@
         <v>1.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>208</v>
@@ -14728,10 +14725,10 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>95</v>
@@ -14740,7 +14737,7 @@
         <v>174</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>93</v>
@@ -14752,7 +14749,7 @@
         <v>1.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>208</v>
@@ -14773,7 +14770,7 @@
         <v>93</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q65" s="2" t="s">
         <v>93</v>
@@ -14823,31 +14820,31 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>205</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>208</v>
@@ -14868,7 +14865,7 @@
         <v>93</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q66" s="2" t="s">
         <v>93</v>
@@ -14918,10 +14915,10 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>95</v>
@@ -14930,19 +14927,19 @@
         <v>178</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>208</v>
@@ -15013,22 +15010,22 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>409</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D68" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>411</v>
-      </c>
       <c r="F68" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>206</v>
@@ -15037,7 +15034,7 @@
         <v>3.0</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>208</v>
@@ -15108,10 +15105,10 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>413</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>95</v>
@@ -15120,7 +15117,7 @@
         <v>181</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>93</v>
@@ -15132,7 +15129,7 @@
         <v>2.0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>208</v>
@@ -15153,7 +15150,7 @@
         <v>93</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="Q69" s="2" t="s">
         <v>93</v>
@@ -15203,10 +15200,10 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>414</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>415</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>95</v>
@@ -15215,19 +15212,19 @@
         <v>133</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>208</v>
@@ -15248,7 +15245,7 @@
         <v>93</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="Q70" s="2" t="s">
         <v>93</v>
@@ -15257,7 +15254,7 @@
         <v>93</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T70" s="2" t="s">
         <v>93</v>
@@ -15298,10 +15295,10 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>417</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>95</v>
@@ -15310,7 +15307,7 @@
         <v>211</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>93</v>
@@ -15322,7 +15319,7 @@
         <v>2.0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>208</v>
@@ -15393,10 +15390,10 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>418</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>419</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>95</v>
@@ -15405,19 +15402,19 @@
         <v>136</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>208</v>
@@ -15438,7 +15435,7 @@
         <v>93</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>214</v>
+        <v>93</v>
       </c>
       <c r="Q72" s="2" t="s">
         <v>93</v>
@@ -15488,31 +15485,31 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>421</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>208</v>
@@ -15604,10 +15601,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="2"/>
@@ -15616,16 +15613,16 @@
         <v>184</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="4">
@@ -15665,7 +15662,7 @@
     <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>72.0</v>
@@ -15812,7 +15809,7 @@
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -15973,7 +15970,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -16301,7 +16298,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>107</v>
@@ -16471,7 +16468,7 @@
         <v>93</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>93</v>
@@ -16591,7 +16588,7 @@
         <v>139</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -16628,7 +16625,7 @@
         <v>141</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -18379,7 +18376,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>107</v>
@@ -18420,10 +18417,10 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>93</v>
@@ -18461,13 +18458,13 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>93</v>
